--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>maa://25390 (95.47), maa://24702 (94.84), maa://36681 (86.42)</t>
+          <t>maa://25390 (95.48), maa://24702 (94.84), maa://36681 (86.42)</t>
         </is>
       </c>
       <c r="E2" s="11" t="n"/>
@@ -725,12 +725,12 @@
       </c>
       <c r="K2" s="11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>maa://39402 (94.87), *maa://30515 (70.37), *maa://34787 (73.91)</t>
+          <t>maa://39402 (94.87), *maa://34787 (73.91)</t>
         </is>
       </c>
       <c r="M2" s="11" t="n"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>maa://40192 (96.23), maa://36987 (96.23), maa://39849 (88.89)</t>
+          <t>maa://40192 (96.26), maa://36987 (96.23), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="11" t="n"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>maa://21247 (98.46)</t>
+          <t>maa://21247 (98.47)</t>
         </is>
       </c>
       <c r="I3" s="11" t="n"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>*maa://22880 (65.95), maa://20276 (88.63), *maa://22749 (77.78)</t>
+          <t>*maa://22880 (66.24), maa://20276 (88.63), *maa://22749 (77.78)</t>
         </is>
       </c>
       <c r="M3" s="11" t="n"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="AB3" s="14" t="inlineStr">
         <is>
-          <t>maa://24390 (95.6), maa://52241 (100.0)</t>
+          <t>maa://24390 (95.65), maa://52241 (100.0)</t>
         </is>
       </c>
       <c r="AC3" s="11" t="n"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="T4" s="14" t="inlineStr">
         <is>
-          <t>maa://32509 (93.98), maa://27295 (88.3), maa://22754 (89.19), *maa://31008 (79.55)</t>
+          <t>maa://32509 (93.98), maa://27295 (88.42), maa://22754 (89.19), *maa://31008 (79.55)</t>
         </is>
       </c>
       <c r="U4" s="11" t="n"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>maa://21245 (84.56), maa://22744 (82.14), maa://54105 (100.0)</t>
+          <t>maa://21245 (84.62), maa://22744 (82.14), maa://54105 (100.0)</t>
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>maa://24839 (98.83)</t>
+          <t>maa://24839 (98.84)</t>
         </is>
       </c>
       <c r="M6" s="11" t="n"/>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="X6" s="14" t="inlineStr">
         <is>
-          <t>maa://52754 (82.35)</t>
+          <t>maa://52754 (83.33)</t>
         </is>
       </c>
       <c r="Y6" s="11" t="n"/>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>maa://28624 (93.84), maa://24957 (97.78)</t>
+          <t>maa://28624 (93.88), maa://24957 (97.78)</t>
         </is>
       </c>
       <c r="M7" s="11" t="n"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="T7" s="14" t="inlineStr">
         <is>
-          <t>maa://21291 (86.67)</t>
+          <t>maa://21291 (87.1)</t>
         </is>
       </c>
       <c r="U7" s="11" t="n"/>
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.14 13:21:08</t>
+          <t>更新日期：2025.06.15 13:20:11</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>*maa://24371 (55.13)</t>
+          <t>*maa://24371 (55.7)</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="P9" s="14" t="inlineStr">
         <is>
-          <t>maa://22736 (83.33)</t>
+          <t>maa://22736 (83.48)</t>
         </is>
       </c>
       <c r="Q9" s="11" t="n"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="T9" s="14" t="inlineStr">
         <is>
-          <t>maa://26222 (98.33)</t>
+          <t>maa://26222 (98.36)</t>
         </is>
       </c>
       <c r="U9" s="11" t="n"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" s="14" t="inlineStr">
         <is>
-          <t>maa://28711 (87.32), maa://40166 (93.88)</t>
+          <t>maa://28711 (87.41), maa://40166 (93.88)</t>
         </is>
       </c>
       <c r="AC9" s="11" t="n"/>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="AF9" s="14" t="inlineStr">
         <is>
-          <t>maa://26206 (89.27), *maa://22865 (53.57)</t>
+          <t>maa://26206 (89.33), *maa://22865 (53.57)</t>
         </is>
       </c>
       <c r="AG9" s="27" t="n"/>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.72), ***maa://39951 (11.84), ***maa://34206 (22.22), *maa://45271 (60.76), ***maa://39243 (25.0), **maa://54000 (33.33)</t>
+          <t>***maa://25695 (18.63), ***maa://39951 (11.84), ***maa://34206 (22.22), *maa://45271 (61.73), ***maa://39243 (25.0), **maa://54000 (33.33)</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="T10" s="14" t="inlineStr">
         <is>
-          <t>maa://27395 (96.75), maa://22755 (89.15)</t>
+          <t>maa://27395 (96.76), maa://22755 (89.15)</t>
         </is>
       </c>
       <c r="U10" s="11" t="n"/>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="X10" s="14" t="inlineStr">
         <is>
-          <t>maa://22301 (97.91), maa://45828 (93.48), maa://22726 (100.0)</t>
+          <t>maa://22301 (97.93), maa://45828 (93.48), maa://22726 (100.0)</t>
         </is>
       </c>
       <c r="Y10" s="11" t="n"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="AF10" s="14" t="inlineStr">
         <is>
-          <t>*maa://25021 (54.21), *maa://22733 (64.29), **maa://22761 (50.0)</t>
+          <t>*maa://25021 (53.7), *maa://22733 (64.29), **maa://22761 (50.0)</t>
         </is>
       </c>
       <c r="AG10" s="27" t="n"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="X12" s="14" t="inlineStr">
         <is>
-          <t>maa://22753 (91.94), *maa://21485 (75.84), maa://37962 (92.65)</t>
+          <t>maa://22753 (91.98), *maa://21485 (75.84), maa://37962 (92.75)</t>
         </is>
       </c>
       <c r="Y12" s="11" t="n"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB12" s="14" t="inlineStr">
         <is>
-          <t>maa://23669 (95.67), maa://36677 (95.35), maa://39872 (93.1)</t>
+          <t>maa://23669 (95.68), maa://36677 (95.35), maa://39872 (93.1)</t>
         </is>
       </c>
       <c r="AC12" s="11" t="n"/>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>maa://24999 (92.74), maa://36673 (91.95), maa://25001 (86.49)</t>
+          <t>maa://24999 (92.75), maa://36673 (91.95), maa://25001 (86.49)</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>maa://30764 (89.86)</t>
+          <t>maa://30764 (90.0)</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>maa://39841 (94.41), maa://26245 (96.72), maa://21288 (96.3), maa://36682 (95.92)</t>
+          <t>maa://39841 (94.44), maa://26245 (96.72), maa://21288 (96.3), maa://36682 (95.92)</t>
         </is>
       </c>
       <c r="M14" s="11" t="n"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="P14" s="14" t="inlineStr">
         <is>
-          <t>maa://23250 (98.87), maa://20107 (87.1), maa://22772 (100.0)</t>
+          <t>maa://23250 (98.88), maa://20107 (87.1), maa://22772 (100.0)</t>
         </is>
       </c>
       <c r="Q14" s="11" t="n"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="T14" s="14" t="inlineStr">
         <is>
-          <t>maa://22521 (94.87), maa://42751 (100.0)</t>
+          <t>maa://22521 (94.92), maa://42751 (100.0)</t>
         </is>
       </c>
       <c r="U14" s="11" t="n"/>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="X14" s="14" t="inlineStr">
         <is>
-          <t>maa://37468 (92.0)</t>
+          <t>maa://37468 (92.31)</t>
         </is>
       </c>
       <c r="Y14" s="11" t="n"/>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>maa://24304 (87.06), maa://21478 (90.0)</t>
+          <t>maa://24304 (87.16), maa://21478 (90.0)</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>maa://24762 (91.35), *maa://22727 (70.0)</t>
+          <t>maa://24762 (91.4), *maa://22727 (70.0)</t>
         </is>
       </c>
       <c r="Q15" s="11" t="n"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>maa://23892 (96.63)</t>
+          <t>maa://23892 (96.67)</t>
         </is>
       </c>
       <c r="U15" s="11" t="n"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>maa://22430 (89.67), maa://39599 (86.75)</t>
+          <t>maa://22430 (89.72), maa://39599 (86.9)</t>
         </is>
       </c>
       <c r="I17" s="11" t="n"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AF17" s="14" t="inlineStr">
         <is>
-          <t>maa://50136 (95.45)</t>
+          <t>maa://50136 (95.83)</t>
         </is>
       </c>
       <c r="AG17" s="27" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>maa://24570 (97.07)</t>
+          <t>maa://24570 (97.08)</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>maa://22466 (92.12), maa://52226 (95.65)</t>
+          <t>maa://22466 (92.16), maa://52226 (95.65)</t>
         </is>
       </c>
       <c r="M18" s="11" t="n"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AB19" s="14" t="inlineStr">
         <is>
-          <t>*maa://30709 (68.66), *maa://36668 (57.32)</t>
+          <t>*maa://30709 (68.79), *maa://36668 (57.32)</t>
         </is>
       </c>
       <c r="AC19" s="11" t="n"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>maa://22864 (90.86)</t>
+          <t>maa://22864 (90.37)</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>maa://41331 (86.17)</t>
+          <t>maa://41331 (86.27)</t>
         </is>
       </c>
       <c r="M20" s="11" t="n"/>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>maa://37442 (96.15)</t>
+          <t>maa://37442 (96.23)</t>
         </is>
       </c>
       <c r="Q20" s="11" t="n"/>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="X20" s="14" t="inlineStr">
         <is>
-          <t>maa://50085 (88.03), maa://49976 (86.59), maa://56241 (88.89)</t>
+          <t>maa://50085 (88.28), maa://49976 (86.59), maa://56241 (88.89)</t>
         </is>
       </c>
       <c r="Y20" s="11" t="n"/>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>maa://21261 (98.0)</t>
+          <t>maa://21261 (98.04)</t>
         </is>
       </c>
       <c r="E21" s="11" t="n"/>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>maa://24372 (97.17)</t>
+          <t>maa://24372 (97.2)</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB21" s="14" t="inlineStr">
         <is>
-          <t>maa://21443 (82.81), ***maa://23820 (30.0), **maa://52223 (40.62)</t>
+          <t>maa://21443 (82.81), ***maa://23820 (30.0), **maa://52223 (39.39)</t>
         </is>
       </c>
       <c r="AC21" s="11" t="n"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="X22" s="14" t="inlineStr">
         <is>
-          <t>maa://21282 (98.72), *maa://37649 (73.81)</t>
+          <t>maa://21282 (98.73), *maa://37649 (73.81)</t>
         </is>
       </c>
       <c r="Y22" s="11" t="n"/>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>maa://30587 (92.09), *maa://29748 (76.3), *maa://37566 (78.26)</t>
+          <t>maa://30587 (92.13), *maa://29748 (76.3), *maa://37566 (78.26)</t>
         </is>
       </c>
       <c r="Q23" s="11" t="n"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>maa://31212 (89.47), maa://24387 (82.93)</t>
+          <t>maa://31212 (89.74), maa://24387 (82.93)</t>
         </is>
       </c>
       <c r="U23" s="11" t="n"/>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="X24" s="14" t="inlineStr">
         <is>
-          <t>maa://29988 (84.92), maa://23504 (93.7), *maa://25141 (77.37), *maa://36663 (78.0), maa://52227 (100.0)</t>
+          <t>maa://29988 (84.92), maa://23504 (93.71), *maa://25141 (77.37), *maa://36663 (78.0), maa://52227 (100.0)</t>
         </is>
       </c>
       <c r="Y24" s="11" t="n"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AF24" s="14" t="inlineStr">
         <is>
-          <t>maa://22523 (81.74), *maa://36672 (75.76), maa://29910 (93.75), maa://45831 (86.67)</t>
+          <t>maa://22523 (81.74), *maa://36672 (74.63), maa://29910 (93.85), maa://45831 (87.5)</t>
         </is>
       </c>
       <c r="AG24" s="27" t="n"/>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>maa://29753 (95.47)</t>
+          <t>maa://29753 (95.48)</t>
         </is>
       </c>
       <c r="E25" s="11" t="n"/>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AB25" s="14" t="inlineStr">
         <is>
-          <t>maa://31215 (89.51), *maa://24516 (79.57), maa://26001 (84.75)</t>
+          <t>maa://31215 (89.66), *maa://24516 (79.57), maa://26001 (84.75)</t>
         </is>
       </c>
       <c r="AC25" s="11" t="n"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AF25" s="14" t="inlineStr">
         <is>
-          <t>maa://20108 (95.89), maa://24621 (97.18), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (80.0)</t>
+          <t>maa://20108 (95.92), maa://24621 (97.18), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (80.0)</t>
         </is>
       </c>
       <c r="AG25" s="27" t="n"/>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AB26" s="14" t="inlineStr">
         <is>
-          <t>maa://42235 (96.05)</t>
+          <t>maa://42235 (96.08)</t>
         </is>
       </c>
       <c r="AC26" s="11" t="n"/>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AF26" s="14" t="inlineStr">
         <is>
-          <t>*maa://30511 (75.0), *maa://29760 (52.94)</t>
+          <t>*maa://30511 (75.47), *maa://29760 (52.94)</t>
         </is>
       </c>
       <c r="AG26" s="27" t="n"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>*maa://39601 (79.17), maa://34494 (97.3)</t>
+          <t>maa://39601 (80.77), maa://34494 (97.3)</t>
         </is>
       </c>
       <c r="I27" s="11" t="n"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AF27" s="14" t="inlineStr">
         <is>
-          <t>maa://24023 (96.15)</t>
+          <t>maa://24023 (96.2)</t>
         </is>
       </c>
       <c r="AG27" s="27" t="n"/>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="X28" s="14" t="inlineStr">
         <is>
-          <t>maa://39929 (91.97), maa://41749 (92.25)</t>
+          <t>maa://39929 (91.97), maa://41749 (92.31)</t>
         </is>
       </c>
       <c r="Y28" s="11" t="n"/>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="AF28" s="14" t="inlineStr">
         <is>
-          <t>maa://36660 (92.54)</t>
+          <t>maa://36660 (92.58)</t>
         </is>
       </c>
       <c r="AG28" s="27" t="n"/>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>maa://28432 (94.05), maa://31400 (98.89), maa://28440 (83.94), *maa://28650 (71.43)</t>
+          <t>maa://28432 (94.05), maa://31400 (98.89), maa://28440 (84.06), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="11" t="n"/>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>maa://45792 (89.66)</t>
+          <t>maa://45792 (90.0)</t>
         </is>
       </c>
       <c r="E30" s="11" t="n"/>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>maa://35926 (93.75), maa://36258 (87.88), *maa://43904 (73.33)</t>
+          <t>maa://35926 (93.75), maa://36258 (87.95), *maa://43904 (73.33)</t>
         </is>
       </c>
       <c r="M31" s="11" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>maa://21895 (97.63), maa://36667 (97.32), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.64), maa://36667 (97.32), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="11" t="n"/>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="T32" s="14" t="inlineStr">
         <is>
-          <t>maa://42859 (96.98), maa://41108 (86.27), maa://41238 (97.99), maa://45523 (100.0)</t>
+          <t>maa://42859 (97.0), maa://41108 (86.27), maa://41238 (97.99), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="11" t="n"/>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="P34" s="14" t="inlineStr">
         <is>
-          <t>maa://48817 (96.88), maa://56235 (100.0)</t>
+          <t>maa://48817 (96.92), maa://56235 (100.0)</t>
         </is>
       </c>
       <c r="Q34" s="11" t="n"/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>maa://24375 (90.7)</t>
+          <t>maa://24375 (90.91)</t>
         </is>
       </c>
       <c r="I36" s="11" t="n"/>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AF38" s="14" t="inlineStr">
         <is>
-          <t>maa://36697 (89.31)</t>
+          <t>maa://36697 (89.34)</t>
         </is>
       </c>
       <c r="AG38" s="27" t="n"/>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>maa://36670 (89.57), maa://25199 (85.22), maa://30434 (93.13), *maa://45059 (79.41)</t>
+          <t>maa://36670 (89.57), maa://25199 (85.22), maa://30434 (93.18), *maa://45059 (79.41)</t>
         </is>
       </c>
       <c r="I39" s="11" t="n"/>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>maa://24466 (93.88)</t>
+          <t>maa://24466 (94.0)</t>
         </is>
       </c>
       <c r="I41" s="11" t="n"/>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>maa://21229 (84.42), maa://30807 (93.51), maa://42459 (89.47)</t>
+          <t>maa://21229 (84.42), maa://30807 (93.51), maa://42459 (87.18)</t>
         </is>
       </c>
       <c r="I45" s="11" t="n"/>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>maa://35931 (92.67), maa://43901 (94.74)</t>
+          <t>maa://35931 (92.71), maa://43901 (94.74)</t>
         </is>
       </c>
       <c r="I46" s="11" t="n"/>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="P52" s="14" t="inlineStr">
         <is>
-          <t>maa://59378 (96.88), maa://59394 (91.67)</t>
+          <t>maa://59378 (96.88), maa://59394 (93.33)</t>
         </is>
       </c>
       <c r="Q52" s="11" t="n"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>maa://32534 (95.13)</t>
+          <t>maa://32534 (95.15)</t>
         </is>
       </c>
       <c r="I53" s="11" t="n"/>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>*maa://40438 (74.68)</t>
+          <t>*maa://40438 (75.0)</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>maa://59534 (97.5), maa://59413 (100.0)</t>
+          <t>maa://59534 (97.62), maa://59413 (100.0)</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -6958,7 +6958,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="17">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.14 13:21:08</t>
+          <t>更新日期：2025.06.15 13:20:11</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>maa://36644 (88.42), maa://36866 (96.15), maa://45572 (91.67), maa://27794 (100.0), maa://20960 (100.0), maa://20843 (100.0), **maa://24483 (50.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
+          <t>maa://36644 (88.42), maa://36866 (96.23), maa://45572 (91.67), maa://27794 (100.0), maa://20960 (100.0), maa://20843 (100.0), **maa://24483 (50.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>maa://20916 (82.86), maa://52658 (87.5)</t>
+          <t>maa://20916 (82.86), maa://52658 (88.89)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>maa://20991 (100.0), maa://51015 (85.71)</t>
+          <t>maa://20991 (100.0), maa://51015 (86.36)</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="D99" s="20" t="inlineStr">
         <is>
-          <t>maa://20929 (94.74)</t>
+          <t>maa://20929 (95.0)</t>
         </is>
       </c>
       <c r="E99" s="21" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>maa://25018 (96.63), maa://51881 (99.16), maa://25776 (92.11), maa://28361 (97.37), maa://25772 (94.12), maa://56588 (94.12), maa://45194 (87.5), maa://32653 (85.71), maa://25161 (81.25)</t>
+          <t>maa://25018 (96.64), maa://51881 (99.17), maa://25776 (92.11), maa://28361 (97.37), maa://25772 (94.12), maa://56588 (94.44), maa://45194 (87.5), maa://32653 (85.71), maa://25161 (81.25)</t>
         </is>
       </c>
       <c r="E108" s="21" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>maa://29037 (98.46)</t>
+          <t>maa://29037 (98.48)</t>
         </is>
       </c>
       <c r="E113" s="21" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>maa://29650 (98.31), maa://45570 (97.87)</t>
+          <t>maa://29650 (98.31), maa://45570 (97.92)</t>
         </is>
       </c>
       <c r="E122" s="21" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="D139" s="20" t="inlineStr">
         <is>
-          <t>**maa://30679 (50.0), maa://45258 (92.86)</t>
+          <t>**maa://30679 (50.0), maa://45258 (93.33)</t>
         </is>
       </c>
       <c r="E139" s="21" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="D143" s="20" t="inlineStr">
         <is>
-          <t>maa://30670 (96.6), maa://31470 (96.67), *maa://45066 (66.67), **maa://30867 (40.0)</t>
+          <t>maa://30670 (96.64), maa://31470 (96.67), *maa://45066 (66.67), **maa://30867 (40.0)</t>
         </is>
       </c>
       <c r="E143" s="21" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>maa://36641 (98.44), maa://40957 (93.36), maa://36865 (96.32), maa://44635 (87.74), maa://44660 (92.31), maa://41128 (83.78), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
+          <t>maa://36641 (98.44), maa://40957 (93.38), maa://36865 (96.32), maa://44635 (87.74), maa://44660 (92.31), maa://41128 (83.78), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>maa://51549 (95.12), maa://51923 (95.65)</t>
+          <t>maa://51549 (95.24), maa://51923 (95.65)</t>
         </is>
       </c>
       <c r="E150" s="21" t="inlineStr">
@@ -17758,7 +17758,7 @@
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>maa://42223 (99.59), maa://49077 (94.29), maa://42292 (97.22), maa://42402 (100.0)</t>
+          <t>maa://42223 (99.6), maa://49077 (94.29), maa://42292 (97.22), maa://42402 (100.0)</t>
         </is>
       </c>
       <c r="E201" s="21" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="D240" s="20" t="inlineStr">
         <is>
-          <t>*maa://30667 (78.63), maa://30666 (83.41), **maa://30739 (43.24), *maa://30723 (56.45), maa://39588 (88.68)</t>
+          <t>*maa://30667 (78.63), maa://30666 (83.41), **maa://30739 (43.24), *maa://30723 (56.45), maa://39588 (88.89)</t>
         </is>
       </c>
       <c r="E240" s="21" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="D249" s="20" t="inlineStr">
         <is>
-          <t>maa://42287 (90.48), maa://45570 (97.87), maa://42225 (100.0)</t>
+          <t>maa://42287 (90.48), maa://45570 (97.92), maa://42225 (100.0)</t>
         </is>
       </c>
       <c r="E249" s="21" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="D267" s="20" t="inlineStr">
         <is>
-          <t>maa://49643 (86.36)</t>
+          <t>maa://49643 (86.96)</t>
         </is>
       </c>
       <c r="E267" s="21" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="D272" s="20" t="inlineStr">
         <is>
-          <t>maa://51881 (99.16), maa://51630 (96.59), maa://56588 (94.12), *maa://55171 (57.14), maa://51893 (88.89)</t>
+          <t>maa://51881 (99.17), maa://51630 (96.59), maa://56588 (94.44), *maa://55171 (57.14), maa://51893 (88.89)</t>
         </is>
       </c>
       <c r="E272" s="21" t="inlineStr">
@@ -22510,7 +22510,7 @@
       </c>
       <c r="D289" s="20" t="inlineStr">
         <is>
-          <t>maa://30710 (97.87), maa://36845 (95.59), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.67)</t>
+          <t>maa://30710 (97.87), maa://36845 (95.62), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.67)</t>
         </is>
       </c>
       <c r="E289" s="21" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="D303" s="20" t="inlineStr">
         <is>
-          <t>maa://50280 (97.52), maa://49642 (96.88), maa://49660 (92.86), *maa://50517 (80.0)</t>
+          <t>maa://50280 (97.54), maa://49642 (96.88), maa://49660 (92.86), *maa://50517 (80.0)</t>
         </is>
       </c>
       <c r="E303" s="21" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="D321" s="20" t="inlineStr">
         <is>
-          <t>maa://39692 (99.61), maa://39810 (86.36)</t>
+          <t>maa://39692 (99.62), maa://39810 (86.36)</t>
         </is>
       </c>
       <c r="E321" s="21" t="inlineStr">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="D352" s="17" t="inlineStr">
         <is>
-          <t>maa://49696 (99.55), maa://49695 (100.0), maa://49758 (98.44), *maa://52357 (71.43), *maa://59402 (66.67)</t>
+          <t>maa://49696 (99.55), maa://49695 (100.0), maa://49758 (98.44), *maa://52357 (71.43), *maa://59402 (71.43)</t>
         </is>
       </c>
       <c r="E352" s="17" t="inlineStr">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="D356" s="17" t="inlineStr">
         <is>
-          <t>maa://36646 (98.79), maa://36845 (95.59), **maa://39217 (41.18), maa://51007 (98.15)</t>
+          <t>maa://36646 (98.79), maa://36845 (95.62), **maa://39217 (41.18), maa://51007 (98.15)</t>
         </is>
       </c>
       <c r="E356" s="17" t="inlineStr">
@@ -26398,7 +26398,7 @@
       </c>
       <c r="D361" s="17" t="inlineStr">
         <is>
-          <t>maa://40957 (93.36), maa://44635 (87.74), maa://48026 (96.39), maa://41035 (92.42), maa://44660 (92.31), maa://41128 (83.78)</t>
+          <t>maa://40957 (93.38), maa://44635 (87.74), maa://48026 (96.39), maa://41035 (92.42), maa://44660 (92.31), maa://41128 (83.78)</t>
         </is>
       </c>
       <c r="E361" s="17" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="D372" s="17" t="inlineStr">
         <is>
-          <t>maa://44233 (92.16), maa://45570 (97.87)</t>
+          <t>maa://44233 (92.16), maa://45570 (97.92)</t>
         </is>
       </c>
       <c r="E372" s="17" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="D377" s="17" t="inlineStr">
         <is>
-          <t>maa://42970 (83.86), maa://44745 (98.17), **maa://49516 (42.11), *maa://45952 (80.0), ***maa://46851 (14.29), *maa://44896 (77.78)</t>
+          <t>maa://42970 (83.53), maa://44745 (98.2), **maa://49516 (42.11), *maa://45952 (80.0), ***maa://46851 (14.29), *maa://44896 (77.78)</t>
         </is>
       </c>
       <c r="E377" s="17" t="inlineStr">
@@ -28018,7 +28018,7 @@
       </c>
       <c r="D391" s="17" t="inlineStr">
         <is>
-          <t>maa://51872 (96.65), maa://51876 (98.77), maa://51873 (100.0)</t>
+          <t>maa://51872 (96.7), maa://51876 (98.77), maa://51873 (100.0)</t>
         </is>
       </c>
       <c r="E391" s="17" t="inlineStr">
@@ -28072,7 +28072,7 @@
       </c>
       <c r="D392" s="17" t="inlineStr">
         <is>
-          <t>maa://59493 (96.3), maa://59603 (100.0)</t>
+          <t>maa://59493 (96.63), maa://59603 (100.0)</t>
         </is>
       </c>
       <c r="E392" s="17" t="inlineStr">

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>maa://25390 (95.54), maa://24702 (94.87), maa://36681 (86.42)</t>
+          <t>maa://25390 (95.55), maa://24702 (94.87), maa://36681 (86.42)</t>
         </is>
       </c>
       <c r="E2" s="11" t="n"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="T2" s="14" t="inlineStr">
         <is>
-          <t>maa://22742 (91.74)</t>
+          <t>maa://22742 (91.32)</t>
         </is>
       </c>
       <c r="U2" s="11" t="n"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="AB2" s="14" t="inlineStr">
         <is>
-          <t>maa://21246 (91.48), maa://36684 (93.33)</t>
+          <t>maa://21246 (91.48), maa://36684 (93.37)</t>
         </is>
       </c>
       <c r="AC2" s="11" t="n"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>maa://40192 (96.43), maa://36987 (96.3), maa://39849 (88.89)</t>
+          <t>maa://40192 (96.46), maa://36987 (96.3), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="11" t="n"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>maa://21247 (98.49)</t>
+          <t>maa://21247 (98.5)</t>
         </is>
       </c>
       <c r="I3" s="11" t="n"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>*maa://22880 (66.39), maa://20276 (88.68), *maa://22749 (78.95)</t>
+          <t>*maa://22880 (66.11), maa://20276 (88.32), *maa://22749 (78.95)</t>
         </is>
       </c>
       <c r="M3" s="11" t="n"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="P3" s="14" t="inlineStr">
         <is>
-          <t>maa://21249 (94.81), maa://26254 (97.3)</t>
+          <t>maa://21249 (94.81), maa://26254 (97.37)</t>
         </is>
       </c>
       <c r="Q3" s="11" t="n"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="X3" s="14" t="inlineStr">
         <is>
-          <t>maa://27396 (84.03), maa://27484 (96.35), maa://27480 (84.62)</t>
+          <t>maa://27396 (84.03), maa://27484 (96.38), maa://27480 (84.62)</t>
         </is>
       </c>
       <c r="Y3" s="11" t="n"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>maa://24632 (93.72), maa://22499 (86.67), maa://22746 (100.0)</t>
+          <t>maa://24632 (93.27), maa://22499 (86.67), maa://22746 (100.0)</t>
         </is>
       </c>
       <c r="E4" s="11" t="n"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="P4" s="14" t="inlineStr">
         <is>
-          <t>maa://49983 (96.51), maa://50121 (95.12)</t>
+          <t>maa://49983 (96.55), maa://50121 (95.12)</t>
         </is>
       </c>
       <c r="Q4" s="11" t="n"/>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="T4" s="14" t="inlineStr">
         <is>
-          <t>maa://32509 (94.03), maa://27295 (88.66), maa://22754 (89.19), *maa://31008 (79.55)</t>
+          <t>maa://32509 (94.03), maa://27295 (88.78), maa://22754 (89.19), *maa://31008 (79.55)</t>
         </is>
       </c>
       <c r="U4" s="11" t="n"/>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="X4" s="14" t="inlineStr">
         <is>
-          <t>maa://43217 (94.07)</t>
+          <t>maa://43217 (94.12)</t>
         </is>
       </c>
       <c r="Y4" s="11" t="n"/>
@@ -1476,7 +1476,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.29 13:23:12</t>
+          <t>更新日期：2025.06.30 13:23:46</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="P8" s="14" t="inlineStr">
         <is>
-          <t>maa://32931 (83.92), maa://23252 (91.67), maa://37496 (97.56)</t>
+          <t>maa://32931 (83.92), maa://23252 (91.67), maa://37496 (97.62)</t>
         </is>
       </c>
       <c r="Q8" s="11" t="n"/>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB8" s="14" t="inlineStr">
         <is>
-          <t>maa://25389 (88.37)</t>
+          <t>maa://25389 (88.64)</t>
         </is>
       </c>
       <c r="AC8" s="11" t="n"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>maa://22765 (90.38), *maa://21915 (71.88)</t>
+          <t>maa://22765 (90.48), *maa://21915 (71.88)</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>***maa://25695 (18.45), ***maa://39951 (11.69), ***maa://34206 (22.22), *maa://45271 (62.2), ***maa://39243 (25.0), **maa://54000 (50.0)</t>
+          <t>***maa://25695 (18.45), ***maa://39951 (11.69), ***maa://34206 (22.22), *maa://45271 (61.45), ***maa://39243 (25.0), **maa://54000 (50.0)</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="T10" s="14" t="inlineStr">
         <is>
-          <t>maa://27395 (96.81), maa://22755 (89.31)</t>
+          <t>maa://27395 (96.83), maa://22755 (89.31)</t>
         </is>
       </c>
       <c r="U10" s="11" t="n"/>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>maa://24999 (92.79), maa://36673 (92.13), maa://25001 (86.49)</t>
+          <t>maa://24999 (92.8), maa://36673 (92.13), maa://25001 (86.49)</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>maa://39841 (94.58), maa://26245 (96.74), maa://21288 (96.3), maa://36682 (96.15)</t>
+          <t>maa://39841 (94.61), maa://26245 (96.77), maa://21288 (96.3), maa://36682 (96.15)</t>
         </is>
       </c>
       <c r="M14" s="11" t="n"/>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="P14" s="14" t="inlineStr">
         <is>
-          <t>maa://23250 (98.89), maa://20107 (87.1), maa://22772 (100.0)</t>
+          <t>maa://23250 (98.9), maa://20107 (87.1), maa://22772 (100.0)</t>
         </is>
       </c>
       <c r="Q14" s="11" t="n"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>*maa://22743 (78.78), maa://22734 (84.55), *maa://30808 (64.38), *maa://36048 (70.43), maa://45058 (85.71)</t>
+          <t>*maa://22743 (78.86), maa://22734 (84.55), *maa://30808 (64.38), *maa://36048 (69.83), maa://45058 (85.71)</t>
         </is>
       </c>
       <c r="E15" s="11" t="n"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>maa://24304 (87.45), maa://21478 (90.24)</t>
+          <t>maa://24304 (87.12), maa://21478 (90.24)</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>maa://22729 (94.57), *maa://28648 (74.39), *maa://36674 (79.37)</t>
+          <t>maa://22729 (94.57), *maa://28648 (74.7), *maa://36674 (79.37)</t>
         </is>
       </c>
       <c r="U16" s="11" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="X20" s="14" t="inlineStr">
         <is>
-          <t>maa://50085 (88.96), maa://49976 (86.75), maa://56241 (88.89)</t>
+          <t>maa://50085 (89.1), maa://49976 (86.75), maa://56241 (88.89)</t>
         </is>
       </c>
       <c r="Y20" s="11" t="n"/>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AF21" s="14" t="inlineStr">
         <is>
-          <t>maa://22524 (88.14), maa://22432 (82.61)</t>
+          <t>maa://22524 (88.14), maa://22432 (82.86)</t>
         </is>
       </c>
       <c r="AG21" s="27" t="n"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>*maa://27127 (77.78), *maa://22751 (70.67)</t>
+          <t>*maa://27127 (77.94), *maa://22751 (70.67)</t>
         </is>
       </c>
       <c r="M22" s="11" t="n"/>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="X22" s="14" t="inlineStr">
         <is>
-          <t>maa://21282 (98.74), *maa://37649 (73.33)</t>
+          <t>maa://21282 (98.74), *maa://37649 (71.74)</t>
         </is>
       </c>
       <c r="Y22" s="11" t="n"/>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>maa://39756 (95.65), maa://39875 (93.83)</t>
+          <t>maa://39756 (95.66), maa://39875 (93.83)</t>
         </is>
       </c>
       <c r="M23" s="11" t="n"/>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="X24" s="14" t="inlineStr">
         <is>
-          <t>maa://29988 (84.97), maa://23504 (93.76), *maa://25141 (77.37), *maa://36663 (78.0), maa://52227 (95.24)</t>
+          <t>maa://29988 (84.97), maa://23504 (93.76), *maa://25141 (77.37), *maa://36663 (78.0), maa://52227 (95.45)</t>
         </is>
       </c>
       <c r="Y24" s="11" t="n"/>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AF29" s="14" t="inlineStr">
         <is>
-          <t>*maa://24080 (69.17), maa://42865 (81.03)</t>
+          <t>*maa://24080 (69.17), maa://42865 (81.2)</t>
         </is>
       </c>
       <c r="AG29" s="27" t="n"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="AB30" s="14" t="inlineStr">
         <is>
-          <t>maa://42979 (97.18), maa://45822 (100.0), maa://45045 (83.33)</t>
+          <t>maa://42979 (97.19), maa://45822 (100.0), maa://45045 (83.33)</t>
         </is>
       </c>
       <c r="AC30" s="11" t="n"/>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AF38" s="14" t="inlineStr">
         <is>
-          <t>maa://36697 (89.26)</t>
+          <t>maa://36697 (89.3)</t>
         </is>
       </c>
       <c r="AG38" s="27" t="n"/>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="T39" s="14" t="inlineStr">
         <is>
-          <t>maa://47079 (95.15), *maa://45788 (71.9), maa://45790 (82.76)</t>
+          <t>maa://47079 (95.19), *maa://45788 (71.9), maa://45790 (82.76)</t>
         </is>
       </c>
       <c r="U39" s="11" t="n"/>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="P52" s="14" t="inlineStr">
         <is>
-          <t>maa://59378 (97.78), maa://59394 (96.43)</t>
+          <t>maa://59378 (97.83), maa://59394 (96.55)</t>
         </is>
       </c>
       <c r="Q52" s="11" t="n"/>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>maa://32534 (95.23)</t>
+          <t>maa://32534 (95.24)</t>
         </is>
       </c>
       <c r="I53" s="11" t="n"/>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>maa://42981 (96.72), maa://43903 (100.0), maa://56228 (100.0)</t>
+          <t>maa://42981 (96.77), maa://43903 (100.0), maa://56228 (100.0)</t>
         </is>
       </c>
       <c r="I62" s="11" t="n"/>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>maa://59534 (98.46), maa://59413 (100.0)</t>
+          <t>maa://59534 (98.51), maa://59413 (100.0)</t>
         </is>
       </c>
       <c r="I63" s="11" t="n"/>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>maa://44405 (86.84)</t>
+          <t>maa://44405 (87.18)</t>
         </is>
       </c>
       <c r="I64" s="11" t="n"/>
@@ -6961,7 +6961,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="17">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.29 13:23:12</t>
+          <t>更新日期：2025.06.30 13:23:46</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>maa://36644 (88.08), maa://36866 (96.23), maa://45572 (91.67), maa://27794 (100.0), maa://20960 (100.0), maa://20843 (100.0), **maa://24483 (50.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
+          <t>maa://36644 (88.14), maa://36866 (96.3), maa://45572 (91.67), maa://27794 (100.0), maa://20960 (100.0), maa://20843 (100.0), **maa://24483 (50.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>maa://20916 (82.86), maa://52658 (88.89)</t>
+          <t>maa://20916 (82.86), maa://52658 (90.0)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>maa://25018 (96.68), maa://51881 (99.21), maa://25776 (92.11), maa://28361 (95.0), maa://25772 (94.12), maa://56588 (94.74), maa://45194 (82.35), maa://32653 (85.71), maa://25161 (81.25), maa://60902 (100.0)</t>
+          <t>maa://25018 (96.68), maa://51881 (99.21), maa://25776 (92.11), maa://28361 (95.0), maa://25772 (94.12), maa://56588 (94.74), maa://45194 (82.35), maa://32653 (85.71), maa://25161 (81.25), **maa://60902 (50.0)</t>
         </is>
       </c>
       <c r="E108" s="21" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>maa://36641 (98.44), maa://40957 (93.99), maa://36865 (95.76), maa://44635 (88.07), maa://44660 (92.31), maa://41128 (83.78), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
+          <t>maa://36641 (98.44), maa://40957 (94.01), maa://36865 (95.76), maa://44635 (88.07), maa://44660 (92.31), maa://41128 (83.78), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="21" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>maa://44224 (90.13), maa://35854 (85.42), maa://50388 (97.93), maa://25760 (86.96), ***maa://43911 (13.04), *maa://20872 (52.0), maa://51066 (100.0)</t>
+          <t>maa://44224 (90.15), maa://35854 (85.57), maa://50388 (97.93), maa://25760 (86.96), ***maa://43911 (13.04), *maa://20872 (52.0), maa://51066 (100.0)</t>
         </is>
       </c>
       <c r="E197" s="21" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="D211" s="20" t="inlineStr">
         <is>
-          <t>maa://20956 (95.94), *maa://20830 (80.0), maa://44703 (91.67)</t>
+          <t>maa://20956 (95.96), *maa://20830 (80.0), maa://44703 (91.67)</t>
         </is>
       </c>
       <c r="E211" s="21" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="D222" s="20" t="inlineStr">
         <is>
-          <t>maa://39695 (100.0), ***maa://39911 (25.0)</t>
+          <t>maa://39695 (100.0), ***maa://39911 (20.0)</t>
         </is>
       </c>
       <c r="E222" s="21" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="D248" s="20" t="inlineStr">
         <is>
-          <t>maa://28923 (92.35), maa://28906 (98.28), ***maa://28825 (11.54)</t>
+          <t>maa://28923 (91.41), maa://28906 (98.28), ***maa://28825 (11.54)</t>
         </is>
       </c>
       <c r="E248" s="21" t="inlineStr">
@@ -20677,7 +20677,7 @@
       </c>
       <c r="D255" s="20" t="inlineStr">
         <is>
-          <t>maa://20877 (98.68), *maa://45067 (75.0), maa://20836 (100.0), maa://20632 (100.0)</t>
+          <t>maa://20877 (98.7), *maa://45067 (75.0), maa://20836 (100.0), maa://20632 (100.0)</t>
         </is>
       </c>
       <c r="E255" s="21" t="inlineStr">
@@ -21325,7 +21325,7 @@
       </c>
       <c r="D267" s="20" t="inlineStr">
         <is>
-          <t>maa://49643 (86.96)</t>
+          <t>maa://49643 (88.0)</t>
         </is>
       </c>
       <c r="E267" s="21" t="inlineStr">
@@ -21487,7 +21487,7 @@
       </c>
       <c r="D270" s="20" t="inlineStr">
         <is>
-          <t>maa://25769 (97.45)</t>
+          <t>maa://25769 (97.47)</t>
         </is>
       </c>
       <c r="E270" s="21" t="inlineStr">
@@ -21595,7 +21595,7 @@
       </c>
       <c r="D272" s="20" t="inlineStr">
         <is>
-          <t>maa://51881 (99.21), maa://51630 (96.59), maa://56588 (94.74), *maa://55171 (57.14), maa://51893 (88.89), maa://60902 (100.0)</t>
+          <t>maa://51881 (99.21), maa://51630 (96.59), maa://56588 (94.74), *maa://55171 (57.14), maa://51893 (88.89), **maa://60902 (50.0)</t>
         </is>
       </c>
       <c r="E272" s="21" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="D289" s="20" t="inlineStr">
         <is>
-          <t>maa://30710 (97.89), maa://36845 (95.68), maa://31558 (97.14), **maa://39217 (41.18), maa://30668 (86.67)</t>
+          <t>maa://30710 (97.89), maa://36845 (95.71), maa://31558 (97.14), **maa://39217 (41.18), maa://30668 (86.67)</t>
         </is>
       </c>
       <c r="E289" s="21" t="inlineStr">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="D303" s="20" t="inlineStr">
         <is>
-          <t>maa://50280 (97.64), maa://49642 (96.94), maa://49660 (93.1), *maa://50517 (80.0)</t>
+          <t>maa://50280 (97.66), maa://49642 (96.94), maa://49660 (93.1), *maa://50517 (80.0)</t>
         </is>
       </c>
       <c r="E303" s="21" t="inlineStr">
@@ -25645,7 +25645,7 @@
       </c>
       <c r="D347" s="17" t="inlineStr">
         <is>
-          <t>maa://34865 (97.82), maa://34717 (94.03), *maa://45066 (66.67)</t>
+          <t>maa://34865 (97.83), maa://34717 (94.03), *maa://45066 (66.67)</t>
         </is>
       </c>
       <c r="E347" s="17" t="inlineStr">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="D352" s="17" t="inlineStr">
         <is>
-          <t>maa://49696 (99.55), maa://49695 (100.0), maa://49758 (98.44), *maa://59402 (64.29), *maa://52357 (75.0)</t>
+          <t>maa://49696 (99.56), maa://49695 (100.0), maa://49758 (98.44), *maa://59402 (66.67), *maa://52357 (75.0)</t>
         </is>
       </c>
       <c r="E352" s="17" t="inlineStr">
@@ -26131,7 +26131,7 @@
       </c>
       <c r="D356" s="17" t="inlineStr">
         <is>
-          <t>maa://36646 (98.8), maa://36845 (95.68), **maa://39217 (41.18), maa://51007 (98.18)</t>
+          <t>maa://36646 (98.8), maa://36845 (95.71), **maa://39217 (41.18), maa://51007 (98.18)</t>
         </is>
       </c>
       <c r="E356" s="17" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="D361" s="17" t="inlineStr">
         <is>
-          <t>maa://40957 (93.99), maa://44635 (88.07), maa://48026 (95.19), maa://41035 (92.65), maa://44660 (92.31), maa://41128 (83.78), *maa://60251 (75.0)</t>
+          <t>maa://40957 (94.01), maa://44635 (88.07), maa://48026 (95.28), maa://41035 (92.75), maa://44660 (92.31), maa://41128 (83.78), *maa://60251 (66.67)</t>
         </is>
       </c>
       <c r="E361" s="17" t="inlineStr">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="D377" s="17" t="inlineStr">
         <is>
-          <t>maa://42970 (82.82), maa://44745 (98.44), **maa://49516 (38.1), *maa://45952 (72.73), ***maa://46851 (14.29), *maa://44896 (77.78)</t>
+          <t>maa://42970 (82.82), maa://44745 (98.47), **maa://49516 (38.1), *maa://45952 (72.73), ***maa://46851 (14.29), *maa://44896 (77.78)</t>
         </is>
       </c>
       <c r="E377" s="17" t="inlineStr">
@@ -28075,7 +28075,7 @@
       </c>
       <c r="D392" s="17" t="inlineStr">
         <is>
-          <t>maa://51880 (99.09), maa://51878 (100.0), maa://56651 (100.0)</t>
+          <t>maa://51880 (99.1), maa://51878 (100.0), maa://56651 (100.0)</t>
         </is>
       </c>
       <c r="E392" s="17" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>maa://51872 (96.69), maa://51876 (98.86), maa://51873 (100.0)</t>
+          <t>maa://51872 (96.72), maa://51876 (98.88), maa://51873 (100.0)</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -28156,7 +28156,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://59493 (96.55), maa://59603 (100.0), maa://60449 (100.0)</t>
+          <t>maa://59493 (96.55), maa://60449 (100.0), maa://59603 (100.0)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -87,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -170,6 +170,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -700,7 +701,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>maa://25390 (95.7), maa://24702 (94.89), maa://36681 (86.59)</t>
+          <t>maa://25390 (95.74), maa://24702 (94.9), maa://36681 (86.59)</t>
         </is>
       </c>
       <c r="E2" s="19" t="n"/>
@@ -732,7 +733,7 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>maa://39402 (95.12), *maa://34787 (74.19), maa://58660 (92.86)</t>
+          <t>maa://39402 (95.16), *maa://34787 (74.47), maa://58660 (93.33)</t>
         </is>
       </c>
       <c r="M2" s="19" t="n"/>
@@ -796,7 +797,7 @@
       </c>
       <c r="AB2" s="8" t="inlineStr">
         <is>
-          <t>maa://21246 (91.53), maa://36684 (93.75)</t>
+          <t>maa://21246 (91.56), maa://36684 (93.89)</t>
         </is>
       </c>
       <c r="AC2" s="19" t="n"/>
@@ -830,7 +831,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>maa://40192 (95.97), maa://36987 (96.3), maa://39849 (88.89)</t>
+          <t>maa://40192 (96.03), maa://36987 (96.3), maa://39849 (88.89)</t>
         </is>
       </c>
       <c r="E3" s="19" t="n"/>
@@ -846,7 +847,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>maa://21247 (98.53)</t>
+          <t>maa://21247 (98.54)</t>
         </is>
       </c>
       <c r="I3" s="19" t="n"/>
@@ -862,7 +863,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>*maa://22880 (66.4), maa://20276 (87.96), *maa://22749 (78.95)</t>
+          <t>*maa://22880 (66.4), maa://20276 (88.02), *maa://22749 (80.0)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -878,7 +879,7 @@
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>maa://21249 (94.95), maa://26254 (97.44), *maa://22738 (75.0)</t>
+          <t>maa://21249 (94.98), maa://26254 (97.44), *maa://22738 (75.0)</t>
         </is>
       </c>
       <c r="Q3" s="19" t="n"/>
@@ -894,7 +895,7 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>maa://45854 (81.9), maa://24617 (91.18)</t>
+          <t>maa://45854 (82.08), maa://24617 (91.18)</t>
         </is>
       </c>
       <c r="U3" s="19" t="n"/>
@@ -910,7 +911,7 @@
       </c>
       <c r="X3" s="8" t="inlineStr">
         <is>
-          <t>maa://27396 (83.93), maa://27484 (96.58), maa://27480 (85.0)</t>
+          <t>maa://27396 (83.98), maa://27484 (96.6), maa://27480 (85.0)</t>
         </is>
       </c>
       <c r="Y3" s="19" t="n"/>
@@ -926,7 +927,7 @@
       </c>
       <c r="AB3" s="8" t="inlineStr">
         <is>
-          <t>maa://24390 (95.79), maa://52241 (93.75)</t>
+          <t>maa://24390 (95.83), maa://52241 (93.75)</t>
         </is>
       </c>
       <c r="AC3" s="19" t="n"/>
@@ -960,7 +961,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>maa://24632 (93.33), maa://22499 (88.24), maa://22746 (100.0)</t>
+          <t>maa://24632 (93.4), maa://22499 (88.24), maa://22746 (100.0)</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
@@ -1008,7 +1009,7 @@
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>maa://49983 (95.96), maa://50121 (95.35)</t>
+          <t>maa://49983 (96.0), maa://50121 (95.35)</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
@@ -1024,7 +1025,7 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>maa://32509 (94.07), maa://27295 (87.25), maa://22754 (89.19), *maa://31008 (79.55)</t>
+          <t>maa://32509 (94.16), maa://27295 (87.25), maa://22754 (89.19), *maa://31008 (79.55)</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>
@@ -1040,7 +1041,7 @@
       </c>
       <c r="X4" s="8" t="inlineStr">
         <is>
-          <t>maa://43217 (93.42)</t>
+          <t>maa://43217 (92.86)</t>
         </is>
       </c>
       <c r="Y4" s="19" t="n"/>
@@ -1095,7 +1096,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>maa://21245 (83.67), maa://22744 (82.14), maa://54105 (90.48)</t>
+          <t>maa://21245 (83.5), maa://22744 (82.14), maa://54105 (91.3)</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -1257,7 +1258,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>maa://24839 (98.86)</t>
+          <t>maa://24839 (98.87)</t>
         </is>
       </c>
       <c r="M6" s="19" t="n"/>
@@ -1387,7 +1388,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>maa://28624 (94.38), maa://24957 (97.83)</t>
+          <t>maa://28624 (94.51), maa://24957 (97.83)</t>
         </is>
       </c>
       <c r="M7" s="19" t="n"/>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>maa://21291 (87.88)</t>
+          <t>maa://21291 (88.06)</t>
         </is>
       </c>
       <c r="U7" s="19" t="n"/>
@@ -1475,7 +1476,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.16 13:27:18</t>
+          <t>更新日期：2025.07.19 13:26:03</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1570,7 +1571,7 @@
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>maa://21411 (95.33)</t>
+          <t>maa://21411 (95.13)</t>
         </is>
       </c>
       <c r="Y8" s="19" t="n"/>
@@ -1602,7 +1603,7 @@
       </c>
       <c r="AF8" s="8" t="inlineStr">
         <is>
-          <t>*maa://24479 (77.23), *maa://21990 (51.85)</t>
+          <t>*maa://24479 (77.23), **maa://21990 (50.0)</t>
         </is>
       </c>
       <c r="AG8" s="16" t="n"/>
@@ -1716,7 +1717,7 @@
       </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
-          <t>maa://28711 (87.67), maa://40166 (91.84)</t>
+          <t>maa://28711 (87.76), maa://40166 (91.84)</t>
         </is>
       </c>
       <c r="AC9" s="19" t="n"/>
@@ -1732,7 +1733,7 @@
       </c>
       <c r="AF9" s="8" t="inlineStr">
         <is>
-          <t>maa://26206 (89.13), *maa://22865 (53.45)</t>
+          <t>maa://26206 (89.19), *maa://22865 (53.45)</t>
         </is>
       </c>
       <c r="AG9" s="16" t="n"/>
@@ -1814,7 +1815,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (96.85), maa://22755 (89.39)</t>
+          <t>maa://27395 (96.86), maa://22755 (88.72)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1944,7 +1945,7 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>maa://22747 (90.0), maa://22501 (98.29), maa://45521 (91.89)</t>
+          <t>maa://22747 (90.0), maa://22501 (98.31), maa://45521 (91.89)</t>
         </is>
       </c>
       <c r="U11" s="19" t="n"/>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="AB11" s="8" t="inlineStr">
         <is>
-          <t>maa://29912 (97.92), maa://22516 (87.36)</t>
+          <t>maa://29912 (97.96), maa://22516 (87.36)</t>
         </is>
       </c>
       <c r="AC11" s="19" t="n"/>
@@ -2090,7 +2091,7 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>maa://22753 (92.17), maa://37962 (90.67), *maa://21485 (76.16)</t>
+          <t>maa://22753 (92.2), maa://37962 (90.67), *maa://21485 (76.16)</t>
         </is>
       </c>
       <c r="Y12" s="19" t="n"/>
@@ -2106,7 +2107,7 @@
       </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
-          <t>maa://23669 (95.7), maa://36677 (95.65), maa://39872 (93.1)</t>
+          <t>maa://23669 (95.7), maa://36677 (95.74), maa://39872 (93.1)</t>
         </is>
       </c>
       <c r="AC12" s="19" t="n"/>
@@ -2122,7 +2123,7 @@
       </c>
       <c r="AF12" s="8" t="inlineStr">
         <is>
-          <t>*maa://28932 (79.33), *maa://20106 (64.29), *maa://22769 (64.29)</t>
+          <t>*maa://28932 (78.89), *maa://20106 (64.29), *maa://22769 (62.07)</t>
         </is>
       </c>
       <c r="AG12" s="16" t="n"/>
@@ -2140,7 +2141,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>maa://24999 (92.89), maa://36673 (92.22), maa://25001 (86.49)</t>
+          <t>maa://24999 (92.92), maa://36673 (92.22), maa://25001 (86.49)</t>
         </is>
       </c>
       <c r="E13" s="19" t="n"/>
@@ -2156,7 +2157,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.94), **maa://22728 (46.94)</t>
+          <t>*maa://21248 (73.78), **maa://22728 (46.94)</t>
         </is>
       </c>
       <c r="I13" s="19" t="n"/>
@@ -2188,7 +2189,7 @@
       </c>
       <c r="P13" s="8" t="inlineStr">
         <is>
-          <t>maa://22676 (93.84), *maa://22583 (78.57), maa://48321 (85.71)</t>
+          <t>maa://22676 (93.92), *maa://22583 (78.57), maa://48321 (85.71)</t>
         </is>
       </c>
       <c r="Q13" s="19" t="n"/>
@@ -2252,7 +2253,7 @@
       </c>
       <c r="AF13" s="8" t="inlineStr">
         <is>
-          <t>maa://39883 (87.69), **maa://39885 (50.0)</t>
+          <t>maa://39883 (87.79), **maa://39885 (50.0)</t>
         </is>
       </c>
       <c r="AG13" s="16" t="n"/>
@@ -2400,7 +2401,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>*maa://22743 (78.63), maa://22734 (84.55), *maa://30808 (63.51), *maa://36048 (69.42), maa://45058 (82.61)</t>
+          <t>*maa://22743 (78.71), maa://22734 (84.55), *maa://30808 (63.51), *maa://36048 (69.67), maa://45058 (82.61)</t>
         </is>
       </c>
       <c r="E15" s="19" t="n"/>
@@ -2448,7 +2449,7 @@
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>maa://24762 (91.05), *maa://22727 (70.0)</t>
+          <t>maa://24762 (91.1), *maa://22727 (70.0)</t>
         </is>
       </c>
       <c r="Q15" s="19" t="n"/>
@@ -2594,7 +2595,7 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>maa://22729 (94.59), *maa://28648 (75.29), *maa://36674 (79.69)</t>
+          <t>maa://22729 (94.65), *maa://28648 (75.29), *maa://36674 (79.69)</t>
         </is>
       </c>
       <c r="U16" s="19" t="n"/>
@@ -2676,7 +2677,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>maa://22430 (89.4), maa://39599 (87.21)</t>
+          <t>maa://22430 (89.45), maa://39599 (87.36)</t>
         </is>
       </c>
       <c r="I17" s="19" t="n"/>
@@ -2790,7 +2791,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>maa://24570 (97.14)</t>
+          <t>maa://24570 (97.16)</t>
         </is>
       </c>
       <c r="E18" s="19" t="n"/>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>maa://24421 (87.15)</t>
+          <t>maa://24421 (87.2)</t>
         </is>
       </c>
       <c r="I18" s="19" t="n"/>
@@ -2854,7 +2855,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>maa://24385 (97.5)</t>
+          <t>maa://24385 (97.56)</t>
         </is>
       </c>
       <c r="U18" s="19" t="n"/>
@@ -3016,7 +3017,7 @@
       </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
-          <t>*maa://30709 (69.23), *maa://36668 (57.83)</t>
+          <t>*maa://30709 (69.29), *maa://36668 (57.83)</t>
         </is>
       </c>
       <c r="AC19" s="19" t="n"/>
@@ -3082,7 +3083,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>maa://41331 (86.26)</t>
+          <t>maa://41331 (86.36)</t>
         </is>
       </c>
       <c r="M20" s="19" t="n"/>
@@ -3130,7 +3131,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://50085 (89.53), maa://49976 (87.21), maa://56241 (90.0)</t>
+          <t>maa://50085 (89.71), maa://49976 (87.21), maa://56241 (90.0)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3292,7 +3293,7 @@
       </c>
       <c r="AF21" s="8" t="inlineStr">
         <is>
-          <t>maa://22524 (87.26), maa://22432 (83.67)</t>
+          <t>maa://22524 (86.92), maa://22432 (83.67)</t>
         </is>
       </c>
       <c r="AG21" s="16" t="n"/>
@@ -3326,7 +3327,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>maa://25236 (96.33)</t>
+          <t>maa://25236 (96.36)</t>
         </is>
       </c>
       <c r="I22" s="19" t="n"/>
@@ -3390,7 +3391,7 @@
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>maa://21282 (98.76), *maa://37649 (72.55)</t>
+          <t>maa://21282 (98.77), *maa://37649 (72.55)</t>
         </is>
       </c>
       <c r="Y22" s="19" t="n"/>
@@ -3472,7 +3473,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>maa://39756 (95.76), maa://39875 (93.9)</t>
+          <t>maa://39756 (95.77), maa://39875 (93.9)</t>
         </is>
       </c>
       <c r="M23" s="19" t="n"/>
@@ -3570,7 +3571,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>*maa://24368 (79.57), *maa://46650 (61.76)</t>
+          <t>*maa://24368 (79.62), *maa://46650 (61.76)</t>
         </is>
       </c>
       <c r="E24" s="19" t="n"/>
@@ -3650,7 +3651,7 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>maa://29988 (84.98), maa://23504 (93.83), *maa://25141 (77.37), *maa://36663 (78.43), maa://52227 (95.65)</t>
+          <t>maa://29988 (85.03), maa://23504 (93.84), *maa://25141 (77.37), *maa://36663 (78.43), maa://52227 (95.65)</t>
         </is>
       </c>
       <c r="Y24" s="19" t="n"/>
@@ -3695,12 +3696,12 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>maa://29753 (95.6)</t>
+          <t>maa://29753 (95.6), maa://63016 (100.0)</t>
         </is>
       </c>
       <c r="E25" s="19" t="n"/>
@@ -3716,7 +3717,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>*maa://29063 (72.14), *maa://25311 (74.56), ***maa://22725 (4.76), *maa://45047 (73.33)</t>
+          <t>*maa://29063 (72.14), *maa://25311 (74.78), ***maa://22725 (4.76), *maa://45047 (73.33)</t>
         </is>
       </c>
       <c r="I25" s="19" t="n"/>
@@ -3764,7 +3765,7 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>maa://20109 (92.71), maa://22545 (100.0), *maa://42915 (75.0)</t>
+          <t>maa://20109 (92.75), maa://22545 (100.0), *maa://42915 (75.0)</t>
         </is>
       </c>
       <c r="U25" s="19" t="n"/>
@@ -3796,7 +3797,7 @@
       </c>
       <c r="AB25" s="8" t="inlineStr">
         <is>
-          <t>maa://31215 (89.47), *maa://24516 (79.57), maa://26001 (84.75)</t>
+          <t>maa://31215 (89.61), *maa://24516 (79.57), maa://26001 (84.75)</t>
         </is>
       </c>
       <c r="AC25" s="19" t="n"/>
@@ -3812,7 +3813,7 @@
       </c>
       <c r="AF25" s="8" t="inlineStr">
         <is>
-          <t>maa://20108 (95.97), maa://24621 (97.22), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (80.0)</t>
+          <t>maa://20108 (96.0), maa://24621 (97.22), maa://36676 (97.06), maa://22771 (85.71), *maa://37772 (80.0)</t>
         </is>
       </c>
       <c r="AG25" s="16" t="n"/>
@@ -3830,7 +3831,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>maa://41802 (93.55), maa://56374 (100.0)</t>
+          <t>maa://41802 (93.75), maa://56374 (100.0)</t>
         </is>
       </c>
       <c r="E26" s="19" t="n"/>
@@ -3926,7 +3927,7 @@
       </c>
       <c r="AB26" s="8" t="inlineStr">
         <is>
-          <t>maa://42235 (96.3)</t>
+          <t>maa://42235 (96.32)</t>
         </is>
       </c>
       <c r="AC26" s="19" t="n"/>
@@ -4090,7 +4091,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>maa://24465 (90.82), maa://25725 (83.0)</t>
+          <t>maa://24465 (90.83), maa://25725 (83.0)</t>
         </is>
       </c>
       <c r="E28" s="19" t="n"/>
@@ -4170,7 +4171,7 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t>maa://39929 (92.17), maa://41749 (92.0)</t>
+          <t>maa://39929 (92.19), maa://41749 (92.0)</t>
         </is>
       </c>
       <c r="Y28" s="19" t="n"/>
@@ -4202,7 +4203,7 @@
       </c>
       <c r="AF28" s="8" t="inlineStr">
         <is>
-          <t>maa://36660 (92.27)</t>
+          <t>maa://36660 (92.29)</t>
         </is>
       </c>
       <c r="AG28" s="16" t="n"/>
@@ -4252,7 +4253,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>maa://28432 (94.16), maa://31400 (98.9), maa://28440 (84.83), *maa://28650 (71.43)</t>
+          <t>maa://28432 (94.18), maa://31400 (98.9), maa://28440 (84.93), *maa://28650 (71.43)</t>
         </is>
       </c>
       <c r="M29" s="19" t="n"/>
@@ -4332,7 +4333,7 @@
       </c>
       <c r="AF29" s="8" t="inlineStr">
         <is>
-          <t>*maa://24080 (69.25), maa://42865 (81.67)</t>
+          <t>*maa://24080 (69.25), maa://42865 (80.33)</t>
         </is>
       </c>
       <c r="AG29" s="16" t="n"/>
@@ -4446,7 +4447,7 @@
       </c>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>maa://42979 (97.22), maa://45822 (100.0), maa://45045 (83.33)</t>
+          <t>maa://42979 (97.23), maa://45822 (100.0), maa://45045 (83.33)</t>
         </is>
       </c>
       <c r="AC30" s="19" t="n"/>
@@ -4512,7 +4513,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>maa://35926 (93.55), maa://36258 (88.44), *maa://43904 (73.33)</t>
+          <t>maa://35926 (93.55), maa://36258 (88.51), *maa://43904 (73.33)</t>
         </is>
       </c>
       <c r="M31" s="19" t="n"/>
@@ -4626,7 +4627,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>maa://21895 (97.72), maa://36667 (97.44), maa://22760 (100.0)</t>
+          <t>maa://21895 (97.73), maa://36667 (97.46), maa://22760 (100.0)</t>
         </is>
       </c>
       <c r="I32" s="19" t="n"/>
@@ -4674,7 +4675,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>maa://42859 (97.2), maa://41108 (86.27), maa://41238 (98.14), maa://45523 (100.0)</t>
+          <t>maa://42859 (97.24), maa://41108 (86.27), maa://41238 (98.17), maa://45523 (100.0)</t>
         </is>
       </c>
       <c r="U32" s="19" t="n"/>
@@ -5032,7 +5033,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>maa://41296 (97.49)</t>
+          <t>maa://41296 (97.5)</t>
         </is>
       </c>
       <c r="M35" s="19" t="n"/>
@@ -5292,7 +5293,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>maa://45718 (98.59), maa://47069 (81.82), maa://56336 (90.0), maa://45789 (100.0)</t>
+          <t>maa://45718 (98.59), maa://47069 (81.82), maa://56336 (81.82), maa://45789 (100.0)</t>
         </is>
       </c>
       <c r="M37" s="19" t="n"/>
@@ -5457,7 +5458,7 @@
       </c>
       <c r="AF38" s="8" t="inlineStr">
         <is>
-          <t>maa://36697 (89.64)</t>
+          <t>maa://36697 (89.68)</t>
         </is>
       </c>
       <c r="AG38" s="16" t="n"/>
@@ -5478,7 +5479,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>maa://36670 (87.8), maa://25199 (85.47), maa://30434 (93.66), *maa://45059 (75.0), *maa://44165 (75.0)</t>
+          <t>maa://36670 (87.8), maa://25199 (85.47), maa://30434 (93.75), *maa://45059 (75.68), *maa://44165 (75.0)</t>
         </is>
       </c>
       <c r="I39" s="19" t="n"/>
@@ -5510,7 +5511,7 @@
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>maa://24709 (91.67), maa://47093 (100.0)</t>
+          <t>maa://24709 (91.71), maa://47093 (100.0)</t>
         </is>
       </c>
       <c r="Q39" s="19" t="n"/>
@@ -5526,7 +5527,7 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>maa://47079 (94.64), *maa://45788 (70.73), maa://45790 (81.25)</t>
+          <t>maa://47079 (93.86), *maa://45788 (70.73), maa://45790 (81.25)</t>
         </is>
       </c>
       <c r="U39" s="19" t="n"/>
@@ -5558,7 +5559,7 @@
       </c>
       <c r="AF39" s="8" t="inlineStr">
         <is>
-          <t>*maa://62953 (78.57)</t>
+          <t>maa://62953 (90.0)</t>
         </is>
       </c>
       <c r="AG39" s="16" t="n"/>
@@ -5611,7 +5612,7 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>maa://23278 (95.28), maa://21386 (95.83), maa://36664 (90.16), maa://45550 (87.5)</t>
+          <t>maa://23278 (95.31), maa://21386 (95.83), maa://36664 (88.71), maa://45550 (87.5)</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -5951,7 +5952,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>maa://29768 (97.68), maa://27728 (96.19), maa://56386 (100.0)</t>
+          <t>maa://29768 (97.69), maa://27728 (96.19), maa://56386 (100.0)</t>
         </is>
       </c>
       <c r="I44" s="19" t="n"/>
@@ -5983,7 +5984,7 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>maa://39366 (89.74)</t>
+          <t>maa://39366 (90.0)</t>
         </is>
       </c>
       <c r="U44" s="19" t="n"/>
@@ -6089,7 +6090,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>maa://35931 (91.88), maa://43901 (92.31)</t>
+          <t>maa://35931 (91.92), maa://43901 (92.31)</t>
         </is>
       </c>
       <c r="I46" s="19" t="n"/>
@@ -6158,7 +6159,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>maa://27410 (96.92), maa://29661 (97.67), maa://28038 (84.62), maa://56236 (100.0)</t>
+          <t>maa://27410 (96.93), maa://29661 (97.67), maa://28038 (84.62), maa://56236 (100.0)</t>
         </is>
       </c>
       <c r="I47" s="19" t="n"/>
@@ -6333,7 +6334,7 @@
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>*maa://62852 (68.0)</t>
+          <t>*maa://62852 (78.12)</t>
         </is>
       </c>
       <c r="Q50" s="19" t="n"/>
@@ -6433,7 +6434,7 @@
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>maa://59394 (97.87), maa://59378 (94.74)</t>
+          <t>maa://59394 (97.92), maa://59378 (95.0)</t>
         </is>
       </c>
       <c r="Q52" s="19" t="n"/>
@@ -6467,7 +6468,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>maa://32534 (95.32)</t>
+          <t>maa://32534 (95.34)</t>
         </is>
       </c>
       <c r="I53" s="19" t="n"/>
@@ -6551,7 +6552,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>maa://32532 (93.59)</t>
+          <t>maa://32532 (93.61)</t>
         </is>
       </c>
       <c r="I55" s="19" t="n"/>
@@ -6695,7 +6696,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>maa://59534 (97.89), maa://59413 (100.0)</t>
+          <t>maa://59534 (97.94), maa://59413 (100.0)</t>
         </is>
       </c>
       <c r="I63" s="19" t="n"/>
@@ -6713,7 +6714,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>maa://44405 (85.71)</t>
+          <t>maa://44405 (86.05)</t>
         </is>
       </c>
       <c r="I64" s="19" t="n"/>
@@ -7012,7 +7013,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.16 13:27:18</t>
+          <t>更新日期：2025.07.19 13:26:03</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -8200,7 +8201,7 @@
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>maa://20876 (94.74)</t>
+          <t>maa://20876 (95.0)</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -8416,7 +8417,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>*maa://20849 (70.59), *maa://28758 (67.5), maa://29036 (96.0), *maa://42172 (64.29), maa://30285 (100.0)</t>
+          <t>*maa://20849 (70.59), *maa://28758 (67.5), maa://29036 (96.15), *maa://42172 (66.67), maa://30285 (100.0)</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -8686,7 +8687,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>maa://36644 (87.94), maa://36866 (96.49), maa://45572 (93.33), maa://27794 (100.0), maa://20960 (100.0), maa://20843 (100.0), **maa://24483 (50.0), maa://62759 (100.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
+          <t>maa://36644 (88.06), maa://36866 (96.49), maa://45572 (93.33), maa://27794 (100.0), maa://62759 (100.0), maa://20960 (100.0), maa://20843 (100.0), **maa://24483 (50.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -9982,7 +9983,7 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>maa://44235 (98.27), maa://45604 (100.0), maa://20961 (100.0), maa://44220 (100.0), maa://20910 (100.0)</t>
+          <t>maa://44235 (98.28), maa://45604 (100.0), maa://20961 (100.0), maa://44220 (100.0), maa://20910 (100.0)</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -10198,7 +10199,7 @@
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>maa://38298 (87.85)</t>
+          <t>maa://38298 (87.96)</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -10360,7 +10361,7 @@
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>*maa://20845 (68.0), maa://38727 (90.0)</t>
+          <t>*maa://20845 (69.23), maa://38727 (90.0)</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -10684,7 +10685,7 @@
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>maa://20974 (96.55), maa://29079 (80.95), maa://29096 (95.65), maa://29087 (100.0), *maa://20823 (80.0), maa://20855 (93.75), maa://20904 (100.0)</t>
+          <t>maa://20974 (96.59), maa://29079 (80.95), maa://29096 (95.65), maa://29087 (100.0), *maa://20823 (80.0), maa://20855 (93.75), maa://20904 (100.0)</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -10846,7 +10847,7 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>maa://36643 (98.27), maa://36864 (98.02), maa://39140 (100.0)</t>
+          <t>maa://36643 (98.28), maa://36864 (98.02), maa://39140 (100.0)</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -11710,7 +11711,7 @@
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>maa://24472 (88.63), *maa://35841 (61.11)</t>
+          <t>maa://24472 (88.68), *maa://35841 (61.11)</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -12034,7 +12035,7 @@
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>maa://40157 (85.71)</t>
+          <t>maa://40157 (87.5)</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -12196,7 +12197,7 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>maa://20991 (100.0), maa://51015 (88.89)</t>
+          <t>maa://20991 (100.0), maa://51015 (86.21)</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -12304,7 +12305,7 @@
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>maa://20929 (91.67)</t>
+          <t>maa://20929 (92.0)</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
@@ -12790,7 +12791,7 @@
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>maa://25018 (96.73), maa://51881 (99.24), maa://25776 (92.11), maa://28361 (95.24), maa://25772 (94.12), maa://56588 (95.0), maa://45194 (82.35), maa://25161 (81.25), maa://32653 (85.71), ***maa://60902 (28.57), maa://61839 (100.0)</t>
+          <t>maa://25018 (96.73), maa://51881 (99.25), maa://25776 (92.11), maa://28361 (95.24), maa://25772 (94.12), maa://56588 (95.0), maa://45194 (82.35), maa://25161 (82.35), maa://32653 (85.71), ***maa://60902 (25.0), maa://61839 (100.0)</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -13276,7 +13277,7 @@
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>maa://31560 (91.67), maa://20940 (100.0)</t>
+          <t>maa://31560 (91.67), maa://20940 (85.71)</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
@@ -13492,7 +13493,7 @@
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>maa://20869 (100.0), maa://44690 (96.0)</t>
+          <t>maa://20869 (100.0), maa://44690 (96.3)</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -14071,27 +14072,27 @@
     <row r="132" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>月禾</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>DM-3</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
-          <t>maa://20837 (100.0), maa://37666 (90.91)</t>
+          <t>maa://39146 (100.0)</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战W累计造成80歼灭数※此面向敌和通过D12的炸弹击倒的敌人可计数&gt; 3星通关插曲DM-3；必须编入非助战W并上场，且使用W歼灭至少2个萨卡兹穿刺手※允许使用此面向敌或通过D12的炸弹击倒相应目标</t>
+          <t>&gt; 战斗中非助战月禾累计使用迹无8次&gt; 3星通关主题曲S3-6；必须编入非助战月禾并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F132" s="19" t="n"/>
@@ -14125,27 +14126,27 @@
     <row r="133" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>波登可</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>DM-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>maa://29023 (100.0), maa://39515 (91.67)</t>
+          <t>maa://20856 (100.0)</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战W累计使用惊吓盒子10次&gt; 3星通关插曲DM-7；必须编入非助战W并上场，且不编入特种干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战波登可并上场，且每次战斗至少释放2次孢子扩散&gt; 3星通关主题曲4-6；必须编入非助战波登可并上场，且使用波登可歼灭至少2个高能源石虫</t>
         </is>
       </c>
       <c r="F133" s="19" t="n"/>
@@ -14179,12 +14180,12 @@
     <row r="134" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>月禾</t>
+          <t>苦艾</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
@@ -14194,12 +14195,12 @@
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>maa://39146 (100.0)</t>
+          <t>maa://20913 (100.0)</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战月禾累计使用迹无8次&gt; 3星通关主题曲S3-6；必须编入非助战月禾并上场，且所有干员不被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战苦艾并上场，且每次战斗至少释放1次终结连射&gt; 3星通关主题曲3-4；必须编入非助战苦艾并上场，且不编入其他术师干员</t>
         </is>
       </c>
       <c r="F134" s="19" t="n"/>
@@ -14233,12 +14234,12 @@
     <row r="135" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>波登可</t>
+          <t>莱恩哈特</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
@@ -14248,12 +14249,12 @@
       </c>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>maa://20856 (100.0)</t>
+          <t>maa://41856 (100.0)</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战波登可并上场，且每次战斗至少释放2次孢子扩散&gt; 3星通关主题曲4-6；必须编入非助战波登可并上场，且使用波登可歼灭至少2个高能源石虫</t>
+          <t>&gt; 完成5次战斗；必须编入非助战莱恩哈特并上场，且每次战斗至少释放4次解构与爆破&gt; 3星通关主题曲3-5；必须编入非助战莱恩哈特并上场，且莱恩哈特使用技能解构与爆破歼灭至少10名敌人</t>
         </is>
       </c>
       <c r="F135" s="19" t="n"/>
@@ -14287,27 +14288,27 @@
     <row r="136" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>苦艾</t>
+          <t>早露</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>maa://20913 (100.0)</t>
+          <t>maa://29025 (82.76), **maa://21000 (45.16)</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战苦艾并上场，且每次战斗至少释放1次终结连射&gt; 3星通关主题曲3-4；必须编入非助战苦艾并上场，且不编入其他术师干员</t>
+          <t>&gt; 由非助战早露累计造成80000点伤害&gt; 3星通关主题曲7-9；必须编入非助战早露并上场，其他成员不可编入狙击干员</t>
         </is>
       </c>
       <c r="F136" s="19" t="n"/>
@@ -14341,27 +14342,27 @@
     <row r="137" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>莱恩哈特</t>
+          <t>卡达</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>maa://41856 (100.0)</t>
+          <t>**maa://30679 (50.0), maa://45258 (94.12)</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战莱恩哈特并上场，且每次战斗至少释放4次解构与爆破&gt; 3星通关主题曲3-5；必须编入非助战莱恩哈特并上场，且莱恩哈特使用技能解构与爆破歼灭至少10名敌人</t>
+          <t>&gt; 战斗中非助战卡达累计使用同步索敌攻击10次&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战卡达并上场，且使用卡达歼灭至少1名食腐使徒</t>
         </is>
       </c>
       <c r="F137" s="19" t="n"/>
@@ -14395,27 +14396,27 @@
     <row r="138" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>早露</t>
+          <t>亚叶</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>maa://29025 (82.76), **maa://21000 (45.16)</t>
+          <t>maa://20981 (92.86)</t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战早露累计造成80000点伤害&gt; 3星通关主题曲7-9；必须编入非助战早露并上场，其他成员不可编入狙击干员</t>
+          <t>&gt; 由非助战亚叶累计造成80000点伤害&gt; 3星通关主题曲5-2；必须编入非助战亚叶并上场，且使用亚叶至少歼灭8名敌人</t>
         </is>
       </c>
       <c r="F138" s="19" t="n"/>
@@ -14449,27 +14450,27 @@
     <row r="139" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>卡达</t>
+          <t>断崖</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>**maa://30679 (50.0), maa://45258 (93.75)</t>
+          <t>maa://37689 (100.0)</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战卡达累计使用同步索敌攻击10次&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战卡达并上场，且使用卡达歼灭至少1名食腐使徒</t>
+          <t>&gt; 由非助战断崖累计造成80000点伤害&gt; 3星通关主题曲5-8；必须编入非助战断崖并上场，且使用断崖使用至少2次浮游刃启动</t>
         </is>
       </c>
       <c r="F139" s="19" t="n"/>
@@ -14503,27 +14504,27 @@
     <row r="140" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>亚叶</t>
+          <t>铃兰</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>TW-7</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
-          <t>maa://20981 (92.86)</t>
+          <t>maa://28484 (97.22), **maa://23736 (44.93), maa://31185 (85.71), maa://30306 (100.0)</t>
         </is>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战亚叶累计造成80000点伤害&gt; 3星通关主题曲5-2；必须编入非助战亚叶并上场，且使用亚叶至少歼灭8名敌人</t>
+          <t>&gt; 战斗中非助战铃兰累计使用狐火渺然6次&gt; 3星通关别传TW-7；且仅可编入非助战铃兰1名辅助干员并上场</t>
         </is>
       </c>
       <c r="F140" s="19" t="n"/>
@@ -14557,27 +14558,27 @@
     <row r="141" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>断崖</t>
+          <t>铃兰</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>maa://37689 (100.0)</t>
+          <t>maa://30670 (96.75), maa://31470 (96.67), *maa://45066 (71.43), **maa://30867 (40.0)</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战断崖累计造成80000点伤害&gt; 3星通关主题曲5-8；必须编入非助战断崖并上场，且使用断崖使用至少2次浮游刃启动</t>
+          <t>&gt; 完成5次战斗；必须编入非助战铃兰并上场，且每次战斗至少释放1次狐火渺然&gt; 3星通关插曲DM-EX-1；必须编入非助战铃兰并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
       <c r="F141" s="19" t="n"/>
@@ -14611,27 +14612,27 @@
     <row r="142" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>铃兰</t>
+          <t>稀音</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>TW-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>maa://28484 (97.22), **maa://23736 (44.93), maa://31185 (85.71), maa://30306 (100.0)</t>
+          <t>maa://20971 (92.86)</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战铃兰累计使用狐火渺然6次&gt; 3星通关别传TW-7；且仅可编入非助战铃兰1名辅助干员并上场</t>
+          <t>&gt; 完成5次战斗；每次战斗至少召唤5回非助战稀音的召唤物&gt; 使用至多2人（包含助战）的队伍3星通关主题曲3-1；必须编入非助战稀音并上场，其他成员仅可编入狙击干员</t>
         </is>
       </c>
       <c r="F142" s="19" t="n"/>
@@ -14665,27 +14666,27 @@
     <row r="143" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>铃兰</t>
+          <t>蜜蜡</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>maa://30670 (96.75), maa://31470 (96.67), *maa://45066 (71.43), **maa://30867 (40.0)</t>
+          <t>maa://39147 (100.0)</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战铃兰并上场，且每次战斗至少释放1次狐火渺然&gt; 3星通关插曲DM-EX-1；必须编入非助战铃兰并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 战斗中非助战蜜蜡累计使用守卫尖碑8次&gt; 3星通关别传DH-6；必须编入非助战蜜蜡并上场，且不编入重装干员</t>
         </is>
       </c>
       <c r="F143" s="19" t="n"/>
@@ -14719,12 +14720,12 @@
     <row r="144" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>稀音</t>
+          <t>贾维</t>
         </is>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
@@ -14734,12 +14735,12 @@
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>maa://20971 (92.86)</t>
+          <t>maa://20898 (100.0)</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；每次战斗至少召唤5回非助战稀音的召唤物&gt; 使用至多2人（包含助战）的队伍3星通关主题曲3-1；必须编入非助战稀音并上场，其他成员仅可编入狙击干员</t>
+          <t>&gt; 战斗中非助战贾维累计使用火焰剥离5次&gt; 3星通关主题曲1-1；必须编入非助战贾维并上场，其他成员仅可编入1星干员</t>
         </is>
       </c>
       <c r="F144" s="19" t="n"/>
@@ -14773,27 +14774,27 @@
     <row r="145" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>蜜蜡</t>
+          <t>孑</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>S3-2</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>maa://39147 (100.0)</t>
+          <t>maa://29056 (100.0), ***maa://20901 (7.69)</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战蜜蜡累计使用守卫尖碑8次&gt; 3星通关别传DH-6；必须编入非助战蜜蜡并上场，且不编入重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战孑并部署至少2次，且使用孑歼灭至少3名敌人&gt; 3星通关主题曲S3-2；必须编入非助战孑并上场，且使用孑歼灭至少8个源石虫·β</t>
         </is>
       </c>
       <c r="F145" s="19" t="n"/>
@@ -14827,27 +14828,27 @@
     <row r="146" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>贾维</t>
+          <t>安哲拉</t>
         </is>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>maa://20898 (100.0)</t>
+          <t>maa://28828 (88.24), maa://20846 (95.83), *maa://47286 (75.0)</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战贾维累计使用火焰剥离5次&gt; 3星通关主题曲1-1；必须编入非助战贾维并上场，其他成员仅可编入1星干员</t>
+          <t>&gt; 由非助战安哲拉累计造成150000点伤害&gt; 3星通关主题曲3-2；必须编入非助战安哲拉并上场，且使用安哲拉至少歼灭15名敌人</t>
         </is>
       </c>
       <c r="F146" s="19" t="n"/>
@@ -14881,27 +14882,27 @@
     <row r="147" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>孑</t>
+          <t>棘刺</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>S3-2</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>maa://29056 (100.0), ***maa://20901 (7.69)</t>
+          <t>maa://40957 (94.23), maa://36641 (98.45), maa://36865 (95.81), maa://44635 (88.07), maa://44660 (92.5), maa://41128 (84.21), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战孑并部署至少2次，且使用孑歼灭至少3名敌人&gt; 3星通关主题曲S3-2；必须编入非助战孑并上场，且使用孑歼灭至少8个源石虫·β</t>
+          <t>&gt; 由非助战棘刺累计造成100000点伤害&gt; 3星通关插曲SV-6；必须编入非助战棘刺并上场，且使用棘刺至少歼灭20个敌人</t>
         </is>
       </c>
       <c r="F147" s="19" t="n"/>
@@ -14935,27 +14936,27 @@
     <row r="148" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>安哲拉</t>
+          <t>棘刺</t>
         </is>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr">
         <is>
-          <t>maa://28828 (88.24), maa://20846 (95.83), *maa://47286 (75.0)</t>
+          <t>maa://51549 (95.74), maa://51923 (95.83)</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战安哲拉累计造成150000点伤害&gt; 3星通关主题曲3-2；必须编入非助战安哲拉并上场，且使用安哲拉至少歼灭15名敌人</t>
+          <t>&gt; 战斗中非助战棘刺累计使用至高之术8次&gt; 3星通关主题曲7-2；必须编入非助战棘刺并上场，其他成员不可编入近卫干员</t>
         </is>
       </c>
       <c r="F148" s="19" t="n"/>
@@ -14989,27 +14990,27 @@
     <row r="149" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>棘刺</t>
+          <t>酸糖</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>maa://40957 (94.22), maa://36641 (98.45), maa://36865 (95.81), maa://44635 (88.07), maa://44660 (92.31), maa://41128 (84.21), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
+          <t>maa://20961 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战棘刺累计造成100000点伤害&gt; 3星通关插曲SV-6；必须编入非助战棘刺并上场，且使用棘刺至少歼灭20个敌人</t>
+          <t>&gt; 由非助战酸糖累计造成50歼灭数&gt; 3星通关主题曲2-8；必须编入非助战酸糖并上场，且使用酸糖歼灭至少1个磐蟹</t>
         </is>
       </c>
       <c r="F149" s="19" t="n"/>
@@ -15043,27 +15044,27 @@
     <row r="150" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>棘刺</t>
+          <t>特米米</t>
         </is>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>RI-2</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>maa://51549 (95.56), maa://51923 (95.83)</t>
+          <t>maa://20963 (100.0)</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战棘刺累计使用至高之术8次&gt; 3星通关主题曲7-2；必须编入非助战棘刺并上场，其他成员不可编入近卫干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战特米米并上场，且每次战斗至少释放1次嘉维尔保护方案&gt; 3星通关别传RI-2；必须编入非助战特米米并上场，且不编入其他术师干员</t>
         </is>
       </c>
       <c r="F150" s="19" t="n"/>
@@ -15097,12 +15098,12 @@
     <row r="151" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>酸糖</t>
+          <t>燧石</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>RI-9</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
@@ -15112,12 +15113,12 @@
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>maa://20961 (100.0)</t>
+          <t>maa://39148 (100.0)</t>
         </is>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战酸糖累计造成50歼灭数&gt; 3星通关主题曲2-8；必须编入非助战酸糖并上场，且使用酸糖歼灭至少1个磐蟹</t>
+          <t>&gt; 战斗中非助战燧石累计使用锋芒毕露8次&gt; 3星通关别传RI-9；必须编入非助战燧石并上场，且使用燧石至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F151" s="19" t="n"/>
@@ -15151,27 +15152,27 @@
     <row r="152" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>特米米</t>
+          <t>森蚺</t>
         </is>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>RI-2</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>maa://20963 (100.0)</t>
+          <t>maa://20946 (100.0), maa://20833 (100.0)</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战特米米并上场，且每次战斗至少释放1次嘉维尔保护方案&gt; 3星通关别传RI-2；必须编入非助战特米米并上场，且不编入其他术师干员</t>
+          <t>&gt; 由非助战森蚺累计造成60000点伤害&gt; 3星通关别传RI-EX-4；必须编入非助战森蚺并上场，且使用森蚺歼灭至少1个提亚卡乌冠军</t>
         </is>
       </c>
       <c r="F152" s="19" t="n"/>
@@ -15205,12 +15206,12 @@
     <row r="153" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>燧石</t>
+          <t>森蚺</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>RI-9</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -15220,12 +15221,12 @@
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>maa://39148 (100.0)</t>
+          <t>maa://20945 (88.46)</t>
         </is>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战燧石累计使用锋芒毕露8次&gt; 3星通关别传RI-9；必须编入非助战燧石并上场，且使用燧石至少歼灭10个敌人</t>
+          <t>&gt; 由非助战森蚺累计歼灭10个精英或领袖敌人&gt; 3星通关别传RI-7；必须编入非助战森蚺并上场，且使用森蚺歼灭至少2名提亚卡乌勇士</t>
         </is>
       </c>
       <c r="F153" s="19" t="n"/>
@@ -15259,27 +15260,27 @@
     <row r="154" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>森蚺</t>
+          <t>芳汀</t>
         </is>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>maa://20946 (100.0), maa://20833 (100.0)</t>
+          <t>maa://37694 (100.0)</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战森蚺累计造成60000点伤害&gt; 3星通关别传RI-EX-4；必须编入非助战森蚺并上场，且使用森蚺歼灭至少1个提亚卡乌冠军</t>
+          <t>&gt; 完成5次战斗；必须编入非助战芳汀并上场，且每次战斗至少释放1次致命恶作剧&gt; 3星通关主题曲2-8；必须编入非助战芳汀并上场，且不编入其他狙击干员</t>
         </is>
       </c>
       <c r="F154" s="19" t="n"/>
@@ -15313,12 +15314,12 @@
     <row r="155" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>森蚺</t>
+          <t>薄绿</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
@@ -15328,12 +15329,12 @@
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>maa://20945 (88.46)</t>
+          <t>*maa://39149 (66.67)</t>
         </is>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战森蚺累计歼灭10个精英或领袖敌人&gt; 3星通关别传RI-7；必须编入非助战森蚺并上场，且使用森蚺歼灭至少2名提亚卡乌勇士</t>
+          <t>&gt; 完成5次战斗；必须编入非助战薄绿，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关别传BI-2；必须编入非助战薄绿，且本次战斗有至少4名冰原战士坠落地穴</t>
         </is>
       </c>
       <c r="F155" s="19" t="n"/>
@@ -15367,12 +15368,12 @@
     <row r="156" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>芳汀</t>
+          <t>四月</t>
         </is>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
@@ -15382,12 +15383,12 @@
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>maa://37694 (100.0)</t>
+          <t>maa://20959 (90.0)</t>
         </is>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战芳汀并上场，且每次战斗至少释放1次致命恶作剧&gt; 3星通关主题曲2-8；必须编入非助战芳汀并上场，且不编入其他狙击干员</t>
+          <t>&gt; 战斗中累计部署非助战四月8次&gt; 3星通关主题曲5-3；必须编入非助战四月并上场，且使用四月歼灭至少2个特战术师组长</t>
         </is>
       </c>
       <c r="F156" s="19" t="n"/>
@@ -15421,27 +15422,27 @@
     <row r="157" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>薄绿</t>
+          <t>史尔特尔</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>*maa://39149 (66.67)</t>
+          <t>maa://44232 (98.62), maa://45603 (90.62)</t>
         </is>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战薄绿，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关别传BI-2；必须编入非助战薄绿，且本次战斗有至少4名冰原战士坠落地穴</t>
+          <t>&gt; 完成5次战斗；必须编入非助战史尔特尔并上场，且每次战斗至少释放1次黄昏&gt; 3星通关主题曲3-8；必须编入非助战史尔特尔并上场，且使用史尔特尔歼灭碎骨</t>
         </is>
       </c>
       <c r="F157" s="19" t="n"/>
@@ -15475,12 +15476,12 @@
     <row r="158" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>四月</t>
+          <t>泡泡</t>
         </is>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
@@ -15490,12 +15491,12 @@
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>maa://20959 (90.0)</t>
+          <t>maa://20936 (92.86)</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战四月8次&gt; 3星通关主题曲5-3；必须编入非助战四月并上场，且使用四月歼灭至少2个特战术师组长</t>
+          <t>&gt; 完成5次战斗；必须编入非助战泡泡并上场，且每次战斗至少释放1次挨打&gt; 3星通关主题曲4-6；必须编入非助战泡泡并上场，且使用泡泡灭8个敌人</t>
         </is>
       </c>
       <c r="F158" s="19" t="n"/>
@@ -15529,27 +15530,27 @@
     <row r="159" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>史尔特尔</t>
+          <t>鞭刃</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>maa://44232 (98.61), maa://45603 (90.62)</t>
+          <t>maa://20855 (93.75)</t>
         </is>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战史尔特尔并上场，且每次战斗至少释放1次黄昏&gt; 3星通关主题曲3-8；必须编入非助战史尔特尔并上场，且使用史尔特尔歼灭碎骨</t>
+          <t>&gt; 由非助战鞭刃累计造成50歼灭数&gt; 3星通关主题曲S3-6；必须编入非助战鞭刃并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
       <c r="F159" s="19" t="n"/>
@@ -15583,12 +15584,12 @@
     <row r="160" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>泡泡</t>
+          <t>奥斯塔</t>
         </is>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
@@ -15598,12 +15599,12 @@
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>maa://20936 (92.86)</t>
+          <t>maa://40158 (100.0)</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战泡泡并上场，且每次战斗至少释放1次挨打&gt; 3星通关主题曲4-6；必须编入非助战泡泡并上场，且使用泡泡灭8个敌人</t>
+          <t>&gt; 战斗中非助战奥斯塔累计使用影钉8次&gt; 3星通关主题曲6-8；必须编入非助战奥斯塔并上场，且使用奥斯塔至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F160" s="19" t="n"/>
@@ -15637,27 +15638,27 @@
     <row r="161" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>鞭刃</t>
+          <t>瑕光</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>MN-4</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>maa://20855 (93.75)</t>
+          <t>*maa://32845 (77.78), maa://29054 (100.0)</t>
         </is>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战鞭刃累计造成50歼灭数&gt; 3星通关主题曲S3-6；必须编入非助战鞭刃并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 由非助战瑕光累计造成80000点伤害&gt; 3星通关别传MN-4；必须编入非助战瑕光并上场，且使用瑕光歼灭至少2名持盾独立骑士</t>
         </is>
       </c>
       <c r="F161" s="19" t="n"/>
@@ -15691,12 +15692,12 @@
     <row r="162" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>奥斯塔</t>
+          <t>瑕光</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
@@ -15706,12 +15707,12 @@
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>maa://40158 (100.0)</t>
+          <t>maa://20973 (100.0)</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战奥斯塔累计使用影钉8次&gt; 3星通关主题曲6-8；必须编入非助战奥斯塔并上场，且使用奥斯塔至少歼灭10个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战瑕光并上场，且每次战斗至少释放1次先贤化身&gt; 3星通关别传MN-2；必须编入非助战瑕光并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
       <c r="F162" s="19" t="n"/>
@@ -15745,27 +15746,27 @@
     <row r="163" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>瑕光</t>
+          <t>杰克</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>MN-4</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>*maa://32845 (77.78), maa://29054 (100.0)</t>
+          <t>maa://39150 (100.0)</t>
         </is>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战瑕光累计造成80000点伤害&gt; 3星通关别传MN-4；必须编入非助战瑕光并上场，且使用瑕光歼灭至少2名持盾独立骑士</t>
+          <t>&gt; 战斗中非助战杰克累计使用全神贯注！8次&gt; 3星通关别传CB-4；必须编入非助战杰克并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
       <c r="F163" s="19" t="n"/>
@@ -15799,27 +15800,27 @@
     <row r="164" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>瑕光</t>
+          <t>絮雨</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>maa://20973 (100.0)</t>
+          <t>maa://20975 (90.91), *maa://47950 (80.0), maa://30806 (100.0)</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战瑕光并上场，且每次战斗至少释放1次先贤化身&gt; 3星通关别传MN-2；必须编入非助战瑕光并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战絮雨并上场，且每次战斗至少释放1次痛觉抑制&gt; 3星通关主题曲2-5；且仅可编入非助战絮雨1名医疗干员并上场</t>
         </is>
       </c>
       <c r="F164" s="19" t="n"/>
@@ -15853,12 +15854,12 @@
     <row r="165" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>杰克</t>
+          <t>迷迭香</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -15868,12 +15869,12 @@
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>maa://39150 (100.0)</t>
+          <t>maa://29059 (100.0)</t>
         </is>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战杰克累计使用全神贯注！8次&gt; 3星通关别传CB-4；必须编入非助战杰克并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 由非助战迷迭香累计造成120000点伤害&gt; 3星通关主题曲4-1；必须编入非助战迷迭香并上场，且使用迷迭香歼灭至少10个敌人</t>
         </is>
       </c>
       <c r="F165" s="19" t="n"/>
@@ -15907,27 +15908,27 @@
     <row r="166" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>絮雨</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>maa://20975 (90.91), *maa://47950 (80.0), maa://30806 (100.0)</t>
+          <t>maa://45556 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战絮雨并上场，且每次战斗至少释放1次痛觉抑制&gt; 3星通关主题曲2-5；且仅可编入非助战絮雨1名医疗干员并上场</t>
+          <t>&gt; 完成5次战斗；必须编入非助战近卫职业的阿米娅并上场，且每次战斗至少释放1次影霄·绝影&gt; 3星通关主题曲2-10；必须编入非助战近卫职业的阿米娅并上场，且使用阿米娅歼灭碎骨</t>
         </is>
       </c>
       <c r="F166" s="19" t="n"/>
@@ -15961,27 +15962,27 @@
     <row r="167" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>泥岩</t>
+          <t>松果</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>maa://29633 (92.31), maa://29627 (92.73), maa://29659 (86.11), maa://49074 (95.92), **maa://30679 (50.0), maa://29861 (100.0), maa://42343 (100.0)</t>
+          <t>maa://40159 (100.0)</t>
         </is>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战泥岩累计使用岩崩锤40次&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战泥岩并上场，且不编入其他重装干员</t>
+          <t>&gt; 战斗中非助战松果累计使用电能过载8次&gt; 3星通关主题曲3-6；必须编入非助战松果并上场，且至少使用3次电能过载</t>
         </is>
       </c>
       <c r="F167" s="19" t="n"/>
@@ -16015,27 +16016,27 @@
     <row r="168" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>泥岩</t>
+          <t>罗宾</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>10-16</t>
+          <t>BI-EX-2</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>maa://49867 (91.89), maa://49655 (96.3)</t>
+          <t>maa://39152 (100.0)</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战泥岩累计造成40歼灭数&gt; 3星通关主题曲10-16标准实战环境；必须编入非助战泥岩并上场，其他成员不可编入重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战罗宾，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关别传BI-EX-2；必须编入非助战罗宾，且本次战斗有至少6名冰原御法者坠落地穴</t>
         </is>
       </c>
       <c r="F168" s="19" t="n"/>
@@ -16069,27 +16070,27 @@
     <row r="169" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>迷迭香</t>
+          <t>卡夫卡</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>maa://29059 (100.0)</t>
+          <t>*maa://20905 (80.0), *maa://52268 (66.67)</t>
         </is>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战迷迭香累计造成120000点伤害&gt; 3星通关主题曲4-1；必须编入非助战迷迭香并上场，且使用迷迭香歼灭至少10个敌人</t>
+          <t>&gt; 由非助战卡夫卡使用技能累计歼灭50名敌人&gt; 3星通关主题曲2-7；必须编入非助战卡夫卡并上场，且使用卡夫卡技能至少歼灭10名敌人</t>
         </is>
       </c>
       <c r="F169" s="19" t="n"/>
@@ -16123,12 +16124,12 @@
     <row r="170" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>LE-5</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
@@ -16138,12 +16139,12 @@
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>maa://45556 (100.0)</t>
+          <t>maa://59681 (100.0)</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战近卫职业的阿米娅并上场，且每次战斗至少释放1次影霄·绝影&gt; 3星通关主题曲2-10；必须编入非助战近卫职业的阿米娅并上场，且使用阿米娅歼灭碎骨</t>
+          <t>&gt; 完成5次战斗，必须编入非助战山，且每次战斗使用山造成至少12000点伤害&gt; 3星通关插曲LE-5，必须编入非助战山并上场，且使用山歼灭至少10名敌人</t>
         </is>
       </c>
       <c r="F170" s="19" t="n"/>
@@ -16177,27 +16178,27 @@
     <row r="171" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>松果</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>MB-EX-3</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>maa://40159 (100.0)</t>
+          <t>maa://32418 (99.69), maa://51440 (100.0)</t>
         </is>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战松果累计使用电能过载8次&gt; 3星通关主题曲3-6；必须编入非助战松果并上场，且至少使用3次电能过载</t>
+          <t>&gt; 由非助战山累计造成40歼灭数&gt; 3星通关别传MB-EX-3；必须编入非助战山并上场，且不编入其他近卫干员</t>
         </is>
       </c>
       <c r="F171" s="19" t="n"/>
@@ -16231,12 +16232,12 @@
     <row r="172" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>罗宾</t>
+          <t>豆苗</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>BI-EX-2</t>
+          <t>S3-7</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
@@ -16246,12 +16247,12 @@
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>maa://39152 (100.0)</t>
+          <t>maa://37690 (90.91)</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战罗宾，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关别传BI-EX-2；必须编入非助战罗宾，且本次战斗有至少6名冰原御法者坠落地穴</t>
+          <t>&gt; 完成5次战斗；必须编入非助战豆苗，并确定第一位部署的干员是豆苗&gt; 3星通关主题曲S3-7；必须编入非助战豆苗并上场，且至少使用1次“大家一起上”</t>
         </is>
       </c>
       <c r="F172" s="19" t="n"/>
@@ -16285,27 +16286,27 @@
     <row r="173" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>卡夫卡</t>
+          <t>爱丽丝</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>*maa://20905 (80.0), *maa://52268 (66.67)</t>
+          <t>maa://20842 (94.12)</t>
         </is>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战卡夫卡使用技能累计歼灭50名敌人&gt; 3星通关主题曲2-7；必须编入非助战卡夫卡并上场，且使用卡夫卡技能至少歼灭10名敌人</t>
+          <t>&gt; 由非助战爱丽丝累计造成30歼灭数&gt; 3星通关主题曲2-2；必须编入非助战爱丽丝并上场，且使用爱丽丝歼灭至少2个重装防御者</t>
         </is>
       </c>
       <c r="F173" s="19" t="n"/>
@@ -16339,12 +16340,12 @@
     <row r="174" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>山</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>LE-5</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
@@ -16354,12 +16355,12 @@
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>maa://59681 (100.0)</t>
+          <t>maa://20912 (100.0)</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗，必须编入非助战山，且每次战斗使用山造成至少12000点伤害&gt; 3星通关插曲LE-5，必须编入非助战山并上场，且使用山歼灭至少10名敌人</t>
+          <t>&gt; 由非助战空弦累计造成100000点伤害&gt; 3星通关插曲SV-4；必须编入非助战空弦并上场，其他成员不可编入狙击干员</t>
         </is>
       </c>
       <c r="F174" s="19" t="n"/>
@@ -16393,12 +16394,12 @@
     <row r="175" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>山</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>MB-EX-3</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
@@ -16408,12 +16409,12 @@
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>maa://32418 (99.69), maa://51440 (100.0)</t>
+          <t>maa://20911 (95.65), maa://29012 (85.71)</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战山累计造成40歼灭数&gt; 3星通关别传MB-EX-3；必须编入非助战山并上场，且不编入其他近卫干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战空弦并上场，且使用空弦歼灭至少5名敌人&gt; 3星通关主题曲2-9；必须编入非助战空弦并上场，且不编入其他狙击干员</t>
         </is>
       </c>
       <c r="F175" s="19" t="n"/>
@@ -16447,12 +16448,12 @@
     <row r="176" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>豆苗</t>
+          <t>图耶</t>
         </is>
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>S3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
@@ -16462,12 +16463,12 @@
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>maa://37690 (90.0)</t>
+          <t>maa://20964 (100.0)</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战豆苗，并确定第一位部署的干员是豆苗&gt; 3星通关主题曲S3-7；必须编入非助战豆苗并上场，且至少使用1次“大家一起上”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战图耶并上场，且每次战斗至少释放1次强心剂&gt; 3星通关主题曲4-6；必须编入非助战图耶并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
       <c r="F176" s="19" t="n"/>
@@ -16501,12 +16502,12 @@
     <row r="177" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>爱丽丝</t>
+          <t>炎狱炎熔</t>
         </is>
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>WR-4</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
@@ -16516,12 +16517,12 @@
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>maa://20842 (94.12)</t>
+          <t>maa://20983 (100.0)</t>
         </is>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战爱丽丝累计造成30歼灭数&gt; 3星通关主题曲2-2；必须编入非助战爱丽丝并上场，且使用爱丽丝歼灭至少2个重装防御者</t>
+          <t>&gt; 由非助战炎狱炎熔累计造成80歼灭数&gt; 3星通关别传WR-4； 必须编入非助战炎狱炎熔并上场，且使用炎狱炎熔歼灭至少8名敌人、其中包括至少1名“偷闲”</t>
         </is>
       </c>
       <c r="F177" s="19" t="n"/>
@@ -16555,27 +16556,27 @@
     <row r="178" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>乌有</t>
         </is>
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>maa://20912 (100.0)</t>
+          <t>maa://31560 (91.67), *maa://20968 (66.67)</t>
         </is>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战空弦累计造成100000点伤害&gt; 3星通关插曲SV-4；必须编入非助战空弦并上场，其他成员不可编入狙击干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战乌有并部署至少2次，且使用乌有歼灭至少4名敌人&gt; 3星通关主题曲3-7；必须编入非助战乌有并上场，且使用乌有歼灭至少2个炮手</t>
         </is>
       </c>
       <c r="F178" s="19" t="n"/>
@@ -16609,27 +16610,27 @@
     <row r="179" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>WR-3</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>maa://20911 (95.65), maa://29012 (85.71)</t>
+          <t>maa://28104 (100.0)</t>
         </is>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战空弦并上场，且使用空弦歼灭至少5名敌人&gt; 3星通关主题曲2-9；必须编入非助战空弦并上场，且不编入其他狙击干员</t>
+          <t>&gt; 由非助战嵯峨累计造成80000点伤害&gt; 3星通关别传WR-3；必须编入非助战嵯峨，且第一位部署嵯峨、嵯峨全程不撤退或被击倒</t>
         </is>
       </c>
       <c r="F179" s="19" t="n"/>
@@ -16663,12 +16664,12 @@
     <row r="180" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>图耶</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>WR-1</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
@@ -16678,12 +16679,12 @@
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>maa://20964 (100.0)</t>
+          <t>maa://20861 (100.0)</t>
         </is>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战图耶并上场，且每次战斗至少释放1次强心剂&gt; 3星通关主题曲4-6；必须编入非助战图耶并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战嵯峨，并确定第一位部署的干员是嵯峨&gt; 3星通关别传WR-1；必须编入非助战嵯峨并上场，其他成员仅可编入2名干员</t>
         </is>
       </c>
       <c r="F180" s="19" t="n"/>
@@ -16717,12 +16718,12 @@
     <row r="181" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>炎狱炎熔</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>WR-4</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
@@ -16732,12 +16733,12 @@
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>maa://20983 (100.0)</t>
+          <t>maa://20970 (100.0)</t>
         </is>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战炎狱炎熔累计造成80歼灭数&gt; 3星通关别传WR-4； 必须编入非助战炎狱炎熔并上场，且使用炎狱炎熔歼灭至少8名敌人、其中包括至少1名“偷闲”</t>
+          <t>&gt; 战斗中累计召唤非助战夕的召唤物20回&gt; 使用至多2人（包含助战）的队伍3星通关主题曲1-6；必须编入非助战夕并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
       <c r="F181" s="19" t="n"/>
@@ -16771,12 +16772,12 @@
     <row r="182" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>乌有</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
@@ -16786,12 +16787,12 @@
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>maa://31560 (91.67), *maa://20968 (66.67)</t>
+          <t>maa://20969 (86.21), maa://41303 (100.0)</t>
         </is>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战乌有并部署至少2次，且使用乌有歼灭至少4名敌人&gt; 3星通关主题曲3-7；必须编入非助战乌有并上场，且使用乌有歼灭至少2个炮手</t>
+          <t>&gt; 由非助战夕累计造成80歼灭数&gt; 3星通关主题曲4-3；必须编入非助战夕并上场，其他成员仅可编入先锋干员</t>
         </is>
       </c>
       <c r="F182" s="19" t="n"/>
@@ -16825,12 +16826,12 @@
     <row r="183" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>战车</t>
         </is>
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>WR-3</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
@@ -16840,12 +16841,12 @@
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>maa://28104 (100.0)</t>
+          <t>maa://20999 (100.0)</t>
         </is>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战嵯峨累计造成80000点伤害&gt; 3星通关别传WR-3；必须编入非助战嵯峨，且第一位部署嵯峨、嵯峨全程不撤退或被击倒</t>
+          <t>&gt; 由非助战战车累计造成150000点伤害&gt; 使用至多2人（包含助战）的队伍3星通关主题曲S2-3；必须编入非助战战车并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
       <c r="F183" s="19" t="n"/>
@@ -16879,12 +16880,12 @@
     <row r="184" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>闪击</t>
         </is>
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>WR-1</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
@@ -16894,12 +16895,12 @@
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>maa://20861 (100.0)</t>
+          <t>maa://35198 (100.0)</t>
         </is>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战嵯峨，并确定第一位部署的干员是嵯峨&gt; 3星通关别传WR-1；必须编入非助战嵯峨并上场，其他成员仅可编入2名干员</t>
+          <t>&gt; 由非助战闪击累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战闪击并上场，且使用闪击歼灭至少2名屠夫</t>
         </is>
       </c>
       <c r="F184" s="19" t="n"/>
@@ -16933,12 +16934,12 @@
     <row r="185" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>霜华</t>
         </is>
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
@@ -16948,12 +16949,12 @@
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>maa://20970 (100.0)</t>
+          <t>maa://39153 (100.0)</t>
         </is>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计召唤非助战夕的召唤物20回&gt; 使用至多2人（包含助战）的队伍3星通关主题曲1-6；必须编入非助战夕并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 由非助战霜华累计造成100000点伤害※迎宾踏垫造成的伤害可计数&gt; 3星通关主题曲4-4；必须编入非助战霜华并上场，且使用霜华歼灭弑君者※允许使用迎宾踏垫歼灭弑君者</t>
         </is>
       </c>
       <c r="F185" s="19" t="n"/>
@@ -16987,12 +16988,12 @@
     <row r="186" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>SV-8</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
@@ -17002,12 +17003,12 @@
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>maa://20969 (86.21), maa://41303 (100.0)</t>
+          <t>maa://34866 (93.48), maa://34714 (96.55)</t>
         </is>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战夕累计造成80歼灭数&gt; 3星通关主题曲4-3；必须编入非助战夕并上场，其他成员仅可编入先锋干员</t>
+          <t>&gt; 由非助战灰烬累计造成100000点伤害&gt; 3星通关插曲SV-8；必须编入非助战灰烬并上场，且使用灰烬歼灭至少2名囊海爬行者</t>
         </is>
       </c>
       <c r="F186" s="19" t="n"/>
@@ -17041,27 +17042,27 @@
     <row r="187" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>战车</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>maa://20999 (100.0)</t>
+          <t>maa://34883 (93.75), maa://20895 (100.0)</t>
         </is>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战战车累计造成150000点伤害&gt; 使用至多2人（包含助战）的队伍3星通关主题曲S2-3；必须编入非助战战车并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 由非助战灰烬累计歼灭10个精英敌人&gt; 3星通关主题曲1-12；必须编入非助战灰烬并上场，且使用灰烬歼灭W</t>
         </is>
       </c>
       <c r="F187" s="19" t="n"/>
@@ -17095,12 +17096,12 @@
     <row r="188" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>闪击</t>
+          <t>暴雨</t>
         </is>
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
@@ -17110,12 +17111,12 @@
       </c>
       <c r="D188" s="13" t="inlineStr">
         <is>
-          <t>maa://35198 (100.0)</t>
+          <t>maa://20853 (100.0)</t>
         </is>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战闪击累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战闪击并上场，且使用闪击歼灭至少2名屠夫</t>
+          <t>&gt; 战斗中非助战暴雨累计使用应急迷彩30次&gt; 3星通关主题曲2-7；必须编入非助战暴雨并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F188" s="19" t="n"/>
@@ -17149,12 +17150,12 @@
     <row r="189" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>霜华</t>
+          <t>熔泉</t>
         </is>
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
@@ -17164,12 +17165,12 @@
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
-          <t>maa://39153 (100.0)</t>
+          <t>maa://20942 (100.0)</t>
         </is>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战霜华累计造成100000点伤害※迎宾踏垫造成的伤害可计数&gt; 3星通关主题曲4-4；必须编入非助战霜华并上场，且使用霜华歼灭弑君者※允许使用迎宾踏垫歼灭弑君者</t>
+          <t>&gt; 由非助战熔泉累计歼灭20个萨卡兹敌人&gt; 3星通关主题曲4-6；必须编入非助战熔泉并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
       <c r="F189" s="19" t="n"/>
@@ -17203,27 +17204,27 @@
     <row r="190" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>SV-8</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>maa://34866 (93.48), maa://34714 (96.55)</t>
+          <t>maa://20992 (100.0)</t>
         </is>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战灰烬累计造成100000点伤害&gt; 3星通关插曲SV-8；必须编入非助战灰烬并上场，且使用灰烬歼灭至少2名囊海爬行者</t>
+          <t>&gt; 战斗中非助战异客累计使用辉煌裂片30次&gt; 3星通关主题曲2-2；必须编入非助战异客并上场，其他成员仅可编入先锋和重装干员</t>
         </is>
       </c>
       <c r="F190" s="19" t="n"/>
@@ -17257,12 +17258,12 @@
     <row r="191" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
@@ -17272,12 +17273,12 @@
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>maa://34883 (93.75), maa://20895 (100.0)</t>
+          <t>*maa://28190 (62.86), maa://20994 (100.0)</t>
         </is>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战灰烬累计歼灭10个精英敌人&gt; 3星通关主题曲1-12；必须编入非助战灰烬并上场，且使用灰烬歼灭W</t>
+          <t>&gt; 完成5次战斗；必须编入非助战异客并上场，且使用异客造成至少30000点伤害&gt; 3星通关主题曲5-10；必须编入非助战异客并上场，且使用异客歼灭至少2个粉碎攻坚手</t>
         </is>
       </c>
       <c r="F191" s="19" t="n"/>
@@ -17311,12 +17312,12 @@
     <row r="192" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>暴雨</t>
+          <t>赤冬</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
@@ -17326,12 +17327,12 @@
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
-          <t>maa://20853 (100.0)</t>
+          <t>maa://20860 (100.0)</t>
         </is>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战暴雨累计使用应急迷彩30次&gt; 3星通关主题曲2-7；必须编入非助战暴雨并上场，且所有干员不被击倒</t>
+          <t>&gt; 战斗中非助战赤冬累计使用信影流·十文字胜5次&gt; 3星通关主题曲3-8；必须编入非助战赤冬并上场，且使用赤冬歼灭碎骨</t>
         </is>
       </c>
       <c r="F192" s="19" t="n"/>
@@ -17365,27 +17366,27 @@
     <row r="193" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>熔泉</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>SV-EX-5</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>maa://20942 (100.0)</t>
+          <t>maa://44224 (90.28), maa://35854 (86.27), maa://50388 (98.05), maa://25760 (86.96), ***maa://43911 (12.5), *maa://20872 (52.0), maa://51066 (100.0), maa://63024 (100.0)</t>
         </is>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战熔泉累计歼灭20个萨卡兹敌人&gt; 3星通关主题曲4-6；必须编入非助战熔泉并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅并上场，且每次战斗至少释放1次缺水的碎漩狂舞&gt; 3星通关插曲SV-EX-5；必须编入非助战歌蕾蒂娅，且至少使1个富营养的收割者坠落地穴</t>
         </is>
       </c>
       <c r="F193" s="19" t="n"/>
@@ -17419,27 +17420,27 @@
     <row r="194" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>SN-EX-3</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>maa://20992 (100.0)</t>
+          <t>maa://39156 (93.98), *maa://39550 (57.89), *maa://53417 (71.43)</t>
         </is>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战异客累计使用辉煌裂片30次&gt; 3星通关主题曲2-2；必须编入非助战异客并上场，其他成员仅可编入先锋和重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关插曲SN-EX-3；必须编入非助战歌蕾蒂娅并上场，且使用至少2次缺水的掌握怒海或缺水的碎漩狂舞</t>
         </is>
       </c>
       <c r="F194" s="19" t="n"/>
@@ -17473,27 +17474,27 @@
     <row r="195" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>浊心斯卡蒂</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>*maa://28190 (62.86), maa://20994 (100.0)</t>
+          <t>maa://42223 (99.6), maa://49077 (93.02), maa://42292 (97.22), maa://42402 (100.0)</t>
         </is>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战异客并上场，且使用异客造成至少30000点伤害&gt; 3星通关主题曲5-10；必须编入非助战异客并上场，且使用异客歼灭至少2个粉碎攻坚手</t>
+          <t>&gt; 携带非助战浊心斯卡蒂完成5次战斗，且每次战斗至少发动一次“同葬无光之愿”&gt; 3星通关插曲SV-5；必须编入非助战浊心斯卡蒂并上场，且队伍中不能有医疗干员</t>
         </is>
       </c>
       <c r="F195" s="19" t="n"/>
@@ -17527,12 +17528,12 @@
     <row r="196" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>赤冬</t>
+          <t>深靛</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
@@ -17542,12 +17543,12 @@
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>maa://20860 (100.0)</t>
+          <t>maa://39154 (100.0)</t>
         </is>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战赤冬累计使用信影流·十文字胜5次&gt; 3星通关主题曲3-8；必须编入非助战赤冬并上场，且使用赤冬歼灭碎骨</t>
+          <t>&gt; 由非助战深靛累计造成60000点伤害&gt; 3星通关插曲SV-5；必须编入非助战深靛并上场，且使用2次光影迷宫</t>
         </is>
       </c>
       <c r="F196" s="19" t="n"/>
@@ -17581,27 +17582,27 @@
     <row r="197" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>贝娜</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>SV-EX-5</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>maa://44224 (90.26), maa://35854 (86.14), maa://50388 (98.03), maa://25760 (86.96), ***maa://43911 (12.5), *maa://20872 (52.0), maa://51066 (100.0)</t>
+          <t>maa://20854 (92.86)</t>
         </is>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅并上场，且每次战斗至少释放1次缺水的碎漩狂舞&gt; 3星通关插曲SV-EX-5；必须编入非助战歌蕾蒂娅，且至少使1个富营养的收割者坠落地穴</t>
+          <t>&gt; 完成5次战斗；必须编入非助战贝娜并上场，且每次战斗至少释放1次快速修剪&gt; 3星通关主题曲2-3；必须编入非助战贝娜并上场，且使用贝娜歼灭至少1个重装防御者</t>
         </is>
       </c>
       <c r="F197" s="19" t="n"/>
@@ -17635,27 +17636,27 @@
     <row r="198" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>绮良</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>SN-EX-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>maa://39156 (93.98), *maa://39550 (57.89), *maa://53417 (71.43)</t>
+          <t>maa://20937 (100.0)</t>
         </is>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关插曲SN-EX-3；必须编入非助战歌蕾蒂娅并上场，且使用至少2次缺水的掌握怒海或缺水的碎漩狂舞</t>
+          <t>&gt; 战斗中非助战绮良累计使用锚点捕捉5次&gt; 3星通关主题曲3-1；必须编入非助战绮良并上场，且使用绮良歼灭20个敌人</t>
         </is>
       </c>
       <c r="F198" s="19" t="n"/>
@@ -17689,27 +17690,27 @@
     <row r="199" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>maa://27823 (84.52), *maa://28190 (62.86), maa://22894 (91.43), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>maa://22468 (100.0)</t>
         </is>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战凯尔希累计造成150000点伤害※Mon3tr造成的伤害会计数&gt; 3星通关主题曲5-10；必须编入非助战凯尔希并上场，且使用4次指令：熔毁</t>
+          <t>&gt; 由非助战卡涅利安累计造成120000点伤害&gt; 3星通关主题曲7-3；必须编入非助战卡涅利安并上场，且不编入重装干员</t>
         </is>
       </c>
       <c r="F199" s="19" t="n"/>
@@ -17743,27 +17744,27 @@
     <row r="200" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>maa://27823 (84.52), *maa://28190 (62.86), maa://22894 (91.43), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>maa://30673 (100.0), maa://30672 (100.0)</t>
         </is>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战凯尔希累计使用指令：熔毁10次&gt; 3星通关主题曲5-10；必须编入非助战凯尔希并上场，且使用Mon3tr歼灭梅菲斯特</t>
+          <t>&gt; 由非助战卡涅利安累计造成80歼灭数&gt; 3星通关主题曲4-6；必须编入非助战卡涅利安并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
       <c r="F200" s="19" t="n"/>
@@ -17797,27 +17798,27 @@
     <row r="201" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>浊心斯卡蒂</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>maa://42223 (99.6), maa://49077 (92.86), maa://42292 (97.22), maa://42402 (100.0)</t>
+          <t>maa://20934 (100.0), maa://20827 (100.0), maa://20828 (100.0)</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>&gt; 携带非助战浊心斯卡蒂完成5次战斗，且每次战斗至少发动一次“同葬无光之愿”&gt; 3星通关插曲SV-5；必须编入非助战浊心斯卡蒂并上场，且队伍中不能有医疗干员</t>
+          <t>&gt; 由非助战帕拉斯累计造成50歼灭数&gt; 使用至多2人（包含助战）的队伍3星通关主题曲3-6；必须编入非助战帕拉斯并上场，其他成员仅可编入医疗干员</t>
         </is>
       </c>
       <c r="F201" s="19" t="n"/>
@@ -17851,12 +17852,12 @@
     <row r="202" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>深靛</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
@@ -17866,12 +17867,12 @@
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>maa://39154 (100.0)</t>
+          <t>maa://20935 (100.0)</t>
         </is>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战深靛累计造成60000点伤害&gt; 3星通关插曲SV-5；必须编入非助战深靛并上场，且使用2次光影迷宫</t>
+          <t>&gt; 战斗中非助战帕拉斯累计使用英勇的祝福5次&gt; 3星通关主题曲4-3；必须编入非助战帕拉斯并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
       <c r="F202" s="19" t="n"/>
@@ -17905,12 +17906,12 @@
     <row r="203" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t>贝娜</t>
+          <t>龙舌兰</t>
         </is>
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
@@ -17920,12 +17921,12 @@
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>maa://20854 (92.86)</t>
+          <t>maa://53354 (100.0)</t>
         </is>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战贝娜并上场，且每次战斗至少释放1次快速修剪&gt; 3星通关主题曲2-3；必须编入非助战贝娜并上场，且使用贝娜歼灭至少1个重装防御者</t>
+          <t>&gt; 由非助战龙舌兰累计造成30歼灭数&gt; 3星通关主题曲7-11；必须编入非助战龙舌兰并上场，且使用2次剑走偏锋</t>
         </is>
       </c>
       <c r="F203" s="19" t="n"/>
@@ -17959,27 +17960,27 @@
     <row r="204" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>绮良</t>
+          <t>羽毛笔</t>
         </is>
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>maa://20937 (100.0)</t>
+          <t>maa://28133 (93.1), **maa://39217 (41.18), maa://25369 (94.87)</t>
         </is>
       </c>
       <c r="E204" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战绮良累计使用锚点捕捉5次&gt; 3星通关主题曲3-1；必须编入非助战绮良并上场，且使用绮良歼灭20个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战羽毛笔并上场，且使用羽毛笔造成至少12000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战羽毛笔并上场，且使用羽毛笔至少歼灭15个敌人</t>
         </is>
       </c>
       <c r="F204" s="19" t="n"/>
@@ -18013,27 +18014,27 @@
     <row r="205" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>maa://22468 (100.0)</t>
+          <t>maa://20956 (96.0), *maa://20830 (80.0), maa://44703 (91.67)</t>
         </is>
       </c>
       <c r="E205" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战卡涅利安累计造成120000点伤害&gt; 3星通关主题曲7-3；必须编入非助战卡涅利安并上场，且不编入重装干员</t>
+          <t>&gt; 由非助战水月累计造成150000点伤害&gt; 3星通关主题曲4-3；必须编入非助战水月并上场，且使用水月歼灭至少2名萨卡兹狙击手</t>
         </is>
       </c>
       <c r="F205" s="19" t="n"/>
@@ -18067,27 +18068,27 @@
     <row r="206" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>maa://30673 (100.0), maa://30672 (100.0)</t>
+          <t>maa://20955 (80.95)</t>
         </is>
       </c>
       <c r="E206" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战卡涅利安累计造成80歼灭数&gt; 3星通关主题曲4-6；必须编入非助战卡涅利安并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 由非助战水月累计造成50歼灭数&gt; 3星通关主题曲4-5；必须编入非助战水月并上场，且使用水月歼灭10个敌人</t>
         </is>
       </c>
       <c r="F206" s="19" t="n"/>
@@ -18121,27 +18122,27 @@
     <row r="207" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>假日威龙陈</t>
         </is>
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
-          <t>maa://20934 (100.0), maa://20827 (100.0), maa://20828 (100.0)</t>
+          <t>maa://39238 (99.52)</t>
         </is>
       </c>
       <c r="E207" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战帕拉斯累计造成50歼灭数&gt; 使用至多2人（包含助战）的队伍3星通关主题曲3-6；必须编入非助战帕拉斯并上场，其他成员仅可编入医疗干员</t>
+          <t>&gt; 由非助战假日威龙陈累计造成120000伤害&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战假日威龙陈并上场，且使用假日威龙陈至少歼灭20个敌人</t>
         </is>
       </c>
       <c r="F207" s="19" t="n"/>
@@ -18175,12 +18176,12 @@
     <row r="208" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>罗比菈塔</t>
         </is>
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
@@ -18190,12 +18191,12 @@
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>maa://20935 (100.0)</t>
+          <t>maa://45261 (88.89)</t>
         </is>
       </c>
       <c r="E208" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战帕拉斯累计使用英勇的祝福5次&gt; 3星通关主题曲4-3；必须编入非助战帕拉斯并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 战斗中非助战罗比菈塔累计部署支援装置25个&gt; 3星通关主题曲3-8；必须编入非助战罗比菈塔并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F208" s="19" t="n"/>
@@ -18229,12 +18230,12 @@
     <row r="209" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t>龙舌兰</t>
+          <t>桑葚</t>
         </is>
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
@@ -18244,12 +18245,12 @@
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>maa://53354 (100.0)</t>
+          <t>maa://39694 (100.0)</t>
         </is>
       </c>
       <c r="E209" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战龙舌兰累计造成30歼灭数&gt; 3星通关主题曲7-11；必须编入非助战龙舌兰并上场，且使用2次剑走偏锋</t>
+          <t>&gt; 完成5次战斗；必须编入非助战桑葚并上场，且每次战斗至少释放1次安全区域&gt; 3星通关插曲SV-5；必须编入非助战桑葚并上场，其他成员仅可编入7名干员</t>
         </is>
       </c>
       <c r="F209" s="19" t="n"/>
@@ -18283,27 +18284,27 @@
     <row r="210" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t>羽毛笔</t>
+          <t>琴柳</t>
         </is>
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>maa://28133 (93.1), **maa://39217 (41.18), maa://25369 (94.74)</t>
+          <t>maa://24636 (100.0), maa://25778 (100.0)</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战羽毛笔并上场，且使用羽毛笔造成至少12000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战羽毛笔并上场，且使用羽毛笔至少歼灭15个敌人</t>
+          <t>&gt; 战斗中非助战琴柳累计使用信仰传承10次&gt; 3星通关主题曲9-2；必须编入非助战琴柳并上场，且不编入其他先锋干员</t>
         </is>
       </c>
       <c r="F210" s="19" t="n"/>
@@ -18337,27 +18338,27 @@
     <row r="211" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A211" s="11" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>琴柳</t>
         </is>
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
-          <t>maa://20956 (95.98), *maa://20830 (80.0), maa://44703 (91.67)</t>
+          <t>maa://48261 (100.0)</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战水月累计造成150000点伤害&gt; 3星通关主题曲4-3；必须编入非助战水月并上场，且使用水月歼灭至少2名萨卡兹狙击手</t>
+          <t>&gt; 完成5次战斗；必须编入非助战琴柳并上场，且每次战斗至少释放1次光辉旗帜&gt; 3星通关主题曲5-3；必须编入非助战琴柳并上场，且至少使用3次光辉旗帜</t>
         </is>
       </c>
       <c r="F211" s="19" t="n"/>
@@ -18391,12 +18392,12 @@
     <row r="212" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>灰毫</t>
         </is>
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
@@ -18406,12 +18407,12 @@
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>maa://20955 (80.49)</t>
+          <t>*maa://39157 (80.0)</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战水月累计造成50歼灭数&gt; 3星通关主题曲4-5；必须编入非助战水月并上场，且使用水月歼灭10个敌人</t>
+          <t>&gt; 由非助战灰毫累计造成100000点伤害&gt; 3星通关主题曲7-9；必须编入非助战灰毫并上场，且使用灰毫歼灭至少2名游击队传令兵</t>
         </is>
       </c>
       <c r="F212" s="19" t="n"/>
@@ -18445,27 +18446,27 @@
     <row r="213" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t>假日威龙陈</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>maa://39238 (99.52)</t>
+          <t>***maa://26496 (30.0), *maa://20995 (54.55)</t>
         </is>
       </c>
       <c r="E213" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战假日威龙陈累计造成120000伤害&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战假日威龙陈并上场，且使用假日威龙陈至少歼灭20个敌人</t>
+          <t>&gt; 由非助战远牙累计造成80歼灭数&gt; 3星通关主题曲S2-2；必须编入非助战远牙并上场，且远牙使用光羽箭至少歼灭8名敌人</t>
         </is>
       </c>
       <c r="F213" s="19" t="n"/>
@@ -18499,27 +18500,27 @@
     <row r="214" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t>罗比菈塔</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>maa://45261 (88.89)</t>
+          <t>maa://26499 (100.0), ***maa://20998 (12.5)</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战罗比菈塔累计部署支援装置25个&gt; 3星通关主题曲3-8；必须编入非助战罗比菈塔并上场，且所有干员不被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战远牙并上场，且每次战斗至少释放2次光羽箭&gt; 3星通关主题曲2-5；必须编入非助战远牙并上场，且使用远牙歼灭至少2名高阶术师</t>
         </is>
       </c>
       <c r="F214" s="19" t="n"/>
@@ -18553,12 +18554,12 @@
     <row r="215" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t>桑葚</t>
+          <t>布丁</t>
         </is>
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
@@ -18568,12 +18569,12 @@
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
-          <t>maa://39694 (100.0)</t>
+          <t>maa://20858 (100.0)</t>
         </is>
       </c>
       <c r="E215" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战桑葚并上场，且每次战斗至少释放1次安全区域&gt; 3星通关插曲SV-5；必须编入非助战桑葚并上场，其他成员仅可编入7名干员</t>
+          <t>&gt; 由非助战布丁累计造成150000点伤害&gt; 3星通关主题曲2-10；必须编入非助战布丁并上场，且布丁使用技能扩散电流至少歼灭2个重装防御者</t>
         </is>
       </c>
       <c r="F215" s="19" t="n"/>
@@ -18607,12 +18608,12 @@
     <row r="216" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>蜜莓</t>
         </is>
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>GA-2</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
@@ -18622,12 +18623,12 @@
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>maa://24636 (100.0), maa://25778 (100.0)</t>
+          <t>maa://39695 (100.0), ***maa://39911 (20.0)</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战琴柳累计使用信仰传承10次&gt; 3星通关主题曲9-2；必须编入非助战琴柳并上场，且不编入其他先锋干员</t>
+          <t>&gt; 战斗中非助战蜜莓累计使用振奋8次&gt; 3星通关别传GA-2；必须编入非助战蜜莓并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F216" s="19" t="n"/>
@@ -18661,12 +18662,12 @@
     <row r="217" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>野鬃</t>
         </is>
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
@@ -18676,12 +18677,12 @@
       </c>
       <c r="D217" s="13" t="inlineStr">
         <is>
-          <t>maa://48261 (100.0)</t>
+          <t>maa://20988 (88.89)</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战琴柳并上场，且每次战斗至少释放1次光辉旗帜&gt; 3星通关主题曲5-3；必须编入非助战琴柳并上场，且至少使用3次光辉旗帜</t>
+          <t>&gt; 完成5次战斗；必须编入非助战野鬃，并确定第一位部署的干员是野鬃&gt; 3星通关别传MN-2；必须编入非助战野鬃并上场，其他成员不可编入先锋干员</t>
         </is>
       </c>
       <c r="F217" s="19" t="n"/>
@@ -18715,12 +18716,12 @@
     <row r="218" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t>灰毫</t>
+          <t>蚀清</t>
         </is>
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
@@ -18730,12 +18731,12 @@
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>*maa://39157 (80.0)</t>
+          <t>maa://39158 (100.0)</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战灰毫累计造成100000点伤害&gt; 3星通关主题曲7-9；必须编入非助战灰毫并上场，且使用灰毫歼灭至少2名游击队传令兵</t>
+          <t>&gt; 由非助战蚀清累计造成100000点伤害&gt; 3星通关别传BI-6；必须编入非助战蚀清并上场，且至少使用2次传导蚀滞弹</t>
         </is>
       </c>
       <c r="F218" s="19" t="n"/>
@@ -18769,27 +18770,27 @@
     <row r="219" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A219" s="11" t="inlineStr">
         <is>
-          <t>远牙</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>NL-5</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D219" s="13" t="inlineStr">
         <is>
-          <t>***maa://26496 (30.0), *maa://20995 (54.55)</t>
+          <t>maa://28187 (97.67), maa://43531 (100.0), maa://39520 (100.0)</t>
         </is>
       </c>
       <c r="E219" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战远牙累计造成80歼灭数&gt; 3星通关主题曲S2-2；必须编入非助战远牙并上场，且远牙使用光羽箭至少歼灭8名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战焰尾并上场，且每次战斗至少释放2次焰心&gt; 3星通关别传NL-5；必须编入非助战焰尾，且第一位部署焰尾、焰尾全程不撤退或被击倒</t>
         </is>
       </c>
       <c r="F219" s="19" t="n"/>
@@ -18823,27 +18824,27 @@
     <row r="220" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A220" s="11" t="inlineStr">
         <is>
-          <t>远牙</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>NL-3</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>maa://26499 (100.0), ***maa://20998 (12.5)</t>
+          <t>maa://20985 (100.0)</t>
         </is>
       </c>
       <c r="E220" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战远牙并上场，且每次战斗至少释放2次光羽箭&gt; 3星通关主题曲2-5；必须编入非助战远牙并上场，且使用远牙歼灭至少2名高阶术师</t>
+          <t>&gt; 由非助战焰尾累计造成40000点伤害&gt; 3星通关别传NL-3；必须编入非助战焰尾并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F220" s="19" t="n"/>
@@ -18877,27 +18878,27 @@
     <row r="221" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>布丁</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>MN-8</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>maa://20858 (100.0)</t>
+          <t>maa://20987 (93.88), *maa://35801 (77.78)</t>
         </is>
       </c>
       <c r="E221" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战布丁累计造成150000点伤害&gt; 3星通关主题曲2-10；必须编入非助战布丁并上场，且布丁使用技能扩散电流至少歼灭2个重装防御者</t>
+          <t>&gt; 由非助战耀骑士临光累计造成100歼灭数&gt; 3星通关别传MN-8；必须编入非助战耀骑士临光并上场，且使用耀骑士临光歼灭至少1个腐败骑士或凋零骑士</t>
         </is>
       </c>
       <c r="F221" s="19" t="n"/>
@@ -18931,27 +18932,27 @@
     <row r="222" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t>蜜莓</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>GA-2</t>
+          <t>NL-10</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>maa://39695 (100.0), ***maa://39911 (20.0)</t>
+          <t>*maa://29644 (74.0), maa://39159 (96.67), ***maa://30061 (27.27)</t>
         </is>
       </c>
       <c r="E222" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战蜜莓累计使用振奋8次&gt; 3星通关别传GA-2；必须编入非助战蜜莓并上场，且不编入其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战耀骑士临光并上场，且每次战斗至少释放1次耀阳颔首&gt; 3星通关别传NL-10；必须编入非助战耀骑士临光并上场，且使用耀骑士临光击败血骑士狄开俄波利斯</t>
         </is>
       </c>
       <c r="F222" s="19" t="n"/>
@@ -18985,12 +18986,12 @@
     <row r="223" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t>野鬃</t>
+          <t>耶拉</t>
         </is>
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
@@ -19000,12 +19001,12 @@
       </c>
       <c r="D223" s="13" t="inlineStr">
         <is>
-          <t>maa://20988 (87.5)</t>
+          <t>maa://30677 (100.0)</t>
         </is>
       </c>
       <c r="E223" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战野鬃，并确定第一位部署的干员是野鬃&gt; 3星通关别传MN-2；必须编入非助战野鬃并上场，其他成员不可编入先锋干员</t>
+          <t>&gt; 由非助战耶拉累计造成80000点伤害&gt; 3星通关别传BI-7；必须编入非助战耶拉并上场，且至少使用2次心随意动</t>
         </is>
       </c>
       <c r="F223" s="19" t="n"/>
@@ -19039,12 +19040,12 @@
     <row r="224" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>蚀清</t>
+          <t>极光</t>
         </is>
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
@@ -19054,12 +19055,12 @@
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>maa://39158 (100.0)</t>
+          <t>maa://20896 (100.0)</t>
         </is>
       </c>
       <c r="E224" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战蚀清累计造成100000点伤害&gt; 3星通关别传BI-6；必须编入非助战蚀清并上场，且至少使用2次传导蚀滞弹</t>
+          <t>&gt; 由非助战极光累计造成40000点伤害&gt; 3星通关主题曲3-8；必须编入非助战极光并上场，且使用极光歼灭碎骨</t>
         </is>
       </c>
       <c r="F224" s="19" t="n"/>
@@ -19093,12 +19094,12 @@
     <row r="225" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>NL-5</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
@@ -19108,12 +19109,12 @@
       </c>
       <c r="D225" s="13" t="inlineStr">
         <is>
-          <t>maa://28187 (97.67), maa://43531 (100.0), maa://39520 (100.0)</t>
+          <t>maa://29058 (96.2), maa://39140 (100.0), maa://38723 (100.0)</t>
         </is>
       </c>
       <c r="E225" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战焰尾并上场，且每次战斗至少释放2次焰心&gt; 3星通关别传NL-5；必须编入非助战焰尾，且第一位部署焰尾、焰尾全程不撤退或被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战灵知并上场，且每次战斗至少释放1次失温症&gt; 3星通关别传BI-7，必须编入非助战灵知并上场，且不编入其他辅助干员</t>
         </is>
       </c>
       <c r="F225" s="19" t="n"/>
@@ -19147,12 +19148,12 @@
     <row r="226" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>NL-3</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
@@ -19162,12 +19163,12 @@
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>maa://20985 (100.0)</t>
+          <t>*maa://48263 (76.92)</t>
         </is>
       </c>
       <c r="E226" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战焰尾累计造成40000点伤害&gt; 3星通关别传NL-3；必须编入非助战焰尾并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战灵知累计使用10次失温症&gt; 3星通关主题曲5-6；必须编入非助战灵知并上场，且使用灵知击败至少5个法术大师A1</t>
         </is>
       </c>
       <c r="F226" s="19" t="n"/>
@@ -19201,27 +19202,27 @@
     <row r="227" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>九色鹿</t>
         </is>
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>MN-8</t>
+          <t>IW-3</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>maa://20987 (93.88), *maa://35801 (77.78)</t>
+          <t>maa://39160 (100.0)</t>
         </is>
       </c>
       <c r="E227" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战耀骑士临光累计造成100歼灭数&gt; 3星通关别传MN-8；必须编入非助战耀骑士临光并上场，且使用耀骑士临光歼灭至少1个腐败骑士或凋零骑士</t>
+          <t>&gt; 战斗中非助战九色鹿累计使用仙山去远8次&gt; 3星通关别传IW-3；必须编入非助战九色鹿并上场，且不编入其他辅助干员</t>
         </is>
       </c>
       <c r="F227" s="19" t="n"/>
@@ -19255,27 +19256,27 @@
     <row r="228" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>寒芒克洛丝</t>
         </is>
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>NL-10</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>*maa://29644 (74.0), maa://39159 (96.67), ***maa://30061 (27.27)</t>
+          <t>maa://49491 (91.67)</t>
         </is>
       </c>
       <c r="E228" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战耀骑士临光并上场，且每次战斗至少释放1次耀阳颔首&gt; 3星通关别传NL-10；必须编入非助战耀骑士临光并上场，且使用耀骑士临光击败血骑士狄开俄波利斯</t>
+          <t>&gt; 战斗中非助战寒芒克洛丝累计使用封喉5次&gt; 3星通关主题曲3-8；必须编入非助战寒芒克洛丝并上场，且使用寒芒克洛丝歼灭碎骨</t>
         </is>
       </c>
       <c r="F228" s="19" t="n"/>
@@ -19309,12 +19310,12 @@
     <row r="229" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A229" s="11" t="inlineStr">
         <is>
-          <t>耶拉</t>
+          <t>夜半</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
@@ -19324,12 +19325,12 @@
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>maa://30677 (100.0)</t>
+          <t>maa://35952 (100.0)</t>
         </is>
       </c>
       <c r="E229" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战耶拉累计造成80000点伤害&gt; 3星通关别传BI-7；必须编入非助战耶拉并上场，且至少使用2次心随意动</t>
+          <t>&gt; 战斗中非助战夜半累计使用安眠10次&gt; 3星通关主题曲3-1；必须编入非助战夜半并上场，且至少使用3次安眠</t>
         </is>
       </c>
       <c r="F229" s="19" t="n"/>
@@ -19363,12 +19364,12 @@
     <row r="230" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>极光</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
@@ -19378,12 +19379,12 @@
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>maa://20896 (100.0)</t>
+          <t>maa://20917 (98.36)</t>
         </is>
       </c>
       <c r="E230" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战极光累计造成40000点伤害&gt; 3星通关主题曲3-8；必须编入非助战极光并上场，且使用极光歼灭碎骨</t>
+          <t>&gt; 由非助战老鲤累计造成80歼灭数&gt; 3星通关主题曲3-1；必须编入非助战老鲤并上场，其他成员仅可编入狙击、先锋与医疗干员</t>
         </is>
       </c>
       <c r="F230" s="19" t="n"/>
@@ -19417,27 +19418,27 @@
     <row r="231" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>IW-EX-1</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D231" s="13" t="inlineStr">
         <is>
-          <t>maa://29058 (96.2), maa://39140 (100.0), maa://38723 (100.0)</t>
+          <t>maa://30714 (97.67), maa://30675 (100.0)</t>
         </is>
       </c>
       <c r="E231" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战灵知并上场，且每次战斗至少释放1次失温症&gt; 3星通关别传BI-7，必须编入非助战灵知并上场，且不编入其他辅助干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战老鲤并上场，且每次战斗至少释放1次贵客盈门&gt; 3星通关别传IW-EX-1；必须编入非助战老鲤并上场，且使用老鲤至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F231" s="19" t="n"/>
@@ -19471,27 +19472,27 @@
     <row r="232" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>令</t>
         </is>
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>*maa://48263 (76.92)</t>
+          <t>maa://20922 (94.2), *maa://32623 (76.19), maa://34242 (85.71)</t>
         </is>
       </c>
       <c r="E232" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战灵知累计使用10次失温症&gt; 3星通关主题曲5-6；必须编入非助战灵知并上场，且使用灵知击败至少5个法术大师A1</t>
+          <t>&gt; 完成5次战斗；必须编入非助战令并上场，且使用令与令的召唤物歼灭至少7名敌人&gt; 3星通关主题曲3-4；必须编入非助战令并上场，且整场战斗仅部署过令与至多4位其他干员</t>
         </is>
       </c>
       <c r="F232" s="19" t="n"/>
@@ -19525,12 +19526,12 @@
     <row r="233" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A233" s="11" t="inlineStr">
         <is>
-          <t>九色鹿</t>
+          <t>夏栎</t>
         </is>
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>IW-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
@@ -19540,12 +19541,12 @@
       </c>
       <c r="D233" s="13" t="inlineStr">
         <is>
-          <t>maa://39160 (100.0)</t>
+          <t>maa://32999 (100.0)</t>
         </is>
       </c>
       <c r="E233" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战九色鹿累计使用仙山去远8次&gt; 3星通关别传IW-3；必须编入非助战九色鹿并上场，且不编入其他辅助干员</t>
+          <t>&gt; 战斗中非助战夏栎累计使用生灵的回响8次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战夏栎并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F233" s="19" t="n"/>
@@ -19579,27 +19580,27 @@
     <row r="234" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>寒芒克洛丝</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>R8-8</t>
         </is>
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>maa://49491 (91.67)</t>
+          <t>*maa://30667 (78.65), maa://30666 (83.55), **maa://30739 (43.24), *maa://30723 (56.45), maa://39588 (89.29)</t>
         </is>
       </c>
       <c r="E234" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战寒芒克洛丝累计使用封喉5次&gt; 3星通关主题曲3-8；必须编入非助战寒芒克洛丝并上场，且使用寒芒克洛丝歼灭碎骨</t>
+          <t>&gt; 由非助战澄闪累计造成100000点伤害&gt; 3星通关主题曲R8-8；必须编入非助战澄闪并上场，且使用澄闪歼灭至少2名帝国炮火先兆者</t>
         </is>
       </c>
       <c r="F234" s="19" t="n"/>
@@ -19633,27 +19634,27 @@
     <row r="235" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>夜半</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>maa://35952 (100.0)</t>
+          <t>maa://62759 (100.0), maa://62764 (100.0)</t>
         </is>
       </c>
       <c r="E235" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战夜半累计使用安眠10次&gt; 3星通关主题曲3-1；必须编入非助战夜半并上场，且至少使用3次安眠</t>
+          <t>&gt; 战斗中非助战澄闪累计使用“澄净闪耀”10次&gt; 3星通关主题曲4-7；必须编入非助战澄闪并上场，其他成员仅可编入5名干员</t>
         </is>
       </c>
       <c r="F235" s="19" t="n"/>
@@ -19687,12 +19688,12 @@
     <row r="236" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>见行者</t>
         </is>
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>GA-EX-1</t>
         </is>
       </c>
       <c r="C236" s="12" t="inlineStr">
@@ -19702,12 +19703,12 @@
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>maa://20917 (98.36)</t>
+          <t>maa://30512 (100.0)</t>
         </is>
       </c>
       <c r="E236" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战老鲤累计造成80歼灭数&gt; 3星通关主题曲3-1；必须编入非助战老鲤并上场，其他成员仅可编入狙击、先锋与医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战见行者并上场，且每次战斗至少释放2次惊爆射击&gt; 3星通关别传GA-EX-1；必须编入非助战见行者，且本场战斗至少使3个寻路者精锐狙击手坠落地穴</t>
         </is>
       </c>
       <c r="F236" s="19" t="n"/>
@@ -19741,27 +19742,27 @@
     <row r="237" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>风丸</t>
         </is>
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>IW-EX-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D237" s="15" t="inlineStr">
         <is>
-          <t>maa://30714 (97.62), maa://30675 (100.0)</t>
+          <t>maa://20870 (100.0)</t>
         </is>
       </c>
       <c r="E237" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战老鲤并上场，且每次战斗至少释放1次贵客盈门&gt; 3星通关别传IW-EX-1；必须编入非助战老鲤并上场，且使用老鲤至少歼灭10个敌人</t>
+          <t>&gt; 由非助战风丸累计使用纸艺·双影10次&gt; 3星通关主题曲3-1；必须编入非助战风丸并上场，且使用风丸歼灭至少30名敌人</t>
         </is>
       </c>
       <c r="F237" s="19" t="n"/>
@@ -19795,27 +19796,27 @@
     <row r="238" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>令</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>GA-4</t>
         </is>
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>maa://20922 (94.2), *maa://32623 (76.19), maa://34242 (85.71)</t>
+          <t>maa://29024 (100.0)</t>
         </is>
       </c>
       <c r="E238" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战令并上场，且使用令与令的召唤物歼灭至少7名敌人&gt; 3星通关主题曲3-4；必须编入非助战令并上场，且整场战斗仅部署过令与至多4位其他干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔歼灭至少10个敌人&gt; 3星通关别传GA-4；必须编入非助战菲亚梅塔并上场，且队伍中不能有其他狙击干员</t>
         </is>
       </c>
       <c r="F238" s="19" t="n"/>
@@ -19849,27 +19850,27 @@
     <row r="239" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>夏栎</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>maa://32999 (100.0)</t>
+          <t>maa://20867 (93.33), maa://38485 (96.15), *maa://32202 (80.0)</t>
         </is>
       </c>
       <c r="E239" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战夏栎累计使用生灵的回响8次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战夏栎并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战菲亚梅塔累计造成180000点伤害&gt; 3星通关主题曲S5-9；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔造成至少60000点伤害</t>
         </is>
       </c>
       <c r="F239" s="19" t="n"/>
@@ -19903,27 +19904,27 @@
     <row r="240" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>褐果</t>
         </is>
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>R8-8</t>
+          <t>SV-3</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>*maa://30667 (78.81), maa://30666 (83.55), **maa://30739 (43.24), *maa://30723 (56.45), maa://39588 (89.09)</t>
+          <t>maa://40160 (100.0)</t>
         </is>
       </c>
       <c r="E240" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战澄闪累计造成100000点伤害&gt; 3星通关主题曲R8-8；必须编入非助战澄闪并上场，且使用澄闪歼灭至少2名帝国炮火先兆者</t>
+          <t>&gt; 完成5次战斗；必须编入非助战褐果并上场，且每次战斗至少释放1次厚土迸发&gt; 3星通关插曲SV-3；必须编入非助战褐果并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F240" s="19" t="n"/>
@@ -19957,27 +19958,27 @@
     <row r="241" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>海蒂</t>
         </is>
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D241" s="13" t="inlineStr">
         <is>
-          <t>maa://62759 (100.0), maa://62764 (100.0)</t>
+          <t>maa://43089 (100.0)</t>
         </is>
       </c>
       <c r="E241" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战澄闪累计使用“澄净闪耀”10次&gt; 3星通关主题曲4-7；必须编入非助战澄闪并上场，其他成员仅可编入5名干员</t>
+          <t>&gt; 战斗中非助战海蒂累计使用8次“虚构故事·怒士”&gt; 3星通关主题曲9-7标准实战环境；必须编入非助战海蒂并上场，且海蒂使用至少3次“虚构故事·锈城”</t>
         </is>
       </c>
       <c r="F241" s="19" t="n"/>
@@ -20011,12 +20012,12 @@
     <row r="242" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>见行者</t>
+          <t>洛洛</t>
         </is>
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>GA-EX-1</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C242" s="12" t="inlineStr">
@@ -20026,12 +20027,12 @@
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>maa://30512 (100.0)</t>
+          <t>maa://30674 (90.0)</t>
         </is>
       </c>
       <c r="E242" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战见行者并上场，且每次战斗至少释放2次惊爆射击&gt; 3星通关别传GA-EX-1；必须编入非助战见行者，且本场战斗至少使3个寻路者精锐狙击手坠落地穴</t>
+          <t>&gt; 战斗中非助战洛洛累计使用自负此轭10次&gt; 3星通关别传RI-EX-4；必须编入非助战洛洛并上场，且使用洛洛歼灭至少2名提亚卡乌冠军</t>
         </is>
       </c>
       <c r="F242" s="19" t="n"/>
@@ -20065,27 +20066,27 @@
     <row r="243" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>风丸</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>7-15</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D243" s="13" t="inlineStr">
         <is>
-          <t>maa://20870 (100.0)</t>
+          <t>maa://28923 (91.5), maa://28906 (98.28), ***maa://28825 (11.54)</t>
         </is>
       </c>
       <c r="E243" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战风丸累计使用纸艺·双影10次&gt; 3星通关主题曲3-1；必须编入非助战风丸并上场，且使用风丸歼灭至少30名敌人</t>
+          <t>&gt; 战斗中非助战号角累计使用终极防线10次&gt; 3星通关主题曲7-15；必须编入非助战号角并上场，且使用号角至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F243" s="19" t="n"/>
@@ -20119,27 +20120,27 @@
     <row r="244" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>GA-4</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>maa://29024 (100.0)</t>
+          <t>maa://42287 (90.53), maa://45570 (96.43), maa://42225 (100.0)</t>
         </is>
       </c>
       <c r="E244" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔歼灭至少10个敌人&gt; 3星通关别传GA-4；必须编入非助战菲亚梅塔并上场，且队伍中不能有其他狙击干员</t>
+          <t>&gt; 由非助战号角累计造成100000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战号角并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F244" s="19" t="n"/>
@@ -20173,27 +20174,27 @@
     <row r="245" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>掠风</t>
         </is>
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>11-9</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D245" s="13" t="inlineStr">
         <is>
-          <t>maa://20867 (93.33), maa://38485 (96.15), *maa://32202 (80.0)</t>
+          <t>maa://39161 (100.0)</t>
         </is>
       </c>
       <c r="E245" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战菲亚梅塔累计造成180000点伤害&gt; 3星通关主题曲S5-9；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔造成至少60000点伤害</t>
+          <t>&gt; 战斗中非助战掠风累计使用此身为源10次&gt; 3星通关主题曲11-9标准实战环境；必须编入非助战掠风并上场，其他成员仅可编入术师、重装与医疗干员</t>
         </is>
       </c>
       <c r="F245" s="19" t="n"/>
@@ -20227,27 +20228,27 @@
     <row r="246" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t>褐果</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>SV-3</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>maa://40160 (100.0)</t>
+          <t>maa://20923 (92.86), *maa://60577 (66.67)</t>
         </is>
       </c>
       <c r="E246" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战褐果并上场，且每次战斗至少释放1次厚土迸发&gt; 3星通关插曲SV-3；必须编入非助战褐果并上场，且不编入其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战流明并上场，且每次战斗至少释放2次灯火不灭&gt; 3星通关主题曲6-9；且仅可编入非助战流明1名医疗干员并上场</t>
         </is>
       </c>
       <c r="F246" s="19" t="n"/>
@@ -20281,27 +20282,27 @@
     <row r="247" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>海蒂</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D247" s="13" t="inlineStr">
         <is>
-          <t>maa://43089 (100.0)</t>
+          <t>maa://24093 (100.0), maa://31559 (94.74), maa://20924 (95.24), **maa://49440 (50.0)</t>
         </is>
       </c>
       <c r="E247" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战海蒂累计使用8次“虚构故事·怒士”&gt; 3星通关主题曲9-7标准实战环境；必须编入非助战海蒂并上场，且海蒂使用至少3次“虚构故事·锈城”</t>
+          <t>&gt; 战斗中非助战流明累计使用沛霖10次&gt; 3星通关别传OF-5；必须编入非助战流明并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F247" s="19" t="n"/>
@@ -20335,27 +20336,27 @@
     <row r="248" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>洛洛</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>maa://30674 (90.0)</t>
+          <t>maa://40958 (89.29), *maa://45067 (75.0)</t>
         </is>
       </c>
       <c r="E248" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战洛洛累计使用自负此轭10次&gt; 3星通关别传RI-EX-4；必须编入非助战洛洛并上场，且使用洛洛歼灭至少2名提亚卡乌冠军</t>
+          <t>&gt; 由非助战艾丽妮累计造成100000点伤害&gt; 3星通关插曲SV-EX-1；必须编入非助战艾丽妮并上场，且使用2次判决</t>
         </is>
       </c>
       <c r="F248" s="19" t="n"/>
@@ -20389,27 +20390,27 @@
     <row r="249" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>7-15</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D249" s="13" t="inlineStr">
         <is>
-          <t>maa://28923 (91.5), maa://28906 (98.28), ***maa://28825 (11.54)</t>
+          <t>maa://20840 (100.0)</t>
         </is>
       </c>
       <c r="E249" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战号角累计使用终极防线10次&gt; 3星通关主题曲7-15；必须编入非助战号角并上场，且使用号角至少歼灭10个敌人</t>
+          <t>&gt; 由非助战艾丽妮使用技能累计造成50歼灭数&gt; 3星通关插曲SV-4；必须编入非助战艾丽妮并上场，且使用艾丽妮歼灭15个敌人</t>
         </is>
       </c>
       <c r="F249" s="19" t="n"/>
@@ -20443,27 +20444,27 @@
     <row r="250" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>maa://42287 (90.53), maa://45570 (96.43), maa://42225 (100.0)</t>
+          <t>maa://20877 (98.73), *maa://45067 (75.0), maa://20836 (100.0), maa://20632 (100.0)</t>
         </is>
       </c>
       <c r="E250" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战号角累计造成100000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战号角并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战归溟幽灵鲨累计造成30歼灭数&gt; 3星通关插曲SV-EX-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭至少1个囊海爬行者</t>
         </is>
       </c>
       <c r="F250" s="19" t="n"/>
@@ -20497,27 +20498,27 @@
     <row r="251" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>掠风</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>11-9</t>
+          <t>S4-1</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D251" s="13" t="inlineStr">
         <is>
-          <t>maa://39161 (100.0)</t>
+          <t>maa://20879 (86.67), maa://20834 (92.86)</t>
         </is>
       </c>
       <c r="E251" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战掠风累计使用此身为源10次&gt; 3星通关主题曲11-9标准实战环境；必须编入非助战掠风并上场，其他成员仅可编入术师、重装与医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战归溟幽灵鲨并上场，且每次战斗至少释放1次生存的重压&gt; 3星通关主题曲S4-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭10个敌人</t>
         </is>
       </c>
       <c r="F251" s="19" t="n"/>
@@ -20551,27 +20552,27 @@
     <row r="252" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>埃拉托</t>
         </is>
       </c>
       <c r="B252" s="11" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>maa://20923 (92.86), *maa://60577 (66.67)</t>
+          <t>maa://20839 (100.0)</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战流明并上场，且每次战斗至少释放2次灯火不灭&gt; 3星通关主题曲6-9；且仅可编入非助战流明1名医疗干员并上场</t>
+          <t>&gt; 战斗中非助战埃拉托累计使用英雄赞歌5次&gt; 3星通关主题曲S5-9；必须编入非助战埃拉托并上场，其他成员不可编入狙击干员</t>
         </is>
       </c>
       <c r="F252" s="19" t="n"/>
@@ -20605,27 +20606,27 @@
     <row r="253" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>濯尘芙蓉</t>
         </is>
       </c>
       <c r="B253" s="11" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D253" s="13" t="inlineStr">
         <is>
-          <t>maa://24093 (100.0), maa://31559 (94.74), maa://20924 (95.24), **maa://49440 (50.0)</t>
+          <t>maa://30676 (100.0)</t>
         </is>
       </c>
       <c r="E253" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战流明累计使用沛霖10次&gt; 3星通关别传OF-5；必须编入非助战流明并上场，且不编入其他医疗干员</t>
+          <t>&gt; 战斗中非助战濯尘芙蓉累计使用抚业之触10次&gt; 3星通关别传LE-4；必须编入非助战濯尘芙蓉并上场，且至少使用2次抚业之触</t>
         </is>
       </c>
       <c r="F253" s="19" t="n"/>
@@ -20659,12 +20660,12 @@
     <row r="254" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A254" s="11" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B254" s="11" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C254" s="12" t="inlineStr">
@@ -20674,12 +20675,12 @@
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>maa://40958 (89.29), *maa://45067 (75.0)</t>
+          <t>maa://31560 (91.67), maa://20884 (96.3)</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战艾丽妮累计造成100000点伤害&gt; 3星通关插曲SV-EX-1；必须编入非助战艾丽妮并上场，且使用2次判决</t>
+          <t>&gt; 由非助战黑键累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-7；必须编入非助战黑键并上场，且使用黑键歼灭至少1个重装防御组长</t>
         </is>
       </c>
       <c r="F254" s="19" t="n"/>
@@ -20713,12 +20714,12 @@
     <row r="255" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B255" s="11" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
@@ -20728,12 +20729,12 @@
       </c>
       <c r="D255" s="13" t="inlineStr">
         <is>
-          <t>maa://20840 (100.0)</t>
+          <t>maa://47204 (100.0)</t>
         </is>
       </c>
       <c r="E255" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战艾丽妮使用技能累计造成50歼灭数&gt; 3星通关插曲SV-4；必须编入非助战艾丽妮并上场，且使用艾丽妮歼灭15个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战黑键并上场，且使用黑键歼灭至少6个敌人&gt; 3星通关主题曲3-6；必须编入非助战黑键并上场，且使用黑键歼灭屠宰老手</t>
         </is>
       </c>
       <c r="F255" s="19" t="n"/>
@@ -20767,27 +20768,27 @@
     <row r="256" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B256" s="11" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>maa://20877 (98.72), *maa://45067 (75.0), maa://20836 (100.0), maa://20632 (100.0)</t>
+          <t>maa://29027 (98.11)</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战归溟幽灵鲨累计造成30歼灭数&gt; 3星通关插曲SV-EX-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭至少1个囊海爬行者</t>
+          <t>&gt; 战斗中非助战黑键累计使用寂静之声10次&gt; 3星通关主题曲11-12标准实战环境；必须编入非助战黑键并上场，且使用黑键歼灭至少2名伦蒂尼姆城防自行炮</t>
         </is>
       </c>
       <c r="F256" s="19" t="n"/>
@@ -20821,27 +20822,27 @@
     <row r="257" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>星源</t>
         </is>
       </c>
       <c r="B257" s="11" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D257" s="13" t="inlineStr">
         <is>
-          <t>maa://20879 (87.5), maa://20834 (92.86)</t>
+          <t>maa://20977 (100.0)</t>
         </is>
       </c>
       <c r="E257" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战归溟幽灵鲨并上场，且每次战斗至少释放1次生存的重压&gt; 3星通关主题曲S4-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭10个敌人</t>
+          <t>&gt; 由非助战星源累计造成40歼灭数&gt; 3星通关主题曲4-3；必须编入非助战星源并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
       <c r="F257" s="19" t="n"/>
@@ -20875,12 +20876,12 @@
     <row r="258" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t>埃拉托</t>
+          <t>承曦格雷伊</t>
         </is>
       </c>
       <c r="B258" s="11" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C258" s="12" t="inlineStr">
@@ -20890,12 +20891,12 @@
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>maa://20839 (100.0)</t>
+          <t>maa://39162 (100.0)</t>
         </is>
       </c>
       <c r="E258" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战埃拉托累计使用英雄赞歌5次&gt; 3星通关主题曲S5-9；必须编入非助战埃拉托并上场，其他成员不可编入狙击干员</t>
+          <t>&gt; 战斗中非助战承曦格雷伊累计使用晨曦信标10次&gt; 3星通关主题曲1-3；必须编入非助战承曦格雷伊并上场，其他成员仅可编入先锋干员</t>
         </is>
       </c>
       <c r="F258" s="19" t="n"/>
@@ -20929,27 +20930,27 @@
     <row r="259" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t>濯尘芙蓉</t>
+          <t>至简</t>
         </is>
       </c>
       <c r="B259" s="11" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>IC-8</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D259" s="13" t="inlineStr">
         <is>
-          <t>maa://30676 (100.0)</t>
+          <t>**maa://30678 (37.5), maa://59689 (100.0)</t>
         </is>
       </c>
       <c r="E259" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战濯尘芙蓉累计使用抚业之触10次&gt; 3星通关别传LE-4；必须编入非助战濯尘芙蓉并上场，且至少使用2次抚业之触</t>
+          <t>&gt; 战斗中非助战至简累计使用神工意匠20次&gt; 3星通关别传IC-8；必须编入非助战至简并上场，且使用至简歼灭至少2名蜜酿级醒酒助手</t>
         </is>
       </c>
       <c r="F259" s="19" t="n"/>
@@ -20983,27 +20984,27 @@
     <row r="260" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A260" s="11" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>晓歌</t>
         </is>
       </c>
       <c r="B260" s="11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>maa://31560 (91.67), maa://20884 (96.3)</t>
+          <t>maa://49643 (89.66)</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战黑键累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-7；必须编入非助战黑键并上场，且使用黑键歼灭至少1个重装防御组长</t>
+          <t>&gt; 战斗中累计部署非助战晓歌12次&gt; 3星通关主题曲5-3；必须编入非助战晓歌并上场，且使用晓歌歼灭至少3个特战术师或特战术师组长</t>
         </is>
       </c>
       <c r="F260" s="19" t="n"/>
@@ -21037,12 +21038,12 @@
     <row r="261" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B261" s="11" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
@@ -21052,12 +21053,12 @@
       </c>
       <c r="D261" s="13" t="inlineStr">
         <is>
-          <t>maa://47204 (100.0)</t>
+          <t>maa://48265 (83.33)</t>
         </is>
       </c>
       <c r="E261" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战黑键并上场，且使用黑键歼灭至少6个敌人&gt; 3星通关主题曲3-6；必须编入非助战黑键并上场，且使用黑键歼灭屠宰老手</t>
+          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
         </is>
       </c>
       <c r="F261" s="19" t="n"/>
@@ -21091,27 +21092,27 @@
     <row r="262" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B262" s="11" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>maa://29027 (98.11)</t>
+          <t>*maa://20825 (72.41), *maa://21445 (72.22), *maa://35726 (66.67), ***maa://20891 (30.0)</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战黑键累计使用寂静之声10次&gt; 3星通关主题曲11-12标准实战环境；必须编入非助战黑键并上场，且使用黑键歼灭至少2名伦蒂尼姆城防自行炮</t>
+          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
         </is>
       </c>
       <c r="F262" s="19" t="n"/>
@@ -21145,12 +21146,12 @@
     <row r="263" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A263" s="11" t="inlineStr">
         <is>
-          <t>星源</t>
+          <t>百炼嘉维尔</t>
         </is>
       </c>
       <c r="B263" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
@@ -21160,12 +21161,12 @@
       </c>
       <c r="D263" s="13" t="inlineStr">
         <is>
-          <t>maa://20977 (100.0)</t>
+          <t>maa://25769 (97.48)</t>
         </is>
       </c>
       <c r="E263" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战星源累计造成40歼灭数&gt; 3星通关主题曲4-3；必须编入非助战星源并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 战斗中非助战百炼嘉维尔累计使用链锯强袭10次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战百炼嘉维尔并上场，且使用百炼嘉维尔至少歼灭15个敌人</t>
         </is>
       </c>
       <c r="F263" s="19" t="n"/>
@@ -21197,29 +21198,29 @@
       <c r="AF263" s="8" t="n"/>
     </row>
     <row r="264" ht="13.5" customFormat="1" customHeight="1" s="22">
-      <c r="A264" s="11" t="inlineStr">
-        <is>
-          <t>承曦格雷伊</t>
-        </is>
-      </c>
-      <c r="B264" s="11" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="C264" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D264" s="13" t="inlineStr">
-        <is>
-          <t>maa://39162 (100.0)</t>
-        </is>
-      </c>
-      <c r="E264" s="14" t="inlineStr">
-        <is>
-          <t>&gt; 战斗中非助战承曦格雷伊累计使用晨曦信标10次&gt; 3星通关主题曲1-3；必须编入非助战承曦格雷伊并上场，其他成员仅可编入先锋干员</t>
+      <c r="A264" s="24" t="inlineStr">
+        <is>
+          <t>百炼嘉维尔</t>
+        </is>
+      </c>
+      <c r="B264" s="24" t="inlineStr">
+        <is>
+          <t>RI-9</t>
+        </is>
+      </c>
+      <c r="C264" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D264" s="26" t="inlineStr">
+        <is>
+          <t>**maa://62757 (37.5)</t>
+        </is>
+      </c>
+      <c r="E264" s="27" t="inlineStr">
+        <is>
+          <t>&gt; 由非助战百炼嘉维尔累计造成40歼灭数&gt; 3星通关插曲RI-9；必须编入非助战百炼嘉维尔并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F264" s="19" t="n"/>
@@ -21253,12 +21254,12 @@
     <row r="265" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t>多萝西</t>
+          <t>但书</t>
         </is>
       </c>
       <c r="B265" s="11" t="inlineStr">
         <is>
-          <t>MB-EX-1</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
@@ -21268,12 +21269,12 @@
       </c>
       <c r="D265" s="13" t="inlineStr">
         <is>
-          <t>maa://59682 (100.0)</t>
+          <t>maa://20862 (83.33)</t>
         </is>
       </c>
       <c r="E265" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战多萝西累计造成120000点伤害&gt; 3星通关插曲MB-EX-1，必须编入非助战多萝西并上场，其他成员仅可编入近卫干员</t>
+          <t>&gt; 战斗中非助战但书累计使用致胜立论14次&gt; 3星通关主题曲4-7；必须编入非助战但书并上场，且使用但书至少歼灭3只高能源石虫</t>
         </is>
       </c>
       <c r="F265" s="19" t="n"/>
@@ -21307,27 +21308,27 @@
     <row r="266" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t>多萝西</t>
+          <t>玛恩纳</t>
         </is>
       </c>
       <c r="B266" s="11" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C266" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>maa://22467 (95.92)</t>
+          <t>maa://51881 (99.25), maa://51630 (96.7), maa://56588 (95.0), *maa://55171 (57.14), maa://51893 (88.89), ***maa://60902 (25.0)</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战多萝西累计部署共振装置50个&gt; 3星通关主题曲4-5；必须编入非助战多萝西并上场，其他成员仅可编入3名干员</t>
+          <t>&gt; 使用非助战玛恩纳累计造成120000点伤害&gt; 3星通关主题曲11-15标准实战环境；必须编入非助战玛恩纳并上场，且使用2次未照耀的荣光</t>
         </is>
       </c>
       <c r="F266" s="19" t="n"/>
@@ -21361,27 +21362,27 @@
     <row r="267" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t>至简</t>
+          <t>罗小黑</t>
         </is>
       </c>
       <c r="B267" s="11" t="inlineStr">
         <is>
-          <t>IC-8</t>
+          <t>IW-4</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D267" s="13" t="inlineStr">
         <is>
-          <t>**maa://30678 (37.5), maa://59689 (100.0)</t>
+          <t>maa://39163 (100.0)</t>
         </is>
       </c>
       <c r="E267" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战至简累计使用神工意匠20次&gt; 3星通关别传IC-8；必须编入非助战至简并上场，且使用至简歼灭至少2名蜜酿级醒酒助手</t>
+          <t>&gt; 完成5次战斗；必须编入非助战罗小黑并上场，且每次战斗至少释放1次碎金为刃&gt; 3星通关别传IW-4；必须编入非助战罗小黑并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
       <c r="F267" s="19" t="n"/>
@@ -21415,12 +21416,12 @@
     <row r="268" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t>晓歌</t>
+          <t>海沫</t>
         </is>
       </c>
       <c r="B268" s="11" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C268" s="12" t="inlineStr">
@@ -21430,12 +21431,12 @@
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>maa://49643 (88.89)</t>
+          <t>maa://29061 (100.0)</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战晓歌12次&gt; 3星通关主题曲5-3；必须编入非助战晓歌并上场，且使用晓歌歼灭至少3个特战术师或特战术师组长</t>
+          <t>&gt; 完成5次战斗；必须编入非助战海沫并上场，且使用海沫造成至少12000点伤害&gt; 3星通关插曲SN-2；必须携带并部署非助战海沫，其他成员仅可编入2名干员</t>
         </is>
       </c>
       <c r="F268" s="19" t="n"/>
@@ -21469,12 +21470,12 @@
     <row r="269" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>铅踝</t>
         </is>
       </c>
       <c r="B269" s="11" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
@@ -21484,12 +21485,12 @@
       </c>
       <c r="D269" s="13" t="inlineStr">
         <is>
-          <t>maa://48265 (83.33)</t>
+          <t>maa://20939 (81.82)</t>
         </is>
       </c>
       <c r="E269" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
+          <t>&gt; 由非助战铅踝累计造成30歼灭数&gt; 3星通关主题曲S3-5；必须编入非助战铅踝并上场，且使用铅踝歼灭至少2个隐形弩手</t>
         </is>
       </c>
       <c r="F269" s="19" t="n"/>
@@ -21523,27 +21524,27 @@
     <row r="270" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>达格达</t>
         </is>
       </c>
       <c r="B270" s="11" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>*maa://20825 (72.41), *maa://21445 (72.22), *maa://35726 (66.67), ***maa://20891 (30.0)</t>
+          <t>maa://39164 (100.0)</t>
         </is>
       </c>
       <c r="E270" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
+          <t>&gt; 由非助战达格达累计造成30歼灭数&gt; 3星通关主题曲11-5标准实战环境；必须编入非助战达格达并上场，且使用达格达至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F270" s="19" t="n"/>
@@ -21577,27 +21578,27 @@
     <row r="271" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t>百炼嘉维尔</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B271" s="11" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>maa://25769 (97.47)</t>
+          <t>maa://28133 (93.1), maa://33394 (100.0)</t>
         </is>
       </c>
       <c r="E271" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战百炼嘉维尔累计使用链锯强袭10次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战百炼嘉维尔并上场，且使用百炼嘉维尔至少歼灭15个敌人</t>
+          <t>&gt; 战斗中非助战白铁累计部署支援装置25个&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战白铁并上场，且使用白铁或白铁的支援装置歼灭至少15名萨卡兹枯朽战士</t>
         </is>
       </c>
       <c r="F271" s="19" t="n"/>
@@ -21629,29 +21630,29 @@
       <c r="AF271" s="8" t="n"/>
     </row>
     <row r="272" ht="13.5" customFormat="1" customHeight="1" s="22">
-      <c r="A272" s="24" t="inlineStr">
-        <is>
-          <t>百炼嘉维尔</t>
-        </is>
-      </c>
-      <c r="B272" s="24" t="inlineStr">
-        <is>
-          <t>RI-9</t>
-        </is>
-      </c>
-      <c r="C272" s="25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D272" s="26" t="inlineStr">
-        <is>
-          <t>**maa://62757 (38.46)</t>
-        </is>
-      </c>
-      <c r="E272" s="27" t="inlineStr">
-        <is>
-          <t>&gt; 由非助战百炼嘉维尔累计造成40歼灭数&gt; 3星通关插曲RI-9；必须编入非助战百炼嘉维尔并上场，且所有干员不被击倒</t>
+      <c r="A272" s="11" t="inlineStr">
+        <is>
+          <t>白铁</t>
+        </is>
+      </c>
+      <c r="B272" s="11" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="C272" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D272" s="13" t="inlineStr">
+        <is>
+          <t>maa://42311 (100.0)</t>
+        </is>
+      </c>
+      <c r="E272" s="14" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战白铁累计使用8次“铁钳号·原型机”&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战白铁并上场，且使用白铁至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F272" s="19" t="n"/>
@@ -21685,12 +21686,12 @@
     <row r="273" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t>但书</t>
+          <t>石英</t>
         </is>
       </c>
       <c r="B273" s="11" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>DH-4</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
@@ -21700,12 +21701,12 @@
       </c>
       <c r="D273" s="13" t="inlineStr">
         <is>
-          <t>maa://20862 (83.33)</t>
+          <t>maa://41362 (100.0)</t>
         </is>
       </c>
       <c r="E273" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战但书累计使用致胜立论14次&gt; 3星通关主题曲4-7；必须编入非助战但书并上场，且使用但书至少歼灭3只高能源石虫</t>
+          <t>&gt; 完成3次战斗；必须编入非助战石英并上场，且每次战斗至少释放1次全力相搏&gt; 3星通关别传DH-4；必须编入非助战石英并上场，并使用石英至少击败2名控潮术师</t>
         </is>
       </c>
       <c r="F273" s="19" t="n"/>
@@ -21739,27 +21740,27 @@
     <row r="274" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A274" s="11" t="inlineStr">
         <is>
-          <t>玛恩纳</t>
+          <t>雪绒</t>
         </is>
       </c>
       <c r="B274" s="11" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>maa://51881 (99.24), maa://51630 (96.67), maa://56588 (95.0), *maa://55171 (57.14), maa://51893 (88.89), ***maa://60902 (28.57)</t>
+          <t>maa://20978 (100.0)</t>
         </is>
       </c>
       <c r="E274" s="14" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战玛恩纳累计造成120000点伤害&gt; 3星通关主题曲11-15标准实战环境；必须编入非助战玛恩纳并上场，且使用2次未照耀的荣光</t>
+          <t>&gt; 战斗中非助战雪绒累计使用坠雪10次&gt; 3星通关主题曲2-3；必须编入非助战雪绒并上场，且使用雪绒歼灭至少2名重装防御者</t>
         </is>
       </c>
       <c r="F274" s="19" t="n"/>
@@ -21793,12 +21794,12 @@
     <row r="275" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A275" s="11" t="inlineStr">
         <is>
-          <t>罗小黑</t>
+          <t>子月</t>
         </is>
       </c>
       <c r="B275" s="11" t="inlineStr">
         <is>
-          <t>IW-4</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
@@ -21808,12 +21809,12 @@
       </c>
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>maa://39163 (100.0)</t>
+          <t>maa://21002 (100.0)</t>
         </is>
       </c>
       <c r="E275" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战罗小黑并上场，且每次战斗至少释放1次碎金为刃&gt; 3星通关别传IW-4；必须编入非助战罗小黑并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 由非助战子月累计造成30歼灭数&gt; 3星通关主题曲2-5；必须编入非助战子月并上场，且使用子月歼灭至少2个高阶术师</t>
         </is>
       </c>
       <c r="F275" s="19" t="n"/>
@@ -21847,12 +21848,12 @@
     <row r="276" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t>海沫</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B276" s="11" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C276" s="12" t="inlineStr">
@@ -21862,12 +21863,12 @@
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>maa://29061 (100.0)</t>
+          <t>*maa://39165 (70.0)</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战海沫并上场，且使用海沫造成至少12000点伤害&gt; 3星通关插曲SN-2；必须携带并部署非助战海沫，其他成员仅可编入2名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战伺夜并上场，且每次战斗至少释放1次领袖的尊严&gt; 3星通关主题曲3-8；必须编入非助战伺夜并上场，且使用伺夜歼灭碎骨</t>
         </is>
       </c>
       <c r="F276" s="19" t="n"/>
@@ -21901,27 +21902,27 @@
     <row r="277" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t>铅踝</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B277" s="11" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>IS-6</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D277" s="13" t="inlineStr">
         <is>
-          <t>maa://20939 (81.82)</t>
+          <t>maa://48267 (100.0), maa://48266 (100.0)</t>
         </is>
       </c>
       <c r="E277" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战铅踝累计造成30歼灭数&gt; 3星通关主题曲S3-5；必须编入非助战铅踝并上场，且使用铅踝歼灭至少2个隐形弩手</t>
+          <t>&gt; 完成5次战斗；必须编入非助战伺夜，并确定第一位部署的干员是伺夜&gt; 3星通关别传IS-6；必须编入非助战伺夜并上场，且至少使用3次领袖的尊严</t>
         </is>
       </c>
       <c r="F277" s="19" t="n"/>
@@ -21955,12 +21956,12 @@
     <row r="278" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t>达格达</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B278" s="11" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C278" s="12" t="inlineStr">
@@ -21970,12 +21971,12 @@
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>maa://39164 (100.0)</t>
+          <t>maa://29635 (100.0)</t>
         </is>
       </c>
       <c r="E278" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战达格达累计造成30歼灭数&gt; 3星通关主题曲11-5标准实战环境；必须编入非助战达格达并上场，且使用达格达至少歼灭10个敌人</t>
+          <t>&gt; 由非助战斥罪累计造成40歼灭数&gt; 3星通关别传CB-4；必须携带并部署非助战斥罪，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F278" s="19" t="n"/>
@@ -22009,27 +22010,27 @@
     <row r="279" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B279" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>IS-7</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D279" s="13" t="inlineStr">
         <is>
-          <t>maa://28133 (93.1), maa://33394 (100.0)</t>
+          <t>maa://38296 (90.62)</t>
         </is>
       </c>
       <c r="E279" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战白铁累计部署支援装置25个&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战白铁并上场，且使用白铁或白铁的支援装置歼灭至少15名萨卡兹枯朽战士</t>
+          <t>&gt; 战斗中非助战斥罪累计使用披荆斩棘5次&gt; 3星通关别传IS-7；必须编入非助战斥罪并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F279" s="19" t="n"/>
@@ -22063,27 +22064,27 @@
     <row r="280" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>缄默德克萨斯</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>CB-8</t>
         </is>
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>maa://42311 (100.0)</t>
+          <t>maa://20899 (89.71), maa://46332 (95.65), ***maa://44744 (25.0)</t>
         </is>
       </c>
       <c r="E280" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战白铁累计使用8次“铁钳号·原型机”&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战白铁并上场，且使用白铁至少歼灭10个敌人</t>
+          <t>&gt; 由非助战缄默德克萨斯累计歼灭10个精英或领袖敌人&gt; 3星通关别传CB-8；必须编入非助战缄默德克萨斯并上场，且使用缄默德克萨斯歼灭至少2个灰尾</t>
         </is>
       </c>
       <c r="F280" s="19" t="n"/>
@@ -22117,12 +22118,12 @@
     <row r="281" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t>石英</t>
+          <t>谜图</t>
         </is>
       </c>
       <c r="B281" s="11" t="inlineStr">
         <is>
-          <t>DH-4</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
@@ -22132,12 +22133,12 @@
       </c>
       <c r="D281" s="13" t="inlineStr">
         <is>
-          <t>maa://41362 (100.0)</t>
+          <t>maa://53353 (100.0)</t>
         </is>
       </c>
       <c r="E281" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成3次战斗；必须编入非助战石英并上场，且每次战斗至少释放1次全力相搏&gt; 3星通关别传DH-4；必须编入非助战石英并上场，并使用石英至少击败2名控潮术师</t>
+          <t>&gt; 完成5次战斗；必须编入非助战谜图并上场，且使用谜图歼灭至少3个敌人&gt; 3星通关主题曲9-4标准实战环境；必须编入非助战谜图并上场，其他成员不可编入先锋干员</t>
         </is>
       </c>
       <c r="F281" s="19" t="n"/>
@@ -22171,12 +22172,12 @@
     <row r="282" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t>雪绒</t>
+          <t>和弦</t>
         </is>
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
@@ -22186,12 +22187,12 @@
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>maa://20978 (100.0)</t>
+          <t>maa://20881 (100.0)</t>
         </is>
       </c>
       <c r="E282" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战雪绒累计使用坠雪10次&gt; 3星通关主题曲2-3；必须编入非助战雪绒并上场，且使用雪绒歼灭至少2名重装防御者</t>
+          <t>&gt; 完成5次战斗；必须编入非助战和弦并上场，且每次战斗至少释放一次沉溺之灾&gt; 3星通关主题曲6-5；必须编入非助战和弦并上场，且使用和弦歼灭至少2个宿主重装士兵</t>
         </is>
       </c>
       <c r="F282" s="19" t="n"/>
@@ -22225,27 +22226,27 @@
     <row r="283" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t>子月</t>
+          <t>焰影苇草</t>
         </is>
       </c>
       <c r="B283" s="11" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D283" s="13" t="inlineStr">
         <is>
-          <t>maa://21002 (100.0)</t>
+          <t>maa://30710 (97.89), maa://36845 (95.71), maa://31558 (97.14), **maa://39217 (41.18), maa://30668 (86.67)</t>
         </is>
       </c>
       <c r="E283" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战子月累计造成30歼灭数&gt; 3星通关主题曲2-5；必须编入非助战子月并上场，且使用子月歼灭至少2个高阶术师</t>
+          <t>&gt; 战斗中非助战焰影苇草累计使用枯荣共息10次&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战焰影苇草并上场，且使用焰影苇草至少歼灭40个敌人</t>
         </is>
       </c>
       <c r="F283" s="19" t="n"/>
@@ -22279,12 +22280,12 @@
     <row r="284" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>截云</t>
         </is>
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C284" s="12" t="inlineStr">
@@ -22294,12 +22295,12 @@
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>*maa://39165 (70.0)</t>
+          <t>maa://20902 (100.0)</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战伺夜并上场，且每次战斗至少释放1次领袖的尊严&gt; 3星通关主题曲3-8；必须编入非助战伺夜并上场，且使用伺夜歼灭碎骨</t>
+          <t>&gt; 由非助战截云累计造成100000点伤害&gt; 3星通关主题曲S2-2；必须编入非助战截云并上场，且使用截云至少歼灭10名敌人</t>
         </is>
       </c>
       <c r="F284" s="19" t="n"/>
@@ -22333,27 +22334,27 @@
     <row r="285" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A285" s="11" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>火哨</t>
         </is>
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>IS-6</t>
+          <t>S4-6</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D285" s="13" t="inlineStr">
         <is>
-          <t>maa://48267 (100.0), maa://48266 (100.0)</t>
+          <t>maa://29159 (100.0)</t>
         </is>
       </c>
       <c r="E285" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战伺夜，并确定第一位部署的干员是伺夜&gt; 3星通关别传IS-6；必须编入非助战伺夜并上场，且至少使用3次领袖的尊严</t>
+          <t>&gt; 战斗中非助战火哨累计使用焦土8次&gt; 3星通关主题曲S4-6；必须携带并部署非助战火哨，其他成员仅可编入远程位干员</t>
         </is>
       </c>
       <c r="F285" s="19" t="n"/>
@@ -22387,27 +22388,27 @@
     <row r="286" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>maa://29635 (100.0)</t>
+          <t>maa://25774 (97.18), maa://28133 (93.1), maa://22469 (92.86), **maa://39217 (41.18), **maa://31349 (50.0)</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战斥罪累计造成40歼灭数&gt; 3星通关别传CB-4；必须携带并部署非助战斥罪，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战林累计歼灭80个敌人&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战林并上场，且不编入重装干员</t>
         </is>
       </c>
       <c r="F286" s="19" t="n"/>
@@ -22441,12 +22442,12 @@
     <row r="287" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>IS-7</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
@@ -22456,12 +22457,12 @@
       </c>
       <c r="D287" s="13" t="inlineStr">
         <is>
-          <t>maa://38296 (90.62)</t>
+          <t>maa://47882 (100.0)</t>
         </is>
       </c>
       <c r="E287" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战斥罪累计使用披荆斩棘5次&gt; 3星通关别传IS-7；必须编入非助战斥罪并上场，且不编入其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战林并上场，且每次战斗至少释放1次流光乍裂&gt; 3星通关主题曲6-5；必须携带且部署非助战林，且至少释放3次流光乍裂</t>
         </is>
       </c>
       <c r="F287" s="19" t="n"/>
@@ -22495,12 +22496,12 @@
     <row r="288" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t>缄默德克萨斯</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B288" s="11" t="inlineStr">
         <is>
-          <t>CB-8</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C288" s="12" t="inlineStr">
@@ -22510,12 +22511,12 @@
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>maa://20899 (89.71), maa://46332 (95.65), ***maa://44744 (25.0)</t>
+          <t>maa://32414 (98.79), maa://32505 (100.0), maa://39155 (97.44)</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战缄默德克萨斯累计歼灭10个精英或领袖敌人&gt; 3星通关别传CB-8；必须编入非助战缄默德克萨斯并上场，且使用缄默德克萨斯歼灭至少2个灰尾</t>
+          <t>&gt; 由非助战重岳累计造成120000点伤害&gt; 3星通关别传WB-7；必须携带并部署非助战重岳，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F288" s="19" t="n"/>
@@ -22549,27 +22550,27 @@
     <row r="289" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t>谜图</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B289" s="11" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>GA-5</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D289" s="13" t="inlineStr">
         <is>
-          <t>maa://53353 (100.0)</t>
+          <t>maa://45799 (100.0), maa://57199 (100.0)</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战谜图并上场，且使用谜图歼灭至少3个敌人&gt; 3星通关主题曲9-4标准实战环境；必须编入非助战谜图并上场，其他成员不可编入先锋干员</t>
+          <t>&gt; 使用非助战重岳累计使用50次我无&gt; 3星通关别传GA-5；必须携带且部署非助战重岳，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F289" s="19" t="n"/>
@@ -22603,12 +22604,12 @@
     <row r="290" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t>和弦</t>
+          <t>铎铃</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C290" s="12" t="inlineStr">
@@ -22618,12 +22619,12 @@
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>maa://20881 (100.0)</t>
+          <t>maa://42312 (100.0)</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战和弦并上场，且每次战斗至少释放一次沉溺之灾&gt; 3星通关主题曲6-5；必须编入非助战和弦并上场，且使用和弦歼灭至少2个宿主重装士兵</t>
+          <t>&gt; 战斗中非助战铎铃累计使用乡心无改6次&gt; 3星通关主题曲2-1；必须编入非助战铎铃并上场，且使用3次乡心无改</t>
         </is>
       </c>
       <c r="F290" s="19" t="n"/>
@@ -22657,27 +22658,27 @@
     <row r="291" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A291" s="11" t="inlineStr">
         <is>
-          <t>焰影苇草</t>
+          <t>仇白</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D291" s="13" t="inlineStr">
         <is>
-          <t>maa://30710 (97.89), maa://36845 (95.71), maa://31558 (97.14), **maa://39217 (41.18), maa://30668 (86.67)</t>
+          <t>maa://36642 (100.0), maa://36867 (97.06), maa://39155 (97.44)</t>
         </is>
       </c>
       <c r="E291" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战焰影苇草累计使用枯荣共息10次&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战焰影苇草并上场，且使用焰影苇草至少歼灭40个敌人</t>
+          <t>&gt; 由非助战仇白累计造成40歼灭数&gt; 3星通关别传WB-7；必须编入非助战仇白并上场，并使用仇白至少击败3名“破坚”</t>
         </is>
       </c>
       <c r="F291" s="19" t="n"/>
@@ -22711,27 +22712,27 @@
     <row r="292" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t>截云</t>
+          <t>火龙S黑角</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C292" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>maa://20902 (100.0)</t>
+          <t>**maa://39166 (50.0), maa://39167 (100.0)</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战截云累计造成100000点伤害&gt; 3星通关主题曲S2-2；必须编入非助战截云并上场，且使用截云至少歼灭10名敌人</t>
+          <t>&gt; 由非助战火龙S黑角累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-8；必须编入非助战火龙S黑角并上场，且使用火龙S黑角歼灭碎骨</t>
         </is>
       </c>
       <c r="F292" s="19" t="n"/>
@@ -22765,27 +22766,27 @@
     <row r="293" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t>火哨</t>
+          <t>麒麟R夜刀</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>S4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D293" s="13" t="inlineStr">
         <is>
-          <t>maa://29159 (100.0)</t>
+          <t>maa://29005 (98.77), maa://31560 (91.67)</t>
         </is>
       </c>
       <c r="E293" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战火哨累计使用焦土8次&gt; 3星通关主题曲S4-6；必须携带并部署非助战火哨，其他成员仅可编入远程位干员</t>
+          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战的麒麟R夜刀&gt; 3星通关主题曲3-7；必须编入非助战麒麟R夜刀并上场，且使用麒麟R夜刀歼灭至少2名炮手</t>
         </is>
       </c>
       <c r="F293" s="19" t="n"/>
@@ -22819,27 +22820,27 @@
     <row r="294" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A294" s="11" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>休谟斯</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C294" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>maa://25774 (97.18), maa://28133 (93.1), maa://22469 (92.86), **maa://39217 (41.18), **maa://31349 (50.0)</t>
+          <t>maa://39168 (100.0)</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战林累计歼灭80个敌人&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战林并上场，且不编入重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战休谟斯并上场，且每次战斗至少释放1次高效处理&gt; 3星通关主题曲7-8；必须编入非助战休谟斯并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
       <c r="F294" s="19" t="n"/>
@@ -22873,12 +22874,12 @@
     <row r="295" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A295" s="11" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>摩根</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
@@ -22888,12 +22889,12 @@
       </c>
       <c r="D295" s="13" t="inlineStr">
         <is>
-          <t>maa://47882 (100.0)</t>
+          <t>maa://39169 (100.0)</t>
         </is>
       </c>
       <c r="E295" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战林并上场，且每次战斗至少释放1次流光乍裂&gt; 3星通关主题曲6-5；必须携带且部署非助战林，且至少释放3次流光乍裂</t>
+          <t>&gt; 由非助战摩根累计造成80000点伤害&gt; 3星通关主题曲4-5，必须编入非助战摩根并上场，且使用摩根至少歼灭10名敌人</t>
         </is>
       </c>
       <c r="F295" s="19" t="n"/>
@@ -22927,27 +22928,27 @@
     <row r="296" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>洋灰</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>IW-EX-6</t>
         </is>
       </c>
       <c r="C296" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>maa://32414 (98.79), maa://32505 (100.0), maa://39155 (97.44)</t>
+          <t>maa://39170 (100.0)</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战重岳累计造成120000点伤害&gt; 3星通关别传WB-7；必须携带并部署非助战重岳，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战洋灰并上场，且每次战斗至少释放1次结构加固&gt; 3星通关别传IW-EX-6，必须编入非助战洋灰并上场，且不编入其他重装干员</t>
         </is>
       </c>
       <c r="F296" s="19" t="n"/>
@@ -22981,27 +22982,27 @@
     <row r="297" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A297" s="11" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>伊内丝</t>
         </is>
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>GA-5</t>
+          <t>12-12</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>maa://45799 (100.0), maa://57199 (100.0)</t>
+          <t>maa://50280 (97.49), maa://49642 (97.0), maa://49660 (90.32), *maa://50517 (80.0)</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战重岳累计使用50次我无&gt; 3星通关别传GA-5；必须携带且部署非助战重岳，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中累计部署非助战伊内丝12次&gt; 3星通关主题曲12-12标准实战环境；必须编入非助战伊内丝并上场，且至少使用3次暗夜无明</t>
         </is>
       </c>
       <c r="F297" s="19" t="n"/>
@@ -23035,12 +23036,12 @@
     <row r="298" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t>铎铃</t>
+          <t>玫拉</t>
         </is>
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C298" s="12" t="inlineStr">
@@ -23050,12 +23051,12 @@
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>maa://42312 (100.0)</t>
+          <t>maa://39171 (100.0)</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战铎铃累计使用乡心无改6次&gt; 3星通关主题曲2-1；必须编入非助战铎铃并上场，且使用3次乡心无改</t>
+          <t>&gt; 完成5次战斗；必须编入非助战玫拉并上场，且每次战斗至少释放1次临界爆发&gt; 3星通关主题曲S3-5；必须编入非助战玫拉并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
       <c r="F298" s="19" t="n"/>
@@ -23089,27 +23090,27 @@
     <row r="299" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t>仇白</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D299" s="13" t="inlineStr">
         <is>
-          <t>maa://36642 (100.0), maa://36867 (97.06), maa://39155 (97.44)</t>
+          <t>maa://27939 (100.0)</t>
         </is>
       </c>
       <c r="E299" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战仇白累计造成40歼灭数&gt; 3星通关别传WB-7；必须编入非助战仇白并上场，并使用仇白至少击败3名“破坚”</t>
+          <t>&gt; 战斗中非助战淬羽赫默累计使用无畏者协议8次&gt; 3星通关主题曲6-3；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F299" s="19" t="n"/>
@@ -23143,27 +23144,27 @@
     <row r="300" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t>火龙S黑角</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B300" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C300" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>**maa://39166 (50.0), maa://39167 (100.0)</t>
+          <t>maa://53352 (100.0)</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战火龙S黑角累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-8；必须编入非助战火龙S黑角并上场，且使用火龙S黑角歼灭碎骨</t>
+          <t>&gt; 完成5次战斗；必须编入非助战淬羽赫默并上场，且每次战斗至少释放1次无畏者协议&gt; 3星通关插曲WB-5；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F300" s="19" t="n"/>
@@ -23197,27 +23198,27 @@
     <row r="301" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t>麒麟R夜刀</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B301" s="11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D301" s="13" t="inlineStr">
         <is>
-          <t>maa://29005 (98.77), maa://31560 (91.67)</t>
+          <t>maa://29129 (100.0)</t>
         </is>
       </c>
       <c r="E301" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战的麒麟R夜刀&gt; 3星通关主题曲3-7；必须编入非助战麒麟R夜刀并上场，且使用麒麟R夜刀歼灭至少2名炮手</t>
+          <t>&gt; 由非助战霍尔海雅累计造成120000点伤害&gt; 3星通关别传OF-7；必须编入非助战霍尔海雅并上场，且至少使用2次博览者的狂语</t>
         </is>
       </c>
       <c r="F301" s="19" t="n"/>
@@ -23251,12 +23252,12 @@
     <row r="302" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t>休谟斯</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B302" s="11" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C302" s="12" t="inlineStr">
@@ -23266,12 +23267,12 @@
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>maa://39168 (100.0)</t>
+          <t>maa://36005 (93.33)</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战休谟斯并上场，且每次战斗至少释放1次高效处理&gt; 3星通关主题曲7-8；必须编入非助战休谟斯并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战霍尔海雅并上场，且每次战斗至少释放1次博览者的狂语&gt; 3星通关主题曲4-3；必须编入非助战霍尔海雅并上场，且使用霍尔海雅至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F302" s="19" t="n"/>
@@ -23305,12 +23306,12 @@
     <row r="303" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t>摩根</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B303" s="11" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
@@ -23320,12 +23321,12 @@
       </c>
       <c r="D303" s="13" t="inlineStr">
         <is>
-          <t>maa://39169 (100.0)</t>
+          <t>maa://35859 (97.78)</t>
         </is>
       </c>
       <c r="E303" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战摩根累计造成80000点伤害&gt; 3星通关主题曲4-5，必须编入非助战摩根并上场，且使用摩根至少歼灭10名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思，并确定第一位部署的干员是缪尔赛思&gt; 3星通关主题曲3-4；必须编入非助战缪尔赛思并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F303" s="19" t="n"/>
@@ -23359,12 +23360,12 @@
     <row r="304" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A304" s="11" t="inlineStr">
         <is>
-          <t>洋灰</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B304" s="11" t="inlineStr">
         <is>
-          <t>IW-EX-6</t>
+          <t>6-12</t>
         </is>
       </c>
       <c r="C304" s="12" t="inlineStr">
@@ -23374,12 +23375,12 @@
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>maa://39170 (100.0)</t>
+          <t>maa://53348 (95.24)</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战洋灰并上场，且每次战斗至少释放1次结构加固&gt; 3星通关别传IW-EX-6，必须编入非助战洋灰并上场，且不编入其他重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思并上场，且每次战斗至少释放1次生态耦合&gt; 3星通关主题曲6-12；必须编入非助战缪尔赛思并上场，且使用2次生态耦合</t>
         </is>
       </c>
       <c r="F304" s="19" t="n"/>
@@ -23413,27 +23414,27 @@
     <row r="305" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t>伊内丝</t>
+          <t>隐现</t>
         </is>
       </c>
       <c r="B305" s="11" t="inlineStr">
         <is>
-          <t>12-12</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D305" s="13" t="inlineStr">
         <is>
-          <t>maa://50280 (97.47), maa://49642 (97.0), maa://49660 (90.32), *maa://50517 (80.0)</t>
+          <t>**maa://39172 (50.0)</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战伊内丝12次&gt; 3星通关主题曲12-12标准实战环境；必须编入非助战伊内丝并上场，且至少使用3次暗夜无明</t>
+          <t>&gt; 由非助战隐现累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战隐现并上场，且不编入其他狙击干员</t>
         </is>
       </c>
       <c r="F305" s="19" t="n"/>
@@ -23467,12 +23468,12 @@
     <row r="306" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>玫拉</t>
+          <t>空构</t>
         </is>
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>DM-2</t>
         </is>
       </c>
       <c r="C306" s="12" t="inlineStr">
@@ -23482,12 +23483,12 @@
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>maa://39171 (100.0)</t>
+          <t>maa://39173 (100.0)</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战玫拉并上场，且每次战斗至少释放1次临界爆发&gt; 3星通关主题曲S3-5；必须编入非助战玫拉并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 由非助战空构累计造成60000点伤害&gt; 3星通关插曲DM-2；必须编入非助战空构并上场，且至少使用1次临场铳械改装</t>
         </is>
       </c>
       <c r="F306" s="19" t="n"/>
@@ -23521,27 +23522,27 @@
     <row r="307" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>圣约送葬人</t>
         </is>
       </c>
       <c r="B307" s="11" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D307" s="13" t="inlineStr">
         <is>
-          <t>maa://27939 (100.0)</t>
+          <t>maa://25775 (93.18), *maa://25393 (73.33)</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战淬羽赫默累计使用无畏者协议8次&gt; 3星通关主题曲6-3；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战圣约送葬人累计造成80000点伤害&gt; 3星通关主题曲7-14；必须编入非助战圣约送葬人并上场，且使用圣约送葬人歼灭至少2名游击队盾卫</t>
         </is>
       </c>
       <c r="F307" s="19" t="n"/>
@@ -23575,12 +23576,12 @@
     <row r="308" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>寒檀</t>
         </is>
       </c>
       <c r="B308" s="11" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C308" s="12" t="inlineStr">
@@ -23590,12 +23591,12 @@
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>maa://53352 (100.0)</t>
+          <t>maa://40161 (100.0)</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战淬羽赫默并上场，且每次战斗至少释放1次无畏者协议&gt; 3星通关插曲WB-5；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战寒檀并上场，且每次战斗至少释放1次“女巫之泪”&gt; 3星通关别传BI-2；必须编入非助战寒檀并上场，且使用寒檀至少歼灭8个敌人</t>
         </is>
       </c>
       <c r="F308" s="19" t="n"/>
@@ -23629,12 +23630,12 @@
     <row r="309" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B309" s="11" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>S2-1</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
@@ -23644,12 +23645,12 @@
       </c>
       <c r="D309" s="13" t="inlineStr">
         <is>
-          <t>maa://29129 (100.0)</t>
+          <t>maa://25367 (99.31)</t>
         </is>
       </c>
       <c r="E309" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战霍尔海雅累计造成120000点伤害&gt; 3星通关别传OF-7；必须编入非助战霍尔海雅并上场，且至少使用2次博览者的狂语</t>
+          <t>&gt; 由非助战提丰累计造成120000点伤害&gt; 3星通关主题曲S2-1；必须编入非助战提丰并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
       <c r="F309" s="19" t="n"/>
@@ -23683,27 +23684,27 @@
     <row r="310" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B310" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C310" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>maa://36005 (93.33)</t>
+          <t>*maa://62761 (66.67), **maa://62755 (42.86)</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战霍尔海雅并上场，且每次战斗至少释放1次博览者的狂语&gt; 3星通关主题曲4-3；必须编入非助战霍尔海雅并上场，且使用霍尔海雅至少歼灭10个敌人</t>
+          <t>&gt; 由非助战提丰累计造成30歼灭数&gt; 3星通关主题曲4-8；必须编入非助战提丰并上场，且不编入其他狙击干员</t>
         </is>
       </c>
       <c r="F310" s="19" t="n"/>
@@ -23737,12 +23738,12 @@
     <row r="311" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>凛视</t>
         </is>
       </c>
       <c r="B311" s="11" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-13</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
@@ -23752,12 +23753,12 @@
       </c>
       <c r="D311" s="13" t="inlineStr">
         <is>
-          <t>maa://35859 (97.78)</t>
+          <t>*maa://43090 (57.14)</t>
         </is>
       </c>
       <c r="E311" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思，并确定第一位部署的干员是缪尔赛思&gt; 3星通关主题曲3-4；必须编入非助战缪尔赛思并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战凛视累计造成30次凋亡爆发&gt; 3星通关主题曲7-13；必须编入非助战凛视并上场，且凛视造成至少1次凋亡爆发</t>
         </is>
       </c>
       <c r="F311" s="19" t="n"/>
@@ -23791,12 +23792,12 @@
     <row r="312" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>苍苔</t>
         </is>
       </c>
       <c r="B312" s="11" t="inlineStr">
         <is>
-          <t>6-12</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C312" s="12" t="inlineStr">
@@ -23806,12 +23807,12 @@
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>maa://53348 (95.24)</t>
+          <t>maa://28070 (100.0)</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思并上场，且每次战斗至少释放1次生态耦合&gt; 3星通关主题曲6-12；必须编入非助战缪尔赛思并上场，且使用2次生态耦合</t>
+          <t>&gt; 完成5次战斗；必须编入非助战苍苔并上场，且每次战斗至少释放1次土石的恒心&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战苍苔并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F312" s="19" t="n"/>
@@ -23845,12 +23846,12 @@
     <row r="313" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A313" s="11" t="inlineStr">
         <is>
-          <t>隐现</t>
+          <t>青枳</t>
         </is>
       </c>
       <c r="B313" s="11" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
@@ -23860,12 +23861,12 @@
       </c>
       <c r="D313" s="13" t="inlineStr">
         <is>
-          <t>**maa://39172 (50.0)</t>
+          <t>maa://28241 (100.0)</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战隐现累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战隐现并上场，且不编入其他狙击干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战青枳，并确定第一位部署的干员是青枳&gt; 3星通关别传OF-5；必须编入非助战青枳并上场，且不编入其他先锋干员</t>
         </is>
       </c>
       <c r="F313" s="19" t="n"/>
@@ -23899,27 +23900,27 @@
     <row r="314" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A314" s="11" t="inlineStr">
         <is>
-          <t>空构</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B314" s="11" t="inlineStr">
         <is>
-          <t>DM-2</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C314" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>maa://39173 (100.0)</t>
+          <t>maa://25773 (100.0), *maa://26088 (71.43)</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战空构累计造成60000点伤害&gt; 3星通关插曲DM-2；必须编入非助战空构并上场，且至少使用1次临场铳械改装</t>
+          <t>&gt; 由非助战琳琅诗怀雅累计造成60000点伤害※香槟炸弹造成的伤害也会参与计数&gt; 3星通关主题曲5-2；必须编入非助战琳琅诗怀雅并上场，且使用琳琅诗怀雅至少歼灭15个敌人</t>
         </is>
       </c>
       <c r="F314" s="19" t="n"/>
@@ -23953,27 +23954,27 @@
     <row r="315" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t>圣约送葬人</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B315" s="11" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D315" s="13" t="inlineStr">
         <is>
-          <t>maa://25775 (93.18), *maa://25393 (73.33)</t>
+          <t>maa://39239 (100.0)</t>
         </is>
       </c>
       <c r="E315" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战圣约送葬人累计造成80000点伤害&gt; 3星通关主题曲7-14；必须编入非助战圣约送葬人并上场，且使用圣约送葬人歼灭至少2名游击队盾卫</t>
+          <t>&gt; 由非助战琳琅诗怀雅累计造成40歼灭数&gt; 3星通关主题曲11-16标准实战环境；必须编入非助战琳琅诗怀雅并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F315" s="19" t="n"/>
@@ -24007,27 +24008,27 @@
     <row r="316" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A316" s="11" t="inlineStr">
         <is>
-          <t>寒檀</t>
+          <t>纯烬艾雅法拉</t>
         </is>
       </c>
       <c r="B316" s="11" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>FC-5</t>
         </is>
       </c>
       <c r="C316" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>maa://40161 (100.0)</t>
+          <t>maa://39692 (99.63), maa://39810 (86.36)</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战寒檀并上场，且每次战斗至少释放1次“女巫之泪”&gt; 3星通关别传BI-2；必须编入非助战寒檀并上场，且使用寒檀至少歼灭8个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战纯烬艾雅法拉并上场，且每次战斗至少释放1次火山回响&gt; 3星通关别传FC-5；必须编入非助战纯烬艾雅法拉并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F316" s="19" t="n"/>
@@ -24061,12 +24062,12 @@
     <row r="317" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>冰酿</t>
         </is>
       </c>
       <c r="B317" s="11" t="inlineStr">
         <is>
-          <t>S2-1</t>
+          <t>S3-3</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
@@ -24076,12 +24077,12 @@
       </c>
       <c r="D317" s="13" t="inlineStr">
         <is>
-          <t>maa://25367 (99.31)</t>
+          <t>*maa://39174 (75.0)</t>
         </is>
       </c>
       <c r="E317" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战提丰累计造成120000点伤害&gt; 3星通关主题曲S2-1；必须编入非助战提丰并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 由非助战冰酿累计造成80000伤害&gt; 3星通关主题曲S3-3；必须编入非助战冰酿并上场，且使用冰酿至少歼灭8个敌人</t>
         </is>
       </c>
       <c r="F317" s="19" t="n"/>
@@ -24115,27 +24116,27 @@
     <row r="318" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="B318" s="11" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C318" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>maa://62761 (100.0), **maa://62755 (50.0)</t>
+          <t>maa://39175 (100.0)</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战提丰累计造成30歼灭数&gt; 3星通关主题曲4-8；必须编入非助战提丰并上场，且不编入其他狙击干员</t>
+          <t>&gt; 战斗中非助战杏仁累计使用强力牵引10次&gt; 3星通关别传BI-2；必须编入非助战杏仁并上场，且至少使用2次强力牵引</t>
         </is>
       </c>
       <c r="F318" s="19" t="n"/>
@@ -24169,27 +24170,27 @@
     <row r="319" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t>凛视</t>
+          <t>涤火杰西卡</t>
         </is>
       </c>
       <c r="B319" s="11" t="inlineStr">
         <is>
-          <t>7-13</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D319" s="13" t="inlineStr">
         <is>
-          <t>*maa://43090 (57.14)</t>
+          <t>maa://34867 (96.23), maa://34715 (100.0)</t>
         </is>
       </c>
       <c r="E319" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战凛视累计造成30次凋亡爆发&gt; 3星通关主题曲7-13；必须编入非助战凛视并上场，且凛视造成至少1次凋亡爆发</t>
+          <t>&gt; 由非助战涤火杰西卡累计造成30歼灭数&gt; 3星通关主题曲3-8；必须编入非助战涤火杰西卡并上场，且使用涤火杰西卡歼灭碎骨</t>
         </is>
       </c>
       <c r="F319" s="19" t="n"/>
@@ -24223,7 +24224,7 @@
     <row r="320" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>苍苔</t>
+          <t>维荻</t>
         </is>
       </c>
       <c r="B320" s="11" t="inlineStr">
@@ -24238,12 +24239,12 @@
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>maa://28070 (100.0)</t>
+          <t>maa://39176 (100.0)</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战苍苔并上场，且每次战斗至少释放1次土石的恒心&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战苍苔并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战维荻累计造成60000点伤害&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战维荻并上场，且至少使用2次双刃毒藤</t>
         </is>
       </c>
       <c r="F320" s="19" t="n"/>
@@ -24277,12 +24278,12 @@
     <row r="321" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t>青枳</t>
+          <t>戴菲恩</t>
         </is>
       </c>
       <c r="B321" s="11" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>WD-6</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
@@ -24292,12 +24293,12 @@
       </c>
       <c r="D321" s="13" t="inlineStr">
         <is>
-          <t>maa://28241 (100.0)</t>
+          <t>maa://42316 (88.89)</t>
         </is>
       </c>
       <c r="E321" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战青枳，并确定第一位部署的干员是青枳&gt; 3星通关别传OF-5；必须编入非助战青枳并上场，且不编入其他先锋干员</t>
+          <t>&gt; 由非助战戴菲恩累计造成30歼灭数&gt; 3星通关插曲WD-6；必须携带且部署非助战戴菲恩，且至少使用2次抢攻</t>
         </is>
       </c>
       <c r="F321" s="19" t="n"/>
@@ -24331,27 +24332,27 @@
     <row r="322" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>刺玫</t>
         </is>
       </c>
       <c r="B322" s="11" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>IC-2</t>
         </is>
       </c>
       <c r="C322" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>maa://25773 (100.0), *maa://26088 (71.43)</t>
+          <t>maa://30680 (100.0)</t>
         </is>
       </c>
       <c r="E322" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战琳琅诗怀雅累计造成60000点伤害※香槟炸弹造成的伤害也会参与计数&gt; 3星通关主题曲5-2；必须编入非助战琳琅诗怀雅并上场，且使用琳琅诗怀雅至少歼灭15个敌人</t>
+          <t>&gt; 战斗中非助战刺玫累计使用荆藤庇荫10次&gt; 3星通关别传IC-2；必须编入非助战刺玫并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F322" s="19" t="n"/>
@@ -24385,12 +24386,12 @@
     <row r="323" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>赫德雷</t>
         </is>
       </c>
       <c r="B323" s="11" t="inlineStr">
         <is>
-          <t>11-16</t>
+          <t>IW-7</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
@@ -24400,12 +24401,12 @@
       </c>
       <c r="D323" s="13" t="inlineStr">
         <is>
-          <t>maa://39239 (100.0)</t>
+          <t>maa://40956 (93.48)</t>
         </is>
       </c>
       <c r="E323" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战琳琅诗怀雅累计造成40歼灭数&gt; 3星通关主题曲11-16标准实战环境；必须编入非助战琳琅诗怀雅并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战赫德雷累计歼灭5个精英或领袖敌人&gt; 3星通关别传IW-7；必须编入非助战赫德雷并上场，并使用赫德雷至少击败2名沉沙</t>
         </is>
       </c>
       <c r="F323" s="19" t="n"/>
@@ -24439,27 +24440,27 @@
     <row r="324" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>纯烬艾雅法拉</t>
+          <t>深律</t>
         </is>
       </c>
       <c r="B324" s="11" t="inlineStr">
         <is>
-          <t>FC-5</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C324" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>maa://39692 (99.63), maa://39810 (86.36)</t>
+          <t>maa://59688 (100.0)</t>
         </is>
       </c>
       <c r="E324" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战纯烬艾雅法拉并上场，且每次战斗至少释放1次火山回响&gt; 3星通关别传FC-5；必须编入非助战纯烬艾雅法拉并上场，且不编入其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战深律并上场，且每次战斗至少释放1次沉音宁神&gt; 3星通关别传LE-4；必须编入非助战深律并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F324" s="19" t="n"/>
@@ -24493,27 +24494,27 @@
     <row r="325" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>冰酿</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B325" s="11" t="inlineStr">
         <is>
-          <t>S3-3</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D325" s="13" t="inlineStr">
         <is>
-          <t>*maa://39174 (75.0)</t>
+          <t>maa://34205 (90.0), *maa://39541 (75.0)</t>
         </is>
       </c>
       <c r="E325" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战冰酿累计造成80000伤害&gt; 3星通关主题曲S3-3；必须编入非助战冰酿并上场，且使用冰酿至少歼灭8个敌人</t>
+          <t>&gt; 由非助战止颂累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲7-11；必须编入非助战止颂并上场，且使用止颂歼灭至少2名雇佣军萨卡兹战士</t>
         </is>
       </c>
       <c r="F325" s="19" t="n"/>
@@ -24547,27 +24548,27 @@
     <row r="326" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B326" s="11" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>TW-5</t>
         </is>
       </c>
       <c r="C326" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>maa://39175 (100.0)</t>
+          <t>maa://43092 (100.0), maa://43093 (100.0)</t>
         </is>
       </c>
       <c r="E326" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战杏仁累计使用强力牵引10次&gt; 3星通关别传BI-2；必须编入非助战杏仁并上场，且至少使用2次强力牵引</t>
+          <t>&gt; 由非助战止颂累计造成120000点伤害&gt; 3星通关别传TW-5；必须编入非助战止颂并上场，且使用止颂击败至少6名敌人</t>
         </is>
       </c>
       <c r="F326" s="19" t="n"/>
@@ -24601,27 +24602,27 @@
     <row r="327" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>涤火杰西卡</t>
+          <t>薇薇安娜</t>
         </is>
       </c>
       <c r="B327" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>MN-3</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D327" s="13" t="inlineStr">
         <is>
-          <t>maa://34867 (96.23), maa://34715 (100.0)</t>
+          <t>maa://44234 (99.12)</t>
         </is>
       </c>
       <c r="E327" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战涤火杰西卡累计造成30歼灭数&gt; 3星通关主题曲3-8；必须编入非助战涤火杰西卡并上场，且使用涤火杰西卡歼灭碎骨</t>
+          <t>&gt; 由非助战薇薇安娜累计歼灭10个精英或领袖敌人&gt; 3星通关别传MN-3；必须编入非助战薇薇安娜并上场，且使用薇薇安娜歼灭“锈铜”奥尔默·英格拉</t>
         </is>
       </c>
       <c r="F327" s="19" t="n"/>
@@ -24655,27 +24656,27 @@
     <row r="328" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>维荻</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B328" s="11" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>GA-7</t>
         </is>
       </c>
       <c r="C328" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D328" s="13" t="inlineStr">
         <is>
-          <t>maa://39176 (100.0)</t>
+          <t>maa://42968 (99.1), maa://49245 (100.0)</t>
         </is>
       </c>
       <c r="E328" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维荻累计造成60000点伤害&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战维荻并上场，且至少使用2次双刃毒藤</t>
+          <t>&gt; 由非助战塑心累计造成75000点凋亡损伤&gt; 3星通关别传GA-7；必须编入非助战塑心并上场，且塑心造成至少15000点凋亡损伤</t>
         </is>
       </c>
       <c r="F328" s="19" t="n"/>
@@ -24709,12 +24710,12 @@
     <row r="329" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>戴菲恩</t>
+          <t>哈洛德</t>
         </is>
       </c>
       <c r="B329" s="11" t="inlineStr">
         <is>
-          <t>WD-6</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
@@ -24724,12 +24725,12 @@
       </c>
       <c r="D329" s="13" t="inlineStr">
         <is>
-          <t>maa://42316 (88.89)</t>
+          <t>*maa://40162 (71.43)</t>
         </is>
       </c>
       <c r="E329" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战戴菲恩累计造成30歼灭数&gt; 3星通关插曲WD-6；必须携带且部署非助战戴菲恩，且至少使用2次抢攻</t>
+          <t>&gt; 战斗中非助战哈洛德累计使用重症优先8次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战哈洛德并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F329" s="19" t="n"/>
@@ -24763,12 +24764,12 @@
     <row r="330" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>刺玫</t>
+          <t>烈夏</t>
         </is>
       </c>
       <c r="B330" s="11" t="inlineStr">
         <is>
-          <t>IC-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C330" s="12" t="inlineStr">
@@ -24778,12 +24779,12 @@
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>maa://30680 (100.0)</t>
+          <t>maa://37692 (100.0)</t>
         </is>
       </c>
       <c r="E330" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战刺玫累计使用荆藤庇荫10次&gt; 3星通关别传IC-2；必须编入非助战刺玫并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战烈夏累计造成30歼灭数&gt; 3星通关主题曲4-3；必须编入非助战烈夏并上场，且不编入其他近卫干员</t>
         </is>
       </c>
       <c r="F330" s="19" t="n"/>
@@ -24817,27 +24818,27 @@
     <row r="331" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A331" s="12" t="inlineStr">
         <is>
-          <t>赫德雷</t>
+          <t>莱伊</t>
         </is>
       </c>
       <c r="B331" s="11" t="inlineStr">
         <is>
-          <t>IW-7</t>
+          <t>S9-1</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D331" s="15" t="inlineStr">
         <is>
-          <t>maa://40956 (93.41)</t>
+          <t>maa://38295 (94.9), maa://49332 (100.0)</t>
         </is>
       </c>
       <c r="E331" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战赫德雷累计歼灭5个精英或领袖敌人&gt; 3星通关别传IW-7；必须编入非助战赫德雷并上场，并使用赫德雷至少击败2名沉沙</t>
+          <t>&gt; 由非助战莱伊累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲S9-1标准实战环境；必须编入非助战莱伊并上场，且使用莱伊使用至少2次“得见光芒”</t>
         </is>
       </c>
       <c r="F331" s="19" t="n"/>
@@ -24871,12 +24872,12 @@
     <row r="332" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A332" s="12" t="inlineStr">
         <is>
-          <t>深律</t>
+          <t>万顷</t>
         </is>
       </c>
       <c r="B332" s="11" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C332" s="12" t="inlineStr">
@@ -24886,12 +24887,12 @@
       </c>
       <c r="D332" s="15" t="inlineStr">
         <is>
-          <t>maa://59688 (100.0)</t>
+          <t>maa://32417 (100.0)</t>
         </is>
       </c>
       <c r="E332" s="15" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战深律并上场，且每次战斗至少释放1次沉音宁神&gt; 3星通关别传LE-4；必须编入非助战深律并上场，且所有干员不被击倒</t>
+          <t>&gt; 战斗中非助战万顷累计使用支援号令·γ型10次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战万顷并上场，且至少使用2次应东风</t>
         </is>
       </c>
       <c r="F332" s="19" t="n"/>
@@ -24925,27 +24926,27 @@
     <row r="333" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A333" s="12" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>小满</t>
         </is>
       </c>
       <c r="B333" s="11" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>9-11</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D333" s="15" t="inlineStr">
         <is>
-          <t>maa://34205 (90.0), *maa://39541 (75.0)</t>
+          <t>maa://32419 (100.0)</t>
         </is>
       </c>
       <c r="E333" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战止颂累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲7-11；必须编入非助战止颂并上场，且使用止颂歼灭至少2名雇佣军萨卡兹战士</t>
+          <t>&gt; 由非助战小满累计造成60000点伤害&gt; 3星通关主题曲9-11标准实战环境；必须编入非助战小满并上场，且至少使用2次乡音沉沉</t>
         </is>
       </c>
       <c r="F333" s="19" t="n"/>
@@ -24979,27 +24980,27 @@
     <row r="334" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A334" s="12" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B334" s="11" t="inlineStr">
         <is>
-          <t>TW-5</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C334" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D334" s="15" t="inlineStr">
         <is>
-          <t>maa://43092 (100.0), maa://43093 (100.0)</t>
+          <t>maa://32416 (91.8)</t>
         </is>
       </c>
       <c r="E334" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战止颂累计造成120000点伤害&gt; 3星通关别传TW-5；必须编入非助战止颂并上场，且使用止颂击败至少6名敌人</t>
+          <t>&gt; 由非助战左乐累计造成40歼灭数&gt; 3星通关别传WB-5；必须编入非助战左乐并上场，且使用左乐至少歼灭8个敌人</t>
         </is>
       </c>
       <c r="F334" s="19" t="n"/>
@@ -25033,12 +25034,12 @@
     <row r="335" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A335" s="12" t="inlineStr">
         <is>
-          <t>薇薇安娜</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B335" s="11" t="inlineStr">
         <is>
-          <t>MN-3</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C335" s="12" t="inlineStr">
@@ -25048,12 +25049,12 @@
       </c>
       <c r="D335" s="15" t="inlineStr">
         <is>
-          <t>maa://44234 (99.12)</t>
+          <t>maa://45800 (100.0)</t>
         </is>
       </c>
       <c r="E335" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战薇薇安娜累计歼灭10个精英或领袖敌人&gt; 3星通关别传MN-3；必须编入非助战薇薇安娜并上场，且使用薇薇安娜歼灭“锈铜”奥尔默·英格拉</t>
+          <t>&gt; 使用非助战左乐累计造成100000点伤害&gt; 3星通关别传RI-7；必须携带且部署非助战左乐，且至少释放3次佑序有炎</t>
         </is>
       </c>
       <c r="F335" s="19" t="n"/>
@@ -25087,27 +25088,27 @@
     <row r="336" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A336" s="12" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>黍</t>
         </is>
       </c>
       <c r="B336" s="11" t="inlineStr">
         <is>
-          <t>GA-7</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="C336" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D336" s="15" t="inlineStr">
         <is>
-          <t>maa://42968 (99.09), maa://49245 (100.0)</t>
+          <t>maa://32647 (97.89), maa://32415 (96.79), maa://34677 (100.0), maa://32892 (100.0), maa://32653 (85.71), maa://61839 (100.0)</t>
         </is>
       </c>
       <c r="E336" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战塑心累计造成75000点凋亡损伤&gt; 3星通关别传GA-7；必须编入非助战塑心并上场，且塑心造成至少15000点凋亡损伤</t>
+          <t>&gt; 完成5次战斗；必须编入非助战黍并上场，且每次战斗至少释放1次离离枯荣&gt; 3星通关主题曲11-11标准实战环境；必须编入非助战黍并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F336" s="19" t="n"/>
@@ -25141,12 +25142,12 @@
     <row r="337" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A337" s="12" t="inlineStr">
         <is>
-          <t>哈洛德</t>
+          <t>红隼</t>
         </is>
       </c>
       <c r="B337" s="11" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>11-18</t>
         </is>
       </c>
       <c r="C337" s="12" t="inlineStr">
@@ -25156,12 +25157,12 @@
       </c>
       <c r="D337" s="15" t="inlineStr">
         <is>
-          <t>*maa://40162 (71.43)</t>
+          <t>maa://32420 (100.0)</t>
         </is>
       </c>
       <c r="E337" s="15" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战哈洛德累计使用重症优先8次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战哈洛德并上场，且所有干员不被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战红隼并上场，且每次战斗至少释放2次醉刃乱舞&gt; 3星通关主题曲11-18标准实战环境；必须编入非助战红隼，且第一位部署红隼、红隼全程不撤退或被击倒</t>
         </is>
       </c>
       <c r="F337" s="19" t="n"/>
@@ -25195,12 +25196,12 @@
     <row r="338" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A338" s="12" t="inlineStr">
         <is>
-          <t>烈夏</t>
+          <t>导火索</t>
         </is>
       </c>
       <c r="B338" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C338" s="12" t="inlineStr">
@@ -25210,12 +25211,12 @@
       </c>
       <c r="D338" s="22" t="inlineStr">
         <is>
-          <t>maa://37692 (100.0)</t>
+          <t>maa://35606 (100.0)</t>
         </is>
       </c>
       <c r="E338" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战烈夏累计造成30歼灭数&gt; 3星通关主题曲4-3；必须编入非助战烈夏并上场，且不编入其他近卫干员</t>
+          <t>&gt; 由非助战导火索累计造成80000点伤害&gt; 3星通关主题曲3-1；必须编入非助战导火索并上场，且使用导火索至少歼灭30个敌人</t>
         </is>
       </c>
       <c r="F338" s="19" t="n"/>
@@ -25249,27 +25250,27 @@
     <row r="339" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A339" s="12" t="inlineStr">
         <is>
-          <t>锏</t>
+          <t>双月</t>
         </is>
       </c>
       <c r="B339" s="11" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D339" s="22" t="inlineStr">
         <is>
-          <t>maa://30671 (81.44), maa://30669 (99.24), maa://37275 (82.93), *maa://32410 (66.67), maa://41605 (100.0)</t>
+          <t>maa://34716 (87.5)</t>
         </is>
       </c>
       <c r="E339" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战锏并上场，且每次战斗至少释放1次归于宁静&gt; 3星通关别传BI-6；必须编入非助战锏并上场，且使用锏至少歼灭10个敌人</t>
+          <t>&gt; 战斗中非助战双月累计使用全知者的战术10次&gt; 3星通关主题曲3-7；必须编入非助战双月并上场，且至少使用2次全知者的战术</t>
         </is>
       </c>
       <c r="F339" s="19" t="n"/>
@@ -25303,27 +25304,27 @@
     <row r="340" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A340" s="12" t="inlineStr">
         <is>
-          <t>莱伊</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="B340" s="11" t="inlineStr">
         <is>
-          <t>S9-1</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D340" s="22" t="inlineStr">
         <is>
-          <t>maa://38295 (94.9), maa://49332 (100.0)</t>
+          <t>maa://39179 (100.0)</t>
         </is>
       </c>
       <c r="E340" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战莱伊累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲S9-1标准实战环境；必须编入非助战莱伊并上场，且使用莱伊使用至少2次“得见光芒”</t>
+          <t>&gt; 战斗中非助战医生累计使用激素手枪8次&gt; 3星通关主题曲2-5；必须编入非助战医生并上场，且不编入医疗干员</t>
         </is>
       </c>
       <c r="F340" s="19" t="n"/>
@@ -25357,27 +25358,27 @@
     <row r="341" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A341" s="12" t="inlineStr">
         <is>
-          <t>万顷</t>
+          <t>艾拉</t>
         </is>
       </c>
       <c r="B341" s="11" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D341" s="22" t="inlineStr">
         <is>
-          <t>maa://32417 (100.0)</t>
+          <t>maa://34865 (97.87), maa://34717 (94.12), *maa://45066 (71.43)</t>
         </is>
       </c>
       <c r="E341" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战万顷累计使用支援号令·γ型10次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战万顷并上场，且至少使用2次应东风</t>
+          <t>&gt; 战斗中非助战艾拉累计部署雷鸣地雷30个&gt; 3星通关插曲DM-EX-1；必须编入非助战艾拉并上场，且使用艾拉歼灭至少2名萨卡兹穿刺手</t>
         </is>
       </c>
       <c r="F341" s="19" t="n"/>
@@ -25411,12 +25412,12 @@
     <row r="342" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A342" s="12" t="inlineStr">
         <is>
-          <t>小满</t>
+          <t>露托</t>
         </is>
       </c>
       <c r="B342" s="11" t="inlineStr">
         <is>
-          <t>9-11</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C342" s="12" t="inlineStr">
@@ -25426,12 +25427,12 @@
       </c>
       <c r="D342" s="22" t="inlineStr">
         <is>
-          <t>maa://32419 (100.0)</t>
+          <t>maa://39180 (100.0)</t>
         </is>
       </c>
       <c r="E342" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战小满累计造成60000点伤害&gt; 3星通关主题曲9-11标准实战环境；必须编入非助战小满并上场，且至少使用2次乡音沉沉</t>
+          <t>&gt; 战斗中非助战露托累计使用强磁防卫8次&gt; 3星通关主题曲3-1；必须编入非助战露托并上场，且不编入其他重装干员</t>
         </is>
       </c>
       <c r="F342" s="19" t="n"/>
@@ -25465,27 +25466,27 @@
     <row r="343" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A343" s="12" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>奥达</t>
         </is>
       </c>
       <c r="B343" s="11" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C343" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D343" s="22" t="inlineStr">
         <is>
-          <t>maa://32416 (91.67)</t>
+          <t>maa://45834 (100.0), maa://45833 (100.0)</t>
         </is>
       </c>
       <c r="E343" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战左乐累计造成40歼灭数&gt; 3星通关别传WB-5；必须编入非助战左乐并上场，且使用左乐至少歼灭8个敌人</t>
+          <t>&gt; 使用非助战奥达累计使用4次锻锤之力&gt; 3星通关主题曲S3-6；必须携带且部署非助战奥达，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F343" s="19" t="n"/>
@@ -25519,12 +25520,12 @@
     <row r="344" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A344" s="12" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>阿罗玛</t>
         </is>
       </c>
       <c r="B344" s="11" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>GT-HX-3</t>
         </is>
       </c>
       <c r="C344" s="12" t="inlineStr">
@@ -25534,12 +25535,12 @@
       </c>
       <c r="D344" s="22" t="inlineStr">
         <is>
-          <t>maa://45800 (100.0)</t>
+          <t>maa://39181 (88.89)</t>
         </is>
       </c>
       <c r="E344" s="22" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战左乐累计造成100000点伤害&gt; 3星通关别传RI-7；必须携带且部署非助战左乐，且至少释放3次佑序有炎</t>
+          <t>&gt; 完成5次战斗；必须编入非助战阿罗玛并上场，且每次战斗至少释放1次小心地滑&gt; 3星通关别传GT-HX-3；必须编入非助战阿罗玛并上场，且使用阿罗玛至少歼灭20个敌人</t>
         </is>
       </c>
       <c r="F344" s="19" t="n"/>
@@ -25573,27 +25574,27 @@
     <row r="345" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A345" s="12" t="inlineStr">
         <is>
-          <t>黍</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B345" s="11" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D345" s="22" t="inlineStr">
         <is>
-          <t>maa://32647 (97.89), maa://32415 (96.79), maa://34677 (100.0), maa://32892 (100.0), maa://32653 (85.71), maa://61839 (100.0)</t>
+          <t>maa://36868 (99.72), maa://35996 (97.73), **maa://39217 (41.18), maa://47349 (95.24)</t>
         </is>
       </c>
       <c r="E345" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战黍并上场，且每次战斗至少释放1次离离枯荣&gt; 3星通关主题曲11-11标准实战环境；必须编入非助战黍并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战阿斯卡纶累计造成180000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战阿斯卡纶并上场，且使用阿斯卡纶至少歼灭30个敌人</t>
         </is>
       </c>
       <c r="F345" s="19" t="n"/>
@@ -25627,27 +25628,27 @@
     <row r="346" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A346" s="12" t="inlineStr">
         <is>
-          <t>红隼</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B346" s="11" t="inlineStr">
         <is>
-          <t>11-18</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C346" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D346" s="22" t="inlineStr">
         <is>
-          <t>maa://32420 (100.0)</t>
+          <t>maa://49696 (99.56), maa://49695 (100.0), maa://49758 (98.48), *maa://59402 (58.33), *maa://52357 (71.43)</t>
         </is>
       </c>
       <c r="E346" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战红隼并上场，且每次战斗至少释放2次醉刃乱舞&gt; 3星通关主题曲11-18标准实战环境；必须编入非助战红隼，且第一位部署红隼、红隼全程不撤退或被击倒</t>
+          <t>&gt; 战斗中非助战阿斯卡纶累计使用“降临”5次&gt; 3星通关主题曲5-10，必须编入非助战阿斯卡纶并上场，其他成员不可编入特种干员</t>
         </is>
       </c>
       <c r="F346" s="19" t="n"/>
@@ -25681,12 +25682,12 @@
     <row r="347" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A347" s="12" t="inlineStr">
         <is>
-          <t>导火索</t>
+          <t>历阵锐枪芬</t>
         </is>
       </c>
       <c r="B347" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C347" s="12" t="inlineStr">
@@ -25696,12 +25697,12 @@
       </c>
       <c r="D347" s="22" t="inlineStr">
         <is>
-          <t>maa://35606 (100.0)</t>
+          <t>maa://36647 (100.0)</t>
         </is>
       </c>
       <c r="E347" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战导火索累计造成80000点伤害&gt; 3星通关主题曲3-1；必须编入非助战导火索并上场，且使用导火索至少歼灭30个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战历阵锐枪芬，并确定第一位部署的干员是历阵锐枪芬&gt; 3星通关主题曲4-2；必须编入非助战历阵锐枪芬并上场，且不编入其他先锋干员</t>
         </is>
       </c>
       <c r="F347" s="19" t="n"/>
@@ -25735,27 +25736,27 @@
     <row r="348" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A348" s="12" t="inlineStr">
         <is>
-          <t>双月</t>
+          <t>魔王</t>
         </is>
       </c>
       <c r="B348" s="11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C348" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D348" s="22" t="inlineStr">
         <is>
-          <t>maa://34716 (87.5)</t>
+          <t>maa://42299 (97.67), maa://42224 (82.35)</t>
         </is>
       </c>
       <c r="E348" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战双月累计使用全知者的战术10次&gt; 3星通关主题曲3-7；必须编入非助战双月并上场，且至少使用2次全知者的战术</t>
+          <t>&gt; 携带非助战魔王完成5次战斗，且每次战斗至少发动一次“编织重构现世”&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战魔王并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
       <c r="F348" s="19" t="n"/>
@@ -25789,27 +25790,27 @@
     <row r="349" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A349" s="12" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B349" s="11" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="C349" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D349" s="22" t="inlineStr">
         <is>
-          <t>maa://39179 (100.0)</t>
+          <t>maa://49648 (95.83), *maa://49662 (76.47)</t>
         </is>
       </c>
       <c r="E349" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战医生累计使用激素手枪8次&gt; 3星通关主题曲2-5；必须编入非助战医生并上场，且不编入医疗干员</t>
+          <t>&gt; 由非助战逻各斯累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲14-9标准实战环境；必须编入非助战逻各斯并上场，且使用逻各斯至少歼灭7个敌人</t>
         </is>
       </c>
       <c r="F349" s="19" t="n"/>
@@ -25843,27 +25844,27 @@
     <row r="350" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A350" s="12" t="inlineStr">
         <is>
-          <t>艾拉</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B350" s="11" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C350" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D350" s="22" t="inlineStr">
         <is>
-          <t>maa://34865 (97.86), maa://34717 (94.12), *maa://45066 (71.43)</t>
+          <t>maa://36646 (98.8), maa://36845 (95.71), **maa://39217 (41.18), maa://51007 (98.21)</t>
         </is>
       </c>
       <c r="E350" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战艾拉累计部署雷鸣地雷30个&gt; 3星通关插曲DM-EX-1；必须编入非助战艾拉并上场，且使用艾拉歼灭至少2名萨卡兹穿刺手</t>
+          <t>&gt; 由非助战逻各斯累计造成100000点伤害&gt; 3星通关主题曲11-6标准实战环境，必须编入非助战逻各斯并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F350" s="19" t="n"/>
@@ -25897,27 +25898,27 @@
     <row r="351" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A351" s="12" t="inlineStr">
         <is>
-          <t>露托</t>
+          <t>维什戴尔</t>
         </is>
       </c>
       <c r="B351" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D351" s="22" t="inlineStr">
         <is>
-          <t>maa://39180 (100.0)</t>
+          <t>maa://36645 (98.39), maa://36841 (92.65), maa://37484 (94.23), maa://37858 (93.55), *maa://56268 (60.0), maa://40489 (100.0)</t>
         </is>
       </c>
       <c r="E351" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战露托累计使用强磁防卫8次&gt; 3星通关主题曲3-1；必须编入非助战露托并上场，且不编入其他重装干员</t>
+          <t>&gt; 由非助战维什戴尔累计造成120000伤害&gt; 3星通关插曲DM-5；必须编入非助战维什戴尔并上场，且使用维什戴尔至少歼灭20个敌人</t>
         </is>
       </c>
       <c r="F351" s="19" t="n"/>
@@ -25951,27 +25952,27 @@
     <row r="352" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A352" s="12" t="inlineStr">
         <is>
-          <t>奥达</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B352" s="11" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C352" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D352" s="22" t="inlineStr">
         <is>
-          <t>maa://45834 (100.0), maa://45833 (100.0)</t>
+          <t>maa://42635 (95.65), maa://50629 (100.0), maa://48859 (100.0)</t>
         </is>
       </c>
       <c r="E352" s="22" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战奥达累计使用4次锻锤之力&gt; 3星通关主题曲S3-6；必须携带且部署非助战奥达，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战医疗职业的阿米娅累计使用慈悲愿景5次&gt; 3星通关主题曲3-8；必须编入非助战医疗职业的阿米娅并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F352" s="19" t="n"/>
@@ -26005,12 +26006,12 @@
     <row r="353" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A353" s="12" t="inlineStr">
         <is>
-          <t>阿罗玛</t>
+          <t>深巡</t>
         </is>
       </c>
       <c r="B353" s="11" t="inlineStr">
         <is>
-          <t>GT-HX-3</t>
+          <t>SN-5</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
@@ -26020,12 +26021,12 @@
       </c>
       <c r="D353" s="22" t="inlineStr">
         <is>
-          <t>maa://39181 (88.89)</t>
+          <t>maa://39183 (100.0)</t>
         </is>
       </c>
       <c r="E353" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战阿罗玛并上场，且每次战斗至少释放1次小心地滑&gt; 3星通关别传GT-HX-3；必须编入非助战阿罗玛并上场，且使用阿罗玛至少歼灭20个敌人</t>
+          <t>&gt; 战斗中非助战深巡累计使用行动能力剥夺8次&gt; 3星通关插曲SN-5，必须编入非助战深巡并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F353" s="19" t="n"/>
@@ -26059,27 +26060,27 @@
     <row r="354" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A354" s="12" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>海霓</t>
         </is>
       </c>
       <c r="B354" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C354" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D354" s="22" t="inlineStr">
         <is>
-          <t>maa://36868 (99.72), maa://35996 (97.73), **maa://39217 (41.18), maa://47349 (95.12)</t>
+          <t>maa://39184 (100.0)</t>
         </is>
       </c>
       <c r="E354" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战阿斯卡纶累计造成180000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战阿斯卡纶并上场，且使用阿斯卡纶至少歼灭30个敌人</t>
+          <t>&gt; 战斗中非助战海霓累计使用阻滞性显色剂8次&gt; 3星通关插曲SV-4；必须编入非助战海霓并上场，且不编入其他辅助干员</t>
         </is>
       </c>
       <c r="F354" s="19" t="n"/>
@@ -26113,27 +26114,27 @@
     <row r="355" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A355" s="12" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>乌尔比安</t>
         </is>
       </c>
       <c r="B355" s="11" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C355" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D355" s="22" t="inlineStr">
         <is>
-          <t>maa://49696 (99.56), maa://49695 (100.0), maa://49758 (98.48), *maa://59402 (58.33), *maa://52357 (71.43)</t>
+          <t>maa://40957 (94.23), maa://44635 (88.07), maa://48026 (93.81), maa://41035 (93.15), maa://44660 (92.5), maa://41128 (84.21), *maa://60251 (66.67)</t>
         </is>
       </c>
       <c r="E355" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战阿斯卡纶累计使用“降临”5次&gt; 3星通关主题曲5-10，必须编入非助战阿斯卡纶并上场，其他成员不可编入特种干员</t>
+          <t>&gt; 战斗中非助战乌尔比安累计使用必须开辟的通路10次&gt; 3星通关插曲SV-6；必须编入非助战乌尔比安并上场，并使用乌尔比安至少击败2名囊海爬行者</t>
         </is>
       </c>
       <c r="F355" s="19" t="n"/>
@@ -26167,12 +26168,12 @@
     <row r="356" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A356" s="12" t="inlineStr">
         <is>
-          <t>历阵锐枪芬</t>
+          <t>渡桥</t>
         </is>
       </c>
       <c r="B356" s="11" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C356" s="12" t="inlineStr">
@@ -26182,12 +26183,12 @@
       </c>
       <c r="D356" s="22" t="inlineStr">
         <is>
-          <t>maa://36647 (100.0)</t>
+          <t>maa://40164 (100.0)</t>
         </is>
       </c>
       <c r="E356" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战历阵锐枪芬，并确定第一位部署的干员是历阵锐枪芬&gt; 3星通关主题曲4-2；必须编入非助战历阵锐枪芬并上场，且不编入其他先锋干员</t>
+          <t>&gt; 战斗中非助战渡桥累计使用承压功率8次&gt; 3星通关主题曲3-1；必须编入非助战渡桥并上场，且至少使用3次承压功率</t>
         </is>
       </c>
       <c r="F356" s="19" t="n"/>
@@ -26221,27 +26222,27 @@
     <row r="357" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A357" s="12" t="inlineStr">
         <is>
-          <t>魔王</t>
+          <t>锡人</t>
         </is>
       </c>
       <c r="B357" s="11" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C357" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D357" s="22" t="inlineStr">
         <is>
-          <t>maa://42299 (97.67), maa://42224 (82.35)</t>
+          <t>maa://48268 (91.67)</t>
         </is>
       </c>
       <c r="E357" s="22" t="inlineStr">
         <is>
-          <t>&gt; 携带非助战魔王完成5次战斗，且每次战斗至少发动一次“编织重构现世”&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战魔王并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 战斗中非助战锡人累计使用8次“大拉里”&gt; 3星通关主题曲4-3，必须编入非助战锡人并上场，且队伍中不能有其他医疗干员</t>
         </is>
       </c>
       <c r="F357" s="19" t="n"/>
@@ -26275,27 +26276,27 @@
     <row r="358" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A358" s="12" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>衡沙</t>
         </is>
       </c>
       <c r="B358" s="11" t="inlineStr">
         <is>
-          <t>14-9</t>
+          <t>DV-2</t>
         </is>
       </c>
       <c r="C358" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D358" s="22" t="inlineStr">
         <is>
-          <t>maa://49648 (95.83), *maa://49662 (76.47)</t>
+          <t>maa://40165 (100.0)</t>
         </is>
       </c>
       <c r="E358" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战逻各斯累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲14-9标准实战环境；必须编入非助战逻各斯并上场，且使用逻各斯至少歼灭7个敌人</t>
+          <t>&gt; 战斗中累计召唤非助战衡沙的召唤物20回&gt; 3星通关别传DV-2；必须编入非助战衡沙并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F358" s="19" t="n"/>
@@ -26329,27 +26330,27 @@
     <row r="359" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A359" s="12" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B359" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D359" s="22" t="inlineStr">
         <is>
-          <t>maa://36646 (98.8), maa://36845 (95.71), **maa://39217 (41.18), maa://51007 (98.21)</t>
+          <t>maa://45798 (98.48)</t>
         </is>
       </c>
       <c r="E359" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战逻各斯累计造成100000点伤害&gt; 3星通关主题曲11-6标准实战环境，必须编入非助战逻各斯并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战佩佩累计造成40歼灭数&gt; 3星通关主题曲3-8；必须编入非助战佩佩并上场，且使用佩佩歼灭碎骨</t>
         </is>
       </c>
       <c r="F359" s="19" t="n"/>
@@ -26383,27 +26384,27 @@
     <row r="360" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A360" s="12" t="inlineStr">
         <is>
-          <t>维什戴尔</t>
+          <t>森西</t>
         </is>
       </c>
       <c r="B360" s="11" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C360" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D360" s="22" t="inlineStr">
         <is>
-          <t>maa://36645 (98.38), maa://36841 (92.65), maa://37484 (94.23), maa://37858 (93.55), *maa://56268 (60.0), maa://40489 (100.0)</t>
+          <t>maa://42331 (100.0)</t>
         </is>
       </c>
       <c r="E360" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维什戴尔累计造成120000伤害&gt; 3星通关插曲DM-5；必须编入非助战维什戴尔并上场，且使用维什戴尔至少歼灭20个敌人</t>
+          <t>&gt; 战斗中非助战森西累计使用团体魔物大餐6次&gt; 3星通关主题曲1-12；必须编入非助战森西并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F360" s="19" t="n"/>
@@ -26437,12 +26438,12 @@
     <row r="361" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A361" s="12" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>齐尔查克</t>
         </is>
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C361" s="12" t="inlineStr">
@@ -26452,12 +26453,12 @@
       </c>
       <c r="D361" s="22" t="inlineStr">
         <is>
-          <t>maa://42635 (95.65), maa://50629 (100.0), maa://48859 (100.0)</t>
+          <t>maa://42333 (100.0), maa://50518 (100.0), maa://41977 (100.0)</t>
         </is>
       </c>
       <c r="E361" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战医疗职业的阿米娅累计使用慈悲愿景5次&gt; 3星通关主题曲3-8；必须编入非助战医疗职业的阿米娅并上场，且不编入其他医疗干员</t>
+          <t>&gt; 战斗中非助战齐尔查克累计使用随机应变6次&gt; 3星通关主题曲4-3；必须编入非助战齐尔查克并上场，其他成员不可编入先锋干员</t>
         </is>
       </c>
       <c r="F361" s="19" t="n"/>
@@ -26491,27 +26492,27 @@
     <row r="362" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A362" s="12" t="inlineStr">
         <is>
-          <t>深巡</t>
+          <t>莱欧斯</t>
         </is>
       </c>
       <c r="B362" s="11" t="inlineStr">
         <is>
-          <t>SN-5</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C362" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D362" s="22" t="inlineStr">
         <is>
-          <t>maa://39183 (100.0)</t>
+          <t>maa://42338 (100.0), maa://41976 (100.0)</t>
         </is>
       </c>
       <c r="E362" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战深巡累计使用行动能力剥夺8次&gt; 3星通关插曲SN-5，必须编入非助战深巡并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战莱欧斯并上场，且每次战斗至少释放1次威吓战法&gt; 3星通关主题曲2-4；必须编入非助战莱欧斯并上场，并使用莱欧斯至少击败1名高阶术师</t>
         </is>
       </c>
       <c r="F362" s="19" t="n"/>
@@ -26545,27 +26546,27 @@
     <row r="363" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A363" s="12" t="inlineStr">
         <is>
-          <t>海霓</t>
+          <t>玛露西尔</t>
         </is>
       </c>
       <c r="B363" s="11" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D363" s="22" t="inlineStr">
         <is>
-          <t>maa://39184 (100.0)</t>
+          <t>maa://41110 (98.4), maa://45605 (100.0)</t>
         </is>
       </c>
       <c r="E363" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战海霓累计使用阻滞性显色剂8次&gt; 3星通关插曲SV-4；必须编入非助战海霓并上场，且不编入其他辅助干员</t>
+          <t>&gt; 由非助战玛露西尔累计造成100000点伤害&gt; 3星通关主题曲5-10；必须编入非助战玛露西尔并上场，且使用玛露西尔至少歼灭10名敌人</t>
         </is>
       </c>
       <c r="F363" s="19" t="n"/>
@@ -26599,27 +26600,27 @@
     <row r="364" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A364" s="12" t="inlineStr">
         <is>
-          <t>乌尔比安</t>
+          <t>凯瑟琳</t>
         </is>
       </c>
       <c r="B364" s="11" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C364" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D364" s="22" t="inlineStr">
         <is>
-          <t>maa://40957 (94.22), maa://44635 (88.07), maa://48026 (93.75), maa://41035 (93.06), maa://44660 (92.31), maa://41128 (84.21), *maa://60251 (66.67)</t>
+          <t>maa://42343 (100.0)</t>
         </is>
       </c>
       <c r="E364" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战乌尔比安累计使用必须开辟的通路10次&gt; 3星通关插曲SV-6；必须编入非助战乌尔比安并上场，并使用乌尔比安至少击败2名囊海爬行者</t>
+          <t>&gt; 使用非助战凯瑟琳累计部署15个“支援装置”&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战凯瑟琳并上场，且凯瑟琳使用至少2次“战火淬炼”</t>
         </is>
       </c>
       <c r="F364" s="19" t="n"/>
@@ -26653,12 +26654,12 @@
     <row r="365" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A365" s="12" t="inlineStr">
         <is>
-          <t>渡桥</t>
+          <t>波卜</t>
         </is>
       </c>
       <c r="B365" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C365" s="12" t="inlineStr">
@@ -26668,12 +26669,12 @@
       </c>
       <c r="D365" s="22" t="inlineStr">
         <is>
-          <t>maa://40164 (100.0)</t>
+          <t>maa://43095 (100.0)</t>
         </is>
       </c>
       <c r="E365" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战渡桥累计使用承压功率8次&gt; 3星通关主题曲3-1；必须编入非助战渡桥并上场，且至少使用3次承压功率</t>
+          <t>&gt; 由非助战波卜累计造成30次灼燃爆发&gt; 3星通关主题曲4-8；必须编入非助战波卜并上场，且波卜使用至少2次“此路不通”</t>
         </is>
       </c>
       <c r="F365" s="19" t="n"/>
@@ -26707,27 +26708,27 @@
     <row r="366" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A366" s="12" t="inlineStr">
         <is>
-          <t>锡人</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B366" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C366" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D366" s="22" t="inlineStr">
         <is>
-          <t>maa://48268 (91.67)</t>
+          <t>maa://44233 (91.07), maa://45570 (96.43)</t>
         </is>
       </c>
       <c r="E366" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战锡人累计使用8次“大拉里”&gt; 3星通关主题曲4-3，必须编入非助战锡人并上场，且队伍中不能有其他医疗干员</t>
+          <t>&gt; 由非助战维娜·维多利亚累计造成120000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战维娜·维多利亚并上场，其他成员仅可编入5名干员</t>
         </is>
       </c>
       <c r="F366" s="19" t="n"/>
@@ -26761,12 +26762,12 @@
     <row r="367" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A367" s="12" t="inlineStr">
         <is>
-          <t>衡沙</t>
+          <t>裁度</t>
         </is>
       </c>
       <c r="B367" s="11" t="inlineStr">
         <is>
-          <t>DV-2</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C367" s="12" t="inlineStr">
@@ -26776,12 +26777,12 @@
       </c>
       <c r="D367" s="22" t="inlineStr">
         <is>
-          <t>maa://40165 (100.0)</t>
+          <t>maa://43097 (87.5)</t>
         </is>
       </c>
       <c r="E367" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计召唤非助战衡沙的召唤物20回&gt; 3星通关别传DV-2；必须编入非助战衡沙并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战裁度并部署至少2次，且使用裁度击败至少4名敌人&gt; 3星通关主题曲5-8；必须编入非助战裁度并上场，且至少束缚12次敌人</t>
         </is>
       </c>
       <c r="F367" s="19" t="n"/>
@@ -26815,12 +26816,12 @@
     <row r="368" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A368" s="12" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>忍冬</t>
         </is>
       </c>
       <c r="B368" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C368" s="12" t="inlineStr">
@@ -26830,12 +26831,12 @@
       </c>
       <c r="D368" s="22" t="inlineStr">
         <is>
-          <t>maa://45798 (98.48)</t>
+          <t>maa://43875 (98.21)</t>
         </is>
       </c>
       <c r="E368" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战佩佩累计造成40歼灭数&gt; 3星通关主题曲3-8；必须编入非助战佩佩并上场，且使用佩佩歼灭碎骨</t>
+          <t>&gt; 由非助战忍冬累计造成80000点伤害&gt; 3星通关主题曲S2-3；必须编入非助战忍冬并上场，且使用忍冬击败至少24名敌人</t>
         </is>
       </c>
       <c r="F368" s="19" t="n"/>
@@ -26869,27 +26870,27 @@
     <row r="369" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A369" s="12" t="inlineStr">
         <is>
-          <t>森西</t>
+          <t>荒芜拉普兰德</t>
         </is>
       </c>
       <c r="B369" s="11" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>IS-8</t>
         </is>
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D369" s="22" t="inlineStr">
         <is>
-          <t>maa://42331 (100.0)</t>
+          <t>maa://42970 (82.71), maa://44745 (97.39), **maa://49516 (34.78), *maa://45952 (72.73), ***maa://46851 (14.29), *maa://44896 (77.78)</t>
         </is>
       </c>
       <c r="E369" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战森西累计使用团体魔物大餐6次&gt; 3星通关主题曲1-12；必须编入非助战森西并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战荒芜拉普兰德累计造成150000点伤害&gt; 3星通关别传IS-8；必须编入非助战荒芜拉普兰德并上场，且荒芜拉普兰德使用至少2次逐猎狂飙或终幕·浩劫</t>
         </is>
       </c>
       <c r="F369" s="19" t="n"/>
@@ -26923,27 +26924,27 @@
     <row r="370" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A370" s="12" t="inlineStr">
         <is>
-          <t>齐尔查克</t>
+          <t>瑰盐</t>
         </is>
       </c>
       <c r="B370" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C370" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D370" s="22" t="inlineStr">
         <is>
-          <t>maa://42333 (100.0), maa://50518 (100.0), maa://41977 (100.0)</t>
+          <t>maa://44389 (100.0)</t>
         </is>
       </c>
       <c r="E370" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战齐尔查克累计使用随机应变6次&gt; 3星通关主题曲4-3；必须编入非助战齐尔查克并上场，其他成员不可编入先锋干员</t>
+          <t>&gt; 战斗中非助战瑰盐累计使用绝妙的长效药呀8次&gt; 3星通关主题曲4-6；必须编入非助战瑰盐并上场，且至少使用1次绝妙的长效药呀</t>
         </is>
       </c>
       <c r="F370" s="19" t="n"/>
@@ -26977,27 +26978,27 @@
     <row r="371" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A371" s="12" t="inlineStr">
         <is>
-          <t>莱欧斯</t>
+          <t>特克诺</t>
         </is>
       </c>
       <c r="B371" s="11" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C371" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D371" s="22" t="inlineStr">
         <is>
-          <t>maa://42338 (100.0), maa://41976 (100.0)</t>
+          <t>maa://59690 (100.0)</t>
         </is>
       </c>
       <c r="E371" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战莱欧斯并上场，且每次战斗至少释放1次威吓战法&gt; 3星通关主题曲2-4；必须编入非助战莱欧斯并上场，并使用莱欧斯至少击败1名高阶术师</t>
+          <t>&gt; 完成5次战斗；必须编入非助战特克诺并上场，且每次战斗至少释放1次“恣意挥洒”&gt; 3星通关插曲DH-6，必须编入非助战特克诺并上场，其他成员仅可编入7名干员</t>
         </is>
       </c>
       <c r="F371" s="19" t="n"/>
@@ -27031,27 +27032,27 @@
     <row r="372" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A372" s="12" t="inlineStr">
         <is>
-          <t>玛露西尔</t>
+          <t>引星棘刺</t>
         </is>
       </c>
       <c r="B372" s="11" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C372" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D372" s="22" t="inlineStr">
         <is>
-          <t>maa://41110 (98.4), maa://45605 (100.0)</t>
+          <t>maa://48113 (100.0)</t>
         </is>
       </c>
       <c r="E372" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战玛露西尔累计造成100000点伤害&gt; 3星通关主题曲5-10；必须编入非助战玛露西尔并上场，且使用玛露西尔至少歼灭10名敌人</t>
+          <t>&gt; 战斗中非助战引星棘刺累计使用20次解构涌潮&gt; 3星通关别传OF-7；必须编入非助战引星棘刺并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F372" s="19" t="n"/>
@@ -27085,12 +27086,12 @@
     <row r="373" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A373" s="12" t="inlineStr">
         <is>
-          <t>凯瑟琳</t>
+          <t>行箸</t>
         </is>
       </c>
       <c r="B373" s="11" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C373" s="12" t="inlineStr">
@@ -27100,12 +27101,12 @@
       </c>
       <c r="D373" s="22" t="inlineStr">
         <is>
-          <t>maa://42343 (100.0)</t>
+          <t>maa://45807 (100.0)</t>
         </is>
       </c>
       <c r="E373" s="22" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战凯瑟琳累计部署15个“支援装置”&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战凯瑟琳并上场，且凯瑟琳使用至少2次“战火淬炼”</t>
+          <t>&gt; 使用非助战行箸累计使用8次食不厌精&gt; 3星通关主题曲3-2；必须编入非助战行箸并上场，且所有干员不能被击倒</t>
         </is>
       </c>
       <c r="F373" s="19" t="n"/>
@@ -27139,12 +27140,12 @@
     <row r="374" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A374" s="12" t="inlineStr">
         <is>
-          <t>波卜</t>
+          <t>寻澜</t>
         </is>
       </c>
       <c r="B374" s="11" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C374" s="12" t="inlineStr">
@@ -27154,12 +27155,12 @@
       </c>
       <c r="D374" s="22" t="inlineStr">
         <is>
-          <t>maa://43095 (100.0)</t>
+          <t>maa://50552 (100.0)</t>
         </is>
       </c>
       <c r="E374" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战波卜累计造成30次灼燃爆发&gt; 3星通关主题曲4-8；必须编入非助战波卜并上场，且波卜使用至少2次“此路不通”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战寻澜并上场，且使用寻澜歼灭至少3个敌人&gt; 3星通关主题曲3-5；必须编入非助战寻澜并上场，且至少使用2次洞悉</t>
         </is>
       </c>
       <c r="F374" s="19" t="n"/>
@@ -27193,12 +27194,12 @@
     <row r="375" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A375" s="12" t="inlineStr">
         <is>
-          <t>维娜·维多利亚</t>
+          <t>诺威尔</t>
         </is>
       </c>
       <c r="B375" s="11" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="C375" s="12" t="inlineStr">
@@ -27208,12 +27209,12 @@
       </c>
       <c r="D375" s="22" t="inlineStr">
         <is>
-          <t>maa://44233 (91.07), maa://45570 (96.43)</t>
+          <t>*maa://47175 (66.67), maa://47174 (100.0)</t>
         </is>
       </c>
       <c r="E375" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维娜·维多利亚累计造成120000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战维娜·维多利亚并上场，其他成员仅可编入5名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战诺威尔并上场，且每次战斗至少释放1次生命不息&gt; 3星通关主题曲5-7；必须编入非助战诺威尔并上场，且队伍中不能有其他医疗干员</t>
         </is>
       </c>
       <c r="F375" s="19" t="n"/>
@@ -27247,12 +27248,12 @@
     <row r="376" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A376" s="12" t="inlineStr">
         <is>
-          <t>裁度</t>
+          <t>隐德来希</t>
         </is>
       </c>
       <c r="B376" s="11" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C376" s="12" t="inlineStr">
@@ -27262,12 +27263,12 @@
       </c>
       <c r="D376" s="22" t="inlineStr">
         <is>
-          <t>maa://43097 (87.5)</t>
+          <t>maa://47023 (88.24)</t>
         </is>
       </c>
       <c r="E376" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战裁度并部署至少2次，且使用裁度击败至少4名敌人&gt; 3星通关主题曲5-8；必须编入非助战裁度并上场，且至少束缚12次敌人</t>
+          <t>&gt; 使用非助战隐德来希累计造成100000点伤害&gt; 3星通关主题曲10-12标准实战环境；必须编入非助战隐德来希并上场，且隐德来希至少使用3次灵与欲的惜别</t>
         </is>
       </c>
       <c r="F376" s="19" t="n"/>
@@ -27301,12 +27302,12 @@
     <row r="377" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A377" s="12" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>钼铅</t>
         </is>
       </c>
       <c r="B377" s="11" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C377" s="12" t="inlineStr">
@@ -27316,12 +27317,12 @@
       </c>
       <c r="D377" s="22" t="inlineStr">
         <is>
-          <t>maa://43872 (91.67)</t>
+          <t>**maa://48618 (50.0)</t>
         </is>
       </c>
       <c r="E377" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战弑君者&gt; 3星通关主题曲4-4；必须编入非助战弑君者并上场，且不编入其他特种干员</t>
+          <t>&gt; 战斗中非助战钼铅累计部署矿石“杀手”30个&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战钼铅并上场，且使用钼铅至少击败1名深池重甲卫士</t>
         </is>
       </c>
       <c r="F377" s="19" t="n"/>
@@ -27355,7 +27356,7 @@
     <row r="378" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A378" s="12" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>死芒</t>
         </is>
       </c>
       <c r="B378" s="11" t="inlineStr">
@@ -27365,17 +27366,17 @@
       </c>
       <c r="C378" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D378" s="22" t="inlineStr">
         <is>
-          <t>*maa://53307 (61.11)</t>
+          <t>maa://59533 (100.0), maa://59577 (100.0)</t>
         </is>
       </c>
       <c r="E378" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战弑君者累计使用8次烽烟行刑场&gt; 3星通关主题曲4-8；必须编入非助战弑君者并上场，且使用2次烽烟行刑场</t>
+          <t>&gt; 完成5次战斗；必须编入非助战死芒并上场，且每次战斗至少释放2次“冠死以冕”&gt; 3星通关主题曲4-8，必须编入非助战死芒并上场，其他成员仅可编入辅助干员</t>
         </is>
       </c>
       <c r="F378" s="19" t="n"/>
@@ -27409,27 +27410,27 @@
     <row r="379" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A379" s="12" t="inlineStr">
         <is>
-          <t>忍冬</t>
+          <t>骋风</t>
         </is>
       </c>
       <c r="B379" s="11" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C379" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D379" s="22" t="inlineStr">
         <is>
-          <t>maa://43875 (98.21)</t>
+          <t>maa://51907 (100.0), maa://51908 (100.0)</t>
         </is>
       </c>
       <c r="E379" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战忍冬累计造成80000点伤害&gt; 3星通关主题曲S2-3；必须编入非助战忍冬并上场，且使用忍冬击败至少24名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战骋风并上场，且每次战斗至少释放1次招无虚发&gt; 3星通关插曲SN-2；必须编入非助战骋风并上场，且使用2次招无虚发</t>
         </is>
       </c>
       <c r="F379" s="19" t="n"/>
@@ -27463,27 +27464,27 @@
     <row r="380" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A380" s="12" t="inlineStr">
         <is>
-          <t>荒芜拉普兰德</t>
+          <t>阿兰娜</t>
         </is>
       </c>
       <c r="B380" s="11" t="inlineStr">
         <is>
-          <t>IS-8</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C380" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D380" s="22" t="inlineStr">
         <is>
-          <t>maa://42970 (82.71), maa://44745 (97.39), **maa://49516 (34.78), *maa://45952 (72.73), ***maa://46851 (14.29), *maa://44896 (77.78)</t>
+          <t>**maa://59691 (50.0)</t>
         </is>
       </c>
       <c r="E380" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战荒芜拉普兰德累计造成150000点伤害&gt; 3星通关别传IS-8；必须编入非助战荒芜拉普兰德并上场，且荒芜拉普兰德使用至少2次逐猎狂飙或终幕·浩劫</t>
+          <t>&gt; 使用非助战阿兰娜累计部署15个“支援装置”&gt; 3星通关主题曲7-14；必须编入非助战阿兰娜并上场，且至少使用2次“万斤顶”</t>
         </is>
       </c>
       <c r="F380" s="19" t="n"/>
@@ -27517,27 +27518,27 @@
     <row r="381" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A381" s="12" t="inlineStr">
         <is>
-          <t>瑰盐</t>
+          <t>信仰搅拌机</t>
         </is>
       </c>
       <c r="B381" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C381" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D381" s="22" t="inlineStr">
         <is>
-          <t>maa://44389 (100.0)</t>
+          <t>maa://51898 (100.0), maa://57241 (100.0)</t>
         </is>
       </c>
       <c r="E381" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战瑰盐累计使用绝妙的长效药呀8次&gt; 3星通关主题曲4-6；必须编入非助战瑰盐并上场，且至少使用1次绝妙的长效药呀</t>
+          <t>&gt; 完成5次战斗；必须编入非助战信仰搅拌机并上场，且每次战斗至少释放1次退休前布道&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战信仰搅拌机并上场，且使用信仰搅拌机歼灭至少10名敌人</t>
         </is>
       </c>
       <c r="F381" s="19" t="n"/>
@@ -27571,27 +27572,27 @@
     <row r="382" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A382" s="12" t="inlineStr">
         <is>
-          <t>特克诺</t>
+          <t>蕾缪安</t>
         </is>
       </c>
       <c r="B382" s="11" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>13-13</t>
         </is>
       </c>
       <c r="C382" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D382" s="22" t="inlineStr">
         <is>
-          <t>maa://59690 (100.0)</t>
+          <t>maa://51880 (99.15), maa://56651 (100.0), maa://51878 (100.0)</t>
         </is>
       </c>
       <c r="E382" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战特克诺并上场，且每次战斗至少释放1次“恣意挥洒”&gt; 3星通关插曲DH-6，必须编入非助战特克诺并上场，其他成员仅可编入7名干员</t>
+          <t>&gt; 由非助战蕾缪安累计造成30歼灭数&gt; 3星通关主题曲13-13标准实战环境；必须编入非助战蕾缪安并上场，且蕾缪安歼灭至少2个萨卡兹骸骨鞭笞者</t>
         </is>
       </c>
       <c r="F382" s="19" t="n"/>
@@ -27625,27 +27626,27 @@
     <row r="383" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A383" s="12" t="inlineStr">
         <is>
-          <t>引星棘刺</t>
+          <t>新约能天使</t>
         </is>
       </c>
       <c r="B383" s="11" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>GA-EX-5</t>
         </is>
       </c>
       <c r="C383" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D383" s="22" t="inlineStr">
         <is>
-          <t>maa://48113 (100.0)</t>
+          <t>maa://51872 (96.49), maa://51876 (98.94), maa://51873 (100.0), maa://62047 (92.86), maa://63228 (100.0)</t>
         </is>
       </c>
       <c r="E383" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战引星棘刺累计使用20次解构涌潮&gt; 3星通关别传OF-7；必须编入非助战引星棘刺并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战新约能天使累计使用开火成瘾症8次&gt; 3星通关插曲GA-EX-5；必须编入非助战新约能天使并上场，且使用2次开火成瘾症</t>
         </is>
       </c>
       <c r="F383" s="19" t="n"/>
@@ -27679,27 +27680,27 @@
     <row r="384" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A384" s="12" t="inlineStr">
         <is>
-          <t>行箸</t>
+          <t>酒神</t>
         </is>
       </c>
       <c r="B384" s="11" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C384" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D384" s="22" t="inlineStr">
         <is>
-          <t>maa://45807 (100.0)</t>
+          <t>maa://59493 (96.75), maa://60449 (98.72)</t>
         </is>
       </c>
       <c r="E384" s="22" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战行箸累计使用8次食不厌精&gt; 3星通关主题曲3-2；必须编入非助战行箸并上场，且所有干员不能被击倒</t>
+          <t>&gt; 使用非助战酒神累计造成60000点神经损伤&gt; 3星通关主题曲9-6标准实战环境，必须编入非助战酒神并上场，且酒神使用至少2次“空剧场”</t>
         </is>
       </c>
       <c r="F384" s="19" t="n"/>
@@ -27731,29 +27732,29 @@
       <c r="AF384" s="8" t="n"/>
     </row>
     <row r="385" ht="13.5" customFormat="1" customHeight="1" s="22">
-      <c r="A385" s="12" t="inlineStr">
-        <is>
-          <t>寻澜</t>
-        </is>
-      </c>
-      <c r="B385" s="11" t="inlineStr">
-        <is>
-          <t>3-5</t>
-        </is>
-      </c>
-      <c r="C385" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D385" s="22" t="inlineStr">
-        <is>
-          <t>maa://50552 (100.0)</t>
-        </is>
-      </c>
-      <c r="E385" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 完成5次战斗；必须编入非助战寻澜并上场，且使用寻澜歼灭至少3个敌人&gt; 3星通关主题曲3-5；必须编入非助战寻澜并上场，且至少使用2次洞悉</t>
+      <c r="A385" s="25" t="inlineStr">
+        <is>
+          <t>录武官</t>
+        </is>
+      </c>
+      <c r="B385" s="24" t="inlineStr">
+        <is>
+          <t>HS-5</t>
+        </is>
+      </c>
+      <c r="C385" s="25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D385" s="30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E385" s="30" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战录武官累计使用“一点关窍”6次&gt; 3星通关插曲HS-5，必须编入非助战录武官并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F385" s="19" t="n"/>
@@ -27787,27 +27788,27 @@
     <row r="386" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A386" s="12" t="inlineStr">
         <is>
-          <t>诺威尔</t>
+          <t>司霆惊蛰</t>
         </is>
       </c>
       <c r="B386" s="11" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>DV-7</t>
         </is>
       </c>
       <c r="C386" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D386" s="22" t="inlineStr">
         <is>
-          <t>*maa://47175 (66.67), maa://47174 (100.0)</t>
+          <t>maa://62756 (93.83)</t>
         </is>
       </c>
       <c r="E386" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战诺威尔并上场，且每次战斗至少释放1次生命不息&gt; 3星通关主题曲5-7；必须编入非助战诺威尔并上场，且队伍中不能有其他医疗干员</t>
+          <t>&gt; 由非助战司霆惊蛰累计造成120000点伤害&gt; 3星通关插曲DV-7；必须编入非助战司霆惊蛰并上场，且使用1次“天地通明”</t>
         </is>
       </c>
       <c r="F386" s="19" t="n"/>

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>maa://25390 (100.00), maa://24702 (98.92), maa://36681 (83.87)</t>
+          <t>maa://25390 (100.00), maa://24702 (98.92), maa://36681 (81.72)</t>
         </is>
       </c>
       <c r="E2" s="19" t="n"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>maa://39402 (100.00), *maa://34787 (73.03), maa://58660 (83.15)</t>
+          <t>maa://39402 (100.00), *maa://34787 (73.03), maa://58660 (87.64)</t>
         </is>
       </c>
       <c r="M2" s="19" t="n"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>maa://25251 (100.00), maa://59087 (91.86)</t>
+          <t>maa://25251 (100.00), maa://59087 (93.02)</t>
         </is>
       </c>
       <c r="AG2" s="16" t="n"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>*maa://22880 (72.29), maa://20276 (100.00), *maa://22749 (69.88)</t>
+          <t>*maa://22880 (72.62), maa://20276 (100.00), *maa://22749 (71.43)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="X3" s="8" t="inlineStr">
         <is>
-          <t>maa://27396 (86.96), maa://27484 (100.00), *maa://27480 (78.26)</t>
+          <t>maa://27396 (86.02), maa://27484 (100.00), *maa://27480 (77.42)</t>
         </is>
       </c>
       <c r="Y3" s="19" t="n"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="AB3" s="8" t="inlineStr">
         <is>
-          <t>maa://24390 (100.00), maa://52241 (81.11)</t>
+          <t>maa://24390 (100.00), maa://52241 (82.22)</t>
         </is>
       </c>
       <c r="AC3" s="19" t="n"/>
@@ -1476,7 +1476,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.30 14:18:05</t>
+          <t>更新日期：2025.08.02 13:27:24</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="X9" s="8" t="inlineStr">
         <is>
-          <t>maa://26223 (100.00), maa://52237 (84.21)</t>
+          <t>maa://26223 (100.00), maa://52237 (85.26)</t>
         </is>
       </c>
       <c r="Y9" s="19" t="n"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>***maa://25695 (28.00), ***maa://39951 (12.00), ***maa://34206 (22.00), maa://45271 (100.00), ***maa://39243 (14.00), ***maa://54000 (30.00)</t>
+          <t>***maa://25695 (28.00), ***maa://39951 (14.00), ***maa://34206 (22.00), maa://45271 (100.00), ***maa://39243 (14.00), ***maa://54000 (30.00)</t>
         </is>
       </c>
       <c r="E10" s="19" t="n"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (100.00), maa://22755 (87.23), **maa://63521 (36.17)</t>
+          <t>maa://27395 (100.00), maa://22755 (87.23), **maa://63521 (46.81)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AF10" s="8" t="inlineStr">
         <is>
-          <t>maa://25021 (82.69), maa://22733 (100.00), ***maa://22761 (17.31)</t>
+          <t>maa://25021 (86.00), maa://22733 (100.00), ***maa://22761 (18.00)</t>
         </is>
       </c>
       <c r="AG10" s="16" t="n"/>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>maa://22747 (89.36), maa://22501 (100.00), maa://45521 (85.11)</t>
+          <t>maa://22747 (89.36), maa://22501 (100.00), maa://45521 (86.17)</t>
         </is>
       </c>
       <c r="U11" s="19" t="n"/>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M12" s="19" t="n"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>maa://22753 (100.00), maa://37962 (94.32), *maa://21485 (78.41)</t>
+          <t>maa://22753 (100.00), maa://37962 (95.45), *maa://21485 (78.41)</t>
         </is>
       </c>
       <c r="Y12" s="19" t="n"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>maa://22521 (100.00), maa://42751 (90.00)</t>
+          <t>maa://22521 (100.00), maa://42751 (91.11)</t>
         </is>
       </c>
       <c r="U14" s="19" t="n"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>maa://28501 (100.00), maa://28051 (84.21)</t>
+          <t>maa://28501 (100.00), maa://28051 (85.26)</t>
         </is>
       </c>
       <c r="Y16" s="19" t="n"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>maa://22466 (100.00), maa://52226 (94.32)</t>
+          <t>maa://22466 (100.00), maa://52226 (95.45)</t>
         </is>
       </c>
       <c r="M18" s="19" t="n"/>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
-          <t>maa://30709 (100.00), *maa://36668 (72.31)</t>
+          <t>maa://30709 (100.00), *maa://36668 (73.85)</t>
         </is>
       </c>
       <c r="AC19" s="19" t="n"/>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>maa://21432 (96.63), maa://25198 (100.00), maa://36680 (86.52)</t>
+          <t>maa://21432 (97.75), maa://25198 (100.00), maa://36680 (86.52)</t>
         </is>
       </c>
       <c r="E20" s="19" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://50085 (100.00), maa://49976 (95.24), *maa://56241 (71.43)</t>
+          <t>maa://50085 (100.00), maa://49976 (94.12), *maa://56241 (70.59)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>maa://21282 (100.00), *maa://37649 (59.38)</t>
+          <t>maa://21282 (100.00), *maa://37649 (61.46)</t>
         </is>
       </c>
       <c r="Y22" s="19" t="n"/>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>maa://29988 (89.01), maa://23504 (100.00), *maa://25141 (76.92), *maa://36663 (75.82), maa://52227 (87.91)</t>
+          <t>maa://29988 (89.01), maa://23504 (100.00), *maa://25141 (76.92), *maa://36663 (75.82), maa://52227 (89.01)</t>
         </is>
       </c>
       <c r="Y24" s="19" t="n"/>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AF24" s="8" t="inlineStr">
         <is>
-          <t>maa://22523 (89.41), *maa://36672 (70.59), maa://29910 (100.00), maa://45831 (82.35)</t>
+          <t>maa://22523 (88.24), *maa://36672 (69.41), maa://29910 (100.00), maa://45831 (84.71)</t>
         </is>
       </c>
       <c r="AG24" s="16" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>maa://29063 (98.48), maa://25311 (100.00), ***maa://22725 (3.03), *maa://45047 (72.73)</t>
+          <t>maa://29063 (96.97), maa://25311 (100.00), ***maa://22725 (3.03), *maa://45047 (72.73)</t>
         </is>
       </c>
       <c r="I25" s="19" t="n"/>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AF29" s="8" t="inlineStr">
         <is>
-          <t>maa://24080 (90.28), maa://42865 (100.00)</t>
+          <t>maa://24080 (89.04), maa://42865 (100.00)</t>
         </is>
       </c>
       <c r="AG29" s="16" t="n"/>
@@ -4686,12 +4686,12 @@
       </c>
       <c r="W32" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Y32" s="19" t="n"/>
@@ -5092,12 +5092,12 @@
       </c>
       <c r="AA35" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC35" s="19" t="n"/>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="AA36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB36" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC36" s="19" t="n"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>maa://45718 (100.00), *maa://47069 (62.89), *maa://56336 (61.86), *maa://45789 (67.01)</t>
+          <t>maa://45718 (100.00), *maa://47069 (62.89), *maa://56336 (56.70), *maa://45789 (67.01)</t>
         </is>
       </c>
       <c r="M37" s="19" t="n"/>
@@ -5522,12 +5522,12 @@
       </c>
       <c r="S39" s="19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>maa://47079 (100.00), *maa://45788 (73.81), *maa://45790 (77.38)</t>
+          <t>maa://47079 (100.00), *maa://45790 (78.57)</t>
         </is>
       </c>
       <c r="U39" s="19" t="n"/>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>maa://23278 (100.00), maa://21386 (98.92), maa://36664 (83.87), *maa://45550 (56.99)</t>
+          <t>maa://23278 (100.00), maa://21386 (98.92), maa://36664 (84.95), *maa://45550 (56.99)</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="AE40" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>maa://29768 (100.00), maa://27728 (95.79), *maa://56386 (64.21)</t>
+          <t>maa://29768 (100.00), maa://27728 (95.79), *maa://56386 (68.42)</t>
         </is>
       </c>
       <c r="I44" s="19" t="n"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>maa://21229 (91.86), maa://30807 (100.00), maa://42459 (87.21)</t>
+          <t>maa://21229 (91.86), maa://30807 (100.00), maa://42459 (88.37)</t>
         </is>
       </c>
       <c r="I45" s="19" t="n"/>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>maa://25176 (100.00), *maa://56237 (61.29)</t>
+          <t>maa://25176 (100.00), *maa://56237 (69.89)</t>
         </is>
       </c>
       <c r="I57" s="19" t="n"/>
@@ -7013,7 +7013,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.30 14:18:05</t>
+          <t>更新日期：2025.08.02 13:27:24</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>maa://20876 (100.00)</t>
+          <t>maa://20876 (100.00), ***maa://63498 (24.42)</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>*maa://20849 (70.37), *maa://28758 (64.20), maa://29036 (100.00), *maa://42172 (51.85), maa://30285 (83.95)</t>
+          <t>*maa://20849 (70.37), *maa://28758 (65.43), maa://29036 (100.00), *maa://42172 (54.32), maa://30285 (83.95)</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>maa://20993 (100.00), maa://45606 (89.47), **maa://20914 (46.32), maa://20829 (81.05), maa://20900 (85.26), **maa://40159 (46.32)</t>
+          <t>maa://20993 (100.00), maa://45606 (90.53), **maa://20914 (46.32), maa://20829 (81.05), maa://20900 (85.26), **maa://40159 (46.32)</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>maa://20944 (94.51), maa://35393 (100.00)</t>
+          <t>maa://20944 (93.48), maa://35393 (100.00)</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>maa://24472 (100.00), **maa://35841 (49.40)</t>
+          <t>maa://24472 (100.00), **maa://35841 (48.81)</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>maa://20991 (100.00), *maa://51015 (72.16)</t>
+          <t>maa://20991 (100.00), *maa://51015 (73.20)</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>maa://25018 (96.94), maa://51881 (100.00), maa://25776 (85.71), maa://28361 (85.71), maa://25772 (85.71), *maa://56588 (78.57), *maa://45194 (60.20), *maa://25161 (60.20), *maa://32653 (61.22), ***maa://60902 (7.14), ***maa://61275 (21.43), **maa://61839 (34.69)</t>
+          <t>maa://51881 (100.00), maa://25018 (96.94), maa://25776 (85.71), maa://28361 (85.71), maa://25772 (85.71), *maa://56588 (78.57), *maa://45194 (60.20), *maa://32653 (63.27), *maa://25161 (60.20), ***maa://60902 (7.14), **maa://61275 (34.69), **maa://61839 (34.69)</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>maa://29650 (100.00), maa://45570 (96.70)</t>
+          <t>maa://29650 (100.00), maa://45570 (95.65)</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>maa://49867 (96.43), maa://49655 (100.00)</t>
+          <t>maa://49867 (94.05), maa://49655 (100.00)</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>maa://20905 (100.00), **maa://52268 (36.21)</t>
+          <t>maa://20905 (100.00), **maa://52268 (38.18)</t>
         </is>
       </c>
       <c r="E173" s="14" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>maa://32418 (100.00), maa://51440 (88.89), *maa://63320 (51.52)</t>
+          <t>maa://32418 (100.00), maa://51440 (88.89), *maa://63320 (61.62)</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>maa://44224 (92.55), maa://35854 (82.98), maa://50388 (100.00), maa://25760 (85.11), ***maa://43911 (4.26), **maa://20872 (35.11), *maa://51066 (69.15), *maa://63024 (76.60)</t>
+          <t>maa://44224 (92.55), maa://35854 (82.98), maa://50388 (100.00), maa://25760 (85.11), ***maa://43911 (4.26), **maa://20872 (35.11), *maa://51066 (69.15), *maa://63024 (78.72)</t>
         </is>
       </c>
       <c r="E197" s="14" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>maa://28133 (100.00), ***maa://39217 (26.19), maa://25369 (98.81)</t>
+          <t>maa://28133 (100.00), ***maa://39217 (26.19), maa://25369 (100.00)</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>maa://30667 (94.94), maa://30666 (98.73), **maa://30739 (36.71), *maa://30723 (55.70), maa://39588 (100.00)</t>
+          <t>maa://30667 (96.15), maa://30666 (100.00), **maa://30739 (37.18), *maa://30723 (56.41), maa://39588 (98.72)</t>
         </is>
       </c>
       <c r="E240" s="14" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>maa://20923 (100.00), **maa://60577 (38.96)</t>
+          <t>maa://20923 (100.00), **maa://60577 (38.46)</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>maa://45799 (100.00), maa://57199 (89.36)</t>
+          <t>maa://45799 (100.00), maa://57199 (90.43)</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="D305" s="13" t="inlineStr">
         <is>
-          <t>maa://50280 (100.00), maa://49642 (96.84), *maa://49660 (80.00), **maa://50517 (40.00)</t>
+          <t>maa://50280 (100.00), maa://49642 (96.84), maa://49660 (81.05), **maa://50517 (40.00)</t>
         </is>
       </c>
       <c r="E305" s="14" t="inlineStr">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>maa://62761 (100.00), **maa://62755 (38.78)</t>
+          <t>**maa://62755 (50.00), maa://62761 (100.00)</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -25265,7 +25265,7 @@
       </c>
       <c r="D339" s="22" t="inlineStr">
         <is>
-          <t>*maa://30671 (78.12), maa://30669 (100.00), *maa://37275 (71.88), **maa://32410 (40.63), *maa://41605 (67.71)</t>
+          <t>*maa://30671 (78.12), maa://30669 (100.00), *maa://37275 (71.88), **maa://32410 (37.50), *maa://41605 (67.71)</t>
         </is>
       </c>
       <c r="E339" s="22" t="inlineStr">
@@ -25589,7 +25589,7 @@
       </c>
       <c r="D345" s="22" t="inlineStr">
         <is>
-          <t>maa://32647 (100.00), maa://32415 (96.88), maa://34677 (96.88), maa://32892 (88.54), *maa://32653 (62.50), ***maa://61275 (21.88), **maa://61839 (35.42)</t>
+          <t>maa://32647 (100.00), maa://32415 (95.88), maa://34677 (95.88), maa://32892 (87.63), *maa://32653 (63.92), **maa://61275 (35.05), **maa://61839 (35.05)</t>
         </is>
       </c>
       <c r="E345" s="22" t="inlineStr">
@@ -26075,7 +26075,7 @@
       </c>
       <c r="D354" s="22" t="inlineStr">
         <is>
-          <t>maa://36868 (100.00), maa://35996 (93.88), ***maa://39217 (22.45), maa://47349 (87.76)</t>
+          <t>maa://36868 (100.00), maa://35996 (93.88), ***maa://39217 (22.45), maa://47349 (88.78)</t>
         </is>
       </c>
       <c r="E354" s="22" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="D358" s="22" t="inlineStr">
         <is>
-          <t>maa://49648 (100.00), *maa://49662 (60.92)</t>
+          <t>maa://49648 (100.00), *maa://49662 (63.22)</t>
         </is>
       </c>
       <c r="E358" s="22" t="inlineStr">
@@ -27965,7 +27965,7 @@
       </c>
       <c r="D389" s="22" t="inlineStr">
         <is>
-          <t>maa://59533 (100.00), *maa://59577 (78.16)</t>
+          <t>maa://59533 (100.00), *maa://59577 (77.27)</t>
         </is>
       </c>
       <c r="E389" s="22" t="inlineStr">
@@ -28208,7 +28208,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://51872 (100.00), maa://51876 (100.00), maa://51873 (97.87), *maa://63228 (73.40), *maa://62047 (76.60)</t>
+          <t>maa://51872 (100.00), maa://51876 (100.00), maa://51873 (97.87), *maa://63228 (76.60), *maa://62047 (70.21)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>maa://40192 (100.00), maa://36987 (94.57), *maa://39849 (60.87)</t>
+          <t>maa://40192 (100.00), maa://36987 (96.70), *maa://39849 (61.54)</t>
         </is>
       </c>
       <c r="E3" s="19" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>*maa://22880 (71.43), maa://20276 (100.00), *maa://22749 (72.62)</t>
+          <t>*maa://22880 (72.62), maa://20276 (100.00), *maa://22749 (72.62)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>maa://45854 (87.06), maa://24617 (100.00), *maa://60545 (71.76)</t>
+          <t>maa://45854 (85.88), maa://24617 (100.00), *maa://60545 (71.76)</t>
         </is>
       </c>
       <c r="U3" s="19" t="n"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="X3" s="8" t="inlineStr">
         <is>
-          <t>maa://27396 (86.02), maa://27484 (100.00), *maa://27480 (77.42)</t>
+          <t>maa://27396 (86.02), maa://27484 (100.00), *maa://27480 (78.49)</t>
         </is>
       </c>
       <c r="Y3" s="19" t="n"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>maa://21245 (100.00), maa://54105 (97.47), maa://22744 (81.01)</t>
+          <t>maa://21245 (100.00), maa://54105 (98.73), maa://22744 (81.01)</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>maa://28624 (100.00), maa://24957 (94.51)</t>
+          <t>maa://28624 (100.00), maa://24957 (95.60)</t>
         </is>
       </c>
       <c r="M7" s="19" t="n"/>
@@ -1482,7 +1482,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.08 13:32:35</t>
+          <t>更新日期：2025.08.09 13:24:58</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>maa://22762 (100.00), *maa://39552 (74.42)</t>
+          <t>maa://22762 (100.00), *maa://39552 (75.58)</t>
         </is>
       </c>
       <c r="M9" s="19" t="n"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AF9" s="8" t="inlineStr">
         <is>
-          <t>maa://26206 (100.00), **maa://22865 (47.06)</t>
+          <t>maa://26206 (100.00), **maa://22865 (45.88)</t>
         </is>
       </c>
       <c r="AG9" s="16" t="n"/>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="S10" s="19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (100.00), maa://22755 (87.23), **maa://63521 (50.00)</t>
+          <t>maa://27395 (100.00), maa://22755 (87.23)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t>maa://22301 (100.00), maa://45828 (90.53), maa://22726 (82.11)</t>
+          <t>maa://22301 (100.00), maa://45828 (91.58), maa://22726 (82.11)</t>
         </is>
       </c>
       <c r="Y10" s="19" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>maa://21867 (100.00), *maa://54294 (66.28)</t>
+          <t>maa://21867 (100.00), *maa://54294 (75.58)</t>
         </is>
       </c>
       <c r="I12" s="19" t="n"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>maa://63896 (98.84), maa://64046 (100.00)</t>
+          <t>maa://63896 (95.40), maa://64046 (100.00)</t>
         </is>
       </c>
       <c r="M12" s="19" t="n"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
-          <t>maa://23669 (100.00), maa://36677 (96.77), maa://39872 (86.02)</t>
+          <t>maa://23669 (100.00), maa://36677 (96.77), maa://39872 (87.10)</t>
         </is>
       </c>
       <c r="AC12" s="19" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>maa://22743 (94.81), maa://22734 (100.00), *maa://30808 (67.53), maa://36048 (84.42), maa://45058 (83.12)</t>
+          <t>maa://22743 (96.10), maa://22734 (100.00), *maa://30808 (67.53), maa://36048 (83.12), maa://45058 (83.12)</t>
         </is>
       </c>
       <c r="E15" s="19" t="n"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>*maa://23911 (71.59), maa://27755 (100.00)</t>
+          <t>*maa://23911 (70.45), maa://27755 (100.00)</t>
         </is>
       </c>
       <c r="AG16" s="16" t="n"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://50085 (100.00), maa://49976 (94.12), *maa://56241 (78.82)</t>
+          <t>maa://50085 (100.00), maa://49976 (94.12), *maa://56241 (70.59)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>maa://20110 (90.59), maa://34946 (100.00)</t>
+          <t>maa://34946 (100.00), maa://20110 (90.59)</t>
         </is>
       </c>
       <c r="Y21" s="19" t="n"/>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>maa://24368 (100.00), *maa://46650 (68.42)</t>
+          <t>maa://24368 (100.00), *maa://46650 (69.74)</t>
         </is>
       </c>
       <c r="E24" s="19" t="n"/>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>maa://29063 (95.45), maa://25311 (100.00), ***maa://22725 (3.03), maa://45047 (80.30)</t>
+          <t>maa://29063 (96.92), maa://25311 (100.00), ***maa://22725 (3.08), maa://45047 (81.54)</t>
         </is>
       </c>
       <c r="I25" s="19" t="n"/>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AF26" s="8" t="inlineStr">
         <is>
-          <t>maa://30511 (100.00), **maa://29760 (46.77)</t>
+          <t>maa://30511 (100.00), **maa://29760 (47.54)</t>
         </is>
       </c>
       <c r="AG26" s="16" t="n"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>maa://35926 (100.00), maa://36258 (91.21), *maa://43904 (52.75)</t>
+          <t>maa://35926 (100.00), maa://36258 (92.22), *maa://43904 (53.33)</t>
         </is>
       </c>
       <c r="M31" s="19" t="n"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="AE40" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>maa://64205 (100.00)</t>
+          <t>maa://64107 (93.18), maa://64205 (100.00)</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>maa://22525 (91.14), maa://21284 (100.00)</t>
+          <t>maa://22525 (90.00), maa://21284 (100.00)</t>
         </is>
       </c>
       <c r="I43" s="19" t="n"/>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>maa://59394 (100.00), maa://59378 (92.39)</t>
+          <t>maa://59394 (100.00), maa://59378 (91.40)</t>
         </is>
       </c>
       <c r="Q52" s="19" t="n"/>
@@ -7080,7 +7080,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.08 13:32:35</t>
+          <t>更新日期：2025.08.09 13:24:58</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>maa://36644 (93.26), maa://36866 (100.00), *maa://45572 (78.65), maa://62759 (87.64), *maa://27794 (64.04), *maa://20960 (78.65), **maa://20843 (49.44), ***maa://24483 (10.11), **maa://20862 (49.44), *maa://20893 (61.80)</t>
+          <t>maa://36644 (93.26), maa://36866 (100.00), *maa://45572 (78.65), maa://62759 (89.89), *maa://27794 (64.04), *maa://20960 (78.65), **maa://20843 (49.44), ***maa://24483 (10.11), **maa://20862 (49.44), *maa://20893 (61.80)</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -15067,12 +15067,12 @@
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>maa://40957 (94.85), maa://36641 (100.00), maa://36865 (94.85), maa://44635 (83.51), maa://44660 (82.47), *maa://41128 (72.16), maa://42918 (92.78), maa://44119 (89.69), maa://46108 (88.66), *maa://37300 (58.76), **maa://42917 (35.05)</t>
+          <t>maa://40957 (94.85), maa://36641 (100.00), maa://36865 (94.85), maa://44635 (83.51), maa://44660 (82.47), *maa://41128 (72.16), maa://42918 (92.78), maa://44119 (89.69), maa://46108 (88.66), *maa://37300 (58.76), **maa://42917 (35.05), **maa://64408 (35.05)</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>maa://32418 (100.00), maa://51440 (89.90), *maa://63320 (68.69)</t>
+          <t>maa://32418 (100.00), maa://51440 (89.90), *maa://63320 (72.73)</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>maa://42223 (100.00), maa://49077 (83.67), maa://42292 (87.76), *maa://42402 (69.39)</t>
+          <t>maa://42223 (100.00), maa://49077 (84.69), maa://42292 (87.76), *maa://42402 (69.39)</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>maa://62759 (100.00), **maa://62764 (43.59)</t>
+          <t>maa://62759 (100.00), **maa://62764 (42.50)</t>
         </is>
       </c>
       <c r="E242" s="14" t="inlineStr">
@@ -26466,7 +26466,7 @@
       </c>
       <c r="D360" s="22" t="inlineStr">
         <is>
-          <t>maa://42299 (100.00), *maa://42224 (69.32)</t>
+          <t>maa://42299 (100.00), *maa://42224 (70.45)</t>
         </is>
       </c>
       <c r="E360" s="22" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="D369" s="22" t="inlineStr">
         <is>
-          <t>maa://63883 (100.00), **maa://64045 (47.73), **maa://64041 (47.73)</t>
+          <t>maa://63883 (100.00), *maa://64045 (66.67), ***maa://64041 (17.65)</t>
         </is>
       </c>
       <c r="E369" s="22" t="inlineStr">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>maa://51880 (100.00), maa://56651 (93.88), maa://51878 (90.82)</t>
+          <t>maa://51880 (100.00), maa://56651 (93.88), maa://51878 (91.84)</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>maa://39402 (100.00), *maa://34787 (73.86), maa://58660 (89.77)</t>
+          <t>maa://39402 (100.00), *maa://34787 (73.86), maa://58660 (92.05)</t>
         </is>
       </c>
       <c r="M2" s="19" t="n"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>maa://25251 (100.00), maa://59087 (97.67)</t>
+          <t>maa://25251 (100.00), maa://59087 (98.84)</t>
         </is>
       </c>
       <c r="AG2" s="16" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>*maa://22880 (72.62), maa://20276 (100.00), *maa://22749 (72.62)</t>
+          <t>*maa://22880 (72.62), maa://20276 (100.00), *maa://22749 (75.00)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="X3" s="8" t="inlineStr">
         <is>
-          <t>maa://27396 (86.02), maa://27484 (100.00), *maa://27480 (78.49)</t>
+          <t>maa://27396 (86.02), maa://27484 (100.00), *maa://27480 (79.57)</t>
         </is>
       </c>
       <c r="Y3" s="19" t="n"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="AB3" s="8" t="inlineStr">
         <is>
-          <t>maa://24390 (100.00), maa://52241 (91.11)</t>
+          <t>maa://24390 (100.00), maa://52241 (92.22)</t>
         </is>
       </c>
       <c r="AC3" s="19" t="n"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>maa://31836 (100.00), maa://30381 (89.29)</t>
+          <t>maa://31836 (100.00), maa://30381 (88.24)</t>
         </is>
       </c>
       <c r="Q6" s="19" t="n"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>**maa://64972 (42.00)</t>
+          <t>*maa://64972 (69.39)</t>
         </is>
       </c>
       <c r="I7" s="19" t="n"/>
@@ -1482,7 +1482,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.22 13:21:00</t>
+          <t>更新日期：2025.08.25 13:23:23</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>maa://22762 (100.00), *maa://39552 (75.58)</t>
+          <t>maa://22762 (100.00), *maa://39552 (70.93)</t>
         </is>
       </c>
       <c r="M9" s="19" t="n"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AF9" s="8" t="inlineStr">
         <is>
-          <t>maa://26206 (100.00), **maa://22865 (45.88)</t>
+          <t>maa://26206 (100.00), **maa://22865 (44.71)</t>
         </is>
       </c>
       <c r="AG9" s="16" t="n"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>***maa://25695 (26.42), ***maa://39951 (11.32), maa://45271 (100.00), ***maa://34206 (20.75), ***maa://39243 (13.21), **maa://54000 (43.40)</t>
+          <t>***maa://25695 (26.92), ***maa://39951 (11.54), maa://45271 (100.00), ***maa://34206 (21.15), ***maa://39243 (13.46), **maa://54000 (44.23)</t>
         </is>
       </c>
       <c r="E10" s="19" t="n"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (100.00), maa://22755 (87.23), *maa://63521 (51.06)</t>
+          <t>maa://27395 (100.00), maa://22755 (88.30), *maa://63521 (51.06)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="S11" s="19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>maa://22747 (89.47), maa://22501 (100.00), maa://45521 (88.42)</t>
+          <t>maa://22747 (89.47), maa://22501 (100.00), maa://45521 (88.42), ***maa://64808 (22.11)</t>
         </is>
       </c>
       <c r="U11" s="19" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>maa://21867 (100.00), maa://54294 (83.72)</t>
+          <t>maa://21867 (100.00), maa://54294 (86.05)</t>
         </is>
       </c>
       <c r="I12" s="19" t="n"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>maa://63896 (93.26), maa://64046 (100.00)</t>
+          <t>maa://63896 (92.22), maa://64046 (100.00)</t>
         </is>
       </c>
       <c r="M12" s="19" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>maa://39841 (96.77), maa://26245 (100.00), maa://21288 (98.92), maa://36682 (92.47)</t>
+          <t>maa://39841 (96.77), maa://26245 (100.00), maa://21288 (98.92), maa://36682 (90.32)</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>maa://22743 (96.10), maa://22734 (100.00), *maa://30808 (66.23), maa://36048 (84.42), maa://45058 (84.42)</t>
+          <t>maa://22743 (94.87), maa://22734 (100.00), *maa://30808 (65.38), maa://36048 (83.33), maa://45058 (84.62)</t>
         </is>
       </c>
       <c r="E15" s="19" t="n"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>*maa://23911 (70.45), maa://27755 (100.00)</t>
+          <t>*maa://23911 (71.59), maa://27755 (100.00)</t>
         </is>
       </c>
       <c r="AG16" s="16" t="n"/>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>maa://24379 (100.00), maa://54153 (86.17), *maa://24380 (69.15)</t>
+          <t>maa://24379 (100.00), maa://54153 (86.32), *maa://24380 (68.42)</t>
         </is>
       </c>
       <c r="Q18" s="19" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AF18" s="8" t="inlineStr">
         <is>
-          <t>maa://24313 (88.33), maa://47854 (100.00), *maa://29784 (55.00)</t>
+          <t>maa://24313 (85.48), maa://47854 (100.00), *maa://29784 (53.23)</t>
         </is>
       </c>
       <c r="AG18" s="16" t="n"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://50085 (100.00), maa://49976 (95.29), *maa://56241 (76.47)</t>
+          <t>maa://50085 (100.00), maa://49976 (95.29), *maa://56241 (77.65)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AF24" s="8" t="inlineStr">
         <is>
-          <t>maa://22523 (87.21), *maa://36672 (69.77), maa://29910 (100.00), maa://45831 (84.88), maa://64165 (81.40)</t>
+          <t>maa://22523 (87.21), *maa://36672 (68.60), maa://29910 (100.00), maa://45831 (86.05), maa://64165 (86.05)</t>
         </is>
       </c>
       <c r="AG24" s="16" t="n"/>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>maa://29753 (100.00), *maa://63016 (75.27)</t>
+          <t>maa://29753 (100.00), *maa://63016 (77.42)</t>
         </is>
       </c>
       <c r="E25" s="19" t="n"/>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>maa://41802 (100.00), maa://56374 (80.25)</t>
+          <t>maa://41802 (100.00), maa://56374 (86.42)</t>
         </is>
       </c>
       <c r="E26" s="19" t="n"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>maa://39870 (100.00), maa://56625 (94.20)</t>
+          <t>maa://39870 (100.00), maa://56625 (98.55)</t>
         </is>
       </c>
       <c r="Q26" s="19" t="n"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>*maa://39601 (75.00), maa://34494 (100.00)</t>
+          <t>*maa://39601 (76.14), maa://34494 (100.00)</t>
         </is>
       </c>
       <c r="I27" s="19" t="n"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AF28" s="8" t="inlineStr">
         <is>
-          <t>maa://36660 (100.00), ***maa://65700 (23.33)</t>
+          <t>maa://36660 (100.00), **maa://65700 (48.89)</t>
         </is>
       </c>
       <c r="AG28" s="16" t="n"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>maa://45792 (100.00), *maa://64191 (57.14)</t>
+          <t>maa://45792 (100.00), *maa://64191 (66.23)</t>
         </is>
       </c>
       <c r="E30" s="19" t="n"/>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="S30" s="19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>*maa://32940 (55.84), maa://24388 (100.00)</t>
+          <t>maa://24388 (100.00)</t>
         </is>
       </c>
       <c r="U30" s="19" t="n"/>
@@ -4660,12 +4660,12 @@
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P32" s="8" t="inlineStr">
         <is>
-          <t>maa://26203 (100.00)</t>
+          <t>maa://26203 (100.00), ***maa://56429 (24.42)</t>
         </is>
       </c>
       <c r="Q32" s="19" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>maa://42859 (98.95), *maa://41108 (77.89), maa://41238 (100.00), maa://45523 (98.95)</t>
+          <t>maa://42859 (100.00), *maa://41108 (77.89), maa://41238 (100.00), maa://45523 (98.95)</t>
         </is>
       </c>
       <c r="U32" s="19" t="n"/>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>maa://21956 (100.00), *maa://22730 (73.68)</t>
+          <t>maa://21956 (100.00), *maa://22730 (72.73)</t>
         </is>
       </c>
       <c r="Q33" s="19" t="n"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>maa://48817 (100.00), *maa://56235 (70.65)</t>
+          <t>maa://48817 (100.00), *maa://56235 (73.91)</t>
         </is>
       </c>
       <c r="Q34" s="19" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>maa://45718 (100.00), *maa://47069 (59.79), *maa://56336 (68.04), *maa://45789 (67.01)</t>
+          <t>maa://45718 (100.00), *maa://47069 (59.79), *maa://56336 (71.13), *maa://45789 (67.01)</t>
         </is>
       </c>
       <c r="M37" s="19" t="n"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>maa://24709 (100.00), maa://47093 (95.40)</t>
+          <t>maa://24709 (100.00), maa://47093 (94.25)</t>
         </is>
       </c>
       <c r="Q39" s="19" t="n"/>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>maa://64205 (100.00), *maa://65283 (71.25)</t>
+          <t>maa://64205 (100.00), maa://65283 (81.25)</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>maa://29768 (100.00), maa://27728 (95.79), *maa://56386 (77.89)</t>
+          <t>maa://29768 (100.00), maa://27728 (95.79), *maa://56386 (80.00)</t>
         </is>
       </c>
       <c r="I44" s="19" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>maa://27410 (100.00), maa://29661 (98.95), *maa://28038 (61.05), *maa://56236 (75.79)</t>
+          <t>maa://27410 (100.00), maa://29661 (98.95), maa://56236 (81.05), *maa://28038 (61.05)</t>
         </is>
       </c>
       <c r="I47" s="19" t="n"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>maa://25176 (100.00), *maa://56237 (77.42)</t>
+          <t>maa://25176 (100.00), *maa://56237 (79.57)</t>
         </is>
       </c>
       <c r="I57" s="19" t="n"/>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>maa://59534 (100.00), *maa://59693 (61.70), *maa://59413 (72.34)</t>
+          <t>maa://59534 (100.00), *maa://59693 (68.09), *maa://59413 (72.34)</t>
         </is>
       </c>
       <c r="I63" s="19" t="n"/>
@@ -7080,7 +7080,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.22 13:21:00</t>
+          <t>更新日期：2025.08.25 13:23:23</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>maa://20919 (100.00), *maa://31611 (51.09)</t>
+          <t>maa://20919 (100.00), *maa://31611 (50.54)</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>maa://36644 (95.51), maa://36866 (100.00), maa://62759 (96.63), *maa://45572 (74.16), *maa://27794 (64.04), *maa://20960 (78.65), **maa://20843 (49.44), ***maa://24483 (10.11), **maa://20862 (49.44), *maa://20893 (61.80)</t>
+          <t>maa://36644 (95.51), maa://36866 (100.00), maa://62759 (97.75), *maa://45572 (74.16), *maa://27794 (64.04), *maa://20960 (78.65), **maa://20843 (49.44), ***maa://24483 (10.11), **maa://20862 (49.44), *maa://20893 (61.80)</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>maa://20916 (100.00), maa://52658 (92.54)</t>
+          <t>maa://20916 (100.00), maa://52658 (100.00)</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>maa://27376 (98.81), maa://42635 (100.00), **maa://20838 (40.48)</t>
+          <t>maa://27376 (100.00), maa://42635 (100.00), **maa://20838 (40.48)</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>maa://20841 (100.00), maa://24093 (100.00), maa://31559 (89.47), maa://20924 (81.05), *maa://25777 (64.21), *maa://20631 (60.00), **maa://28241 (46.32)</t>
+          <t>maa://20841 (100.00), maa://31559 (89.47), maa://24093 (100.00), maa://20924 (81.05), *maa://25777 (64.21), *maa://20631 (60.00), **maa://28241 (46.32)</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>maa://20976 (100.00), maa://20815 (84.21)</t>
+          <t>maa://20976 (100.00), maa://20815 (83.33)</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>maa://20944 (93.48), maa://35393 (100.00)</t>
+          <t>maa://20944 (94.57), maa://35393 (100.00)</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>maa://20943 (100.00), *maa://30673 (73.47), maa://63790 (89.80), *maa://30672 (66.33), maa://20856 (82.65)</t>
+          <t>maa://20943 (100.00), *maa://30673 (73.47), maa://63790 (90.82), *maa://30672 (66.33), maa://20856 (82.65)</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>maa://20991 (100.00), *maa://51015 (75.26)</t>
+          <t>maa://20991 (100.00), *maa://51015 (76.29)</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>maa://29650 (100.00), maa://45570 (95.65)</t>
+          <t>maa://29650 (100.00), maa://45570 (96.74)</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>maa://45258 (100.00), **maa://30679 (44.93)</t>
+          <t>maa://45258 (100.00), **maa://30679 (44.29)</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="D142" s="13" t="inlineStr">
         <is>
-          <t>maa://28484 (100.00), **maa://23736 (40.43), *maa://31185 (63.83), *maa://30306 (54.26)</t>
+          <t>maa://28484 (100.00), **maa://23736 (41.49), *maa://31185 (65.96), *maa://30306 (54.26)</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>maa://30670 (100.00), maa://31470 (89.25), **maa://45066 (38.71), *maa://61380 (61.29), ***maa://30867 (12.90)</t>
+          <t>maa://30670 (100.00), maa://31470 (84.95), **maa://45066 (38.71), *maa://61380 (69.89), ***maa://30867 (12.90)</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>maa://51549 (100.00), maa://51923 (92.05)</t>
+          <t>maa://51549 (100.00), maa://51923 (91.01)</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>maa://44232 (100.00), *maa://45603 (78.35), ***maa://63114 (9.28)</t>
+          <t>maa://44232 (100.00), *maa://45603 (78.35), ***maa://63114 (21.65), ***maa://65963 (9.28)</t>
         </is>
       </c>
       <c r="E159" s="14" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>maa://49867 (97.70), maa://49655 (100.00)</t>
+          <t>maa://49867 (98.85), maa://49655 (100.00)</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>maa://59681 (100.00), *maa://64200 (74.47)</t>
+          <t>maa://59681 (100.00), maa://64200 (81.91)</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>maa://32418 (100.00), maa://51440 (89.90), maa://63320 (87.88)</t>
+          <t>maa://32418 (100.00), maa://51440 (89.90), maa://63320 (88.89)</t>
         </is>
       </c>
       <c r="E175" s="14" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>maa://44224 (92.63), maa://35854 (82.11), maa://50388 (100.00), maa://25760 (83.16), ***maa://43911 (4.21), **maa://20872 (34.74), *maa://51066 (68.42), maa://63024 (82.11)</t>
+          <t>maa://44224 (92.63), maa://35854 (82.11), maa://50388 (100.00), maa://25760 (83.16), ***maa://43911 (4.21), **maa://20872 (34.74), *maa://51066 (68.42), maa://63024 (84.21)</t>
         </is>
       </c>
       <c r="E197" s="14" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>maa://39156 (100.00), **maa://39550 (39.08), **maa://53417 (47.13), *maa://63806 (65.52)</t>
+          <t>maa://39156 (100.00), **maa://39550 (39.08), **maa://53417 (47.13), *maa://63806 (70.11)</t>
         </is>
       </c>
       <c r="E198" s="14" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>maa://42223 (100.00), maa://49077 (84.69), maa://42292 (87.76), *maa://42402 (69.39)</t>
+          <t>maa://42223 (100.00), maa://49077 (85.71), maa://42292 (87.76), *maa://42402 (69.39)</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
@@ -18420,7 +18420,7 @@
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
-          <t>maa://20956 (100.00), *maa://20830 (63.04), *maa://44703 (70.65)</t>
+          <t>maa://20956 (100.00), *maa://20830 (62.37), *maa://44703 (72.04)</t>
         </is>
       </c>
       <c r="E211" s="14" t="inlineStr">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="D217" s="13" t="inlineStr">
         <is>
-          <t>maa://24636 (100.00), maa://25778 (86.02)</t>
+          <t>maa://24636 (100.00), maa://25778 (85.11)</t>
         </is>
       </c>
       <c r="E217" s="14" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="D221" s="13" t="inlineStr">
         <is>
-          <t>maa://26499 (100.00), ***maa://20998 (2.86)</t>
+          <t>maa://26499 (100.00), ***maa://20998 (2.78)</t>
         </is>
       </c>
       <c r="E221" s="14" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>maa://20922 (100.00), *maa://32623 (63.95), *maa://34242 (56.98)</t>
+          <t>maa://20922 (100.00), *maa://32623 (66.28), *maa://34242 (56.98)</t>
         </is>
       </c>
       <c r="E239" s="14" t="inlineStr">
@@ -20035,12 +20035,12 @@
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D241" s="13" t="inlineStr">
         <is>
-          <t>maa://30667 (94.94), maa://30666 (100.00), **maa://30739 (35.44), *maa://30723 (56.96), maa://39588 (97.47), maa://64079 (84.81)</t>
+          <t>maa://30667 (94.94), maa://30666 (100.00), **maa://30739 (35.44), *maa://30723 (56.96), maa://39588 (97.47), maa://64079 (84.81), **maa://65726 (43.04)</t>
         </is>
       </c>
       <c r="E241" s="14" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>maa://62759 (100.00), ***maa://62764 (24.42)</t>
+          <t>maa://62759 (100.00), ***maa://62764 (24.14)</t>
         </is>
       </c>
       <c r="E242" s="14" t="inlineStr">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="D251" s="13" t="inlineStr">
         <is>
-          <t>maa://42287 (96.59), maa://45570 (100.00), *maa://60678 (76.14), maa://42225 (88.64)</t>
+          <t>maa://42287 (95.51), maa://45570 (100.00), *maa://60678 (75.28), maa://42225 (87.64)</t>
         </is>
       </c>
       <c r="E251" s="14" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>maa://24093 (100.00), maa://31559 (89.47), maa://20924 (81.05), ***maa://49440 (16.84)</t>
+          <t>maa://31559 (89.47), maa://24093 (100.00), maa://20924 (81.05), ***maa://49440 (16.84)</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="D275" s="13" t="inlineStr">
         <is>
-          <t>maa://51881 (100.00), maa://51630 (91.84), maa://56588 (83.67), **maa://55171 (41.84), *maa://51893 (61.22), ***maa://60902 (15.31)</t>
+          <t>maa://51881 (100.00), maa://51630 (92.86), maa://56588 (83.67), **maa://55171 (41.84), *maa://51893 (61.22), ***maa://60902 (15.31)</t>
         </is>
       </c>
       <c r="E275" s="14" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="D289" s="13" t="inlineStr">
         <is>
-          <t>maa://20899 (100.00), maa://46332 (96.43), ***maa://44744 (5.95)</t>
+          <t>maa://20899 (100.00), maa://46332 (95.29), ***maa://44744 (5.88)</t>
         </is>
       </c>
       <c r="E289" s="14" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>maa://45799 (100.00), maa://57199 (91.49)</t>
+          <t>maa://45799 (100.00), maa://57199 (92.55)</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>maa://50280 (100.00), maa://49642 (95.88), maa://49660 (84.54), *maa://50517 (50.52)</t>
+          <t>maa://50280 (100.00), maa://49642 (95.88), maa://49660 (85.57), *maa://50517 (50.52)</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="D341" s="22" t="inlineStr">
         <is>
-          <t>*maa://30671 (78.12), maa://30669 (100.00), *maa://37275 (71.88), **maa://32410 (37.50), *maa://41605 (67.71)</t>
+          <t>*maa://30671 (78.12), maa://30669 (100.00), *maa://37275 (69.79), **maa://32410 (37.50), *maa://41605 (67.71)</t>
         </is>
       </c>
       <c r="E341" s="22" t="inlineStr">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="D357" s="22" t="inlineStr">
         <is>
-          <t>maa://36868 (100.00), maa://35996 (94.90), ***maa://39217 (20.41), maa://47349 (89.80)</t>
+          <t>maa://36868 (100.00), maa://35996 (94.90), ***maa://39217 (20.41), maa://47349 (90.82)</t>
         </is>
       </c>
       <c r="E357" s="22" t="inlineStr">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="D358" s="22" t="inlineStr">
         <is>
-          <t>maa://49696 (99.00), maa://49695 (100.00), maa://49758 (92.00), **maa://59402 (39.00), **maa://52357 (48.00), ***maa://63091 (25.00)</t>
+          <t>maa://49696 (99.00), maa://49695 (100.00), maa://49758 (92.00), **maa://59402 (41.00), **maa://52357 (48.00), ***maa://63091 (25.00)</t>
         </is>
       </c>
       <c r="E358" s="22" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="D361" s="22" t="inlineStr">
         <is>
-          <t>maa://49648 (100.00), *maa://49662 (71.91)</t>
+          <t>maa://49648 (100.00), *maa://49662 (73.03)</t>
         </is>
       </c>
       <c r="E361" s="22" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="D367" s="22" t="inlineStr">
         <is>
-          <t>maa://40957 (100.00), maa://48026 (95.70), maa://44635 (87.10), maa://41035 (91.40), maa://44660 (87.10), *maa://60251 (56.99), *maa://41128 (75.27)</t>
+          <t>maa://40957 (100.00), maa://48026 (95.70), maa://44635 (87.10), maa://41035 (92.47), maa://44660 (87.10), *maa://60251 (56.99), *maa://41128 (75.27)</t>
         </is>
       </c>
       <c r="E367" s="22" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="D369" s="22" t="inlineStr">
         <is>
-          <t>maa://63883 (100.00), maa://64045 (84.42), **maa://64041 (38.96)</t>
+          <t>maa://63883 (100.00), maa://64045 (84.71), **maa://64041 (35.29)</t>
         </is>
       </c>
       <c r="E369" s="22" t="inlineStr">
@@ -27492,7 +27492,7 @@
       </c>
       <c r="D379" s="22" t="inlineStr">
         <is>
-          <t>maa://44233 (92.05), maa://45570 (100.00)</t>
+          <t>maa://44233 (92.13), maa://45570 (100.00)</t>
         </is>
       </c>
       <c r="E379" s="22" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="D384" s="22" t="inlineStr">
         <is>
-          <t>maa://42970 (81.05), maa://44745 (100.00), ***maa://49516 (26.32), **maa://45952 (37.89), ***maa://46851 (2.11), **maa://44896 (47.37)</t>
+          <t>*maa://42970 (80.00), maa://44745 (100.00), ***maa://49516 (26.32), **maa://45952 (34.74), ***maa://46851 (2.11), **maa://44896 (47.37)</t>
         </is>
       </c>
       <c r="E384" s="22" t="inlineStr">
@@ -28086,7 +28086,7 @@
       </c>
       <c r="D390" s="22" t="inlineStr">
         <is>
-          <t>maa://63890 (100.00), ***maa://64043 (25.61)</t>
+          <t>maa://63890 (100.00), ***maa://64043 (24.42)</t>
         </is>
       </c>
       <c r="E390" s="22" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>maa://51898 (100.00), *maa://57241 (76.47)</t>
+          <t>maa://51898 (100.00), *maa://57241 (80.00)</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>maa://51872 (100.00), maa://51876 (100.00), *maa://63228 (76.84), maa://51873 (96.84), *maa://62047 (75.79)</t>
+          <t>maa://51872 (100.00), maa://51876 (100.00), *maa://63228 (77.89), maa://51873 (96.84), *maa://62047 (76.84)</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -28567,12 +28567,12 @@
       </c>
       <c r="C405" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>maa://64040 (100.00), ***maa://65803 (21.65)</t>
+          <t>maa://64040 (100.00)</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>maa://25390 (98.20), maa://24702 (95.06), maa://36681 (86.21)</t>
+          <t>maa://25390 (98.23), maa://24702 (95.06), maa://36681 (86.21)</t>
         </is>
       </c>
       <c r="E2" s="19" t="n"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>maa://58660 (98.77), maa://39402 (95.11), *maa://34787 (75.00)</t>
+          <t>maa://58660 (98.80), maa://39402 (95.15), *maa://34787 (75.00)</t>
         </is>
       </c>
       <c r="M2" s="19" t="n"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>maa://22742 (97.22), maa://66635 (99.51)</t>
+          <t>maa://22742 (97.25), maa://66635 (99.52)</t>
         </is>
       </c>
       <c r="U2" s="19" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="AB2" s="8" t="inlineStr">
         <is>
-          <t>maa://36684 (98.26), maa://21246 (91.32)</t>
+          <t>maa://36684 (98.29), maa://21246 (91.32)</t>
         </is>
       </c>
       <c r="AC2" s="19" t="n"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>maa://59087 (97.18), maa://25251 (91.61)</t>
+          <t>maa://59087 (97.21), maa://25251 (91.61)</t>
         </is>
       </c>
       <c r="AG2" s="16" t="n"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>maa://40192 (99.34), maa://36987 (97.14), maa://39849 (91.67)</t>
+          <t>maa://40192 (99.35), maa://36987 (97.14), maa://39849 (91.67)</t>
         </is>
       </c>
       <c r="E3" s="19" t="n"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>maa://21247 (99.34)</t>
+          <t>maa://21247 (99.35)</t>
         </is>
       </c>
       <c r="I3" s="19" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>maa://22880 (90.66), maa://20276 (93.98), maa://22749 (84.62)</t>
+          <t>maa://22880 (90.77), maa://20276 (93.98), maa://22749 (84.62)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>maa://21249 (98.30), maa://26254 (98.11), *maa://22738 (80.00)</t>
+          <t>maa://21249 (98.32), maa://26254 (98.11), *maa://22738 (80.00)</t>
         </is>
       </c>
       <c r="Q3" s="19" t="n"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>maa://60545 (98.63), maa://45854 (86.73), maa://24617 (91.18)</t>
+          <t>maa://60545 (98.66), maa://45854 (86.87), maa://24617 (91.18)</t>
         </is>
       </c>
       <c r="U3" s="19" t="n"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="X3" s="8" t="inlineStr">
         <is>
-          <t>maa://27396 (91.70), maa://27484 (99.17), maa://27480 (85.45)</t>
+          <t>maa://27396 (91.81), maa://27484 (99.18), maa://27480 (85.45)</t>
         </is>
       </c>
       <c r="Y3" s="19" t="n"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="AB3" s="8" t="inlineStr">
         <is>
-          <t>maa://52241 (99.05), maa://24390 (96.77)</t>
+          <t>maa://52241 (99.07), maa://24390 (96.77)</t>
         </is>
       </c>
       <c r="AC3" s="19" t="n"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>maa://24632 (98.05), maa://22499 (90.00), maa://22746 (100.00)</t>
+          <t>maa://24632 (97.98), maa://22499 (90.00), maa://22746 (100.00)</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>maa://49983 (99.13), maa://50121 (96.64)</t>
+          <t>maa://49983 (99.14), maa://50121 (96.72)</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>maa://27295 (97.68), maa://32509 (96.19), maa://31008 (95.05), maa://22754 (88.16)</t>
+          <t>maa://27295 (97.70), maa://32509 (96.25), maa://31008 (95.14), maa://22754 (88.16)</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="X4" s="8" t="inlineStr">
         <is>
-          <t>maa://43217 (98.78)</t>
+          <t>maa://43217 (98.80)</t>
         </is>
       </c>
       <c r="Y4" s="19" t="n"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>maa://21245 (91.05), maa://54105 (98.38), *maa://22744 (80.00)</t>
+          <t>maa://21245 (91.08), maa://54105 (98.40), *maa://22744 (80.00)</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>maa://21919 (99.04), maa://21281 (81.25)</t>
+          <t>maa://21919 (99.05), maa://21281 (81.25)</t>
         </is>
       </c>
       <c r="Q5" s="19" t="n"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="X5" s="8" t="inlineStr">
         <is>
-          <t>maa://21290 (99.21)</t>
+          <t>maa://21290 (99.22)</t>
         </is>
       </c>
       <c r="Y5" s="19" t="n"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>maa://42407 (97.30)</t>
+          <t>maa://42407 (97.31)</t>
         </is>
       </c>
       <c r="E6" s="19" t="n"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>maa://24839 (99.39)</t>
+          <t>maa://24839 (99.40)</t>
         </is>
       </c>
       <c r="M6" s="19" t="n"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>maa://31836 (98.76), maa://30381 (95.00)</t>
+          <t>maa://31836 (98.77), maa://30381 (95.00)</t>
         </is>
       </c>
       <c r="Q6" s="19" t="n"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="X6" s="8" t="inlineStr">
         <is>
-          <t>maa://52754 (96.23)</t>
+          <t>maa://52754 (96.30)</t>
         </is>
       </c>
       <c r="Y6" s="19" t="n"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB6" s="8" t="inlineStr">
         <is>
-          <t>maa://22739 (89.13)</t>
+          <t>maa://22739 (89.25)</t>
         </is>
       </c>
       <c r="AC6" s="19" t="n"/>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AF6" s="8" t="inlineStr">
         <is>
-          <t>*maa://33152 (79.71), ***maa://22770 (26.09)</t>
+          <t>*maa://33152 (79.86), ***maa://22770 (26.09)</t>
         </is>
       </c>
       <c r="AG6" s="16" t="n"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>maa://28624 (98.69), maa://24957 (94.55)</t>
+          <t>maa://28624 (98.72), maa://24957 (94.55)</t>
         </is>
       </c>
       <c r="M7" s="19" t="n"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="P7" s="8" t="inlineStr">
         <is>
-          <t>maa://22750 (96.77)</t>
+          <t>maa://22750 (96.84)</t>
         </is>
       </c>
       <c r="Q7" s="19" t="n"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>maa://21291 (93.79)</t>
+          <t>maa://21291 (93.83)</t>
         </is>
       </c>
       <c r="U7" s="19" t="n"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="X7" s="8" t="inlineStr">
         <is>
-          <t>maa://22399 (97.05), maa://22758 (82.18)</t>
+          <t>maa://22399 (97.09), maa://22758 (82.18)</t>
         </is>
       </c>
       <c r="Y7" s="19" t="n"/>
@@ -1482,7 +1482,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.09.26 13:19:42</t>
+          <t>更新日期：2025.09.27 13:18:55</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>*maa://24371 (78.49)</t>
+          <t>*maa://24371 (78.61)</t>
         </is>
       </c>
       <c r="I8" s="19" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>maa://32931 (91.38), maa://23252 (91.67), maa://37496 (98.28)</t>
+          <t>maa://32931 (91.42), maa://23252 (91.67), maa://37496 (98.28)</t>
         </is>
       </c>
       <c r="Q8" s="19" t="n"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>maa://21411 (96.00), maa://67587 (98.36)</t>
+          <t>maa://21411 (96.02), maa://67587 (98.40)</t>
         </is>
       </c>
       <c r="Y8" s="19" t="n"/>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AF8" s="8" t="inlineStr">
         <is>
-          <t>maa://24479 (84.24), *maa://21990 (51.72)</t>
+          <t>maa://24479 (84.49), *maa://21990 (51.72)</t>
         </is>
       </c>
       <c r="AG8" s="16" t="n"/>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>maa://22762 (96.23), maa://39552 (86.96)</t>
+          <t>maa://22762 (96.24), maa://39552 (86.96)</t>
         </is>
       </c>
       <c r="M9" s="19" t="n"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
-          <t>maa://28711 (95.04), maa://40166 (95.02)</t>
+          <t>maa://28711 (95.06), maa://40166 (95.05)</t>
         </is>
       </c>
       <c r="AC9" s="19" t="n"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AF9" s="8" t="inlineStr">
         <is>
-          <t>maa://26206 (91.09), maa://66916 (97.95)</t>
+          <t>maa://26206 (91.15), maa://66916 (98.00)</t>
         </is>
       </c>
       <c r="AG9" s="16" t="n"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>maa://54000 (91.86)</t>
+          <t>maa://54000 (91.95)</t>
         </is>
       </c>
       <c r="E10" s="19" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="P10" s="8" t="inlineStr">
         <is>
-          <t>maa://28977 (91.70), *maa://36669 (74.03)</t>
+          <t>maa://28977 (91.73), *maa://36669 (74.03)</t>
         </is>
       </c>
       <c r="Q10" s="19" t="n"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (99.22), maa://22755 (91.43), maa://63521 (94.61)</t>
+          <t>maa://27395 (99.22), maa://22755 (91.43), maa://63521 (94.63)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t>maa://45828 (99.19), maa://22301 (97.64), maa://22726 (100.00)</t>
+          <t>maa://45828 (99.21), maa://22301 (97.64), maa://22726 (100.00)</t>
         </is>
       </c>
       <c r="Y10" s="19" t="n"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>maa://21287 (93.68)</t>
+          <t>maa://21287 (93.75)</t>
         </is>
       </c>
       <c r="M11" s="19" t="n"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="P11" s="8" t="inlineStr">
         <is>
-          <t>maa://45557 (95.83)</t>
+          <t>maa://45557 (95.92)</t>
         </is>
       </c>
       <c r="Q11" s="19" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>maa://22747 (93.28), maa://22501 (99.53), maa://64808 (100.00), maa://45521 (95.16)</t>
+          <t>maa://22747 (93.37), maa://22501 (99.53), maa://64808 (100.00), maa://45521 (95.24)</t>
         </is>
       </c>
       <c r="U11" s="19" t="n"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="X11" s="8" t="inlineStr">
         <is>
-          <t>maa://36713 (99.24)</t>
+          <t>maa://36713 (99.25)</t>
         </is>
       </c>
       <c r="Y11" s="19" t="n"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AB11" s="8" t="inlineStr">
         <is>
-          <t>maa://29912 (99.70), maa://22516 (86.52)</t>
+          <t>maa://29912 (99.71), maa://22516 (86.52)</t>
         </is>
       </c>
       <c r="AC11" s="19" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>maa://21867 (93.41), maa://54294 (96.41)</t>
+          <t>maa://21867 (93.41), maa://54294 (96.47)</t>
         </is>
       </c>
       <c r="I12" s="19" t="n"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>maa://63896 (97.93), maa://64046 (98.55)</t>
+          <t>maa://63896 (97.96), maa://64046 (98.57)</t>
         </is>
       </c>
       <c r="M12" s="19" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>maa://37962 (98.77), maa://21485 (81.62), maa://22753 (92.80)</t>
+          <t>maa://37962 (98.78), maa://21485 (81.62), maa://22753 (92.80)</t>
         </is>
       </c>
       <c r="Y12" s="19" t="n"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
-          <t>maa://36677 (99.00), maa://23669 (95.11), maa://39872 (98.20)</t>
+          <t>maa://36677 (99.02), maa://23669 (95.11), maa://39872 (98.23)</t>
         </is>
       </c>
       <c r="AC12" s="19" t="n"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AF12" s="8" t="inlineStr">
         <is>
-          <t>maa://28932 (94.44)</t>
+          <t>maa://28932 (94.47)</t>
         </is>
       </c>
       <c r="AG12" s="16" t="n"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>maa://24999 (96.51), maa://36673 (93.94), maa://25001 (88.76)</t>
+          <t>maa://24999 (96.56), maa://36673 (93.98), maa://25001 (88.76)</t>
         </is>
       </c>
       <c r="E13" s="19" t="n"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>*maa://21248 (72.91), maa://66545 (98.99)</t>
+          <t>*maa://21248 (73.05), maa://66545 (99.00)</t>
         </is>
       </c>
       <c r="I13" s="19" t="n"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="P13" s="8" t="inlineStr">
         <is>
-          <t>maa://22676 (97.54), maa://22583 (87.82)</t>
+          <t>maa://22676 (97.56), maa://22583 (87.90)</t>
         </is>
       </c>
       <c r="Q13" s="19" t="n"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="X13" s="8" t="inlineStr">
         <is>
-          <t>maa://34957 (94.47)</t>
+          <t>maa://34957 (94.29)</t>
         </is>
       </c>
       <c r="Y13" s="19" t="n"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AF13" s="8" t="inlineStr">
         <is>
-          <t>maa://39883 (93.86)</t>
+          <t>maa://39883 (93.99)</t>
         </is>
       </c>
       <c r="AG13" s="16" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>maa://39841 (98.97), maa://26245 (97.06), maa://36682 (98.26), maa://21288 (96.40)</t>
+          <t>maa://39841 (98.99), maa://36682 (98.27), maa://26245 (97.06), maa://21288 (96.40)</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>maa://42751 (98.90), maa://22521 (95.12)</t>
+          <t>maa://42751 (98.91), maa://22521 (95.15)</t>
         </is>
       </c>
       <c r="U14" s="19" t="n"/>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="X14" s="8" t="inlineStr">
         <is>
-          <t>maa://37468 (97.96)</t>
+          <t>maa://37468 (97.98)</t>
         </is>
       </c>
       <c r="Y14" s="19" t="n"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AB14" s="8" t="inlineStr">
         <is>
-          <t>maa://22764 (98.85)</t>
+          <t>maa://22764 (98.86)</t>
         </is>
       </c>
       <c r="AC14" s="19" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>maa://22743 (85.28), maa://45058 (98.07), maa://22734 (84.85), *maa://36048 (74.72)</t>
+          <t>maa://22743 (85.15), maa://45058 (98.10), maa://22734 (84.85), *maa://36048 (74.73)</t>
         </is>
       </c>
       <c r="E15" s="19" t="n"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>maa://24304 (96.86), maa://21478 (90.48)</t>
+          <t>maa://24304 (96.91), maa://21478 (90.48)</t>
         </is>
       </c>
       <c r="I15" s="19" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>maa://24762 (97.58), *maa://22727 (70.00)</t>
+          <t>maa://24762 (97.59), *maa://22727 (70.00)</t>
         </is>
       </c>
       <c r="Q15" s="19" t="n"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AF15" s="8" t="inlineStr">
         <is>
-          <t>maa://36666 (96.23), maa://21364 (83.64), *maa://22766 (70.71), maa://68306 (83.33)</t>
+          <t>maa://36666 (96.26), maa://21364 (83.64), *maa://22766 (70.71), maa://68306 (84.00)</t>
         </is>
       </c>
       <c r="AG15" s="16" t="n"/>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>maa://28504 (96.09)</t>
+          <t>maa://28504 (96.12)</t>
         </is>
       </c>
       <c r="Q16" s="19" t="n"/>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>maa://36674 (97.97), maa://22729 (96.08), *maa://28648 (77.89)</t>
+          <t>maa://36674 (97.98), maa://22729 (96.11), *maa://28648 (77.89)</t>
         </is>
       </c>
       <c r="U16" s="19" t="n"/>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>maa://28501 (99.28), maa://28051 (96.97)</t>
+          <t>maa://28501 (99.29), maa://28051 (96.97)</t>
         </is>
       </c>
       <c r="Y16" s="19" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB16" s="8" t="inlineStr">
         <is>
-          <t>maa://26228 (97.86)</t>
+          <t>maa://26228 (97.87)</t>
         </is>
       </c>
       <c r="AC16" s="19" t="n"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>maa://23911 (90.38), maa://27755 (93.75), maa://67613 (99.36)</t>
+          <t>maa://23911 (90.38), maa://27755 (93.75), maa://67613 (99.38)</t>
         </is>
       </c>
       <c r="AG16" s="16" t="n"/>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>maa://39599 (98.13), maa://22430 (90.21)</t>
+          <t>maa://39599 (98.16), maa://22430 (90.21)</t>
         </is>
       </c>
       <c r="I17" s="19" t="n"/>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>maa://21679 (87.76)</t>
+          <t>maa://21679 (88.00)</t>
         </is>
       </c>
       <c r="M17" s="19" t="n"/>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>maa://23890 (82.64), maa://56238 (98.43)</t>
+          <t>maa://23890 (82.64), maa://56238 (98.44)</t>
         </is>
       </c>
       <c r="Q17" s="19" t="n"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>*maa://42324 (69.05)</t>
+          <t>*maa://42324 (69.41)</t>
         </is>
       </c>
       <c r="U17" s="19" t="n"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AF17" s="8" t="inlineStr">
         <is>
-          <t>maa://50136 (98.96)</t>
+          <t>maa://50136 (98.97)</t>
         </is>
       </c>
       <c r="AG17" s="16" t="n"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>maa://24570 (98.28)</t>
+          <t>maa://24570 (98.29)</t>
         </is>
       </c>
       <c r="E18" s="19" t="n"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>maa://24421 (95.21)</t>
+          <t>maa://24421 (95.17)</t>
         </is>
       </c>
       <c r="I18" s="19" t="n"/>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>maa://52226 (99.70), maa://22466 (92.83)</t>
+          <t>maa://52226 (99.71), maa://22466 (92.83)</t>
         </is>
       </c>
       <c r="M18" s="19" t="n"/>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>maa://24379 (100.00), maa://54153 (99.63), maa://24380 (100.00)</t>
+          <t>maa://24379 (100.00), maa://54153 (99.64), maa://24380 (100.00)</t>
         </is>
       </c>
       <c r="Q18" s="19" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AF18" s="8" t="inlineStr">
         <is>
-          <t>maa://47854 (92.70)</t>
+          <t>maa://47854 (92.81)</t>
         </is>
       </c>
       <c r="AG18" s="16" t="n"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>maa://24386 (99.65)</t>
+          <t>maa://24386 (99.66)</t>
         </is>
       </c>
       <c r="U19" s="19" t="n"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
-          <t>maa://30709 (85.62), *maa://36668 (69.03)</t>
+          <t>maa://30709 (85.78), *maa://36668 (69.03)</t>
         </is>
       </c>
       <c r="AC19" s="19" t="n"/>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AF19" s="8" t="inlineStr">
         <is>
-          <t>*maa://21663 (65.91), maa://52239 (87.10)</t>
+          <t>*maa://21663 (65.91), maa://52239 (87.50)</t>
         </is>
       </c>
       <c r="AG19" s="16" t="n"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>maa://25198 (97.62), maa://36680 (99.06), maa://21432 (91.49)</t>
+          <t>maa://25198 (97.63), maa://36680 (99.07), maa://21432 (91.49)</t>
         </is>
       </c>
       <c r="E20" s="19" t="n"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>maa://22864 (96.07)</t>
+          <t>maa://22864 (96.10)</t>
         </is>
       </c>
       <c r="I20" s="19" t="n"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>maa://41331 (95.24)</t>
+          <t>maa://41331 (95.30)</t>
         </is>
       </c>
       <c r="M20" s="19" t="n"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://50085 (96.43), maa://56241 (98.23), maa://49976 (88.46)</t>
+          <t>maa://50085 (96.47), maa://56241 (98.25), maa://49976 (88.57)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>maa://24372 (98.85)</t>
+          <t>maa://24372 (98.86)</t>
         </is>
       </c>
       <c r="I21" s="19" t="n"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>maa://31731 (96.43)</t>
+          <t>maa://31731 (96.46)</t>
         </is>
       </c>
       <c r="M21" s="19" t="n"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>maa://34946 (98.34), maa://20110 (87.01)</t>
+          <t>maa://34946 (98.35), maa://20110 (87.01)</t>
         </is>
       </c>
       <c r="Y21" s="19" t="n"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB21" s="8" t="inlineStr">
         <is>
-          <t>maa://21443 (86.62), maa://52223 (82.59)</t>
+          <t>maa://21443 (86.62), maa://52223 (82.79)</t>
         </is>
       </c>
       <c r="AC21" s="19" t="n"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AF21" s="8" t="inlineStr">
         <is>
-          <t>maa://22432 (93.93), maa://22524 (83.16), maa://64221 (97.83)</t>
+          <t>maa://22432 (93.97), maa://22524 (83.16), maa://64221 (97.87)</t>
         </is>
       </c>
       <c r="AG21" s="16" t="n"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>maa://25236 (99.19)</t>
+          <t>maa://25236 (99.20)</t>
         </is>
       </c>
       <c r="I22" s="19" t="n"/>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>maa://27127 (83.04), *maa://22751 (70.93), maa://66865 (99.38)</t>
+          <t>maa://27127 (83.19), *maa://22751 (70.93), maa://66865 (99.39)</t>
         </is>
       </c>
       <c r="M22" s="19" t="n"/>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>maa://37649 (94.44), maa://21282 (98.95)</t>
+          <t>maa://37649 (94.53), maa://21282 (98.95)</t>
         </is>
       </c>
       <c r="Y22" s="19" t="n"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>maa://39756 (98.57), maa://39875 (95.76)</t>
+          <t>maa://39756 (98.59), maa://39875 (95.76)</t>
         </is>
       </c>
       <c r="M23" s="19" t="n"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>maa://30587 (96.65), maa://29748 (81.68), *maa://37566 (78.12)</t>
+          <t>maa://30587 (96.67), maa://29748 (81.68), *maa://37566 (78.46)</t>
         </is>
       </c>
       <c r="Q23" s="19" t="n"/>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>maa://31212 (94.50), maa://24387 (84.44), maa://67084 (87.50)</t>
+          <t>maa://31212 (94.55), maa://24387 (84.44), maa://67084 (87.50)</t>
         </is>
       </c>
       <c r="U23" s="19" t="n"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AF23" s="8" t="inlineStr">
         <is>
-          <t>maa://31489 (98.31)</t>
+          <t>maa://31489 (98.33)</t>
         </is>
       </c>
       <c r="AG23" s="16" t="n"/>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>maa://24368 (85.22), maa://46650 (90.08)</t>
+          <t>maa://24368 (85.26), maa://46650 (90.21)</t>
         </is>
       </c>
       <c r="E24" s="19" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>maa://29988 (96.23), maa://23504 (94.05), *maa://25141 (79.74), maa://52227 (97.35), *maa://36663 (79.44)</t>
+          <t>maa://29988 (96.26), maa://23504 (94.05), *maa://25141 (79.74), maa://52227 (97.37), *maa://36663 (79.44)</t>
         </is>
       </c>
       <c r="Y24" s="19" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AF24" s="8" t="inlineStr">
         <is>
-          <t>maa://64165 (99.27), maa://22523 (80.09), maa://29910 (94.20), maa://45831 (93.55)</t>
+          <t>maa://64165 (99.16), maa://22523 (80.09), maa://29910 (94.20), maa://45831 (93.55)</t>
         </is>
       </c>
       <c r="AG24" s="16" t="n"/>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>maa://29753 (96.53), maa://63016 (99.10)</t>
+          <t>maa://29753 (96.54), maa://63016 (99.10)</t>
         </is>
       </c>
       <c r="E25" s="19" t="n"/>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>*maa://29063 (76.02), *maa://25311 (70.42), maa://45047 (88.00)</t>
+          <t>*maa://29063 (76.09), *maa://25311 (70.63), maa://45047 (88.00)</t>
         </is>
       </c>
       <c r="I25" s="19" t="n"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>maa://20109 (96.21), maa://22545 (100.00)</t>
+          <t>maa://20109 (96.24), maa://22545 (100.00)</t>
         </is>
       </c>
       <c r="U25" s="19" t="n"/>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="X25" s="8" t="inlineStr">
         <is>
-          <t>maa://29890 (91.20)</t>
+          <t>maa://29890 (91.27)</t>
         </is>
       </c>
       <c r="Y25" s="19" t="n"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB25" s="8" t="inlineStr">
         <is>
-          <t>maa://31215 (93.32), *maa://24516 (79.80), maa://26001 (83.33), maa://68311 (100.00)</t>
+          <t>maa://31215 (93.33), *maa://24516 (79.80), maa://26001 (83.33), maa://68311 (100.00)</t>
         </is>
       </c>
       <c r="AC25" s="19" t="n"/>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AF25" s="8" t="inlineStr">
         <is>
-          <t>maa://20108 (98.05), maa://36676 (99.84), maa://24621 (96.86), maa://22771 (88.24), maa://37772 (83.33)</t>
+          <t>maa://20108 (98.08), maa://36676 (99.84), maa://24621 (96.86), maa://22771 (88.24), maa://37772 (83.33)</t>
         </is>
       </c>
       <c r="AG25" s="16" t="n"/>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>maa://56374 (100.00), maa://41802 (96.36)</t>
+          <t>maa://56374 (100.00), maa://41802 (96.43)</t>
         </is>
       </c>
       <c r="E26" s="19" t="n"/>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>maa://56240 (96.02), maa://24913 (92.24)</t>
+          <t>maa://56240 (96.06), maa://24913 (92.24)</t>
         </is>
       </c>
       <c r="I26" s="19" t="n"/>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB26" s="8" t="inlineStr">
         <is>
-          <t>maa://42235 (98.34)</t>
+          <t>maa://42235 (98.36)</t>
         </is>
       </c>
       <c r="AC26" s="19" t="n"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>maa://39601 (90.74), maa://34494 (95.35)</t>
+          <t>maa://39601 (90.91), maa://34494 (95.40)</t>
         </is>
       </c>
       <c r="I27" s="19" t="n"/>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AF27" s="8" t="inlineStr">
         <is>
-          <t>maa://24023 (97.73)</t>
+          <t>maa://24023 (97.76)</t>
         </is>
       </c>
       <c r="AG27" s="16" t="n"/>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>maa://24465 (95.87), maa://25725 (85.27)</t>
+          <t>maa://24465 (95.88), maa://25725 (85.27)</t>
         </is>
       </c>
       <c r="E28" s="19" t="n"/>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>maa://29765 (93.33), maa://23263 (96.24)</t>
+          <t>maa://29765 (93.39), maa://23263 (96.24)</t>
         </is>
       </c>
       <c r="U28" s="19" t="n"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t>maa://39929 (97.36), maa://41749 (97.19)</t>
+          <t>maa://39929 (97.39), maa://41749 (97.20)</t>
         </is>
       </c>
       <c r="Y28" s="19" t="n"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AF28" s="8" t="inlineStr">
         <is>
-          <t>maa://36660 (94.22), maa://65700 (98.64)</t>
+          <t>maa://36660 (94.25), maa://65700 (98.65)</t>
         </is>
       </c>
       <c r="AG28" s="16" t="n"/>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>maa://31694 (99.31)</t>
+          <t>maa://31694 (99.32)</t>
         </is>
       </c>
       <c r="E29" s="19" t="n"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>maa://28432 (97.81), maa://31400 (98.06), maa://28440 (86.42)</t>
+          <t>maa://28432 (97.82), maa://31400 (98.06), maa://28440 (86.42)</t>
         </is>
       </c>
       <c r="M29" s="19" t="n"/>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AF29" s="8" t="inlineStr">
         <is>
-          <t>maa://42865 (92.11)</t>
+          <t>maa://42865 (92.15)</t>
         </is>
       </c>
       <c r="AG29" s="16" t="n"/>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>maa://30442 (97.44)</t>
+          <t>maa://30442 (97.46)</t>
         </is>
       </c>
       <c r="M30" s="19" t="n"/>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>maa://42979 (99.55), maa://45822 (100.00), maa://45045 (90.91)</t>
+          <t>maa://42979 (99.56), maa://45822 (100.00), maa://45045 (90.91)</t>
         </is>
       </c>
       <c r="AC30" s="19" t="n"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>maa://35926 (97.98), maa://36258 (93.08), maa://43904 (90.00)</t>
+          <t>maa://35926 (98.01), maa://36258 (93.08), maa://43904 (90.00)</t>
         </is>
       </c>
       <c r="M31" s="19" t="n"/>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>maa://28065 (97.00)</t>
+          <t>maa://28065 (97.06)</t>
         </is>
       </c>
       <c r="M32" s="19" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>maa://42859 (99.26), maa://41108 (87.72), maa://41238 (98.12), maa://45523 (100.00)</t>
+          <t>maa://42859 (99.27), maa://41108 (87.72), maa://41238 (98.12), maa://45523 (100.00)</t>
         </is>
       </c>
       <c r="U32" s="19" t="n"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t>maa://64104 (97.32)</t>
+          <t>maa://64104 (97.35)</t>
         </is>
       </c>
       <c r="Y32" s="19" t="n"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AF32" s="8" t="inlineStr">
         <is>
-          <t>maa://42408 (94.87)</t>
+          <t>maa://42408 (95.12)</t>
         </is>
       </c>
       <c r="AG32" s="16" t="n"/>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>maa://21956 (94.61), *maa://22730 (70.59), maa://69135 (100.00)</t>
+          <t>maa://21956 (94.62), *maa://22730 (70.59), maa://69135 (100.00)</t>
         </is>
       </c>
       <c r="Q33" s="19" t="n"/>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>maa://24526 (97.06)</t>
+          <t>maa://24526 (97.08)</t>
         </is>
       </c>
       <c r="U34" s="19" t="n"/>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB34" s="8" t="inlineStr">
         <is>
-          <t>maa://64329 (97.67)</t>
+          <t>maa://64329 (97.73)</t>
         </is>
       </c>
       <c r="AC34" s="19" t="n"/>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>maa://41296 (99.25)</t>
+          <t>maa://41296 (99.26)</t>
         </is>
       </c>
       <c r="M35" s="19" t="n"/>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>maa://27613 (99.54)</t>
+          <t>maa://27613 (99.55)</t>
         </is>
       </c>
       <c r="U36" s="19" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>maa://45718 (99.20), maa://56336 (99.34), maa://47069 (86.36), maa://45789 (100.00)</t>
+          <t>maa://45718 (99.20), maa://56336 (99.35), maa://47069 (86.36), maa://45789 (100.00)</t>
         </is>
       </c>
       <c r="M37" s="19" t="n"/>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>maa://21280 (97.57)</t>
+          <t>maa://21280 (97.59)</t>
         </is>
       </c>
       <c r="Q37" s="19" t="n"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>maa://30713 (98.25)</t>
+          <t>maa://30713 (98.28)</t>
         </is>
       </c>
       <c r="U38" s="19" t="n"/>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AF38" s="8" t="inlineStr">
         <is>
-          <t>maa://36697 (95.83), maa://68397 (99.35)</t>
+          <t>maa://36697 (95.67), maa://68397 (98.79)</t>
         </is>
       </c>
       <c r="AG38" s="16" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>maa://25199 (84.78), maa://45059 (93.70), maa://30434 (95.26), maa://44165 (85.71)</t>
+          <t>maa://25199 (84.78), maa://45059 (93.93), maa://30434 (95.31), maa://44165 (85.71)</t>
         </is>
       </c>
       <c r="I39" s="19" t="n"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>maa://47093 (98.15), maa://24709 (93.93)</t>
+          <t>maa://47093 (98.18), maa://24709 (93.93)</t>
         </is>
       </c>
       <c r="Q39" s="19" t="n"/>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>maa://47079 (95.58), maa://45790 (87.67)</t>
+          <t>maa://47079 (95.63), maa://45790 (87.84)</t>
         </is>
       </c>
       <c r="U39" s="19" t="n"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AF39" s="8" t="inlineStr">
         <is>
-          <t>maa://62953 (96.72)</t>
+          <t>maa://62953 (96.77)</t>
         </is>
       </c>
       <c r="AG39" s="16" t="n"/>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>maa://23278 (98.09), maa://21386 (95.94), maa://36664 (89.61), *maa://45550 (72.73)</t>
+          <t>maa://23278 (98.10), maa://21386 (95.94), maa://36664 (89.61), *maa://45550 (72.73)</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>maa://65283 (96.74), maa://64205 (93.75)</t>
+          <t>maa://65283 (96.79), maa://64205 (93.75)</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>*maa://22525 (70.39), maa://21284 (97.62)</t>
+          <t>*maa://22525 (70.39), maa://21284 (97.64)</t>
         </is>
       </c>
       <c r="I43" s="19" t="n"/>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>maa://29768 (98.23), maa://56386 (99.39), maa://27728 (96.40)</t>
+          <t>maa://29768 (98.24), maa://56386 (99.39), maa://27728 (96.40)</t>
         </is>
       </c>
       <c r="I44" s="19" t="n"/>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>maa://42459 (98.71), maa://21229 (85.59), maa://30807 (94.62), *maa://22767 (70.59)</t>
+          <t>maa://42459 (98.72), maa://21229 (85.59), maa://30807 (94.62), *maa://22767 (70.59)</t>
         </is>
       </c>
       <c r="I45" s="19" t="n"/>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>*maa://39364 (66.46)</t>
+          <t>*maa://39364 (66.88)</t>
         </is>
       </c>
       <c r="U45" s="19" t="n"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>maa://35931 (95.66), maa://43901 (96.27)</t>
+          <t>maa://35931 (95.70), maa://43901 (96.27)</t>
         </is>
       </c>
       <c r="I46" s="19" t="n"/>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="T49" s="19" t="inlineStr">
         <is>
-          <t>maa://67231 (99.09)</t>
+          <t>maa://67231 (99.10)</t>
         </is>
       </c>
       <c r="U49" s="19" t="n"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>maa://62852 (93.05)</t>
+          <t>maa://62852 (92.97)</t>
         </is>
       </c>
       <c r="Q50" s="19" t="n"/>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>maa://24376 (99.05)</t>
+          <t>maa://24376 (99.07)</t>
         </is>
       </c>
       <c r="I52" s="19" t="n"/>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>maa://59394 (99.36), maa://59378 (93.83), maa://65511 (100.00)</t>
+          <t>maa://59394 (99.37), maa://59378 (93.83), maa://65511 (100.00)</t>
         </is>
       </c>
       <c r="Q52" s="19" t="n"/>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>maa://32534 (97.87)</t>
+          <t>maa://32534 (97.89)</t>
         </is>
       </c>
       <c r="I53" s="19" t="n"/>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>maa://32532 (97.81)</t>
+          <t>maa://32532 (97.83)</t>
         </is>
       </c>
       <c r="I55" s="19" t="n"/>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>maa://56237 (98.69), maa://25176 (98.77)</t>
+          <t>maa://56237 (98.73), maa://25176 (98.77)</t>
         </is>
       </c>
       <c r="I57" s="19" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>*maa://37964 (65.25)</t>
+          <t>*maa://37964 (65.55)</t>
         </is>
       </c>
       <c r="I58" s="19" t="n"/>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>maa://31270 (98.32), maa://27746 (89.25)</t>
+          <t>maa://31270 (98.33), maa://27746 (89.25)</t>
         </is>
       </c>
       <c r="I59" s="19" t="n"/>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>maa://40438 (91.53)</t>
+          <t>maa://40438 (91.57)</t>
         </is>
       </c>
       <c r="I60" s="19" t="n"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>maa://42981 (96.67), maa://56228 (98.68), maa://43903 (100.00)</t>
+          <t>maa://42981 (96.70), maa://56228 (98.06), maa://43903 (100.00)</t>
         </is>
       </c>
       <c r="I62" s="19" t="n"/>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>maa://59534 (99.40), *maa://59693 (74.47), maa://59413 (97.30)</t>
+          <t>maa://59534 (99.41), *maa://59693 (74.47), maa://59413 (97.30)</t>
         </is>
       </c>
       <c r="I63" s="19" t="n"/>
@@ -7164,7 +7164,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.09.26 13:19:42</t>
+          <t>更新日期：2025.09.27 13:18:55</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>maa://20919 (98.00), *maa://31611 (76.92)</t>
+          <t>maa://20919 (98.04), *maa://31611 (76.92)</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>maa://44235 (98.41), maa://45604 (100.00), maa://20961 (100.00), maa://20910 (100.00), maa://44220 (100.00)</t>
+          <t>maa://44235 (98.42), maa://45604 (100.00), maa://20961 (100.00), maa://20910 (100.00), maa://44220 (100.00)</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>*maa://20845 (69.23), maa://38727 (91.67)</t>
+          <t>*maa://20845 (70.37), maa://38727 (91.67)</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>maa://20944 (96.15), maa://35393 (100.00)</t>
+          <t>maa://20944 (96.23), maa://35393 (100.00)</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>maa://20869 (100.00), maa://44690 (95.83)</t>
+          <t>maa://20869 (100.00), maa://44690 (95.92)</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="D150" s="13" t="inlineStr">
         <is>
-          <t>maa://40957 (94.83), maa://36641 (98.24), maa://36865 (95.45), maa://44635 (88.18), maa://44660 (92.68), maa://41128 (84.21), maa://46108 (100.00), maa://42918 (100.00), maa://44119 (97.44), maa://64408 (92.86), maa://37300 (100.00), maa://42917 (100.00)</t>
+          <t>maa://40957 (94.84), maa://36641 (98.24), maa://36865 (95.45), maa://44635 (88.18), maa://44660 (92.68), maa://41128 (84.21), maa://46108 (100.00), maa://42918 (100.00), maa://44119 (97.44), maa://64408 (92.86), maa://37300 (100.00), maa://42917 (100.00)</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>maa://44232 (98.47), maa://45603 (90.62), *maa://65963 (80.00), *maa://63114 (66.67)</t>
+          <t>maa://44232 (98.48), maa://45603 (90.62), *maa://65963 (80.00), *maa://63114 (66.67)</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>maa://49867 (93.59), maa://49655 (97.73)</t>
+          <t>maa://49867 (93.67), maa://49655 (97.73)</t>
         </is>
       </c>
       <c r="E169" s="14" t="inlineStr">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>maa://44224 (90.46), maa://35854 (84.75), maa://50388 (98.25), maa://25760 (86.55), ***maa://43911 (11.11), *maa://20872 (52.00), maa://51066 (87.50), maa://63024 (94.59)</t>
+          <t>maa://44224 (90.46), maa://35854 (84.75), maa://50388 (98.25), maa://25760 (86.55), ***maa://43911 (11.11), *maa://20872 (52.00), maa://51066 (87.50), maa://63024 (94.74)</t>
         </is>
       </c>
       <c r="E198" s="14" t="inlineStr">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>*maa://29644 (73.08), maa://39159 (96.88), ***maa://30061 (27.27)</t>
+          <t>*maa://29644 (73.08), maa://39159 (93.94), ***maa://30061 (27.27)</t>
         </is>
       </c>
       <c r="E230" s="14" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="D247" s="13" t="inlineStr">
         <is>
-          <t>maa://20867 (93.33), maa://38485 (96.43), *maa://32202 (80.00)</t>
+          <t>maa://20867 (93.33), maa://38485 (96.55), *maa://32202 (80.00)</t>
         </is>
       </c>
       <c r="E247" s="14" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="D251" s="13" t="inlineStr">
         <is>
-          <t>maa://28923 (91.87), maa://28906 (98.28), ***maa://28825 (11.54), maa://65613 (100.00)</t>
+          <t>maa://28923 (91.87), maa://28906 (98.31), ***maa://28825 (11.54), maa://65613 (100.00)</t>
         </is>
       </c>
       <c r="E251" s="14" t="inlineStr">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>maa://42287 (91.80), maa://45570 (96.72), maa://60678 (93.33), maa://42225 (100.00)</t>
+          <t>maa://42287 (91.87), maa://45570 (96.72), maa://60678 (93.33), maa://42225 (100.00)</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>maa://53348 (86.67)</t>
+          <t>maa://53348 (87.10)</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>*maa://62755 (70.59), maa://62761 (91.67)</t>
+          <t>*maa://62755 (72.22), maa://62761 (92.31)</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -24714,7 +24714,7 @@
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>maa://39692 (99.54), maa://39810 (90.00)</t>
+          <t>maa://39692 (99.54), maa://39810 (90.32)</t>
         </is>
       </c>
       <c r="E326" s="14" t="inlineStr">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="D350" s="22" t="inlineStr">
         <is>
-          <t>maa://32647 (97.59), maa://32415 (84.73), maa://34677 (100.00), maa://32892 (100.00), maa://32653 (81.25), maa://61839 (100.00), maa://61275 (100.00)</t>
+          <t>maa://32647 (97.59), maa://32415 (84.77), maa://34677 (100.00), maa://32892 (100.00), maa://32653 (81.25), maa://61839 (100.00), maa://61275 (100.00)</t>
         </is>
       </c>
       <c r="E350" s="22" t="inlineStr">
@@ -27036,7 +27036,7 @@
       </c>
       <c r="D369" s="22" t="inlineStr">
         <is>
-          <t>maa://40957 (94.83), maa://48026 (94.70), maa://44635 (88.18), maa://41035 (93.51), *maa://60251 (76.47), maa://44660 (92.68), maa://41128 (84.21)</t>
+          <t>maa://40957 (94.84), maa://48026 (94.70), maa://44635 (88.18), maa://41035 (93.51), *maa://60251 (76.47), maa://44660 (92.68), maa://41128 (84.21)</t>
         </is>
       </c>
       <c r="E369" s="22" t="inlineStr">
@@ -27522,7 +27522,7 @@
       </c>
       <c r="D378" s="22" t="inlineStr">
         <is>
-          <t>maa://41110 (98.52), maa://45605 (90.00)</t>
+          <t>maa://41110 (98.53), maa://45605 (90.00)</t>
         </is>
       </c>
       <c r="E378" s="22" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="D381" s="22" t="inlineStr">
         <is>
-          <t>maa://44233 (91.67), maa://45570 (96.72)</t>
+          <t>maa://44233 (91.80), maa://45570 (96.72)</t>
         </is>
       </c>
       <c r="E381" s="22" t="inlineStr">
@@ -28359,7 +28359,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://47023 (87.80)</t>
+          <t>maa://47023 (86.05)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -28413,7 +28413,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>maa://59533 (97.83), maa://59577 (100.00)</t>
+          <t>maa://59533 (97.87), maa://59577 (100.00)</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -28710,7 +28710,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>maa://64040 (98.98), maa://52505 (98.50), maa://66377 (93.33), ***maa://66376 (25.00)</t>
+          <t>maa://64040 (98.99), maa://52505 (98.50), maa://66377 (93.33), ***maa://66376 (25.00)</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -28764,7 +28764,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>maa://67388 (91.89)</t>
+          <t>maa://67388 (92.11)</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -28845,7 +28845,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>maa://67087 (93.55), maa://67268 (96.05), maa://67269 (88.24), maa://67648 (100.00)</t>
+          <t>maa://67087 (93.62), maa://67268 (96.10), maa://67269 (88.24), maa://67648 (100.00)</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>maa://25390 (98.33), maa://24702 (95.08), maa://36681 (85.39)</t>
+          <t>maa://25390 (98.35), maa://24702 (95.08), maa://36681 (85.39)</t>
         </is>
       </c>
       <c r="E2" s="19" t="n"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>maa://58660 (98.88), maa://39402 (94.94), *maa://34787 (75.00)</t>
+          <t>maa://58660 (98.89), maa://39402 (94.98), *maa://34787 (75.00)</t>
         </is>
       </c>
       <c r="M2" s="19" t="n"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>maa://22742 (97.32), maa://66635 (99.57)</t>
+          <t>maa://22742 (97.33), maa://66635 (99.57)</t>
         </is>
       </c>
       <c r="U2" s="19" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="AB2" s="8" t="inlineStr">
         <is>
-          <t>maa://36684 (98.25), maa://21246 (91.37)</t>
+          <t>maa://36684 (98.26), maa://21246 (91.37)</t>
         </is>
       </c>
       <c r="AC2" s="19" t="n"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>maa://59087 (97.27), maa://25251 (91.61)</t>
+          <t>maa://59087 (97.30), maa://25251 (91.61)</t>
         </is>
       </c>
       <c r="AG2" s="16" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>maa://22880 (91.09), maa://20276 (94.05), maa://22749 (84.62)</t>
+          <t>maa://22880 (91.08), maa://20276 (94.05), maa://22749 (84.62)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>maa://21249 (98.41), maa://26254 (98.15), *maa://22738 (80.00)</t>
+          <t>maa://21249 (98.43), maa://26254 (98.15), *maa://22738 (80.00)</t>
         </is>
       </c>
       <c r="Q3" s="19" t="n"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>maa://60545 (98.75), maa://45854 (87.44), maa://24617 (91.18)</t>
+          <t>maa://60545 (98.76), maa://45854 (87.56), maa://24617 (91.18)</t>
         </is>
       </c>
       <c r="U3" s="19" t="n"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="AF3" s="8" t="inlineStr">
         <is>
-          <t>maa://21289 (92.04)</t>
+          <t>maa://21289 (92.11)</t>
         </is>
       </c>
       <c r="AG3" s="16" t="n"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>maa://24632 (98.07), maa://22499 (90.00), maa://22746 (100.00)</t>
+          <t>maa://24632 (98.08), maa://22499 (90.00), maa://22746 (100.00)</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>maa://49983 (99.11), maa://50121 (96.15)</t>
+          <t>maa://49983 (99.12), maa://50121 (96.15)</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>maa://27295 (97.72), maa://32509 (96.43), maa://31008 (95.21), maa://22754 (88.16)</t>
+          <t>maa://27295 (97.73), maa://32509 (96.44), maa://31008 (95.21), maa://22754 (88.16)</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="X4" s="8" t="inlineStr">
         <is>
-          <t>maa://43217 (98.86)</t>
+          <t>maa://43217 (98.87)</t>
         </is>
       </c>
       <c r="Y4" s="19" t="n"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>maa://21245 (91.33), maa://54105 (98.50), *maa://22744 (80.00)</t>
+          <t>maa://21245 (91.33), maa://54105 (98.52), *maa://22744 (80.00)</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>maa://21919 (98.65), maa://21281 (81.25)</t>
+          <t>maa://21919 (98.67), maa://21281 (81.25)</t>
         </is>
       </c>
       <c r="Q5" s="19" t="n"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>maa://42407 (97.45)</t>
+          <t>maa://42407 (97.46)</t>
         </is>
       </c>
       <c r="E6" s="19" t="n"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>maa://24370 (97.54)</t>
+          <t>maa://24370 (97.56)</t>
         </is>
       </c>
       <c r="I6" s="19" t="n"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB6" s="8" t="inlineStr">
         <is>
-          <t>maa://22739 (89.36)</t>
+          <t>maa://22739 (89.47)</t>
         </is>
       </c>
       <c r="AC6" s="19" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>maa://21955 (98.20)</t>
+          <t>maa://21955 (98.21)</t>
         </is>
       </c>
       <c r="E7" s="19" t="n"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>*maa://22763 (75.00), maa://64972 (95.45)</t>
+          <t>*maa://22763 (75.00), maa://64972 (95.65)</t>
         </is>
       </c>
       <c r="I7" s="19" t="n"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>maa://28624 (98.62), maa://24957 (94.55)</t>
+          <t>maa://28624 (98.64), maa://24957 (94.55)</t>
         </is>
       </c>
       <c r="M7" s="19" t="n"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="P7" s="8" t="inlineStr">
         <is>
-          <t>maa://22750 (96.95)</t>
+          <t>maa://22750 (96.97)</t>
         </is>
       </c>
       <c r="Q7" s="19" t="n"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>maa://21291 (94.01)</t>
+          <t>maa://21291 (94.05)</t>
         </is>
       </c>
       <c r="U7" s="19" t="n"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="X7" s="8" t="inlineStr">
         <is>
-          <t>maa://22399 (97.23), maa://22758 (82.35)</t>
+          <t>maa://22399 (97.24), maa://22758 (82.35)</t>
         </is>
       </c>
       <c r="Y7" s="19" t="n"/>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AF7" s="8" t="inlineStr">
         <is>
-          <t>maa://45272 (99.45)</t>
+          <t>maa://45272 (99.46)</t>
         </is>
       </c>
       <c r="AG7" s="16" t="n"/>
@@ -1482,7 +1482,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.03 13:19:12</t>
+          <t>更新日期：2025.10.04 13:18:25</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>maa://21476 (90.06)</t>
+          <t>maa://21476 (90.18)</t>
         </is>
       </c>
       <c r="E8" s="19" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>maa://32931 (91.29), maa://23252 (91.67), maa://37496 (98.33)</t>
+          <t>maa://32931 (91.31), maa://23252 (91.67), maa://37496 (98.33)</t>
         </is>
       </c>
       <c r="Q8" s="19" t="n"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>maa://21411 (96.07), maa://67587 (98.62)</t>
+          <t>maa://21411 (96.08), maa://67587 (98.65)</t>
         </is>
       </c>
       <c r="Y8" s="19" t="n"/>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AF8" s="8" t="inlineStr">
         <is>
-          <t>maa://24479 (84.38), *maa://21990 (51.72)</t>
+          <t>maa://24479 (84.46), *maa://21990 (51.72)</t>
         </is>
       </c>
       <c r="AG8" s="16" t="n"/>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>maa://22762 (96.33), maa://39552 (88.00)</t>
+          <t>maa://22762 (96.35), maa://39552 (88.00)</t>
         </is>
       </c>
       <c r="M9" s="19" t="n"/>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>maa://26222 (99.45)</t>
+          <t>maa://26222 (99.46)</t>
         </is>
       </c>
       <c r="U9" s="19" t="n"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
-          <t>maa://28711 (95.23), maa://40166 (94.81)</t>
+          <t>maa://28711 (95.27), maa://40166 (94.87)</t>
         </is>
       </c>
       <c r="AC9" s="19" t="n"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AF9" s="8" t="inlineStr">
         <is>
-          <t>maa://26206 (91.32), maa://66916 (98.12)</t>
+          <t>maa://26206 (91.32), maa://66916 (98.15)</t>
         </is>
       </c>
       <c r="AG9" s="16" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="P10" s="8" t="inlineStr">
         <is>
-          <t>maa://28977 (91.97), *maa://36669 (74.36)</t>
+          <t>maa://28977 (92.00), *maa://36669 (74.36)</t>
         </is>
       </c>
       <c r="Q10" s="19" t="n"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (99.26), maa://22755 (91.62), maa://63521 (94.40)</t>
+          <t>maa://27395 (99.26), maa://22755 (91.67), maa://63521 (94.42)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t>maa://45828 (99.26), maa://22301 (97.64), maa://22726 (100.00)</t>
+          <t>maa://45828 (99.26), maa://22301 (97.65), maa://22726 (100.00)</t>
         </is>
       </c>
       <c r="Y10" s="19" t="n"/>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AF10" s="8" t="inlineStr">
         <is>
-          <t>*maa://25021 (57.32), *maa://22733 (64.62), **maa://22761 (33.33)</t>
+          <t>*maa://25021 (57.32), *maa://22733 (65.15), **maa://22761 (33.33)</t>
         </is>
       </c>
       <c r="AG10" s="16" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>maa://22747 (93.33), maa://22501 (99.54), maa://64808 (100.00), maa://45521 (95.24)</t>
+          <t>maa://22747 (93.40), maa://22501 (99.54), maa://64808 (100.00), maa://45521 (95.24)</t>
         </is>
       </c>
       <c r="U11" s="19" t="n"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="X11" s="8" t="inlineStr">
         <is>
-          <t>maa://36713 (99.27)</t>
+          <t>maa://36713 (99.28)</t>
         </is>
       </c>
       <c r="Y11" s="19" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>maa://21867 (93.56), maa://54294 (96.69)</t>
+          <t>maa://21867 (93.58), maa://54294 (96.72)</t>
         </is>
       </c>
       <c r="I12" s="19" t="n"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>maa://63896 (98.01), maa://64046 (98.60)</t>
+          <t>maa://63896 (98.02), maa://64046 (98.60)</t>
         </is>
       </c>
       <c r="M12" s="19" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>maa://37962 (98.83), maa://21485 (81.70), maa://22753 (92.83)</t>
+          <t>maa://37962 (98.84), maa://21485 (81.86), maa://22753 (92.83)</t>
         </is>
       </c>
       <c r="Y12" s="19" t="n"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
-          <t>maa://36677 (99.06), maa://23669 (94.83), maa://39872 (98.32)</t>
+          <t>maa://36677 (99.07), maa://23669 (94.83), maa://39872 (98.32)</t>
         </is>
       </c>
       <c r="AC12" s="19" t="n"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AF12" s="8" t="inlineStr">
         <is>
-          <t>maa://28932 (94.67)</t>
+          <t>maa://28932 (94.70)</t>
         </is>
       </c>
       <c r="AG12" s="16" t="n"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>maa://24999 (96.69), maa://36673 (94.16), maa://25001 (88.76)</t>
+          <t>maa://24999 (96.71), maa://36673 (94.16), maa://25001 (88.76)</t>
         </is>
       </c>
       <c r="E13" s="19" t="n"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.33), maa://66545 (99.04)</t>
+          <t>*maa://21248 (73.40), maa://66545 (98.82)</t>
         </is>
       </c>
       <c r="I13" s="19" t="n"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="P13" s="8" t="inlineStr">
         <is>
-          <t>maa://22676 (97.76), maa://22583 (88.12)</t>
+          <t>maa://22676 (97.78), maa://22583 (88.34)</t>
         </is>
       </c>
       <c r="Q13" s="19" t="n"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="X13" s="8" t="inlineStr">
         <is>
-          <t>maa://34957 (94.57)</t>
+          <t>maa://34957 (94.58)</t>
         </is>
       </c>
       <c r="Y13" s="19" t="n"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AF13" s="8" t="inlineStr">
         <is>
-          <t>maa://39883 (93.97)</t>
+          <t>maa://39883 (93.99)</t>
         </is>
       </c>
       <c r="AG13" s="16" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>maa://39841 (99.05), maa://36682 (98.31), maa://26245 (97.06), maa://21288 (96.40)</t>
+          <t>maa://39841 (99.06), maa://36682 (98.32), maa://26245 (97.06), maa://21288 (96.40)</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>maa://22743 (85.42), maa://45058 (98.20), maa://22734 (84.96), *maa://36048 (74.86), maa://69928 (100.00)</t>
+          <t>maa://22743 (85.45), maa://45058 (98.22), maa://22734 (84.96), *maa://36048 (74.86), maa://69928 (100.00)</t>
         </is>
       </c>
       <c r="E15" s="19" t="n"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>maa://24304 (97.05), maa://21478 (90.48)</t>
+          <t>maa://24304 (97.06), maa://21478 (90.48)</t>
         </is>
       </c>
       <c r="I15" s="19" t="n"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>maa://23892 (97.63)</t>
+          <t>maa://23892 (97.65)</t>
         </is>
       </c>
       <c r="U15" s="19" t="n"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AF15" s="8" t="inlineStr">
         <is>
-          <t>maa://36666 (96.34), maa://21364 (83.80), *maa://22766 (70.71), *maa://68306 (78.95)</t>
+          <t>maa://36666 (96.35), maa://21364 (83.80), *maa://22766 (70.71), *maa://68306 (78.95)</t>
         </is>
       </c>
       <c r="AG15" s="16" t="n"/>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>maa://28504 (96.30)</t>
+          <t>maa://28504 (96.32)</t>
         </is>
       </c>
       <c r="Q16" s="19" t="n"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>maa://23911 (90.64), maa://27755 (93.75), maa://67613 (99.46)</t>
+          <t>maa://23911 (90.64), maa://27755 (93.75), maa://67613 (99.47)</t>
         </is>
       </c>
       <c r="AG16" s="16" t="n"/>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>maa://39599 (98.25), maa://22430 (90.25)</t>
+          <t>maa://39599 (98.26), maa://22430 (90.25)</t>
         </is>
       </c>
       <c r="I17" s="19" t="n"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>maa://24570 (98.37)</t>
+          <t>maa://24570 (98.24)</t>
         </is>
       </c>
       <c r="E18" s="19" t="n"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>maa://24421 (95.15)</t>
+          <t>maa://24421 (95.17)</t>
         </is>
       </c>
       <c r="I18" s="19" t="n"/>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB18" s="8" t="inlineStr">
         <is>
-          <t>maa://24393 (99.01)</t>
+          <t>maa://24393 (99.02)</t>
         </is>
       </c>
       <c r="AC18" s="19" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AF18" s="8" t="inlineStr">
         <is>
-          <t>maa://47854 (93.06)</t>
+          <t>maa://47854 (93.10)</t>
         </is>
       </c>
       <c r="AG18" s="16" t="n"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>maa://24386 (99.68)</t>
+          <t>maa://24386 (99.51)</t>
         </is>
       </c>
       <c r="U19" s="19" t="n"/>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t>maa://31386 (97.56), maa://58490 (85.00)</t>
+          <t>maa://31386 (97.62), maa://58490 (85.00)</t>
         </is>
       </c>
       <c r="Y19" s="19" t="n"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
-          <t>maa://30709 (86.18), *maa://36668 (69.83)</t>
+          <t>maa://30709 (86.20), *maa://36668 (69.83)</t>
         </is>
       </c>
       <c r="AC19" s="19" t="n"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>maa://25198 (97.68), maa://36680 (99.09), maa://21432 (91.53)</t>
+          <t>maa://25198 (97.69), maa://36680 (99.09), maa://21432 (91.53)</t>
         </is>
       </c>
       <c r="E20" s="19" t="n"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>maa://22864 (96.05)</t>
+          <t>maa://22864 (96.08)</t>
         </is>
       </c>
       <c r="I20" s="19" t="n"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>maa://41331 (95.42)</t>
+          <t>maa://41331 (95.43)</t>
         </is>
       </c>
       <c r="M20" s="19" t="n"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://50085 (96.54), maa://56241 (98.27), maa://49976 (88.57)</t>
+          <t>maa://50085 (96.57), maa://56241 (98.28), maa://49976 (88.57)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>maa://21261 (99.03)</t>
+          <t>maa://21261 (99.04)</t>
         </is>
       </c>
       <c r="E21" s="19" t="n"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>maa://24372 (98.88)</t>
+          <t>maa://24372 (98.89)</t>
         </is>
       </c>
       <c r="I21" s="19" t="n"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>maa://31731 (96.52)</t>
+          <t>maa://31731 (96.55)</t>
         </is>
       </c>
       <c r="M21" s="19" t="n"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>maa://34946 (98.09), maa://20110 (87.01)</t>
+          <t>maa://34946 (98.11), maa://20110 (87.01)</t>
         </is>
       </c>
       <c r="Y21" s="19" t="n"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB21" s="8" t="inlineStr">
         <is>
-          <t>maa://21443 (87.07), maa://52223 (83.14)</t>
+          <t>maa://21443 (87.10), maa://52223 (83.33)</t>
         </is>
       </c>
       <c r="AC21" s="19" t="n"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AF21" s="8" t="inlineStr">
         <is>
-          <t>maa://22432 (94.24), maa://22524 (83.16), maa://64221 (97.96)</t>
+          <t>maa://22432 (94.30), maa://22524 (83.22), maa://64221 (97.97)</t>
         </is>
       </c>
       <c r="AG21" s="16" t="n"/>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>maa://27127 (83.47), *maa://22751 (71.26), maa://66865 (99.42)</t>
+          <t>maa://27127 (83.47), *maa://22751 (71.26), maa://66865 (99.43)</t>
         </is>
       </c>
       <c r="M22" s="19" t="n"/>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>maa://37649 (94.80), maa://21282 (98.96)</t>
+          <t>maa://37649 (94.84), maa://21282 (98.97)</t>
         </is>
       </c>
       <c r="Y22" s="19" t="n"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AB22" s="8" t="inlineStr">
         <is>
-          <t>maa://23656 (99.51)</t>
+          <t>maa://23656 (99.52)</t>
         </is>
       </c>
       <c r="AC22" s="19" t="n"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>maa://39756 (98.59), maa://39875 (95.80)</t>
+          <t>maa://39756 (98.60), maa://39875 (95.80)</t>
         </is>
       </c>
       <c r="M23" s="19" t="n"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>maa://30587 (96.76), maa://29748 (81.77), *maa://37566 (78.46)</t>
+          <t>maa://30587 (96.77), maa://29748 (81.77), *maa://37566 (78.46)</t>
         </is>
       </c>
       <c r="Q23" s="19" t="n"/>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>maa://31212 (94.87), maa://24387 (84.44), maa://67084 (87.50)</t>
+          <t>maa://31212 (94.92), maa://24387 (84.44), maa://67084 (87.50)</t>
         </is>
       </c>
       <c r="U23" s="19" t="n"/>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB23" s="8" t="inlineStr">
         <is>
-          <t>maa://29652 (96.59)</t>
+          <t>maa://29652 (96.63)</t>
         </is>
       </c>
       <c r="AC23" s="19" t="n"/>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>maa://24368 (85.50), maa://46650 (90.75)</t>
+          <t>maa://24368 (85.53), maa://46650 (90.77)</t>
         </is>
       </c>
       <c r="E24" s="19" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>maa://29988 (96.42), maa://23504 (94.06), *maa://25141 (79.74), maa://52227 (97.45), *maa://36663 (79.44)</t>
+          <t>maa://29988 (96.37), maa://23504 (94.06), *maa://25141 (79.74), maa://52227 (97.11), *maa://36663 (79.44)</t>
         </is>
       </c>
       <c r="Y24" s="19" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AF24" s="8" t="inlineStr">
         <is>
-          <t>maa://64165 (99.19), maa://22523 (80.18), maa://29910 (94.20), maa://45831 (93.55)</t>
+          <t>maa://64165 (99.20), maa://22523 (80.18), maa://29910 (94.20), maa://45831 (93.55)</t>
         </is>
       </c>
       <c r="AG24" s="16" t="n"/>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>maa://29753 (96.62), maa://63016 (99.14)</t>
+          <t>maa://29753 (96.62), maa://63016 (99.15)</t>
         </is>
       </c>
       <c r="E25" s="19" t="n"/>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>*maa://29063 (76.22), *maa://25311 (70.83), maa://45047 (88.46)</t>
+          <t>*maa://29063 (76.35), *maa://25311 (70.83), maa://45047 (88.46)</t>
         </is>
       </c>
       <c r="I25" s="19" t="n"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB25" s="8" t="inlineStr">
         <is>
-          <t>maa://31215 (93.41), *maa://24516 (79.00), maa://26001 (83.33), maa://68311 (98.57)</t>
+          <t>maa://31215 (93.45), *maa://24516 (79.00), maa://26001 (83.33), maa://68311 (98.59)</t>
         </is>
       </c>
       <c r="AC25" s="19" t="n"/>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>maa://56240 (96.28), maa://24913 (92.24)</t>
+          <t>maa://56240 (96.31), maa://24913 (92.24)</t>
         </is>
       </c>
       <c r="I26" s="19" t="n"/>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="X26" s="8" t="inlineStr">
         <is>
-          <t>maa://24389 (98.31)</t>
+          <t>maa://24389 (98.33)</t>
         </is>
       </c>
       <c r="Y26" s="19" t="n"/>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB26" s="8" t="inlineStr">
         <is>
-          <t>maa://42235 (98.40)</t>
+          <t>maa://42235 (98.41)</t>
         </is>
       </c>
       <c r="AC26" s="19" t="n"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>maa://30624 (89.94)</t>
+          <t>maa://30624 (90.00)</t>
         </is>
       </c>
       <c r="U27" s="19" t="n"/>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>maa://24465 (95.95), maa://25725 (85.38)</t>
+          <t>maa://24465 (95.96), maa://25725 (85.38)</t>
         </is>
       </c>
       <c r="E28" s="19" t="n"/>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>maa://29765 (93.71), maa://23263 (96.27)</t>
+          <t>maa://29765 (93.74), maa://23263 (96.27)</t>
         </is>
       </c>
       <c r="U28" s="19" t="n"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t>maa://39929 (97.36), maa://41749 (97.23)</t>
+          <t>maa://39929 (97.37), maa://41749 (97.24)</t>
         </is>
       </c>
       <c r="Y28" s="19" t="n"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AF28" s="8" t="inlineStr">
         <is>
-          <t>maa://36660 (94.38), maa://65700 (98.69)</t>
+          <t>maa://36660 (94.39), maa://65700 (98.70)</t>
         </is>
       </c>
       <c r="AG28" s="16" t="n"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>maa://28432 (97.80), maa://31400 (98.10), maa://28440 (86.50)</t>
+          <t>maa://28432 (97.81), maa://31400 (98.10), maa://28440 (86.50)</t>
         </is>
       </c>
       <c r="M29" s="19" t="n"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>maa://54169 (97.50)</t>
+          <t>maa://54169 (97.52)</t>
         </is>
       </c>
       <c r="Q29" s="19" t="n"/>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AF29" s="8" t="inlineStr">
         <is>
-          <t>maa://42865 (92.16)</t>
+          <t>maa://42865 (92.17)</t>
         </is>
       </c>
       <c r="AG29" s="16" t="n"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>maa://35926 (98.07), maa://36258 (93.15), maa://43904 (88.10)</t>
+          <t>maa://35926 (98.08), maa://36258 (93.17), maa://43904 (88.10)</t>
         </is>
       </c>
       <c r="M31" s="19" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AB31" s="8" t="inlineStr">
         <is>
-          <t>maa://66997 (100.00)</t>
+          <t>maa://66997 (95.45)</t>
         </is>
       </c>
       <c r="AC31" s="19" t="n"/>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>maa://21956 (94.59), maa://69135 (95.00)</t>
+          <t>maa://21956 (94.61), maa://69135 (91.30)</t>
         </is>
       </c>
       <c r="Q33" s="19" t="n"/>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>maa://24526 (97.15)</t>
+          <t>maa://24526 (97.16)</t>
         </is>
       </c>
       <c r="U34" s="19" t="n"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>maa://24375 (94.44)</t>
+          <t>maa://24375 (94.52)</t>
         </is>
       </c>
       <c r="I36" s="19" t="n"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AB36" s="19" t="inlineStr">
         <is>
-          <t>maa://64106 (97.22)</t>
+          <t>maa://64106 (97.30)</t>
         </is>
       </c>
       <c r="AC36" s="19" t="n"/>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>maa://21280 (97.66)</t>
+          <t>maa://21280 (97.67)</t>
         </is>
       </c>
       <c r="Q37" s="19" t="n"/>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AF38" s="8" t="inlineStr">
         <is>
-          <t>maa://36697 (95.75), maa://68397 (99.10)</t>
+          <t>maa://36697 (95.76), maa://68397 (99.13)</t>
         </is>
       </c>
       <c r="AG38" s="16" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>maa://25199 (84.78), maa://45059 (94.12), maa://30434 (95.34), maa://44165 (85.71)</t>
+          <t>maa://25199 (84.78), maa://45059 (94.20), maa://30434 (95.34), maa://44165 (85.71)</t>
         </is>
       </c>
       <c r="I39" s="19" t="n"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>maa://47093 (98.28), maa://24709 (94.07)</t>
+          <t>maa://47093 (98.29), maa://24709 (94.09)</t>
         </is>
       </c>
       <c r="Q39" s="19" t="n"/>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>maa://47079 (95.70), maa://45790 (88.16)</t>
+          <t>maa://47079 (95.71), maa://45790 (88.16)</t>
         </is>
       </c>
       <c r="U39" s="19" t="n"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AF39" s="8" t="inlineStr">
         <is>
-          <t>maa://62953 (96.81)</t>
+          <t>maa://62953 (96.82)</t>
         </is>
       </c>
       <c r="AG39" s="16" t="n"/>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>maa://23278 (98.14), maa://21386 (95.96), maa://36664 (89.74), *maa://45550 (75.00)</t>
+          <t>maa://23278 (98.15), maa://21386 (95.96), maa://36664 (89.74), *maa://45550 (75.00)</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>maa://65283 (97.03), maa://64205 (93.75)</t>
+          <t>maa://65283 (97.07), maa://64205 (93.94)</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>*maa://22525 (70.09), maa://21284 (97.77)</t>
+          <t>maa://21284 (97.79)</t>
         </is>
       </c>
       <c r="I43" s="19" t="n"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>maa://35931 (95.85), maa://43901 (96.34)</t>
+          <t>maa://35931 (95.88), maa://43901 (96.35)</t>
         </is>
       </c>
       <c r="I46" s="19" t="n"/>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>maa://27410 (97.52), maa://29661 (97.24), maa://56236 (99.79), maa://28038 (84.62)</t>
+          <t>maa://27410 (97.53), maa://29661 (97.24), maa://56236 (99.80), maa://28038 (84.62)</t>
         </is>
       </c>
       <c r="I47" s="19" t="n"/>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>maa://67476 (99.57), maa://68392 (99.61)</t>
+          <t>maa://67476 (99.57), maa://68392 (99.62)</t>
         </is>
       </c>
       <c r="U47" s="19" t="n"/>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="T49" s="19" t="inlineStr">
         <is>
-          <t>maa://67231 (99.15)</t>
+          <t>maa://67231 (99.16)</t>
         </is>
       </c>
       <c r="U49" s="19" t="n"/>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>maa://62852 (93.25)</t>
+          <t>maa://62852 (93.29)</t>
         </is>
       </c>
       <c r="Q50" s="19" t="n"/>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>maa://30769 (90.00)</t>
+          <t>maa://30769 (90.32)</t>
         </is>
       </c>
       <c r="I51" s="19" t="n"/>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>maa://59394 (99.40), maa://59378 (93.83), maa://65511 (100.00)</t>
+          <t>maa://59394 (99.41), maa://59378 (93.83), maa://65511 (100.00)</t>
         </is>
       </c>
       <c r="Q52" s="19" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>maa://32534 (97.94)</t>
+          <t>maa://32534 (97.96)</t>
         </is>
       </c>
       <c r="I53" s="19" t="n"/>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>maa://56237 (98.22), maa://25176 (98.77)</t>
+          <t>maa://56237 (98.24), maa://25176 (98.77)</t>
         </is>
       </c>
       <c r="I57" s="19" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>maa://42981 (96.74), maa://56228 (98.12), maa://43903 (100.00)</t>
+          <t>maa://42981 (96.74), maa://56228 (98.14), maa://43903 (100.00)</t>
         </is>
       </c>
       <c r="I62" s="19" t="n"/>
@@ -7160,7 +7160,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.03 13:19:12</t>
+          <t>更新日期：2025.10.04 13:18:25</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>*maa://20849 (73.21), *maa://28758 (71.74), maa://29036 (96.67), *maa://42172 (71.43), maa://65357 (96.55), maa://30285 (100.00)</t>
+          <t>*maa://20849 (73.21), *maa://28758 (71.74), maa://29036 (96.67), *maa://42172 (71.43), maa://65357 (96.67), maa://30285 (100.00)</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>maa://27376 (93.44), maa://42635 (94.44), *maa://20838 (55.00)</t>
+          <t>maa://27376 (91.94), maa://42635 (94.44), *maa://20838 (55.00)</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>*maa://39025 (77.78)</t>
+          <t>*maa://39025 (80.00)</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>maa://44235 (98.45), maa://45604 (100.00), maa://20961 (100.00), maa://20910 (100.00), maa://44220 (100.00)</t>
+          <t>maa://44235 (98.45), maa://45604 (100.00), maa://20961 (93.75), maa://44220 (100.00), maa://20910 (100.00)</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>maa://40157 (87.50)</t>
+          <t>maa://40157 (88.89)</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>maa://51881 (98.73), maa://25018 (96.96), maa://25776 (92.31), maa://28361 (95.56), maa://25772 (94.12), maa://56588 (93.33), maa://45194 (86.36), maa://32653 (81.25), maa://25161 (84.21), maa://61839 (100.00), **maa://60902 (41.67), maa://61275 (100.00)</t>
+          <t>maa://51881 (98.74), maa://25018 (96.96), maa://25776 (92.31), maa://28361 (95.56), maa://25772 (94.12), maa://56588 (93.33), maa://45194 (86.36), maa://32653 (81.25), maa://25161 (84.21), maa://61839 (100.00), **maa://60902 (41.67), maa://61275 (100.00)</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>maa://28484 (97.84), *maa://23736 (52.44), maa://31185 (91.67), maa://30306 (100.00)</t>
+          <t>maa://28484 (97.86), *maa://23736 (53.01), maa://31185 (91.67), maa://30306 (100.00)</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>maa://51549 (96.97), maa://51923 (96.30), maa://67508 (100.00)</t>
+          <t>maa://51549 (96.97), maa://51923 (96.30), *maa://67508 (66.67)</t>
         </is>
       </c>
       <c r="E151" s="14" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>maa://20961 (100.00)</t>
+          <t>maa://20961 (93.75)</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>maa://44232 (98.48), maa://45603 (90.62), *maa://65963 (80.00), *maa://63114 (66.67)</t>
+          <t>maa://44232 (98.48), maa://45603 (90.62), maa://65963 (83.33), *maa://63114 (66.67)</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr">
@@ -17793,12 +17793,12 @@
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>maa://44224 (90.52), maa://35854 (84.75), maa://50388 (98.25), maa://25760 (86.55), ***maa://43911 (11.11), *maa://20872 (52.00), maa://51066 (87.50), maa://63024 (95.35)</t>
+          <t>maa://44224 (90.52), maa://35854 (84.75), maa://50388 (98.25), maa://25760 (86.55), ***maa://43911 (11.11), *maa://20872 (52.00), maa://51066 (87.50), maa://63024 (95.45), maa://70161 (100.00)</t>
         </is>
       </c>
       <c r="E198" s="14" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="D227" s="13" t="inlineStr">
         <is>
-          <t>maa://28187 (97.73), maa://39520 (100.00), maa://43531 (100.00)</t>
+          <t>maa://28187 (97.73), maa://43531 (100.00), maa://39520 (100.00)</t>
         </is>
       </c>
       <c r="E227" s="14" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="D229" s="13" t="inlineStr">
         <is>
-          <t>maa://20987 (94.17), *maa://35801 (77.78)</t>
+          <t>maa://20987 (94.23), *maa://35801 (77.78)</t>
         </is>
       </c>
       <c r="E229" s="14" t="inlineStr">
@@ -22010,7 +22010,7 @@
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>maa://51881 (98.73), maa://51630 (96.26), maa://56588 (93.33), *maa://55171 (60.87), maa://51893 (90.00), **maa://60902 (41.67), maa://66758 (83.33)</t>
+          <t>maa://51881 (98.74), maa://51630 (96.26), maa://56588 (93.33), *maa://55171 (60.87), maa://51893 (90.00), **maa://60902 (41.67), maa://66758 (83.33)</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="D307" s="13" t="inlineStr">
         <is>
-          <t>maa://50280 (98.49), maa://49642 (97.62), maa://49660 (93.62), maa://50517 (85.71), maa://70004 (100.00)</t>
+          <t>maa://50280 (98.49), maa://49642 (97.64), maa://49660 (93.62), maa://50517 (85.71), maa://70004 (100.00)</t>
         </is>
       </c>
       <c r="E307" s="14" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="D360" s="22" t="inlineStr">
         <is>
-          <t>maa://49696 (99.60), maa://49695 (100.00), maa://49758 (98.72), *maa://59402 (56.67), *maa://52357 (75.00), *maa://63091 (75.00)</t>
+          <t>maa://49696 (99.60), maa://49695 (100.00), maa://49758 (98.73), *maa://52357 (75.00), *maa://59402 (56.67), *maa://63091 (75.00)</t>
         </is>
       </c>
       <c r="E360" s="22" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="D392" s="22" t="inlineStr">
         <is>
-          <t>maa://63890 (97.92), maa://64043 (100.00)</t>
+          <t>maa://63890 (97.96), maa://64043 (100.00)</t>
         </is>
       </c>
       <c r="E392" s="22" t="inlineStr">
@@ -28355,7 +28355,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://47023 (87.04)</t>
+          <t>maa://47023 (87.27)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>maa://51872 (96.67), maa://51876 (99.07), maa://63228 (88.24), maa://51873 (100.00), maa://62047 (92.31)</t>
+          <t>maa://51872 (96.67), maa://51876 (99.07), maa://63228 (88.24), maa://51873 (100.00), maa://62047 (92.59)</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -28571,7 +28571,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>**maa://67814 (50.00)</t>
+          <t>*maa://67814 (66.67)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>maa://67388 (93.75)</t>
+          <t>maa://67388 (93.88)</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>maa://67087 (94.34), maa://67268 (96.70), maa://67269 (88.89), maa://67648 (100.00)</t>
+          <t>maa://67087 (94.39), maa://67268 (96.74), maa://67269 (88.89), maa://67648 (100.00)</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>maa://25390 (98.42), maa://24702 (95.12), maa://36681 (85.39)</t>
+          <t>maa://25390 (98.45), maa://24702 (95.12), maa://36681 (85.39)</t>
         </is>
       </c>
       <c r="E2" s="19" t="n"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>maa://58660 (98.93), maa://39402 (95.10), *maa://34787 (75.00)</t>
+          <t>maa://58660 (98.87), maa://39402 (95.24), *maa://34787 (75.00)</t>
         </is>
       </c>
       <c r="M2" s="19" t="n"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>maa://22742 (97.40), maa://66635 (99.59)</t>
+          <t>maa://22742 (97.42), maa://66635 (99.60)</t>
         </is>
       </c>
       <c r="U2" s="19" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="AB2" s="8" t="inlineStr">
         <is>
-          <t>maa://36684 (98.32), maa://21246 (91.37)</t>
+          <t>maa://36684 (98.35), maa://21246 (91.40)</t>
         </is>
       </c>
       <c r="AC2" s="19" t="n"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>maa://59087 (97.43), maa://25251 (91.61)</t>
+          <t>maa://59087 (97.51), maa://25251 (91.61)</t>
         </is>
       </c>
       <c r="AG2" s="16" t="n"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>maa://40192 (99.42), maa://36987 (97.22), maa://39849 (92.31)</t>
+          <t>maa://40192 (99.44), maa://36987 (97.22), maa://39849 (92.31)</t>
         </is>
       </c>
       <c r="E3" s="19" t="n"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>maa://21247 (99.41)</t>
+          <t>maa://21247 (99.42)</t>
         </is>
       </c>
       <c r="I3" s="19" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>maa://22880 (91.28), maa://20276 (94.10), maa://22749 (84.62)</t>
+          <t>maa://22880 (91.38), maa://20276 (94.13), maa://22749 (84.62)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>maa://21249 (98.48), maa://26254 (98.15), *maa://22738 (80.00)</t>
+          <t>maa://21249 (98.51), maa://26254 (98.21), *maa://22738 (80.00)</t>
         </is>
       </c>
       <c r="Q3" s="19" t="n"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>maa://60545 (98.82), maa://45854 (87.79), maa://24617 (91.18)</t>
+          <t>maa://60545 (98.84), maa://45854 (88.13), maa://24617 (91.18)</t>
         </is>
       </c>
       <c r="U3" s="19" t="n"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="X3" s="8" t="inlineStr">
         <is>
-          <t>maa://27396 (92.62), maa://27484 (99.22), maa://27480 (86.21)</t>
+          <t>maa://27396 (92.81), maa://27484 (99.22), maa://27480 (86.44)</t>
         </is>
       </c>
       <c r="Y3" s="19" t="n"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="AB3" s="8" t="inlineStr">
         <is>
-          <t>maa://52241 (99.44), maa://24390 (96.83)</t>
+          <t>maa://52241 (99.45), maa://24390 (96.83)</t>
         </is>
       </c>
       <c r="AC3" s="19" t="n"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="AF3" s="8" t="inlineStr">
         <is>
-          <t>maa://21289 (92.24)</t>
+          <t>maa://21289 (92.44)</t>
         </is>
       </c>
       <c r="AG3" s="16" t="n"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>maa://24632 (98.13), maa://22499 (90.00), maa://22746 (100.00)</t>
+          <t>maa://24632 (98.17), maa://22499 (90.00), maa://22746 (100.00)</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>maa://49983 (99.15), maa://50121 (96.30)</t>
+          <t>maa://49983 (99.17), maa://50121 (96.35)</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>maa://27295 (97.81), maa://32509 (96.56), maa://31008 (95.31), maa://22754 (88.16), maa://70489 (100.00)</t>
+          <t>maa://27295 (97.84), maa://32509 (96.60), maa://31008 (95.31), maa://22754 (88.16), maa://70489 (100.00)</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="X4" s="8" t="inlineStr">
         <is>
-          <t>maa://43217 (98.92)</t>
+          <t>maa://43217 (98.94)</t>
         </is>
       </c>
       <c r="Y4" s="19" t="n"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>maa://21245 (91.47), maa://54105 (98.34), *maa://22744 (80.00)</t>
+          <t>maa://21245 (91.55), maa://54105 (98.38), *maa://22744 (80.00)</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>maa://22757 (91.15)</t>
+          <t>maa://22757 (91.30)</t>
         </is>
       </c>
       <c r="M5" s="19" t="n"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>maa://21919 (98.69), maa://21281 (82.35)</t>
+          <t>maa://21919 (98.70), maa://21281 (82.35)</t>
         </is>
       </c>
       <c r="Q5" s="19" t="n"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="X5" s="8" t="inlineStr">
         <is>
-          <t>maa://21290 (98.58)</t>
+          <t>maa://21290 (98.60)</t>
         </is>
       </c>
       <c r="Y5" s="19" t="n"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB5" s="8" t="inlineStr">
         <is>
-          <t>*maa://29863 (61.22), ***maa://22752 (12.50), **maa://26013 (33.33)</t>
+          <t>*maa://29863 (60.00), ***maa://22752 (12.50), **maa://26013 (33.33)</t>
         </is>
       </c>
       <c r="AC5" s="19" t="n"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>maa://42407 (97.53)</t>
+          <t>maa://42407 (97.57)</t>
         </is>
       </c>
       <c r="E6" s="19" t="n"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>maa://24370 (97.69)</t>
+          <t>maa://24370 (97.71)</t>
         </is>
       </c>
       <c r="I6" s="19" t="n"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>maa://24839 (99.46)</t>
+          <t>maa://24839 (99.47)</t>
         </is>
       </c>
       <c r="M6" s="19" t="n"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>maa://31836 (98.89), maa://30381 (95.00)</t>
+          <t>maa://31836 (98.90), maa://30381 (95.00)</t>
         </is>
       </c>
       <c r="Q6" s="19" t="n"/>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AF6" s="8" t="inlineStr">
         <is>
-          <t>maa://33152 (81.33)</t>
+          <t>maa://33152 (81.46)</t>
         </is>
       </c>
       <c r="AG6" s="16" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>maa://21955 (98.26)</t>
+          <t>maa://21955 (98.27)</t>
         </is>
       </c>
       <c r="E7" s="19" t="n"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>*maa://22763 (75.00), maa://64972 (95.83)</t>
+          <t>*maa://22763 (75.41), maa://64972 (95.83)</t>
         </is>
       </c>
       <c r="I7" s="19" t="n"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>maa://28624 (98.70), maa://24957 (94.55)</t>
+          <t>maa://28624 (98.73), maa://24957 (94.55)</t>
         </is>
       </c>
       <c r="M7" s="19" t="n"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>maa://21291 (94.22)</t>
+          <t>maa://21291 (94.25)</t>
         </is>
       </c>
       <c r="U7" s="19" t="n"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="X7" s="8" t="inlineStr">
         <is>
-          <t>maa://22399 (97.34), maa://22758 (82.35)</t>
+          <t>maa://22399 (97.38), maa://22758 (82.35)</t>
         </is>
       </c>
       <c r="Y7" s="19" t="n"/>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AF7" s="8" t="inlineStr">
         <is>
-          <t>maa://45272 (99.48)</t>
+          <t>maa://45272 (99.49)</t>
         </is>
       </c>
       <c r="AG7" s="16" t="n"/>
@@ -1482,7 +1482,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.09 13:20:20</t>
+          <t>更新日期：2025.10.11 13:18:19</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>maa://21476 (90.42)</t>
+          <t>maa://21476 (90.59)</t>
         </is>
       </c>
       <c r="E8" s="19" t="n"/>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>*maa://24371 (79.80)</t>
+          <t>*maa://24371 (80.00)</t>
         </is>
       </c>
       <c r="I8" s="19" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>maa://32931 (91.52), maa://23252 (91.67), maa://37496 (98.36)</t>
+          <t>maa://32931 (91.63), maa://23252 (91.67), maa://37496 (98.39)</t>
         </is>
       </c>
       <c r="Q8" s="19" t="n"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>maa://21411 (96.00), maa://67587 (98.36)</t>
+          <t>maa://21411 (96.02), maa://67587 (98.44)</t>
         </is>
       </c>
       <c r="Y8" s="19" t="n"/>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB8" s="8" t="inlineStr">
         <is>
-          <t>maa://25389 (94.87)</t>
+          <t>maa://25389 (95.00)</t>
         </is>
       </c>
       <c r="AC8" s="19" t="n"/>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AF8" s="8" t="inlineStr">
         <is>
-          <t>maa://24479 (84.92), *maa://21990 (51.72)</t>
+          <t>maa://24479 (85.07), **maa://21990 (50.00)</t>
         </is>
       </c>
       <c r="AG8" s="16" t="n"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>maa://22765 (95.82), *maa://21915 (79.07)</t>
+          <t>maa://22765 (95.89), *maa://21915 (79.55)</t>
         </is>
       </c>
       <c r="E9" s="19" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>*maa://47450 (77.27), maa://56348 (95.24)</t>
+          <t>*maa://47450 (79.17), maa://56348 (95.24)</t>
         </is>
       </c>
       <c r="I9" s="19" t="n"/>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>maa://22762 (96.40), maa://39552 (86.27)</t>
+          <t>maa://22762 (96.41), maa://39552 (86.54)</t>
         </is>
       </c>
       <c r="M9" s="19" t="n"/>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="X9" s="8" t="inlineStr">
         <is>
-          <t>maa://52237 (99.78), maa://26223 (98.31)</t>
+          <t>maa://52237 (99.79), maa://26223 (98.31)</t>
         </is>
       </c>
       <c r="Y9" s="19" t="n"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
-          <t>maa://28711 (95.32), maa://40166 (95.02)</t>
+          <t>maa://28711 (95.33), maa://40166 (95.02)</t>
         </is>
       </c>
       <c r="AC9" s="19" t="n"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AF9" s="8" t="inlineStr">
         <is>
-          <t>maa://26206 (91.39), maa://66916 (98.22)</t>
+          <t>maa://26206 (91.42), maa://66916 (98.27)</t>
         </is>
       </c>
       <c r="AG9" s="16" t="n"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>maa://54000 (91.67)</t>
+          <t>maa://54000 (91.84)</t>
         </is>
       </c>
       <c r="E10" s="19" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>maa://32651 (95.35)</t>
+          <t>maa://32651 (95.45)</t>
         </is>
       </c>
       <c r="I10" s="19" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>**maa://24395 (42.55)</t>
+          <t>**maa://24395 (41.67)</t>
         </is>
       </c>
       <c r="M10" s="19" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="P10" s="8" t="inlineStr">
         <is>
-          <t>maa://28977 (91.99), *maa://36669 (74.36)</t>
+          <t>maa://28977 (92.12), *maa://36669 (74.36)</t>
         </is>
       </c>
       <c r="Q10" s="19" t="n"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (99.28), maa://22755 (91.67), maa://63521 (93.89)</t>
+          <t>maa://27395 (99.29), maa://22755 (91.71), maa://63521 (93.95)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t>maa://45828 (99.29), maa://22301 (97.65), maa://22726 (100.00)</t>
+          <t>maa://45828 (99.30), maa://22301 (97.65), maa://22726 (100.00)</t>
         </is>
       </c>
       <c r="Y10" s="19" t="n"/>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AF10" s="8" t="inlineStr">
         <is>
-          <t>*maa://25021 (57.32), *maa://22733 (65.67), **maa://22761 (33.33)</t>
+          <t>*maa://25021 (57.58), *maa://22733 (65.67), **maa://22761 (33.33)</t>
         </is>
       </c>
       <c r="AG10" s="16" t="n"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>maa://36707 (99.75)</t>
+          <t>maa://36707 (99.70)</t>
         </is>
       </c>
       <c r="E11" s="19" t="n"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>maa://21287 (93.59)</t>
+          <t>maa://21287 (93.79)</t>
         </is>
       </c>
       <c r="M11" s="19" t="n"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="P11" s="8" t="inlineStr">
         <is>
-          <t>maa://45557 (94.34)</t>
+          <t>maa://45557 (94.44)</t>
         </is>
       </c>
       <c r="Q11" s="19" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>maa://22747 (93.43), maa://22501 (99.55), maa://64808 (100.00), maa://45521 (95.31)</t>
+          <t>maa://22747 (93.50), maa://22501 (99.56), maa://64808 (100.00), maa://45521 (95.31)</t>
         </is>
       </c>
       <c r="U11" s="19" t="n"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="X11" s="8" t="inlineStr">
         <is>
-          <t>maa://36713 (99.30)</t>
+          <t>maa://36713 (99.31)</t>
         </is>
       </c>
       <c r="Y11" s="19" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>maa://21867 (93.70), maa://54294 (96.86)</t>
+          <t>maa://21867 (93.73), maa://54294 (96.95)</t>
         </is>
       </c>
       <c r="I12" s="19" t="n"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>maa://63896 (98.09), maa://64046 (98.62)</t>
+          <t>maa://63896 (98.12), maa://64046 (98.63)</t>
         </is>
       </c>
       <c r="M12" s="19" t="n"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="P12" s="8" t="inlineStr">
         <is>
-          <t>maa://57541 (91.89)</t>
+          <t>maa://57541 (89.47)</t>
         </is>
       </c>
       <c r="Q12" s="19" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>maa://37962 (98.88), maa://21485 (82.01), maa://22753 (92.89)</t>
+          <t>maa://37962 (98.89), maa://21485 (82.08), maa://22753 (92.89)</t>
         </is>
       </c>
       <c r="Y12" s="19" t="n"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
-          <t>maa://36677 (99.10), maa://23669 (94.85), maa://39872 (98.39)</t>
+          <t>maa://36677 (99.12), maa://23669 (94.85), maa://39872 (98.45)</t>
         </is>
       </c>
       <c r="AC12" s="19" t="n"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AF12" s="8" t="inlineStr">
         <is>
-          <t>maa://28932 (94.81)</t>
+          <t>maa://28932 (94.85)</t>
         </is>
       </c>
       <c r="AG12" s="16" t="n"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>maa://24999 (96.78), maa://36673 (94.29), maa://25001 (88.76)</t>
+          <t>maa://24999 (96.83), maa://36673 (94.29), maa://25001 (88.89)</t>
         </is>
       </c>
       <c r="E13" s="19" t="n"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>*maa://21248 (73.48), maa://66545 (98.84)</t>
+          <t>*maa://21248 (73.30), maa://66545 (98.86)</t>
         </is>
       </c>
       <c r="I13" s="19" t="n"/>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="O13" s="19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" s="8" t="inlineStr">
         <is>
-          <t>maa://22676 (97.85), maa://22583 (88.76)</t>
+          <t>maa://22676 (97.89), maa://22583 (88.82), *maa://22500 (71.21)</t>
         </is>
       </c>
       <c r="Q13" s="19" t="n"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="X13" s="8" t="inlineStr">
         <is>
-          <t>maa://34957 (94.75)</t>
+          <t>maa://34957 (94.63)</t>
         </is>
       </c>
       <c r="Y13" s="19" t="n"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AF13" s="8" t="inlineStr">
         <is>
-          <t>maa://39883 (94.15)</t>
+          <t>maa://39883 (94.24)</t>
         </is>
       </c>
       <c r="AG13" s="16" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>maa://30764 (94.59)</t>
+          <t>maa://30764 (94.63)</t>
         </is>
       </c>
       <c r="E14" s="19" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>maa://39841 (99.04), maa://36682 (98.34), maa://26245 (97.07), maa://21288 (96.40)</t>
+          <t>maa://39841 (99.01), maa://36682 (98.34), maa://26245 (97.07), maa://21288 (96.40)</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="P14" s="8" t="inlineStr">
         <is>
-          <t>maa://23250 (99.67), maa://20107 (87.50), maa://22772 (100.00), maa://68732 (100.00)</t>
+          <t>maa://23250 (99.68), maa://20107 (87.50), maa://22772 (100.00), maa://68732 (100.00)</t>
         </is>
       </c>
       <c r="Q14" s="19" t="n"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>maa://42751 (98.97), maa://22521 (95.37)</t>
+          <t>maa://42751 (98.98), maa://22521 (95.43)</t>
         </is>
       </c>
       <c r="U14" s="19" t="n"/>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="X14" s="8" t="inlineStr">
         <is>
-          <t>maa://37468 (98.11)</t>
+          <t>maa://37468 (98.17)</t>
         </is>
       </c>
       <c r="Y14" s="19" t="n"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AB14" s="8" t="inlineStr">
         <is>
-          <t>maa://22764 (98.94)</t>
+          <t>maa://22764 (98.95)</t>
         </is>
       </c>
       <c r="AC14" s="19" t="n"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>maa://22743 (85.69), maa://45058 (98.26), maa://22734 (84.96), *maa://36048 (75.00), maa://69928 (100.00)</t>
+          <t>maa://22743 (85.92), maa://45058 (98.28), maa://22734 (84.96), *maa://36048 (75.27), maa://69928 (100.00)</t>
         </is>
       </c>
       <c r="E15" s="19" t="n"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>maa://24304 (97.24), maa://21478 (90.48)</t>
+          <t>maa://24304 (97.28), maa://21478 (90.48)</t>
         </is>
       </c>
       <c r="I15" s="19" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>maa://24762 (97.75), *maa://22727 (70.00)</t>
+          <t>maa://24762 (97.77), *maa://22727 (70.00)</t>
         </is>
       </c>
       <c r="Q15" s="19" t="n"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>maa://23892 (97.71)</t>
+          <t>maa://23892 (97.77)</t>
         </is>
       </c>
       <c r="U15" s="19" t="n"/>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="X15" s="8" t="inlineStr">
         <is>
-          <t>maa://38786 (91.89), maa://56102 (100.00)</t>
+          <t>maa://38786 (92.31), maa://56102 (100.00)</t>
         </is>
       </c>
       <c r="Y15" s="19" t="n"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AF15" s="8" t="inlineStr">
         <is>
-          <t>maa://36666 (96.44), maa://21364 (83.83), *maa://22766 (70.71), maa://68306 (82.61)</t>
+          <t>maa://36666 (96.46), maa://21364 (83.91), *maa://22766 (70.71), maa://68306 (84.21)</t>
         </is>
       </c>
       <c r="AG15" s="16" t="n"/>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>maa://28504 (96.45)</t>
+          <t>maa://28504 (96.50)</t>
         </is>
       </c>
       <c r="Q16" s="19" t="n"/>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>maa://36674 (97.96), maa://22729 (96.25), *maa://28648 (77.89)</t>
+          <t>maa://36674 (97.97), maa://22729 (96.28), *maa://28648 (77.89)</t>
         </is>
       </c>
       <c r="U16" s="19" t="n"/>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>maa://28501 (99.37), maa://28051 (97.14)</t>
+          <t>maa://28501 (99.38), maa://28051 (97.14)</t>
         </is>
       </c>
       <c r="Y16" s="19" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AB16" s="8" t="inlineStr">
         <is>
-          <t>maa://26228 (97.98)</t>
+          <t>maa://26228 (98.01)</t>
         </is>
       </c>
       <c r="AC16" s="19" t="n"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>maa://23911 (90.71), maa://27755 (93.75), maa://67613 (99.51)</t>
+          <t>maa://23911 (90.78), maa://27755 (93.75), maa://67613 (99.53)</t>
         </is>
       </c>
       <c r="AG16" s="16" t="n"/>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>maa://21624 (88.00), maa://56358 (100.00)</t>
+          <t>maa://21624 (88.24), maa://56358 (100.00)</t>
         </is>
       </c>
       <c r="E17" s="19" t="n"/>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>maa://39599 (98.32), maa://22430 (90.25)</t>
+          <t>maa://39599 (98.36), maa://22430 (90.25)</t>
         </is>
       </c>
       <c r="I17" s="19" t="n"/>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>maa://23890 (82.93), maa://56238 (98.59)</t>
+          <t>maa://23890 (82.93), maa://56238 (98.61)</t>
         </is>
       </c>
       <c r="Q17" s="19" t="n"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>*maa://42324 (70.79)</t>
+          <t>*maa://42324 (71.74)</t>
         </is>
       </c>
       <c r="U17" s="19" t="n"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AF17" s="8" t="inlineStr">
         <is>
-          <t>maa://50136 (99.01)</t>
+          <t>maa://50136 (99.04)</t>
         </is>
       </c>
       <c r="AG17" s="16" t="n"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>maa://24570 (98.27)</t>
+          <t>maa://24570 (98.29)</t>
         </is>
       </c>
       <c r="E18" s="19" t="n"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>maa://24421 (95.32)</t>
+          <t>maa://24421 (95.40)</t>
         </is>
       </c>
       <c r="I18" s="19" t="n"/>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>maa://52226 (99.65), maa://22466 (92.86)</t>
+          <t>maa://52226 (99.66), maa://22466 (92.86)</t>
         </is>
       </c>
       <c r="M18" s="19" t="n"/>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>maa://24379 (100.00), maa://54153 (99.67), maa://24380 (100.00)</t>
+          <t>maa://24379 (100.00), maa://54153 (99.68), maa://24380 (100.00)</t>
         </is>
       </c>
       <c r="Q18" s="19" t="n"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>maa://24385 (98.46)</t>
+          <t>maa://24385 (98.55)</t>
         </is>
       </c>
       <c r="U18" s="19" t="n"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t>maa://21917 (98.75), maa://22741 (92.31)</t>
+          <t>maa://21917 (98.76), maa://22741 (92.86)</t>
         </is>
       </c>
       <c r="Y18" s="19" t="n"/>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB18" s="8" t="inlineStr">
         <is>
-          <t>maa://24393 (99.04)</t>
+          <t>maa://24393 (99.07)</t>
         </is>
       </c>
       <c r="AC18" s="19" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="AF18" s="8" t="inlineStr">
         <is>
-          <t>maa://47854 (93.51), *maa://68715 (75.00)</t>
+          <t>maa://47854 (93.63), *maa://68715 (75.00)</t>
         </is>
       </c>
       <c r="AG18" s="16" t="n"/>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>maa://62850 (99.30)</t>
+          <t>maa://62850 (99.32)</t>
         </is>
       </c>
       <c r="E19" s="19" t="n"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>maa://24386 (99.53)</t>
+          <t>maa://24386 (99.54)</t>
         </is>
       </c>
       <c r="U19" s="19" t="n"/>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t>maa://31386 (97.62), maa://58490 (85.71)</t>
+          <t>maa://31386 (97.67), maa://58490 (85.71)</t>
         </is>
       </c>
       <c r="Y19" s="19" t="n"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
-          <t>maa://30709 (86.50), *maa://36668 (69.83)</t>
+          <t>maa://30709 (86.71), *maa://36668 (70.09)</t>
         </is>
       </c>
       <c r="AC19" s="19" t="n"/>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AF19" s="8" t="inlineStr">
         <is>
-          <t>*maa://21663 (65.91), maa://52239 (87.80)</t>
+          <t>*maa://21663 (65.91), maa://52239 (88.37)</t>
         </is>
       </c>
       <c r="AG19" s="16" t="n"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>maa://25198 (97.75), maa://36680 (99.12), maa://21432 (91.56)</t>
+          <t>maa://25198 (97.77), maa://36680 (99.13), maa://21432 (91.60)</t>
         </is>
       </c>
       <c r="E20" s="19" t="n"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>maa://22864 (96.16)</t>
+          <t>maa://22864 (96.18)</t>
         </is>
       </c>
       <c r="I20" s="19" t="n"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>maa://41331 (95.46)</t>
+          <t>maa://41331 (95.57)</t>
         </is>
       </c>
       <c r="M20" s="19" t="n"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>maa://37442 (98.63)</t>
+          <t>maa://37442 (98.66)</t>
         </is>
       </c>
       <c r="Q20" s="19" t="n"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>maa://29113 (93.75)</t>
+          <t>maa://29113 (94.05)</t>
         </is>
       </c>
       <c r="U20" s="19" t="n"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://50085 (96.67), maa://56241 (98.29), maa://49976 (88.57)</t>
+          <t>maa://50085 (96.72), maa://56241 (98.33), maa://49976 (88.57)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>maa://21261 (99.06)</t>
+          <t>maa://21261 (99.07)</t>
         </is>
       </c>
       <c r="E21" s="19" t="n"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>maa://24372 (98.94)</t>
+          <t>maa://24372 (98.95)</t>
         </is>
       </c>
       <c r="I21" s="19" t="n"/>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
-          <t>maa://24381 (83.78)</t>
+          <t>maa://24381 (84.21)</t>
         </is>
       </c>
       <c r="Q21" s="19" t="n"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>maa://34946 (98.15), maa://20110 (87.01)</t>
+          <t>maa://34946 (98.19), maa://20110 (87.01)</t>
         </is>
       </c>
       <c r="Y21" s="19" t="n"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AB21" s="8" t="inlineStr">
         <is>
-          <t>maa://21443 (87.32), maa://52223 (83.84)</t>
+          <t>maa://21443 (87.35), maa://52223 (84.32)</t>
         </is>
       </c>
       <c r="AC21" s="19" t="n"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="AF21" s="8" t="inlineStr">
         <is>
-          <t>maa://22432 (94.42), maa://22524 (83.28), maa://64221 (97.93)</t>
+          <t>maa://22432 (94.50), maa://22524 (83.28), maa://64221 (97.99)</t>
         </is>
       </c>
       <c r="AG21" s="16" t="n"/>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>maa://27127 (83.61), *maa://22751 (71.26), maa://66865 (99.46)</t>
+          <t>maa://27127 (83.82), *maa://22751 (71.26), maa://66865 (99.48)</t>
         </is>
       </c>
       <c r="M22" s="19" t="n"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>maa://38495 (84.78)</t>
+          <t>maa://38495 (85.11)</t>
         </is>
       </c>
       <c r="U22" s="19" t="n"/>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>maa://37649 (95.02), maa://21282 (98.97)</t>
+          <t>maa://37649 (94.93), maa://21282 (98.97)</t>
         </is>
       </c>
       <c r="Y22" s="19" t="n"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AB22" s="8" t="inlineStr">
         <is>
-          <t>maa://23656 (99.53)</t>
+          <t>maa://23656 (99.54)</t>
         </is>
       </c>
       <c r="AC22" s="19" t="n"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>maa://39756 (98.64), maa://39875 (95.04)</t>
+          <t>maa://39756 (98.67), maa://39875 (95.04)</t>
         </is>
       </c>
       <c r="M23" s="19" t="n"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>maa://30587 (96.72), maa://29748 (81.77), *maa://37566 (78.46)</t>
+          <t>maa://30587 (96.79), maa://29748 (81.96), *maa://37566 (78.46)</t>
         </is>
       </c>
       <c r="Q23" s="19" t="n"/>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>maa://31212 (94.96), maa://24387 (84.44), maa://67084 (87.50)</t>
+          <t>maa://31212 (95.04), maa://24387 (84.44), maa://67084 (87.50)</t>
         </is>
       </c>
       <c r="U23" s="19" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="X23" s="8" t="inlineStr">
         <is>
-          <t>*maa://28503 (61.25)</t>
+          <t>*maa://28503 (61.49)</t>
         </is>
       </c>
       <c r="Y23" s="19" t="n"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AF23" s="8" t="inlineStr">
         <is>
-          <t>maa://31489 (98.33)</t>
+          <t>maa://31489 (98.36)</t>
         </is>
       </c>
       <c r="AG23" s="16" t="n"/>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>maa://24368 (85.42), maa://46650 (90.91)</t>
+          <t>maa://24368 (85.49), maa://46650 (91.18)</t>
         </is>
       </c>
       <c r="E24" s="19" t="n"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>maa://29988 (96.48), maa://23504 (94.06), *maa://25141 (79.74), maa://52227 (97.13), *maa://36663 (79.63)</t>
+          <t>maa://29988 (96.56), maa://23504 (94.06), *maa://25141 (79.87), maa://52227 (97.20), *maa://36663 (79.63)</t>
         </is>
       </c>
       <c r="Y24" s="19" t="n"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB24" s="8" t="inlineStr">
         <is>
-          <t>maa://39349 (97.30)</t>
+          <t>maa://39349 (97.37)</t>
         </is>
       </c>
       <c r="AC24" s="19" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AF24" s="8" t="inlineStr">
         <is>
-          <t>maa://64165 (99.22), maa://22523 (80.18), maa://29910 (94.20), maa://45831 (93.94)</t>
+          <t>maa://64165 (99.24), maa://22523 (80.18), maa://29910 (94.20), maa://45831 (93.94)</t>
         </is>
       </c>
       <c r="AG24" s="16" t="n"/>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>maa://29753 (96.66), maa://63016 (99.18)</t>
+          <t>maa://29753 (96.71), maa://63016 (99.20)</t>
         </is>
       </c>
       <c r="E25" s="19" t="n"/>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>*maa://29063 (76.82), *maa://25311 (71.03), maa://45047 (88.46)</t>
+          <t>*maa://29063 (76.99), *maa://25311 (71.03), maa://45047 (88.46)</t>
         </is>
       </c>
       <c r="I25" s="19" t="n"/>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>maa://24382 (96.49)</t>
+          <t>maa://24382 (96.61)</t>
         </is>
       </c>
       <c r="Q25" s="19" t="n"/>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>maa://20109 (96.51), maa://22545 (100.00)</t>
+          <t>maa://20109 (96.57), maa://22545 (100.00)</t>
         </is>
       </c>
       <c r="U25" s="19" t="n"/>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="X25" s="8" t="inlineStr">
         <is>
-          <t>maa://29890 (91.97)</t>
+          <t>maa://29890 (92.03)</t>
         </is>
       </c>
       <c r="Y25" s="19" t="n"/>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB25" s="8" t="inlineStr">
         <is>
-          <t>maa://31215 (93.32), *maa://24516 (78.43), maa://26001 (81.97), maa://68311 (96.88)</t>
+          <t>maa://31215 (93.36), *maa://24516 (78.43), maa://26001 (81.97), maa://68311 (97.27)</t>
         </is>
       </c>
       <c r="AC25" s="19" t="n"/>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AF25" s="8" t="inlineStr">
         <is>
-          <t>maa://20108 (98.24), maa://36676 (99.85), maa://24621 (96.91), maa://22771 (88.24), maa://37772 (85.71)</t>
+          <t>maa://20108 (98.31), maa://36676 (99.85), maa://24621 (96.91), maa://22771 (88.24), maa://37772 (85.71)</t>
         </is>
       </c>
       <c r="AG25" s="16" t="n"/>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>maa://56374 (100.00), maa://41802 (96.83)</t>
+          <t>maa://56374 (100.00), maa://41802 (97.01)</t>
         </is>
       </c>
       <c r="E26" s="19" t="n"/>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>maa://56240 (96.44), maa://24913 (92.31)</t>
+          <t>maa://56240 (96.49), maa://24913 (92.31)</t>
         </is>
       </c>
       <c r="I26" s="19" t="n"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>maa://39870 (94.59), maa://56625 (98.65)</t>
+          <t>maa://39870 (94.59), maa://56625 (98.70)</t>
         </is>
       </c>
       <c r="Q26" s="19" t="n"/>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB26" s="8" t="inlineStr">
         <is>
-          <t>maa://42235 (98.45)</t>
+          <t>maa://42235 (98.49)</t>
         </is>
       </c>
       <c r="AC26" s="19" t="n"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>maa://39601 (90.91), maa://34494 (95.51)</t>
+          <t>maa://39601 (91.27), maa://34494 (95.70)</t>
         </is>
       </c>
       <c r="I27" s="19" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P27" s="8" t="inlineStr">
         <is>
-          <t>maa://56400 (93.75)</t>
+          <t>maa://56400 (94.12)</t>
         </is>
       </c>
       <c r="Q27" s="19" t="n"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>maa://30624 (90.27)</t>
+          <t>maa://30624 (90.32)</t>
         </is>
       </c>
       <c r="U27" s="19" t="n"/>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AF27" s="8" t="inlineStr">
         <is>
-          <t>maa://24023 (97.83)</t>
+          <t>maa://24023 (97.86)</t>
         </is>
       </c>
       <c r="AG27" s="16" t="n"/>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>maa://24465 (96.03), maa://25725 (85.38)</t>
+          <t>maa://24465 (96.07), maa://25725 (85.38)</t>
         </is>
       </c>
       <c r="E28" s="19" t="n"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>maa://30770 (90.82)</t>
+          <t>maa://30770 (91.00)</t>
         </is>
       </c>
       <c r="M28" s="19" t="n"/>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>maa://29765 (93.93), maa://23263 (96.30)</t>
+          <t>maa://29765 (94.04), maa://23263 (96.32)</t>
         </is>
       </c>
       <c r="U28" s="19" t="n"/>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t>maa://39929 (97.45), maa://41749 (97.25)</t>
+          <t>maa://39929 (97.50), maa://41749 (97.26)</t>
         </is>
       </c>
       <c r="Y28" s="19" t="n"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AF28" s="8" t="inlineStr">
         <is>
-          <t>maa://36660 (94.35), maa://65700 (98.75)</t>
+          <t>maa://36660 (94.38), maa://65700 (98.79)</t>
         </is>
       </c>
       <c r="AG28" s="16" t="n"/>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>*maa://25175 (51.79)</t>
+          <t>*maa://25175 (52.21)</t>
         </is>
       </c>
       <c r="I29" s="19" t="n"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>maa://28432 (97.86), maa://31400 (98.10), maa://28440 (86.59)</t>
+          <t>maa://28432 (97.91), maa://31400 (98.13), maa://28440 (86.67)</t>
         </is>
       </c>
       <c r="M29" s="19" t="n"/>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AF29" s="8" t="inlineStr">
         <is>
-          <t>maa://42865 (92.37)</t>
+          <t>maa://42865 (92.52)</t>
         </is>
       </c>
       <c r="AG29" s="16" t="n"/>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>maa://30442 (97.58)</t>
+          <t>maa://30442 (97.64)</t>
         </is>
       </c>
       <c r="M30" s="19" t="n"/>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="P30" s="8" t="inlineStr">
         <is>
-          <t>maa://21442 (99.57), maa://66611 (100.00), maa://68394 (100.00)</t>
+          <t>maa://21442 (99.58), maa://66611 (100.00), maa://68394 (100.00)</t>
         </is>
       </c>
       <c r="Q30" s="19" t="n"/>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>maa://32940 (81.82), maa://24388 (96.15)</t>
+          <t>maa://32940 (82.61), maa://24388 (96.15)</t>
         </is>
       </c>
       <c r="U30" s="19" t="n"/>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>maa://42979 (99.58), maa://45822 (100.00), maa://45045 (92.31)</t>
+          <t>maa://42979 (99.59), maa://45822 (100.00), maa://45045 (93.33)</t>
         </is>
       </c>
       <c r="AC30" s="19" t="n"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>maa://35926 (98.14), maa://36258 (93.25), maa://43904 (88.37)</t>
+          <t>maa://35926 (98.17), maa://36258 (93.35), maa://43904 (88.64)</t>
         </is>
       </c>
       <c r="M31" s="19" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="AB31" s="8" t="inlineStr">
         <is>
-          <t>maa://66997 (95.65)</t>
+          <t>maa://66997 (96.00)</t>
         </is>
       </c>
       <c r="AC31" s="19" t="n"/>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>maa://36667 (99.60), maa://21895 (97.97), maa://22760 (100.00)</t>
+          <t>maa://36667 (99.61), maa://21895 (97.99), maa://22760 (100.00)</t>
         </is>
       </c>
       <c r="I32" s="19" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>maa://42859 (99.32), maa://41108 (87.72), maa://41238 (98.16), maa://45523 (100.00)</t>
+          <t>maa://42859 (99.34), maa://41108 (87.93), maa://41238 (98.16), maa://45523 (100.00)</t>
         </is>
       </c>
       <c r="U32" s="19" t="n"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t>maa://64104 (97.62)</t>
+          <t>maa://64104 (97.71)</t>
         </is>
       </c>
       <c r="Y32" s="19" t="n"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>**maa://39351 (36.36)</t>
+          <t>**maa://39351 (30.77)</t>
         </is>
       </c>
       <c r="I33" s="19" t="n"/>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>maa://21956 (94.73), maa://69135 (94.44)</t>
+          <t>maa://21956 (94.77), maa://69135 (96.30)</t>
         </is>
       </c>
       <c r="Q33" s="19" t="n"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>maa://45558 (90.91)</t>
+          <t>maa://45558 (88.57)</t>
         </is>
       </c>
       <c r="U33" s="19" t="n"/>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>maa://48817 (99.27), maa://56235 (99.52)</t>
+          <t>maa://48817 (99.28), maa://56235 (99.54)</t>
         </is>
       </c>
       <c r="Q34" s="19" t="n"/>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>maa://24526 (97.22)</t>
+          <t>maa://24526 (97.26)</t>
         </is>
       </c>
       <c r="U34" s="19" t="n"/>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AB34" s="8" t="inlineStr">
         <is>
-          <t>maa://64329 (98.08)</t>
+          <t>maa://64329 (98.11)</t>
         </is>
       </c>
       <c r="AC34" s="19" t="n"/>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>maa://41296 (99.30)</t>
+          <t>maa://41296 (99.31)</t>
         </is>
       </c>
       <c r="M35" s="19" t="n"/>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>maa://24842 (96.77)</t>
+          <t>maa://24842 (96.81)</t>
         </is>
       </c>
       <c r="U35" s="19" t="n"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AF35" s="8" t="inlineStr">
         <is>
-          <t>maa://39479 (96.43)</t>
+          <t>maa://39479 (96.49)</t>
         </is>
       </c>
       <c r="AG35" s="16" t="n"/>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>maa://27613 (99.57)</t>
+          <t>maa://27613 (99.59)</t>
         </is>
       </c>
       <c r="U36" s="19" t="n"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AB36" s="19" t="inlineStr">
         <is>
-          <t>maa://64106 (97.44)</t>
+          <t>maa://64106 (97.56)</t>
         </is>
       </c>
       <c r="AC36" s="19" t="n"/>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>*maa://24374 (58.73)</t>
+          <t>*maa://24374 (59.38)</t>
         </is>
       </c>
       <c r="I37" s="19" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>maa://45718 (99.07), maa://56336 (99.40), maa://47069 (86.67), maa://45789 (100.00)</t>
+          <t>maa://45718 (99.07), maa://56336 (99.41), maa://47069 (86.96), maa://45789 (100.00)</t>
         </is>
       </c>
       <c r="M37" s="19" t="n"/>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>maa://21280 (97.63)</t>
+          <t>maa://21280 (97.69)</t>
         </is>
       </c>
       <c r="Q37" s="19" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>**maa://39354 (45.45)</t>
+          <t>**maa://39354 (50.00)</t>
         </is>
       </c>
       <c r="U37" s="19" t="n"/>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="P38" s="8" t="inlineStr">
         <is>
-          <t>maa://24383 (82.47)</t>
+          <t>maa://24383 (82.65)</t>
         </is>
       </c>
       <c r="Q38" s="19" t="n"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>maa://30713 (98.39)</t>
+          <t>maa://30713 (98.46)</t>
         </is>
       </c>
       <c r="U38" s="19" t="n"/>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AF38" s="8" t="inlineStr">
         <is>
-          <t>maa://36697 (95.70), maa://68397 (98.68)</t>
+          <t>maa://36697 (95.72), maa://68397 (98.54)</t>
         </is>
       </c>
       <c r="AG38" s="16" t="n"/>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>maa://25199 (84.89), maa://45059 (94.18), maa://30434 (95.36), maa://44165 (85.71)</t>
+          <t>maa://25199 (84.89), maa://45059 (94.28), maa://30434 (95.41), maa://44165 (85.71)</t>
         </is>
       </c>
       <c r="I39" s="19" t="n"/>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>maa://47093 (98.36), maa://24709 (94.16)</t>
+          <t>maa://47093 (98.39), maa://24709 (94.21)</t>
         </is>
       </c>
       <c r="Q39" s="19" t="n"/>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>maa://47079 (95.83), maa://45790 (88.61)</t>
+          <t>maa://47079 (95.81), maa://45790 (88.75)</t>
         </is>
       </c>
       <c r="U39" s="19" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AF39" s="8" t="inlineStr">
         <is>
-          <t>maa://62953 (96.91)</t>
+          <t>maa://62953 (96.99)</t>
         </is>
       </c>
       <c r="AG39" s="16" t="n"/>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>maa://23278 (98.20), maa://21386 (95.96), maa://36664 (89.74), *maa://45550 (75.00)</t>
+          <t>maa://23278 (98.23), maa://21386 (95.96), maa://36664 (89.74), *maa://45550 (75.00)</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>maa://65283 (97.18), maa://64205 (93.94)</t>
+          <t>maa://65283 (97.26), maa://64205 (93.94)</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t>maa://43177 (95.61)</t>
+          <t>maa://43177 (95.69)</t>
         </is>
       </c>
       <c r="Q41" s="19" t="n"/>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>maa://21284 (97.84)</t>
+          <t>maa://21284 (97.89)</t>
         </is>
       </c>
       <c r="I43" s="19" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P43" s="8" t="inlineStr">
         <is>
-          <t>maa://47403 (87.50)</t>
+          <t>maa://47403 (87.88)</t>
         </is>
       </c>
       <c r="Q43" s="19" t="n"/>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>maa://29768 (98.30), maa://56386 (99.45), maa://27728 (96.40)</t>
+          <t>maa://29768 (98.32), maa://56386 (99.46), maa://27728 (96.40)</t>
         </is>
       </c>
       <c r="I44" s="19" t="n"/>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>maa://39366 (93.68)</t>
+          <t>maa://39366 (93.81)</t>
         </is>
       </c>
       <c r="U44" s="19" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>maa://42459 (98.80), maa://21229 (85.84), maa://30807 (94.62), *maa://22767 (72.00)</t>
+          <t>maa://42459 (98.82), maa://21229 (85.90), maa://30807 (94.62), *maa://22767 (72.00)</t>
         </is>
       </c>
       <c r="I45" s="19" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P45" s="8" t="inlineStr">
         <is>
-          <t>maa://36237 (83.78)</t>
+          <t>maa://36237 (84.21)</t>
         </is>
       </c>
       <c r="Q45" s="19" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>*maa://39364 (69.01)</t>
+          <t>*maa://39364 (68.79)</t>
         </is>
       </c>
       <c r="U45" s="19" t="n"/>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>maa://35931 (96.00), maa://43901 (96.44)</t>
+          <t>maa://35931 (96.10), maa://43901 (96.50)</t>
         </is>
       </c>
       <c r="I46" s="19" t="n"/>
@@ -6229,12 +6229,12 @@
       </c>
       <c r="AE46" s="19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://70759 (100.00)</t>
         </is>
       </c>
       <c r="AG46" s="16" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>maa://27410 (97.55), maa://29661 (97.24), maa://56236 (99.80), maa://28038 (84.62)</t>
+          <t>maa://27410 (97.56), maa://29661 (97.24), maa://56236 (99.81), maa://28038 (84.62)</t>
         </is>
       </c>
       <c r="I47" s="19" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>maa://67476 (99.58), maa://68392 (99.37)</t>
+          <t>maa://67476 (99.58), maa://68392 (99.45)</t>
         </is>
       </c>
       <c r="U47" s="19" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P49" s="8" t="inlineStr">
         <is>
-          <t>*maa://39643 (79.87)</t>
+          <t>maa://39643 (80.13)</t>
         </is>
       </c>
       <c r="Q49" s="19" t="n"/>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="T49" s="19" t="inlineStr">
         <is>
-          <t>maa://67231 (99.19)</t>
+          <t>maa://67231 (99.21)</t>
         </is>
       </c>
       <c r="U49" s="19" t="n"/>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>maa://62852 (93.39)</t>
+          <t>maa://62852 (93.52)</t>
         </is>
       </c>
       <c r="Q50" s="19" t="n"/>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>maa://24376 (99.13)</t>
+          <t>maa://24376 (99.15)</t>
         </is>
       </c>
       <c r="I52" s="19" t="n"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>maa://59394 (99.43), maa://59378 (93.83), maa://65511 (100.00)</t>
+          <t>maa://59394 (99.44), maa://59378 (93.83), maa://65511 (100.00)</t>
         </is>
       </c>
       <c r="Q52" s="19" t="n"/>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>maa://32534 (98.01)</t>
+          <t>maa://32534 (98.05)</t>
         </is>
       </c>
       <c r="I53" s="19" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>maa://32532 (97.94)</t>
+          <t>maa://32532 (97.98)</t>
         </is>
       </c>
       <c r="I55" s="19" t="n"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>maa://56237 (98.33), maa://25176 (98.78)</t>
+          <t>maa://56237 (98.34), maa://25176 (98.78)</t>
         </is>
       </c>
       <c r="I57" s="19" t="n"/>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>maa://31270 (98.41), maa://27746 (89.53)</t>
+          <t>maa://31270 (98.43), maa://27746 (89.58)</t>
         </is>
       </c>
       <c r="I59" s="19" t="n"/>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>maa://40438 (92.11)</t>
+          <t>maa://40438 (92.31)</t>
         </is>
       </c>
       <c r="I60" s="19" t="n"/>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>maa://42981 (96.81), maa://56228 (98.18), maa://43903 (100.00)</t>
+          <t>maa://42981 (96.88), maa://56228 (98.24), maa://43903 (100.00)</t>
         </is>
       </c>
       <c r="I62" s="19" t="n"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>maa://59534 (99.45), *maa://59693 (72.00), maa://59413 (97.56)</t>
+          <t>maa://59534 (99.46), *maa://59693 (72.00), maa://59413 (97.56)</t>
         </is>
       </c>
       <c r="I63" s="19" t="n"/>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>maa://44405 (91.55)</t>
+          <t>maa://44405 (91.78)</t>
         </is>
       </c>
       <c r="I64" s="19" t="n"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="H75" s="19" t="inlineStr">
         <is>
-          <t>maa://67748 (80.43)</t>
+          <t>maa://67748 (82.69)</t>
         </is>
       </c>
       <c r="I75" s="19" t="n"/>
@@ -7166,7 +7166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF418"/>
+  <dimension ref="A1:AF420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="8" min="1" max="1"/>
@@ -7209,7 +7209,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.09 13:20:20</t>
+          <t>更新日期：2025.10.11 13:18:19</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>maa://20990 (88.89)</t>
+          <t>maa://20990 (90.00)</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>maa://20930 (88.89)</t>
+          <t>maa://20930 (90.00)</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>maa://20876 (96.49), maa://63498 (100.00)</t>
+          <t>maa://20876 (96.55), maa://63498 (100.00)</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>*maa://20849 (73.21), *maa://28758 (72.34), maa://29036 (96.67), maa://65357 (96.88), *maa://42172 (71.43), maa://30285 (100.00)</t>
+          <t>*maa://20849 (73.21), *maa://28758 (72.34), maa://65357 (97.06), maa://29036 (96.67), *maa://42172 (71.43), maa://30285 (100.00)</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>maa://20863 (90.79), maa://20832 (99.22), maa://20727 (100.00)</t>
+          <t>maa://20863 (90.91), maa://20832 (99.22), maa://20727 (100.00)</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>maa://36644 (89.92), maa://36866 (97.06), maa://62759 (100.00), maa://45572 (88.24), maa://27794 (100.00), maa://20960 (100.00), maa://20843 (100.00), **maa://24483 (50.00), *maa://20893 (73.68), maa://20862 (83.33)</t>
+          <t>maa://36644 (90.19), maa://36866 (97.06), maa://62759 (100.00), maa://45572 (88.24), maa://27794 (100.00), maa://20960 (100.00), maa://20843 (100.00), **maa://24483 (50.00), *maa://20893 (73.68), maa://20862 (83.33), maa://70680 (100.00)</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>maa://44235 (98.45), maa://45604 (100.00), maa://20961 (93.75), maa://44220 (100.00), maa://20910 (100.00)</t>
+          <t>maa://44235 (98.45), maa://45604 (100.00), maa://20961 (94.12), maa://44220 (100.00), maa://20910 (100.00)</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>maa://27970 (98.85), maa://41118 (87.50)</t>
+          <t>maa://27970 (98.86), maa://41118 (87.50)</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>maa://20841 (99.24), maa://31559 (94.00), maa://24093 (100.00), maa://20924 (95.24), maa://25777 (100.00), maa://20631 (100.00), maa://28241 (100.00), maa://66633 (100.00)</t>
+          <t>maa://20841 (99.25), maa://31559 (94.00), maa://24093 (100.00), maa://20924 (95.24), maa://25777 (100.00), maa://20631 (100.00), maa://28241 (100.00), maa://66633 (100.00)</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>maa://20976 (97.85), maa://20815 (100.00)</t>
+          <t>maa://20976 (97.91), maa://20815 (100.00)</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>maa://20944 (96.30), maa://35393 (100.00)</t>
+          <t>maa://20944 (96.36), maa://35393 (100.00)</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>maa://36643 (98.46), maa://36864 (98.11), maa://39140 (100.00), maa://66335 (100.00)</t>
+          <t>maa://36643 (98.47), maa://36864 (98.11), maa://39140 (100.00), maa://66335 (100.00)</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>maa://24472 (91.04), *maa://35841 (65.22)</t>
+          <t>maa://24472 (91.07), *maa://35841 (65.22)</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>maa://20927 (93.33)</t>
+          <t>maa://20927 (93.75)</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>maa://20926 (83.33)</t>
+          <t>maa://20926 (84.62)</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>maa://20991 (100.00), maa://51015 (87.23)</t>
+          <t>maa://20991 (100.00), maa://51015 (87.50)</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>maa://40517 (91.43), *maa://39240 (56.25)</t>
+          <t>maa://40517 (91.67), *maa://39240 (56.25)</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>maa://36646 (98.92), maa://25774 (94.59), maa://35996 (97.92), maa://22469 (92.06), maa://30668 (86.67), maa://67286 (100.00)</t>
+          <t>maa://36646 (98.92), maa://25774 (94.59), maa://35996 (97.94), maa://22469 (92.19), maa://30668 (87.10), maa://67286 (100.00)</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="D114" s="13" t="inlineStr">
         <is>
-          <t>maa://20933 (86.81), maa://20822 (100.00)</t>
+          <t>maa://20933 (86.96), maa://20822 (100.00)</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>maa://29650 (98.53), maa://45570 (96.72)</t>
+          <t>maa://29650 (98.53), maa://45570 (96.77)</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>maa://45258 (90.91), **maa://30679 (50.00)</t>
+          <t>maa://45258 (91.30), **maa://30679 (50.00)</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="D144" s="13" t="inlineStr">
         <is>
-          <t>maa://28484 (97.86), *maa://23736 (53.01), maa://31185 (91.67), maa://30306 (100.00)</t>
+          <t>maa://28484 (97.87), *maa://23736 (52.94), maa://31185 (91.67), maa://30306 (100.00)</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>maa://40957 (94.86), maa://36641 (98.25), maa://36865 (95.48), maa://44635 (88.18), maa://44660 (92.68), maa://41128 (84.21), maa://46108 (100.00), maa://42918 (100.00), maa://44119 (97.44), maa://64408 (92.86), maa://37300 (100.00), maa://42917 (100.00)</t>
+          <t>maa://40957 (94.75), maa://36641 (98.25), maa://36865 (95.48), maa://44635 (88.18), maa://44660 (92.68), maa://41128 (84.21), maa://46108 (100.00), maa://42918 (100.00), maa://44119 (97.44), maa://64408 (93.33), maa://37300 (100.00), maa://42917 (100.00)</t>
         </is>
       </c>
       <c r="E151" s="14" t="inlineStr">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>maa://51549 (97.10), maa://51923 (96.30), *maa://67508 (66.67)</t>
+          <t>maa://51549 (95.71), maa://51923 (96.30), *maa://67508 (66.67)</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>maa://20961 (93.75)</t>
+          <t>maa://20961 (94.12)</t>
         </is>
       </c>
       <c r="E153" s="14" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>maa://20959 (91.67)</t>
+          <t>maa://20959 (92.31)</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>maa://20975 (90.91), maa://47950 (85.71), maa://30806 (100.00)</t>
+          <t>maa://20975 (91.67), maa://47950 (90.00), maa://30806 (100.00)</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>maa://29633 (92.31), maa://29627 (92.95), maa://29659 (85.37), maa://49074 (94.20), **maa://30679 (50.00), maa://29861 (100.00), maa://42343 (100.00)</t>
+          <t>maa://29633 (92.31), maa://29627 (92.98), maa://29659 (85.37), maa://49074 (94.20), **maa://30679 (50.00), maa://29861 (100.00), maa://42343 (100.00)</t>
         </is>
       </c>
       <c r="E169" s="14" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>maa://49867 (93.90), maa://49655 (97.83)</t>
+          <t>maa://49867 (94.05), maa://49655 (97.83)</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>maa://44224 (90.45), maa://35854 (84.75), maa://50388 (98.26), maa://25760 (86.55), ***maa://43911 (11.11), *maa://20872 (52.00), maa://51066 (87.50), maa://63024 (95.83), maa://70161 (100.00)</t>
+          <t>maa://44224 (90.50), maa://35854 (84.75), maa://50388 (98.26), maa://25760 (86.55), ***maa://43911 (11.11), *maa://20872 (52.00), maa://51066 (87.50), maa://63024 (95.83), maa://70161 (100.00)</t>
         </is>
       </c>
       <c r="E199" s="14" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>maa://42223 (99.25), maa://49077 (94.55), maa://42292 (97.22), maa://42402 (100.00)</t>
+          <t>maa://42223 (99.25), maa://49077 (94.64), maa://42292 (97.22), maa://42402 (100.00)</t>
         </is>
       </c>
       <c r="E203" s="14" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>maa://64044 (96.43)</t>
+          <t>maa://64044 (96.49)</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="D235" s="13" t="inlineStr">
         <is>
-          <t>*maa://48263 (75.86)</t>
+          <t>*maa://48263 (76.67)</t>
         </is>
       </c>
       <c r="E235" s="14" t="inlineStr">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="D239" s="13" t="inlineStr">
         <is>
-          <t>maa://20917 (98.39)</t>
+          <t>maa://20917 (98.41)</t>
         </is>
       </c>
       <c r="E239" s="14" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>maa://62759 (100.00), maa://62764 (83.33)</t>
+          <t>maa://62759 (100.00), maa://62764 (83.33), maa://70680 (100.00)</t>
         </is>
       </c>
       <c r="E244" s="14" t="inlineStr">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="D253" s="13" t="inlineStr">
         <is>
-          <t>maa://42287 (91.87), maa://45570 (96.72), maa://60678 (93.33), maa://42225 (100.00)</t>
+          <t>maa://42287 (92.59), maa://45570 (96.77), maa://60678 (90.91), maa://42225 (100.00)</t>
         </is>
       </c>
       <c r="E253" s="14" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="D271" s="13" t="inlineStr">
         <is>
-          <t>maa://49643 (91.11)</t>
+          <t>maa://49643 (91.30)</t>
         </is>
       </c>
       <c r="E271" s="14" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>maa://48265 (81.48)</t>
+          <t>maa://48265 (82.14)</t>
         </is>
       </c>
       <c r="E272" s="14" t="inlineStr">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>maa://30710 (97.95), maa://36845 (95.89), maa://31558 (97.22), **maa://39217 (38.89), maa://30668 (86.67)</t>
+          <t>maa://30710 (97.95), maa://36845 (95.92), maa://31558 (97.22), **maa://39217 (38.89), maa://30668 (87.10)</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
@@ -23193,7 +23193,7 @@
       </c>
       <c r="D297" s="13" t="inlineStr">
         <is>
-          <t>maa://25774 (94.59), maa://28133 (93.33), maa://22469 (92.06), **maa://39217 (38.89), **maa://31349 (50.00)</t>
+          <t>maa://25774 (94.59), maa://28133 (93.33), maa://22469 (92.19), **maa://39217 (38.89), **maa://31349 (50.00)</t>
         </is>
       </c>
       <c r="E297" s="14" t="inlineStr">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>maa://50280 (98.50), maa://49642 (97.66), maa://49660 (93.62), maa://50517 (85.71), maa://70004 (100.00)</t>
+          <t>maa://50280 (98.50), maa://49642 (97.67), maa://49660 (93.62), maa://50517 (85.71), maa://70004 (100.00)</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="D313" s="13" t="inlineStr">
         <is>
-          <t>maa://36005 (94.12)</t>
+          <t>maa://36005 (94.44)</t>
         </is>
       </c>
       <c r="E313" s="14" t="inlineStr">
@@ -24364,29 +24364,29 @@
       <c r="AF318" s="8" t="n"/>
     </row>
     <row r="319" ht="13.5" customFormat="1" customHeight="1" s="22">
-      <c r="A319" s="11" t="inlineStr">
-        <is>
-          <t>寒檀</t>
-        </is>
-      </c>
-      <c r="B319" s="11" t="inlineStr">
-        <is>
-          <t>BI-2</t>
-        </is>
-      </c>
-      <c r="C319" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D319" s="13" t="inlineStr">
-        <is>
-          <t>maa://40161 (100.00)</t>
-        </is>
-      </c>
-      <c r="E319" s="14" t="inlineStr">
-        <is>
-          <t>&gt; 完成5次战斗；必须编入非助战寒檀并上场，且每次战斗至少释放1次“女巫之泪”&gt; 3星通关别传BI-2；必须编入非助战寒檀并上场，且使用寒檀至少歼灭8个敌人</t>
+      <c r="A319" s="24" t="inlineStr">
+        <is>
+          <t>圣约送葬人</t>
+        </is>
+      </c>
+      <c r="B319" s="24" t="inlineStr">
+        <is>
+          <t>GA-3</t>
+        </is>
+      </c>
+      <c r="C319" s="25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D319" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E319" s="27" t="inlineStr">
+        <is>
+          <t>&gt; 由非助战圣约送葬人累计造成40歼灭数&gt; 3星通关插曲吾导先路GA-3；必须编入非助战圣约送葬人并上场，其他成员仅可编入辅助干员</t>
         </is>
       </c>
       <c r="F319" s="19" t="n"/>
@@ -24420,12 +24420,12 @@
     <row r="320" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>寒檀</t>
         </is>
       </c>
       <c r="B320" s="11" t="inlineStr">
         <is>
-          <t>S2-1</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C320" s="12" t="inlineStr">
@@ -24435,12 +24435,12 @@
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>maa://25367 (99.38)</t>
+          <t>maa://40161 (100.00)</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战提丰累计造成120000点伤害&gt; 3星通关主题曲S2-1；必须编入非助战提丰并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战寒檀并上场，且每次战斗至少释放1次“女巫之泪”&gt; 3星通关别传BI-2；必须编入非助战寒檀并上场，且使用寒檀至少歼灭8个敌人</t>
         </is>
       </c>
       <c r="F320" s="19" t="n"/>
@@ -24479,22 +24479,22 @@
       </c>
       <c r="B321" s="11" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>S2-1</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D321" s="13" t="inlineStr">
         <is>
-          <t>*maa://62755 (73.68), maa://62761 (87.50)</t>
+          <t>maa://25367 (99.38)</t>
         </is>
       </c>
       <c r="E321" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战提丰累计造成30歼灭数&gt; 3星通关主题曲4-8；必须编入非助战提丰并上场，且不编入其他狙击干员</t>
+          <t>&gt; 由非助战提丰累计造成120000点伤害&gt; 3星通关主题曲S2-1；必须编入非助战提丰并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
       <c r="F321" s="19" t="n"/>
@@ -24528,27 +24528,27 @@
     <row r="322" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t>凛视</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B322" s="11" t="inlineStr">
         <is>
-          <t>7-13</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C322" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>*maa://43090 (57.14)</t>
+          <t>*maa://62755 (73.68), maa://62761 (88.24)</t>
         </is>
       </c>
       <c r="E322" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战凛视累计造成30次凋亡爆发&gt; 3星通关主题曲7-13；必须编入非助战凛视并上场，且凛视造成至少1次凋亡爆发</t>
+          <t>&gt; 由非助战提丰累计造成30歼灭数&gt; 3星通关主题曲4-8；必须编入非助战提丰并上场，且不编入其他狙击干员</t>
         </is>
       </c>
       <c r="F322" s="19" t="n"/>
@@ -24582,12 +24582,12 @@
     <row r="323" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t>苍苔</t>
+          <t>凛视</t>
         </is>
       </c>
       <c r="B323" s="11" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>7-13</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
@@ -24597,12 +24597,12 @@
       </c>
       <c r="D323" s="13" t="inlineStr">
         <is>
-          <t>maa://28070 (100.00)</t>
+          <t>*maa://43090 (57.14)</t>
         </is>
       </c>
       <c r="E323" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战苍苔并上场，且每次战斗至少释放1次土石的恒心&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战苍苔并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战凛视累计造成30次凋亡爆发&gt; 3星通关主题曲7-13；必须编入非助战凛视并上场，且凛视造成至少1次凋亡爆发</t>
         </is>
       </c>
       <c r="F323" s="19" t="n"/>
@@ -24636,12 +24636,12 @@
     <row r="324" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A324" s="11" t="inlineStr">
         <is>
-          <t>青枳</t>
+          <t>苍苔</t>
         </is>
       </c>
       <c r="B324" s="11" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C324" s="12" t="inlineStr">
@@ -24651,12 +24651,12 @@
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>maa://28241 (100.00)</t>
+          <t>maa://28070 (100.00)</t>
         </is>
       </c>
       <c r="E324" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战青枳，并确定第一位部署的干员是青枳&gt; 3星通关别传OF-5；必须编入非助战青枳并上场，且不编入其他先锋干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战苍苔并上场，且每次战斗至少释放1次土石的恒心&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战苍苔并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F324" s="19" t="n"/>
@@ -24690,27 +24690,27 @@
     <row r="325" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>青枳</t>
         </is>
       </c>
       <c r="B325" s="11" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D325" s="13" t="inlineStr">
         <is>
-          <t>maa://25773 (100.00), *maa://26088 (75.00)</t>
+          <t>maa://28241 (100.00)</t>
         </is>
       </c>
       <c r="E325" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战琳琅诗怀雅累计造成60000点伤害※香槟炸弹造成的伤害也会参与计数&gt; 3星通关主题曲5-2；必须编入非助战琳琅诗怀雅并上场，且使用琳琅诗怀雅至少歼灭15个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战青枳，并确定第一位部署的干员是青枳&gt; 3星通关别传OF-5；必须编入非助战青枳并上场，且不编入其他先锋干员</t>
         </is>
       </c>
       <c r="F325" s="19" t="n"/>
@@ -24749,22 +24749,22 @@
       </c>
       <c r="B326" s="11" t="inlineStr">
         <is>
-          <t>11-16</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C326" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>maa://39239 (100.00)</t>
+          <t>maa://25773 (100.00), *maa://26088 (75.00)</t>
         </is>
       </c>
       <c r="E326" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战琳琅诗怀雅累计造成40歼灭数&gt; 3星通关主题曲11-16标准实战环境；必须编入非助战琳琅诗怀雅并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战琳琅诗怀雅累计造成60000点伤害※香槟炸弹造成的伤害也会参与计数&gt; 3星通关主题曲5-2；必须编入非助战琳琅诗怀雅并上场，且使用琳琅诗怀雅至少歼灭15个敌人</t>
         </is>
       </c>
       <c r="F326" s="19" t="n"/>
@@ -24798,27 +24798,27 @@
     <row r="327" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t>纯烬艾雅法拉</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B327" s="11" t="inlineStr">
         <is>
-          <t>FC-5</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D327" s="13" t="inlineStr">
         <is>
-          <t>maa://39692 (99.55), maa://39810 (90.32)</t>
+          <t>maa://39239 (100.00)</t>
         </is>
       </c>
       <c r="E327" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战纯烬艾雅法拉并上场，且每次战斗至少释放1次火山回响&gt; 3星通关别传FC-5；必须编入非助战纯烬艾雅法拉并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战琳琅诗怀雅累计造成40歼灭数&gt; 3星通关主题曲11-16标准实战环境；必须编入非助战琳琅诗怀雅并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F327" s="19" t="n"/>
@@ -24852,27 +24852,27 @@
     <row r="328" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t>冰酿</t>
+          <t>纯烬艾雅法拉</t>
         </is>
       </c>
       <c r="B328" s="11" t="inlineStr">
         <is>
-          <t>S3-3</t>
+          <t>FC-5</t>
         </is>
       </c>
       <c r="C328" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D328" s="13" t="inlineStr">
         <is>
-          <t>*maa://39174 (75.00)</t>
+          <t>maa://39692 (99.55), maa://39810 (90.32)</t>
         </is>
       </c>
       <c r="E328" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战冰酿累计造成80000伤害&gt; 3星通关主题曲S3-3；必须编入非助战冰酿并上场，且使用冰酿至少歼灭8个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战纯烬艾雅法拉并上场，且每次战斗至少释放1次火山回响&gt; 3星通关别传FC-5；必须编入非助战纯烬艾雅法拉并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F328" s="19" t="n"/>
@@ -24906,12 +24906,12 @@
     <row r="329" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A329" s="11" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>冰酿</t>
         </is>
       </c>
       <c r="B329" s="11" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>S3-3</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
@@ -24921,12 +24921,12 @@
       </c>
       <c r="D329" s="13" t="inlineStr">
         <is>
-          <t>maa://39175 (100.00)</t>
+          <t>*maa://39174 (75.00)</t>
         </is>
       </c>
       <c r="E329" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战杏仁累计使用强力牵引10次&gt; 3星通关别传BI-2；必须编入非助战杏仁并上场，且至少使用2次强力牵引</t>
+          <t>&gt; 由非助战冰酿累计造成80000伤害&gt; 3星通关主题曲S3-3；必须编入非助战冰酿并上场，且使用冰酿至少歼灭8个敌人</t>
         </is>
       </c>
       <c r="F329" s="19" t="n"/>
@@ -24960,27 +24960,27 @@
     <row r="330" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t>涤火杰西卡</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="B330" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C330" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>maa://34715 (94.74), maa://34867 (96.30)</t>
+          <t>maa://39175 (100.00)</t>
         </is>
       </c>
       <c r="E330" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战涤火杰西卡累计造成30歼灭数&gt; 3星通关主题曲3-8；必须编入非助战涤火杰西卡并上场，且使用涤火杰西卡歼灭碎骨</t>
+          <t>&gt; 战斗中非助战杏仁累计使用强力牵引10次&gt; 3星通关别传BI-2；必须编入非助战杏仁并上场，且至少使用2次强力牵引</t>
         </is>
       </c>
       <c r="F330" s="19" t="n"/>
@@ -25014,27 +25014,27 @@
     <row r="331" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A331" s="12" t="inlineStr">
         <is>
-          <t>维荻</t>
+          <t>涤火杰西卡</t>
         </is>
       </c>
       <c r="B331" s="11" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D331" s="15" t="inlineStr">
         <is>
-          <t>maa://39176 (100.00)</t>
+          <t>maa://34715 (94.74), maa://34867 (96.30)</t>
         </is>
       </c>
       <c r="E331" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维荻累计造成60000点伤害&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战维荻并上场，且至少使用2次双刃毒藤</t>
+          <t>&gt; 由非助战涤火杰西卡累计造成30歼灭数&gt; 3星通关主题曲3-8；必须编入非助战涤火杰西卡并上场，且使用涤火杰西卡歼灭碎骨</t>
         </is>
       </c>
       <c r="F331" s="19" t="n"/>
@@ -25068,12 +25068,12 @@
     <row r="332" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A332" s="12" t="inlineStr">
         <is>
-          <t>戴菲恩</t>
+          <t>维荻</t>
         </is>
       </c>
       <c r="B332" s="11" t="inlineStr">
         <is>
-          <t>WD-6</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C332" s="12" t="inlineStr">
@@ -25083,12 +25083,12 @@
       </c>
       <c r="D332" s="15" t="inlineStr">
         <is>
-          <t>maa://42316 (88.89)</t>
+          <t>maa://39176 (100.00)</t>
         </is>
       </c>
       <c r="E332" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战戴菲恩累计造成30歼灭数&gt; 3星通关插曲WD-6；必须携带且部署非助战戴菲恩，且至少使用2次抢攻</t>
+          <t>&gt; 由非助战维荻累计造成60000点伤害&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战维荻并上场，且至少使用2次双刃毒藤</t>
         </is>
       </c>
       <c r="F332" s="19" t="n"/>
@@ -25122,27 +25122,27 @@
     <row r="333" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A333" s="12" t="inlineStr">
         <is>
-          <t>刺玫</t>
+          <t>戴菲恩</t>
         </is>
       </c>
       <c r="B333" s="11" t="inlineStr">
         <is>
-          <t>IC-2</t>
+          <t>WD-6</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D333" s="15" t="inlineStr">
         <is>
-          <t>maa://30680 (100.00), maa://41360 (100.00)</t>
+          <t>maa://42316 (88.89)</t>
         </is>
       </c>
       <c r="E333" s="15" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战刺玫累计使用荆藤庇荫10次&gt; 3星通关别传IC-2；必须编入非助战刺玫并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战戴菲恩累计造成30歼灭数&gt; 3星通关插曲WD-6；必须携带且部署非助战戴菲恩，且至少使用2次抢攻</t>
         </is>
       </c>
       <c r="F333" s="19" t="n"/>
@@ -25176,27 +25176,27 @@
     <row r="334" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A334" s="12" t="inlineStr">
         <is>
-          <t>赫德雷</t>
+          <t>刺玫</t>
         </is>
       </c>
       <c r="B334" s="11" t="inlineStr">
         <is>
-          <t>IW-7</t>
+          <t>IC-2</t>
         </is>
       </c>
       <c r="C334" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D334" s="15" t="inlineStr">
         <is>
-          <t>maa://40956 (94.12)</t>
+          <t>maa://30680 (100.00), maa://41360 (100.00)</t>
         </is>
       </c>
       <c r="E334" s="15" t="inlineStr">
         <is>
-          <t>&gt; 由非助战赫德雷累计歼灭5个精英或领袖敌人&gt; 3星通关别传IW-7；必须编入非助战赫德雷并上场，并使用赫德雷至少击败2名沉沙</t>
+          <t>&gt; 战斗中非助战刺玫累计使用荆藤庇荫10次&gt; 3星通关别传IC-2；必须编入非助战刺玫并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F334" s="19" t="n"/>
@@ -25228,29 +25228,29 @@
       <c r="AF334" s="8" t="n"/>
     </row>
     <row r="335" ht="13.5" customFormat="1" customHeight="1" s="22">
-      <c r="A335" s="25" t="inlineStr">
-        <is>
-          <t>跃跃</t>
-        </is>
-      </c>
-      <c r="B335" s="24" t="inlineStr">
-        <is>
-          <t>4-2</t>
-        </is>
-      </c>
-      <c r="C335" s="25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D335" s="32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E335" s="32" t="inlineStr">
-        <is>
-          <t>&gt; 战斗中非助战跃跃累计使用8次乐趣加倍&gt; 3星通关主题曲4-2；必须编入非助战跃跃并上场，且使用跃跃歼灭至少8名敌人</t>
+      <c r="A335" s="12" t="inlineStr">
+        <is>
+          <t>赫德雷</t>
+        </is>
+      </c>
+      <c r="B335" s="11" t="inlineStr">
+        <is>
+          <t>IW-7</t>
+        </is>
+      </c>
+      <c r="C335" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D335" s="15" t="inlineStr">
+        <is>
+          <t>maa://40956 (94.12)</t>
+        </is>
+      </c>
+      <c r="E335" s="15" t="inlineStr">
+        <is>
+          <t>&gt; 由非助战赫德雷累计歼灭5个精英或领袖敌人&gt; 3星通关别传IW-7；必须编入非助战赫德雷并上场，并使用赫德雷至少击败2名沉沙</t>
         </is>
       </c>
       <c r="F335" s="19" t="n"/>
@@ -25282,29 +25282,29 @@
       <c r="AF335" s="8" t="n"/>
     </row>
     <row r="336" ht="13.5" customFormat="1" customHeight="1" s="22">
-      <c r="A336" s="12" t="inlineStr">
-        <is>
-          <t>折光</t>
-        </is>
-      </c>
-      <c r="B336" s="11" t="inlineStr">
-        <is>
-          <t>6-1</t>
-        </is>
-      </c>
-      <c r="C336" s="12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D336" s="15" t="inlineStr">
-        <is>
-          <t>maa://67818 (100.00)</t>
-        </is>
-      </c>
-      <c r="E336" s="15" t="inlineStr">
-        <is>
-          <t>&gt; 由非助战折光累计造成80000点伤害&gt; 3星通关主题曲6-1，必须编入非助战折光并上场，且使用折光歼灭至少10名敌人</t>
+      <c r="A336" s="25" t="inlineStr">
+        <is>
+          <t>跃跃</t>
+        </is>
+      </c>
+      <c r="B336" s="24" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="C336" s="25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D336" s="32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E336" s="32" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战跃跃累计使用8次乐趣加倍&gt; 3星通关主题曲4-2；必须编入非助战跃跃并上场，且使用跃跃歼灭至少8名敌人</t>
         </is>
       </c>
       <c r="F336" s="19" t="n"/>
@@ -25338,12 +25338,12 @@
     <row r="337" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A337" s="12" t="inlineStr">
         <is>
-          <t>深律</t>
+          <t>折光</t>
         </is>
       </c>
       <c r="B337" s="11" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C337" s="12" t="inlineStr">
@@ -25353,12 +25353,12 @@
       </c>
       <c r="D337" s="15" t="inlineStr">
         <is>
-          <t>maa://59688 (100.00)</t>
+          <t>maa://67818 (100.00)</t>
         </is>
       </c>
       <c r="E337" s="15" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战深律并上场，且每次战斗至少释放1次沉音宁神&gt; 3星通关别传LE-4；必须编入非助战深律并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战折光累计造成80000点伤害&gt; 3星通关主题曲6-1，必须编入非助战折光并上场，且使用折光歼灭至少10名敌人</t>
         </is>
       </c>
       <c r="F337" s="19" t="n"/>
@@ -25392,27 +25392,27 @@
     <row r="338" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A338" s="12" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>深律</t>
         </is>
       </c>
       <c r="B338" s="11" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C338" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D338" s="22" t="inlineStr">
         <is>
-          <t>maa://34205 (90.00), *maa://39541 (75.00)</t>
+          <t>maa://59688 (100.00)</t>
         </is>
       </c>
       <c r="E338" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战止颂累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲7-11；必须编入非助战止颂并上场，且使用止颂歼灭至少2名雇佣军萨卡兹战士</t>
+          <t>&gt; 完成5次战斗；必须编入非助战深律并上场，且每次战斗至少释放1次沉音宁神&gt; 3星通关别传LE-4；必须编入非助战深律并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F338" s="19" t="n"/>
@@ -25451,7 +25451,7 @@
       </c>
       <c r="B339" s="11" t="inlineStr">
         <is>
-          <t>TW-5</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
@@ -25461,12 +25461,12 @@
       </c>
       <c r="D339" s="22" t="inlineStr">
         <is>
-          <t>maa://43092 (100.00), maa://43093 (100.00)</t>
+          <t>maa://34205 (90.00), *maa://39541 (75.00)</t>
         </is>
       </c>
       <c r="E339" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战止颂累计造成120000点伤害&gt; 3星通关别传TW-5；必须编入非助战止颂并上场，且使用止颂击败至少6名敌人</t>
+          <t>&gt; 由非助战止颂累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲7-11；必须编入非助战止颂并上场，且使用止颂歼灭至少2名雇佣军萨卡兹战士</t>
         </is>
       </c>
       <c r="F339" s="19" t="n"/>
@@ -25500,27 +25500,27 @@
     <row r="340" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A340" s="12" t="inlineStr">
         <is>
-          <t>薇薇安娜</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B340" s="11" t="inlineStr">
         <is>
-          <t>MN-3</t>
+          <t>TW-5</t>
         </is>
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D340" s="22" t="inlineStr">
         <is>
-          <t>maa://44234 (99.19)</t>
+          <t>maa://43092 (100.00), maa://43093 (100.00)</t>
         </is>
       </c>
       <c r="E340" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战薇薇安娜累计歼灭10个精英或领袖敌人&gt; 3星通关别传MN-3；必须编入非助战薇薇安娜并上场，且使用薇薇安娜歼灭“锈铜”奥尔默·英格拉</t>
+          <t>&gt; 由非助战止颂累计造成120000点伤害&gt; 3星通关别传TW-5；必须编入非助战止颂并上场，且使用止颂击败至少6名敌人</t>
         </is>
       </c>
       <c r="F340" s="19" t="n"/>
@@ -25554,27 +25554,27 @@
     <row r="341" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A341" s="12" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>薇薇安娜</t>
         </is>
       </c>
       <c r="B341" s="11" t="inlineStr">
         <is>
-          <t>GA-7</t>
+          <t>MN-3</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D341" s="22" t="inlineStr">
         <is>
-          <t>maa://42968 (99.17), maa://49245 (100.00)</t>
+          <t>maa://44234 (99.19)</t>
         </is>
       </c>
       <c r="E341" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战塑心累计造成75000点凋亡损伤&gt; 3星通关别传GA-7；必须编入非助战塑心并上场，且塑心造成至少15000点凋亡损伤</t>
+          <t>&gt; 由非助战薇薇安娜累计歼灭10个精英或领袖敌人&gt; 3星通关别传MN-3；必须编入非助战薇薇安娜并上场，且使用薇薇安娜歼灭“锈铜”奥尔默·英格拉</t>
         </is>
       </c>
       <c r="F341" s="19" t="n"/>
@@ -25613,22 +25613,22 @@
       </c>
       <c r="B342" s="11" t="inlineStr">
         <is>
-          <t>ZT-8</t>
+          <t>GA-7</t>
         </is>
       </c>
       <c r="C342" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D342" s="22" t="inlineStr">
         <is>
-          <t>maa://67275 (100.00)</t>
+          <t>maa://42968 (99.17), maa://49245 (100.00)</t>
         </is>
       </c>
       <c r="E342" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战塑心累计造成30次凋亡爆发&gt; 3星通关插曲崔林特尔梅之金ZT-8；必须编入非助战塑心并上场，且塑心造成至少1次凋亡爆发</t>
+          <t>&gt; 由非助战塑心累计造成75000点凋亡损伤&gt; 3星通关别传GA-7；必须编入非助战塑心并上场，且塑心造成至少15000点凋亡损伤</t>
         </is>
       </c>
       <c r="F342" s="19" t="n"/>
@@ -25662,12 +25662,12 @@
     <row r="343" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A343" s="12" t="inlineStr">
         <is>
-          <t>哈洛德</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B343" s="11" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>ZT-8</t>
         </is>
       </c>
       <c r="C343" s="12" t="inlineStr">
@@ -25677,12 +25677,12 @@
       </c>
       <c r="D343" s="22" t="inlineStr">
         <is>
-          <t>*maa://40162 (71.43)</t>
+          <t>maa://67275 (100.00)</t>
         </is>
       </c>
       <c r="E343" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战哈洛德累计使用重症优先8次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战哈洛德并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战塑心累计造成30次凋亡爆发&gt; 3星通关插曲崔林特尔梅之金ZT-8；必须编入非助战塑心并上场，且塑心造成至少1次凋亡爆发</t>
         </is>
       </c>
       <c r="F343" s="19" t="n"/>
@@ -25716,12 +25716,12 @@
     <row r="344" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A344" s="12" t="inlineStr">
         <is>
-          <t>烈夏</t>
+          <t>哈洛德</t>
         </is>
       </c>
       <c r="B344" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C344" s="12" t="inlineStr">
@@ -25731,12 +25731,12 @@
       </c>
       <c r="D344" s="22" t="inlineStr">
         <is>
-          <t>maa://37692 (100.00)</t>
+          <t>*maa://40162 (71.43)</t>
         </is>
       </c>
       <c r="E344" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战烈夏累计造成30歼灭数&gt; 3星通关主题曲4-3；必须编入非助战烈夏并上场，且不编入其他近卫干员</t>
+          <t>&gt; 战斗中非助战哈洛德累计使用重症优先8次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战哈洛德并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F344" s="19" t="n"/>
@@ -25770,27 +25770,27 @@
     <row r="345" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A345" s="12" t="inlineStr">
         <is>
-          <t>锏</t>
+          <t>烈夏</t>
         </is>
       </c>
       <c r="B345" s="11" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D345" s="22" t="inlineStr">
         <is>
-          <t>maa://30671 (81.59), maa://30669 (99.31), maa://37275 (81.40), *maa://32410 (61.54), maa://41605 (100.00)</t>
+          <t>maa://37692 (100.00)</t>
         </is>
       </c>
       <c r="E345" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战锏并上场，且每次战斗至少释放1次归于宁静&gt; 3星通关别传BI-6；必须编入非助战锏并上场，且使用锏至少歼灭10个敌人</t>
+          <t>&gt; 由非助战烈夏累计造成30歼灭数&gt; 3星通关主题曲4-3；必须编入非助战烈夏并上场，且不编入其他近卫干员</t>
         </is>
       </c>
       <c r="F345" s="19" t="n"/>
@@ -25824,27 +25824,27 @@
     <row r="346" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A346" s="12" t="inlineStr">
         <is>
-          <t>温米</t>
+          <t>锏</t>
         </is>
       </c>
       <c r="B346" s="11" t="inlineStr">
         <is>
-          <t>6-11</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C346" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D346" s="22" t="inlineStr">
         <is>
-          <t>maa://67817 (100.00)</t>
+          <t>maa://30671 (81.59), maa://30669 (99.31), maa://37275 (81.40), *maa://32410 (61.54), maa://41605 (100.00)</t>
         </is>
       </c>
       <c r="E346" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战温米累计造成40000点元素伤害&gt; 3星通关主题曲6-11；必须编入非助战温米并上场，其他成员仅可编入7名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战锏并上场，且每次战斗至少释放1次归于宁静&gt; 3星通关别传BI-6；必须编入非助战锏并上场，且使用锏至少歼灭10个敌人</t>
         </is>
       </c>
       <c r="F346" s="19" t="n"/>
@@ -25878,27 +25878,27 @@
     <row r="347" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A347" s="12" t="inlineStr">
         <is>
-          <t>莱伊</t>
+          <t>温米</t>
         </is>
       </c>
       <c r="B347" s="11" t="inlineStr">
         <is>
-          <t>S9-1</t>
+          <t>6-11</t>
         </is>
       </c>
       <c r="C347" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D347" s="22" t="inlineStr">
         <is>
-          <t>maa://38295 (95.37), maa://49332 (90.91)</t>
+          <t>maa://67817 (100.00)</t>
         </is>
       </c>
       <c r="E347" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战莱伊累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲S9-1标准实战环境；必须编入非助战莱伊并上场，且使用莱伊使用至少2次“得见光芒”</t>
+          <t>&gt; 由非助战温米累计造成40000点元素伤害&gt; 3星通关主题曲6-11；必须编入非助战温米并上场，其他成员仅可编入7名干员</t>
         </is>
       </c>
       <c r="F347" s="19" t="n"/>
@@ -25932,27 +25932,27 @@
     <row r="348" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A348" s="12" t="inlineStr">
         <is>
-          <t>万顷</t>
+          <t>莱伊</t>
         </is>
       </c>
       <c r="B348" s="11" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>S9-1</t>
         </is>
       </c>
       <c r="C348" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D348" s="22" t="inlineStr">
         <is>
-          <t>maa://32417 (100.00)</t>
+          <t>maa://38295 (95.37), maa://49332 (91.67)</t>
         </is>
       </c>
       <c r="E348" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战万顷累计使用支援号令·γ型10次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战万顷并上场，且至少使用2次应东风</t>
+          <t>&gt; 由非助战莱伊累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲S9-1标准实战环境；必须编入非助战莱伊并上场，且使用莱伊使用至少2次“得见光芒”</t>
         </is>
       </c>
       <c r="F348" s="19" t="n"/>
@@ -25986,12 +25986,12 @@
     <row r="349" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A349" s="12" t="inlineStr">
         <is>
-          <t>小满</t>
+          <t>万顷</t>
         </is>
       </c>
       <c r="B349" s="11" t="inlineStr">
         <is>
-          <t>9-11</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C349" s="12" t="inlineStr">
@@ -26001,12 +26001,12 @@
       </c>
       <c r="D349" s="22" t="inlineStr">
         <is>
-          <t>maa://32419 (100.00)</t>
+          <t>maa://32417 (100.00)</t>
         </is>
       </c>
       <c r="E349" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战小满累计造成60000点伤害&gt; 3星通关主题曲9-11标准实战环境；必须编入非助战小满并上场，且至少使用2次乡音沉沉</t>
+          <t>&gt; 战斗中非助战万顷累计使用支援号令·γ型10次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战万顷并上场，且至少使用2次应东风</t>
         </is>
       </c>
       <c r="F349" s="19" t="n"/>
@@ -26040,12 +26040,12 @@
     <row r="350" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A350" s="12" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>小满</t>
         </is>
       </c>
       <c r="B350" s="11" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>9-11</t>
         </is>
       </c>
       <c r="C350" s="12" t="inlineStr">
@@ -26055,12 +26055,12 @@
       </c>
       <c r="D350" s="22" t="inlineStr">
         <is>
-          <t>maa://32416 (92.31)</t>
+          <t>maa://32419 (100.00)</t>
         </is>
       </c>
       <c r="E350" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战左乐累计造成40歼灭数&gt; 3星通关别传WB-5；必须编入非助战左乐并上场，且使用左乐至少歼灭8个敌人</t>
+          <t>&gt; 由非助战小满累计造成60000点伤害&gt; 3星通关主题曲9-11标准实战环境；必须编入非助战小满并上场，且至少使用2次乡音沉沉</t>
         </is>
       </c>
       <c r="F350" s="19" t="n"/>
@@ -26099,7 +26099,7 @@
       </c>
       <c r="B351" s="11" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
@@ -26109,12 +26109,12 @@
       </c>
       <c r="D351" s="22" t="inlineStr">
         <is>
-          <t>maa://45800 (100.00)</t>
+          <t>maa://32416 (92.31)</t>
         </is>
       </c>
       <c r="E351" s="22" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战左乐累计造成100000点伤害&gt; 3星通关别传RI-7；必须携带且部署非助战左乐，且至少释放3次佑序有炎</t>
+          <t>&gt; 由非助战左乐累计造成40歼灭数&gt; 3星通关别传WB-5；必须编入非助战左乐并上场，且使用左乐至少歼灭8个敌人</t>
         </is>
       </c>
       <c r="F351" s="19" t="n"/>
@@ -26148,27 +26148,27 @@
     <row r="352" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A352" s="12" t="inlineStr">
         <is>
-          <t>黍</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B352" s="11" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C352" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D352" s="22" t="inlineStr">
         <is>
-          <t>maa://32647 (97.60), maa://32415 (84.33), maa://34677 (100.00), maa://32892 (100.00), maa://32653 (81.25), maa://61839 (100.00), maa://61275 (100.00)</t>
+          <t>maa://45800 (100.00)</t>
         </is>
       </c>
       <c r="E352" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战黍并上场，且每次战斗至少释放1次离离枯荣&gt; 3星通关主题曲11-11标准实战环境；必须编入非助战黍并上场，且所有干员不被击倒</t>
+          <t>&gt; 使用非助战左乐累计造成100000点伤害&gt; 3星通关别传RI-7；必须携带且部署非助战左乐，且至少释放3次佑序有炎</t>
         </is>
       </c>
       <c r="F352" s="19" t="n"/>
@@ -26202,27 +26202,27 @@
     <row r="353" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A353" s="12" t="inlineStr">
         <is>
-          <t>红隼</t>
+          <t>黍</t>
         </is>
       </c>
       <c r="B353" s="11" t="inlineStr">
         <is>
-          <t>11-18</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D353" s="22" t="inlineStr">
         <is>
-          <t>maa://32420 (100.00)</t>
+          <t>maa://32647 (97.60), maa://32415 (84.33), maa://34677 (100.00), maa://32892 (100.00), maa://32653 (81.25), maa://61839 (100.00), maa://61275 (100.00)</t>
         </is>
       </c>
       <c r="E353" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战红隼并上场，且每次战斗至少释放2次醉刃乱舞&gt; 3星通关主题曲11-18标准实战环境；必须编入非助战红隼，且第一位部署红隼、红隼全程不撤退或被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战黍并上场，且每次战斗至少释放1次离离枯荣&gt; 3星通关主题曲11-11标准实战环境；必须编入非助战黍并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F353" s="19" t="n"/>
@@ -26256,12 +26256,12 @@
     <row r="354" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A354" s="12" t="inlineStr">
         <is>
-          <t>导火索</t>
+          <t>红隼</t>
         </is>
       </c>
       <c r="B354" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>11-18</t>
         </is>
       </c>
       <c r="C354" s="12" t="inlineStr">
@@ -26271,12 +26271,12 @@
       </c>
       <c r="D354" s="22" t="inlineStr">
         <is>
-          <t>maa://35606 (100.00)</t>
+          <t>maa://32420 (100.00)</t>
         </is>
       </c>
       <c r="E354" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战导火索累计造成80000点伤害&gt; 3星通关主题曲3-1；必须编入非助战导火索并上场，且使用导火索至少歼灭30个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战红隼并上场，且每次战斗至少释放2次醉刃乱舞&gt; 3星通关主题曲11-18标准实战环境；必须编入非助战红隼，且第一位部署红隼、红隼全程不撤退或被击倒</t>
         </is>
       </c>
       <c r="F354" s="19" t="n"/>
@@ -26310,12 +26310,12 @@
     <row r="355" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A355" s="12" t="inlineStr">
         <is>
-          <t>双月</t>
+          <t>导火索</t>
         </is>
       </c>
       <c r="B355" s="11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C355" s="12" t="inlineStr">
@@ -26325,12 +26325,12 @@
       </c>
       <c r="D355" s="22" t="inlineStr">
         <is>
-          <t>maa://34716 (90.00)</t>
+          <t>maa://35606 (100.00)</t>
         </is>
       </c>
       <c r="E355" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战双月累计使用全知者的战术10次&gt; 3星通关主题曲3-7；必须编入非助战双月并上场，且至少使用2次全知者的战术</t>
+          <t>&gt; 由非助战导火索累计造成80000点伤害&gt; 3星通关主题曲3-1；必须编入非助战导火索并上场，且使用导火索至少歼灭30个敌人</t>
         </is>
       </c>
       <c r="F355" s="19" t="n"/>
@@ -26364,12 +26364,12 @@
     <row r="356" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A356" s="12" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>双月</t>
         </is>
       </c>
       <c r="B356" s="11" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C356" s="12" t="inlineStr">
@@ -26379,12 +26379,12 @@
       </c>
       <c r="D356" s="22" t="inlineStr">
         <is>
-          <t>maa://39179 (100.00)</t>
+          <t>maa://34716 (90.00)</t>
         </is>
       </c>
       <c r="E356" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战医生累计使用激素手枪8次&gt; 3星通关主题曲2-5；必须编入非助战医生并上场，且不编入医疗干员</t>
+          <t>&gt; 战斗中非助战双月累计使用全知者的战术10次&gt; 3星通关主题曲3-7；必须编入非助战双月并上场，且至少使用2次全知者的战术</t>
         </is>
       </c>
       <c r="F356" s="19" t="n"/>
@@ -26418,27 +26418,27 @@
     <row r="357" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A357" s="12" t="inlineStr">
         <is>
-          <t>艾拉</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="B357" s="11" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C357" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D357" s="22" t="inlineStr">
         <is>
-          <t>maa://34865 (97.89), maa://34717 (94.20), *maa://45066 (71.43)</t>
+          <t>maa://39179 (100.00)</t>
         </is>
       </c>
       <c r="E357" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战艾拉累计部署雷鸣地雷30个&gt; 3星通关插曲DM-EX-1；必须编入非助战艾拉并上场，且使用艾拉歼灭至少2名萨卡兹穿刺手</t>
+          <t>&gt; 战斗中非助战医生累计使用激素手枪8次&gt; 3星通关主题曲2-5；必须编入非助战医生并上场，且不编入医疗干员</t>
         </is>
       </c>
       <c r="F357" s="19" t="n"/>
@@ -26472,27 +26472,27 @@
     <row r="358" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A358" s="12" t="inlineStr">
         <is>
-          <t>露托</t>
+          <t>艾拉</t>
         </is>
       </c>
       <c r="B358" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C358" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D358" s="22" t="inlineStr">
         <is>
-          <t>maa://39180 (100.00)</t>
+          <t>maa://34865 (97.89), maa://34717 (94.20), *maa://45066 (71.43)</t>
         </is>
       </c>
       <c r="E358" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战露托累计使用强磁防卫8次&gt; 3星通关主题曲3-1；必须编入非助战露托并上场，且不编入其他重装干员</t>
+          <t>&gt; 战斗中非助战艾拉累计部署雷鸣地雷30个&gt; 3星通关插曲DM-EX-1；必须编入非助战艾拉并上场，且使用艾拉歼灭至少2名萨卡兹穿刺手</t>
         </is>
       </c>
       <c r="F358" s="19" t="n"/>
@@ -26526,27 +26526,27 @@
     <row r="359" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A359" s="12" t="inlineStr">
         <is>
-          <t>奥达</t>
+          <t>露托</t>
         </is>
       </c>
       <c r="B359" s="11" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D359" s="22" t="inlineStr">
         <is>
-          <t>maa://45834 (100.00), maa://45833 (100.00)</t>
+          <t>maa://39180 (100.00)</t>
         </is>
       </c>
       <c r="E359" s="22" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战奥达累计使用4次锻锤之力&gt; 3星通关主题曲S3-6；必须携带且部署非助战奥达，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战露托累计使用强磁防卫8次&gt; 3星通关主题曲3-1；必须编入非助战露托并上场，且不编入其他重装干员</t>
         </is>
       </c>
       <c r="F359" s="19" t="n"/>
@@ -26580,27 +26580,27 @@
     <row r="360" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A360" s="12" t="inlineStr">
         <is>
-          <t>阿罗玛</t>
+          <t>奥达</t>
         </is>
       </c>
       <c r="B360" s="11" t="inlineStr">
         <is>
-          <t>GT-HX-3</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C360" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D360" s="22" t="inlineStr">
         <is>
-          <t>maa://39181 (88.89)</t>
+          <t>maa://45834 (100.00), maa://45833 (100.00)</t>
         </is>
       </c>
       <c r="E360" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战阿罗玛并上场，且每次战斗至少释放1次小心地滑&gt; 3星通关别传GT-HX-3；必须编入非助战阿罗玛并上场，且使用阿罗玛至少歼灭20个敌人</t>
+          <t>&gt; 使用非助战奥达累计使用4次锻锤之力&gt; 3星通关主题曲S3-6；必须携带且部署非助战奥达，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F360" s="19" t="n"/>
@@ -26634,27 +26634,27 @@
     <row r="361" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A361" s="12" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>阿罗玛</t>
         </is>
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>GT-HX-3</t>
         </is>
       </c>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D361" s="22" t="inlineStr">
         <is>
-          <t>maa://36868 (99.34), maa://35996 (97.92), maa://47349 (97.56), **maa://39217 (38.89)</t>
+          <t>maa://39181 (88.89)</t>
         </is>
       </c>
       <c r="E361" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战阿斯卡纶累计造成180000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战阿斯卡纶并上场，且使用阿斯卡纶至少歼灭30个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战阿罗玛并上场，且每次战斗至少释放1次小心地滑&gt; 3星通关别传GT-HX-3；必须编入非助战阿罗玛并上场，且使用阿罗玛至少歼灭20个敌人</t>
         </is>
       </c>
       <c r="F361" s="19" t="n"/>
@@ -26693,22 +26693,22 @@
       </c>
       <c r="B362" s="11" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C362" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D362" s="22" t="inlineStr">
         <is>
-          <t>maa://49696 (99.60), maa://49695 (100.00), maa://49758 (98.78), *maa://52357 (75.00), *maa://59402 (56.67), *maa://63091 (64.29)</t>
+          <t>maa://36868 (99.35), maa://35996 (97.94), maa://47349 (97.62), **maa://39217 (38.89)</t>
         </is>
       </c>
       <c r="E362" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战阿斯卡纶累计使用“降临”5次&gt; 3星通关主题曲5-10，必须编入非助战阿斯卡纶并上场，其他成员不可编入特种干员</t>
+          <t>&gt; 由非助战阿斯卡纶累计造成180000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战阿斯卡纶并上场，且使用阿斯卡纶至少歼灭30个敌人</t>
         </is>
       </c>
       <c r="F362" s="19" t="n"/>
@@ -26742,27 +26742,27 @@
     <row r="363" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A363" s="12" t="inlineStr">
         <is>
-          <t>历阵锐枪芬</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B363" s="11" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D363" s="22" t="inlineStr">
         <is>
-          <t>maa://36647 (100.00)</t>
+          <t>maa://49696 (99.60), maa://49695 (100.00), maa://49758 (98.81), *maa://52357 (75.00), *maa://59402 (56.67), *maa://63091 (64.29)</t>
         </is>
       </c>
       <c r="E363" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战历阵锐枪芬，并确定第一位部署的干员是历阵锐枪芬&gt; 3星通关主题曲4-2；必须编入非助战历阵锐枪芬并上场，且不编入其他先锋干员</t>
+          <t>&gt; 战斗中非助战阿斯卡纶累计使用“降临”5次&gt; 3星通关主题曲5-10，必须编入非助战阿斯卡纶并上场，其他成员不可编入特种干员</t>
         </is>
       </c>
       <c r="F363" s="19" t="n"/>
@@ -26796,27 +26796,27 @@
     <row r="364" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A364" s="12" t="inlineStr">
         <is>
-          <t>魔王</t>
+          <t>历阵锐枪芬</t>
         </is>
       </c>
       <c r="B364" s="11" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C364" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D364" s="22" t="inlineStr">
         <is>
-          <t>maa://42299 (97.87), maa://42224 (85.00)</t>
+          <t>maa://36647 (100.00)</t>
         </is>
       </c>
       <c r="E364" s="22" t="inlineStr">
         <is>
-          <t>&gt; 携带非助战魔王完成5次战斗，且每次战斗至少发动一次“编织重构现世”&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战魔王并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战历阵锐枪芬，并确定第一位部署的干员是历阵锐枪芬&gt; 3星通关主题曲4-2；必须编入非助战历阵锐枪芬并上场，且不编入其他先锋干员</t>
         </is>
       </c>
       <c r="F364" s="19" t="n"/>
@@ -26850,12 +26850,12 @@
     <row r="365" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A365" s="12" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>魔王</t>
         </is>
       </c>
       <c r="B365" s="11" t="inlineStr">
         <is>
-          <t>14-9</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C365" s="12" t="inlineStr">
@@ -26865,12 +26865,12 @@
       </c>
       <c r="D365" s="22" t="inlineStr">
         <is>
-          <t>maa://49648 (96.15), maa://49662 (81.25)</t>
+          <t>maa://42299 (97.87), maa://42224 (85.00)</t>
         </is>
       </c>
       <c r="E365" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战逻各斯累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲14-9标准实战环境；必须编入非助战逻各斯并上场，且使用逻各斯至少歼灭7个敌人</t>
+          <t>&gt; 携带非助战魔王完成5次战斗，且每次战斗至少发动一次“编织重构现世”&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战魔王并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
       <c r="F365" s="19" t="n"/>
@@ -26909,22 +26909,22 @@
       </c>
       <c r="B366" s="11" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="C366" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D366" s="22" t="inlineStr">
         <is>
-          <t>maa://36646 (98.92), maa://36845 (95.89), **maa://39217 (38.89), maa://51007 (98.33)</t>
+          <t>maa://49648 (96.20), *maa://49662 (78.79)</t>
         </is>
       </c>
       <c r="E366" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战逻各斯累计造成100000点伤害&gt; 3星通关主题曲11-6标准实战环境，必须编入非助战逻各斯并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战逻各斯累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲14-9标准实战环境；必须编入非助战逻各斯并上场，且使用逻各斯至少歼灭7个敌人</t>
         </is>
       </c>
       <c r="F366" s="19" t="n"/>
@@ -26958,27 +26958,27 @@
     <row r="367" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A367" s="12" t="inlineStr">
         <is>
-          <t>维什戴尔</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B367" s="11" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C367" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D367" s="22" t="inlineStr">
         <is>
-          <t>maa://36645 (98.43), maa://36841 (92.65), maa://37484 (94.23), maa://37858 (93.55), **maa://56268 (50.00), maa://40489 (100.00)</t>
+          <t>maa://36646 (98.92), maa://36845 (95.92), **maa://39217 (38.89), maa://51007 (98.33), maa://70752 (100.00)</t>
         </is>
       </c>
       <c r="E367" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维什戴尔累计造成120000伤害&gt; 3星通关插曲DM-5；必须编入非助战维什戴尔并上场，且使用维什戴尔至少歼灭20个敌人</t>
+          <t>&gt; 由非助战逻各斯累计造成100000点伤害&gt; 3星通关主题曲11-6标准实战环境，必须编入非助战逻各斯并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F367" s="19" t="n"/>
@@ -27012,27 +27012,27 @@
     <row r="368" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A368" s="12" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>维什戴尔</t>
         </is>
       </c>
       <c r="B368" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C368" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D368" s="22" t="inlineStr">
         <is>
-          <t>maa://42635 (94.44), maa://50629 (83.33), maa://48859 (100.00)</t>
+          <t>maa://36645 (98.43), maa://36841 (92.65), maa://37484 (94.23), maa://37858 (93.55), **maa://56268 (50.00), maa://40489 (100.00)</t>
         </is>
       </c>
       <c r="E368" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战医疗职业的阿米娅累计使用慈悲愿景5次&gt; 3星通关主题曲3-8；必须编入非助战医疗职业的阿米娅并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战维什戴尔累计造成120000伤害&gt; 3星通关插曲DM-5；必须编入非助战维什戴尔并上场，且使用维什戴尔至少歼灭20个敌人</t>
         </is>
       </c>
       <c r="F368" s="19" t="n"/>
@@ -27066,27 +27066,27 @@
     <row r="369" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A369" s="12" t="inlineStr">
         <is>
-          <t>深巡</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B369" s="11" t="inlineStr">
         <is>
-          <t>SN-5</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C369" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D369" s="22" t="inlineStr">
         <is>
-          <t>maa://39183 (100.00)</t>
+          <t>maa://42635 (94.44), maa://50629 (83.33), maa://48859 (100.00)</t>
         </is>
       </c>
       <c r="E369" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战深巡累计使用行动能力剥夺8次&gt; 3星通关插曲SN-5，必须编入非助战深巡并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战医疗职业的阿米娅累计使用慈悲愿景5次&gt; 3星通关主题曲3-8；必须编入非助战医疗职业的阿米娅并上场，且不编入其他医疗干员</t>
         </is>
       </c>
       <c r="F369" s="19" t="n"/>
@@ -27120,12 +27120,12 @@
     <row r="370" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A370" s="12" t="inlineStr">
         <is>
-          <t>海霓</t>
+          <t>深巡</t>
         </is>
       </c>
       <c r="B370" s="11" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>SN-5</t>
         </is>
       </c>
       <c r="C370" s="12" t="inlineStr">
@@ -27135,12 +27135,12 @@
       </c>
       <c r="D370" s="22" t="inlineStr">
         <is>
-          <t>maa://39184 (100.00)</t>
+          <t>maa://39183 (100.00)</t>
         </is>
       </c>
       <c r="E370" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战海霓累计使用阻滞性显色剂8次&gt; 3星通关插曲SV-4；必须编入非助战海霓并上场，且不编入其他辅助干员</t>
+          <t>&gt; 战斗中非助战深巡累计使用行动能力剥夺8次&gt; 3星通关插曲SN-5，必须编入非助战深巡并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F370" s="19" t="n"/>
@@ -27174,27 +27174,27 @@
     <row r="371" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A371" s="12" t="inlineStr">
         <is>
-          <t>乌尔比安</t>
+          <t>海霓</t>
         </is>
       </c>
       <c r="B371" s="11" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C371" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D371" s="22" t="inlineStr">
         <is>
-          <t>maa://40957 (94.86), maa://48026 (94.70), maa://44635 (88.18), maa://41035 (93.59), *maa://60251 (76.47), maa://44660 (92.68), maa://41128 (84.21)</t>
+          <t>maa://39184 (100.00)</t>
         </is>
       </c>
       <c r="E371" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战乌尔比安累计使用必须开辟的通路10次&gt; 3星通关插曲SV-6；必须编入非助战乌尔比安并上场，并使用乌尔比安至少击败2名囊海爬行者</t>
+          <t>&gt; 战斗中非助战海霓累计使用阻滞性显色剂8次&gt; 3星通关插曲SV-4；必须编入非助战海霓并上场，且不编入其他辅助干员</t>
         </is>
       </c>
       <c r="F371" s="19" t="n"/>
@@ -27228,27 +27228,27 @@
     <row r="372" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A372" s="12" t="inlineStr">
         <is>
-          <t>渡桥</t>
+          <t>乌尔比安</t>
         </is>
       </c>
       <c r="B372" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C372" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D372" s="22" t="inlineStr">
         <is>
-          <t>maa://40164 (83.33)</t>
+          <t>maa://40957 (94.75), maa://48026 (94.70), maa://44635 (88.18), maa://41035 (93.59), *maa://60251 (76.47), maa://44660 (92.68), maa://41128 (84.21)</t>
         </is>
       </c>
       <c r="E372" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战渡桥累计使用承压功率8次&gt; 3星通关主题曲3-1；必须编入非助战渡桥并上场，且至少使用3次承压功率</t>
+          <t>&gt; 战斗中非助战乌尔比安累计使用必须开辟的通路10次&gt; 3星通关插曲SV-6；必须编入非助战乌尔比安并上场，并使用乌尔比安至少击败2名囊海爬行者</t>
         </is>
       </c>
       <c r="F372" s="19" t="n"/>
@@ -27282,27 +27282,27 @@
     <row r="373" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A373" s="12" t="inlineStr">
         <is>
-          <t>妮芙</t>
+          <t>渡桥</t>
         </is>
       </c>
       <c r="B373" s="11" t="inlineStr">
         <is>
-          <t>14-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C373" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D373" s="22" t="inlineStr">
         <is>
-          <t>maa://63883 (100.00), maa://64045 (100.00), *maa://64041 (80.00)</t>
+          <t>maa://40164 (83.33)</t>
         </is>
       </c>
       <c r="E373" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战妮芙累计造成60000点元素伤害&gt; 3星通关主题曲14-7标准实战环境；必须编入非助战妮芙并上场，且使用妮芙造成至少5000点元素伤害</t>
+          <t>&gt; 战斗中非助战渡桥累计使用承压功率8次&gt; 3星通关主题曲3-1；必须编入非助战渡桥并上场，且至少使用3次承压功率</t>
         </is>
       </c>
       <c r="F373" s="19" t="n"/>
@@ -27336,27 +27336,27 @@
     <row r="374" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A374" s="12" t="inlineStr">
         <is>
-          <t>锡人</t>
+          <t>妮芙</t>
         </is>
       </c>
       <c r="B374" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>14-7</t>
         </is>
       </c>
       <c r="C374" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D374" s="22" t="inlineStr">
         <is>
-          <t>maa://48268 (92.86)</t>
+          <t>maa://63883 (100.00), maa://64045 (100.00), *maa://64041 (80.00)</t>
         </is>
       </c>
       <c r="E374" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战锡人累计使用8次“大拉里”&gt; 3星通关主题曲4-3，必须编入非助战锡人并上场，且队伍中不能有其他医疗干员</t>
+          <t>&gt; 由非助战妮芙累计造成60000点元素伤害&gt; 3星通关主题曲14-7标准实战环境；必须编入非助战妮芙并上场，且使用妮芙造成至少5000点元素伤害</t>
         </is>
       </c>
       <c r="F374" s="19" t="n"/>
@@ -27390,12 +27390,12 @@
     <row r="375" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A375" s="12" t="inlineStr">
         <is>
-          <t>衡沙</t>
+          <t>锡人</t>
         </is>
       </c>
       <c r="B375" s="11" t="inlineStr">
         <is>
-          <t>DV-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C375" s="12" t="inlineStr">
@@ -27405,12 +27405,12 @@
       </c>
       <c r="D375" s="22" t="inlineStr">
         <is>
-          <t>maa://40165 (100.00)</t>
+          <t>maa://48268 (92.86)</t>
         </is>
       </c>
       <c r="E375" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计召唤非助战衡沙的召唤物20回&gt; 3星通关别传DV-2；必须编入非助战衡沙并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战锡人累计使用8次“大拉里”&gt; 3星通关主题曲4-3，必须编入非助战锡人并上场，且队伍中不能有其他医疗干员</t>
         </is>
       </c>
       <c r="F375" s="19" t="n"/>
@@ -27442,29 +27442,29 @@
       <c r="AF375" s="8" t="n"/>
     </row>
     <row r="376" ht="13.5" customFormat="1" customHeight="1" s="22">
-      <c r="A376" s="25" t="inlineStr">
-        <is>
-          <t>娜仁图亚</t>
-        </is>
-      </c>
-      <c r="B376" s="24" t="inlineStr">
-        <is>
-          <t>WB-6</t>
-        </is>
-      </c>
-      <c r="C376" s="25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D376" s="30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E376" s="30" t="inlineStr">
-        <is>
-          <t>&gt; 由非助战娜仁图亚累计造成100000点伤害&gt; 3星通关插曲登临意WB-6；必须编入非助战娜仁图亚并上场，其他成员仅可编入5名干员</t>
+      <c r="A376" s="12" t="inlineStr">
+        <is>
+          <t>衡沙</t>
+        </is>
+      </c>
+      <c r="B376" s="11" t="inlineStr">
+        <is>
+          <t>DV-2</t>
+        </is>
+      </c>
+      <c r="C376" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D376" s="22" t="inlineStr">
+        <is>
+          <t>maa://40165 (100.00)</t>
+        </is>
+      </c>
+      <c r="E376" s="22" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中累计召唤非助战衡沙的召唤物20回&gt; 3星通关别传DV-2；必须编入非助战衡沙并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
       <c r="F376" s="19" t="n"/>
@@ -27498,12 +27498,12 @@
     <row r="377" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A377" s="12" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>娜仁图亚</t>
         </is>
       </c>
       <c r="B377" s="11" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>WB-6</t>
         </is>
       </c>
       <c r="C377" s="12" t="inlineStr">
@@ -27513,12 +27513,12 @@
       </c>
       <c r="D377" s="22" t="inlineStr">
         <is>
-          <t>maa://45798 (98.63)</t>
+          <t>maa://70756 (93.75)</t>
         </is>
       </c>
       <c r="E377" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战佩佩累计造成40歼灭数&gt; 3星通关主题曲3-8；必须编入非助战佩佩并上场，且使用佩佩歼灭碎骨</t>
+          <t>&gt; 由非助战娜仁图亚累计造成100000点伤害&gt; 3星通关插曲登临意WB-6；必须编入非助战娜仁图亚并上场，其他成员仅可编入5名干员</t>
         </is>
       </c>
       <c r="F377" s="19" t="n"/>
@@ -27552,12 +27552,12 @@
     <row r="378" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A378" s="12" t="inlineStr">
         <is>
-          <t>森西</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B378" s="11" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C378" s="12" t="inlineStr">
@@ -27567,12 +27567,12 @@
       </c>
       <c r="D378" s="22" t="inlineStr">
         <is>
-          <t>maa://42331 (100.00)</t>
+          <t>maa://45798 (98.63)</t>
         </is>
       </c>
       <c r="E378" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战森西累计使用团体魔物大餐6次&gt; 3星通关主题曲1-12；必须编入非助战森西并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战佩佩累计造成40歼灭数&gt; 3星通关主题曲3-8；必须编入非助战佩佩并上场，且使用佩佩歼灭碎骨</t>
         </is>
       </c>
       <c r="F378" s="19" t="n"/>
@@ -27606,27 +27606,27 @@
     <row r="379" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A379" s="12" t="inlineStr">
         <is>
-          <t>齐尔查克</t>
+          <t>森西</t>
         </is>
       </c>
       <c r="B379" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C379" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D379" s="22" t="inlineStr">
         <is>
-          <t>maa://42333 (100.00), maa://50518 (100.00), maa://41977 (100.00)</t>
+          <t>maa://42331 (100.00)</t>
         </is>
       </c>
       <c r="E379" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战齐尔查克累计使用随机应变6次&gt; 3星通关主题曲4-3；必须编入非助战齐尔查克并上场，其他成员不可编入先锋干员</t>
+          <t>&gt; 战斗中非助战森西累计使用团体魔物大餐6次&gt; 3星通关主题曲1-12；必须编入非助战森西并上场，且所有干员不被击倒</t>
         </is>
       </c>
       <c r="F379" s="19" t="n"/>
@@ -27660,27 +27660,27 @@
     <row r="380" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A380" s="12" t="inlineStr">
         <is>
-          <t>莱欧斯</t>
+          <t>齐尔查克</t>
         </is>
       </c>
       <c r="B380" s="11" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C380" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D380" s="22" t="inlineStr">
         <is>
-          <t>maa://42338 (100.00), maa://41976 (100.00)</t>
+          <t>maa://42333 (100.00), maa://50518 (100.00), maa://41977 (100.00)</t>
         </is>
       </c>
       <c r="E380" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战莱欧斯并上场，且每次战斗至少释放1次威吓战法&gt; 3星通关主题曲2-4；必须编入非助战莱欧斯并上场，并使用莱欧斯至少击败1名高阶术师</t>
+          <t>&gt; 战斗中非助战齐尔查克累计使用随机应变6次&gt; 3星通关主题曲4-3；必须编入非助战齐尔查克并上场，其他成员不可编入先锋干员</t>
         </is>
       </c>
       <c r="F380" s="19" t="n"/>
@@ -27714,12 +27714,12 @@
     <row r="381" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A381" s="12" t="inlineStr">
         <is>
-          <t>玛露西尔</t>
+          <t>莱欧斯</t>
         </is>
       </c>
       <c r="B381" s="11" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C381" s="12" t="inlineStr">
@@ -27729,12 +27729,12 @@
       </c>
       <c r="D381" s="22" t="inlineStr">
         <is>
-          <t>maa://41110 (98.55), maa://45605 (90.00)</t>
+          <t>maa://42338 (100.00), maa://41976 (100.00)</t>
         </is>
       </c>
       <c r="E381" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战玛露西尔累计造成100000点伤害&gt; 3星通关主题曲5-10；必须编入非助战玛露西尔并上场，且使用玛露西尔至少歼灭10名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战莱欧斯并上场，且每次战斗至少释放1次威吓战法&gt; 3星通关主题曲2-4；必须编入非助战莱欧斯并上场，并使用莱欧斯至少击败1名高阶术师</t>
         </is>
       </c>
       <c r="F381" s="19" t="n"/>
@@ -27768,27 +27768,27 @@
     <row r="382" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A382" s="12" t="inlineStr">
         <is>
-          <t>凯瑟琳</t>
+          <t>玛露西尔</t>
         </is>
       </c>
       <c r="B382" s="11" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C382" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D382" s="22" t="inlineStr">
         <is>
-          <t>maa://42343 (100.00)</t>
+          <t>maa://41110 (98.55), maa://45605 (90.00)</t>
         </is>
       </c>
       <c r="E382" s="22" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战凯瑟琳累计部署15个“支援装置”&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战凯瑟琳并上场，且凯瑟琳使用至少2次“战火淬炼”</t>
+          <t>&gt; 由非助战玛露西尔累计造成100000点伤害&gt; 3星通关主题曲5-10；必须编入非助战玛露西尔并上场，且使用玛露西尔至少歼灭10名敌人</t>
         </is>
       </c>
       <c r="F382" s="19" t="n"/>
@@ -27822,12 +27822,12 @@
     <row r="383" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A383" s="12" t="inlineStr">
         <is>
-          <t>波卜</t>
+          <t>凯瑟琳</t>
         </is>
       </c>
       <c r="B383" s="11" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C383" s="12" t="inlineStr">
@@ -27837,12 +27837,12 @@
       </c>
       <c r="D383" s="22" t="inlineStr">
         <is>
-          <t>maa://43095 (100.00)</t>
+          <t>maa://42343 (100.00)</t>
         </is>
       </c>
       <c r="E383" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战波卜累计造成30次灼燃爆发&gt; 3星通关主题曲4-8；必须编入非助战波卜并上场，且波卜使用至少2次“此路不通”</t>
+          <t>&gt; 使用非助战凯瑟琳累计部署15个“支援装置”&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战凯瑟琳并上场，且凯瑟琳使用至少2次“战火淬炼”</t>
         </is>
       </c>
       <c r="F383" s="19" t="n"/>
@@ -27876,27 +27876,27 @@
     <row r="384" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A384" s="12" t="inlineStr">
         <is>
-          <t>维娜·维多利亚</t>
+          <t>波卜</t>
         </is>
       </c>
       <c r="B384" s="11" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C384" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D384" s="22" t="inlineStr">
         <is>
-          <t>maa://44233 (91.80), maa://45570 (96.72)</t>
+          <t>maa://43095 (100.00)</t>
         </is>
       </c>
       <c r="E384" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维娜·维多利亚累计造成120000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战维娜·维多利亚并上场，其他成员仅可编入5名干员</t>
+          <t>&gt; 由非助战波卜累计造成30次灼燃爆发&gt; 3星通关主题曲4-8；必须编入非助战波卜并上场，且波卜使用至少2次“此路不通”</t>
         </is>
       </c>
       <c r="F384" s="19" t="n"/>
@@ -27930,27 +27930,27 @@
     <row r="385" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A385" s="12" t="inlineStr">
         <is>
-          <t>裁度</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B385" s="11" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C385" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D385" s="22" t="inlineStr">
         <is>
-          <t>maa://43097 (87.50)</t>
+          <t>maa://44233 (91.80), maa://45570 (96.77)</t>
         </is>
       </c>
       <c r="E385" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战裁度并部署至少2次，且使用裁度击败至少4名敌人&gt; 3星通关主题曲5-8；必须编入非助战裁度并上场，且至少束缚12次敌人</t>
+          <t>&gt; 由非助战维娜·维多利亚累计造成120000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战维娜·维多利亚并上场，其他成员仅可编入5名干员</t>
         </is>
       </c>
       <c r="F385" s="19" t="n"/>
@@ -27984,12 +27984,12 @@
     <row r="386" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A386" s="12" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>裁度</t>
         </is>
       </c>
       <c r="B386" s="11" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C386" s="12" t="inlineStr">
@@ -27999,12 +27999,12 @@
       </c>
       <c r="D386" s="22" t="inlineStr">
         <is>
-          <t>maa://43872 (93.75)</t>
+          <t>maa://43097 (87.50)</t>
         </is>
       </c>
       <c r="E386" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战弑君者&gt; 3星通关主题曲4-4；必须编入非助战弑君者并上场，且不编入其他特种干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战裁度并部署至少2次，且使用裁度击败至少4名敌人&gt; 3星通关主题曲5-8；必须编入非助战裁度并上场，且至少束缚12次敌人</t>
         </is>
       </c>
       <c r="F386" s="19" t="n"/>
@@ -28043,7 +28043,7 @@
       </c>
       <c r="B387" s="11" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C387" s="12" t="inlineStr">
@@ -28053,12 +28053,12 @@
       </c>
       <c r="D387" s="22" t="inlineStr">
         <is>
-          <t>*maa://53307 (68.97)</t>
+          <t>maa://43872 (93.75)</t>
         </is>
       </c>
       <c r="E387" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战弑君者累计使用8次烽烟行刑场&gt; 3星通关主题曲4-8；必须编入非助战弑君者并上场，且使用2次烽烟行刑场</t>
+          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战弑君者&gt; 3星通关主题曲4-4；必须编入非助战弑君者并上场，且不编入其他特种干员</t>
         </is>
       </c>
       <c r="F387" s="19" t="n"/>
@@ -28092,12 +28092,12 @@
     <row r="388" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A388" s="12" t="inlineStr">
         <is>
-          <t>忍冬</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B388" s="11" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C388" s="12" t="inlineStr">
@@ -28107,12 +28107,12 @@
       </c>
       <c r="D388" s="22" t="inlineStr">
         <is>
-          <t>maa://43875 (98.33)</t>
+          <t>*maa://53307 (68.97)</t>
         </is>
       </c>
       <c r="E388" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战忍冬累计造成80000点伤害&gt; 3星通关主题曲S2-3；必须编入非助战忍冬并上场，且使用忍冬击败至少24名敌人</t>
+          <t>&gt; 战斗中非助战弑君者累计使用8次烽烟行刑场&gt; 3星通关主题曲4-8；必须编入非助战弑君者并上场，且使用2次烽烟行刑场</t>
         </is>
       </c>
       <c r="F388" s="19" t="n"/>
@@ -28146,27 +28146,27 @@
     <row r="389" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A389" s="12" t="inlineStr">
         <is>
-          <t>荒芜拉普兰德</t>
+          <t>忍冬</t>
         </is>
       </c>
       <c r="B389" s="11" t="inlineStr">
         <is>
-          <t>IS-8</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C389" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D389" s="22" t="inlineStr">
         <is>
-          <t>maa://42970 (81.07), maa://44745 (98.08), **maa://49516 (37.93), *maa://45952 (57.14), ***maa://46851 (12.50), *maa://44896 (80.00)</t>
+          <t>maa://43875 (98.33)</t>
         </is>
       </c>
       <c r="E389" s="22" t="inlineStr">
         <is>
-          <t>&gt; 由非助战荒芜拉普兰德累计造成150000点伤害&gt; 3星通关别传IS-8；必须编入非助战荒芜拉普兰德并上场，且荒芜拉普兰德使用至少2次逐猎狂飙或终幕·浩劫</t>
+          <t>&gt; 由非助战忍冬累计造成80000点伤害&gt; 3星通关主题曲S2-3；必须编入非助战忍冬并上场，且使用忍冬击败至少24名敌人</t>
         </is>
       </c>
       <c r="F389" s="19" t="n"/>
@@ -28200,27 +28200,27 @@
     <row r="390" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A390" s="12" t="inlineStr">
         <is>
-          <t>瑰盐</t>
+          <t>荒芜拉普兰德</t>
         </is>
       </c>
       <c r="B390" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>IS-8</t>
         </is>
       </c>
       <c r="C390" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D390" s="22" t="inlineStr">
         <is>
-          <t>maa://44389 (100.00)</t>
+          <t>maa://42970 (81.07), maa://44745 (98.08), **maa://49516 (37.93), *maa://45952 (57.14), ***maa://46851 (12.50), *maa://44896 (80.00)</t>
         </is>
       </c>
       <c r="E390" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战瑰盐累计使用绝妙的长效药呀8次&gt; 3星通关主题曲4-6；必须编入非助战瑰盐并上场，且至少使用1次绝妙的长效药呀</t>
+          <t>&gt; 由非助战荒芜拉普兰德累计造成150000点伤害&gt; 3星通关别传IS-8；必须编入非助战荒芜拉普兰德并上场，且荒芜拉普兰德使用至少2次逐猎狂飙或终幕·浩劫</t>
         </is>
       </c>
       <c r="F390" s="19" t="n"/>
@@ -28254,12 +28254,12 @@
     <row r="391" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A391" s="12" t="inlineStr">
         <is>
-          <t>特克诺</t>
+          <t>瑰盐</t>
         </is>
       </c>
       <c r="B391" s="11" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C391" s="12" t="inlineStr">
@@ -28269,12 +28269,12 @@
       </c>
       <c r="D391" s="22" t="inlineStr">
         <is>
-          <t>maa://59690 (100.00)</t>
+          <t>maa://44389 (100.00)</t>
         </is>
       </c>
       <c r="E391" s="22" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战特克诺并上场，且每次战斗至少释放1次“恣意挥洒”&gt; 3星通关插曲DH-6，必须编入非助战特克诺并上场，其他成员仅可编入7名干员</t>
+          <t>&gt; 战斗中非助战瑰盐累计使用绝妙的长效药呀8次&gt; 3星通关主题曲4-6；必须编入非助战瑰盐并上场，且至少使用1次绝妙的长效药呀</t>
         </is>
       </c>
       <c r="F391" s="19" t="n"/>
@@ -28308,12 +28308,12 @@
     <row r="392" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A392" s="12" t="inlineStr">
         <is>
-          <t>引星棘刺</t>
+          <t>特克诺</t>
         </is>
       </c>
       <c r="B392" s="11" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C392" s="12" t="inlineStr">
@@ -28323,12 +28323,12 @@
       </c>
       <c r="D392" s="22" t="inlineStr">
         <is>
-          <t>maa://48113 (100.00)</t>
+          <t>maa://59690 (100.00)</t>
         </is>
       </c>
       <c r="E392" s="22" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战引星棘刺累计使用20次解构涌潮&gt; 3星通关别传OF-7；必须编入非助战引星棘刺并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战特克诺并上场，且每次战斗至少释放1次“恣意挥洒”&gt; 3星通关插曲DH-6，必须编入非助战特克诺并上场，其他成员仅可编入7名干员</t>
         </is>
       </c>
       <c r="F392" s="19" t="n"/>
@@ -28362,12 +28362,12 @@
     <row r="393">
       <c r="A393" s="17" t="inlineStr">
         <is>
-          <t>行箸</t>
+          <t>引星棘刺</t>
         </is>
       </c>
       <c r="B393" s="23" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C393" s="17" t="inlineStr">
@@ -28377,24 +28377,24 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>maa://45807 (100.00)</t>
+          <t>maa://48113 (100.00)</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战行箸累计使用8次食不厌精&gt; 3星通关主题曲3-2；必须编入非助战行箸并上场，且所有干员不能被击倒</t>
+          <t>&gt; 战斗中非助战引星棘刺累计使用20次解构涌潮&gt; 3星通关别传OF-7；必须编入非助战引星棘刺并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="17" t="inlineStr">
         <is>
-          <t>寻澜</t>
+          <t>行箸</t>
         </is>
       </c>
       <c r="B394" s="23" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C394" s="17" t="inlineStr">
@@ -28404,51 +28404,51 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://50552 (100.00)</t>
+          <t>maa://45807 (100.00)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战寻澜并上场，且使用寻澜歼灭至少3个敌人&gt; 3星通关主题曲3-5；必须编入非助战寻澜并上场，且至少使用2次洞悉</t>
+          <t>&gt; 使用非助战行箸累计使用8次食不厌精&gt; 3星通关主题曲3-2；必须编入非助战行箸并上场，且所有干员不能被击倒</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="17" t="inlineStr">
         <is>
-          <t>烛煌</t>
+          <t>寻澜</t>
         </is>
       </c>
       <c r="B395" s="17" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C395" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>maa://63890 (98.04), maa://64043 (100.00)</t>
+          <t>maa://50552 (100.00)</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战烛煌并上场，且每次战斗至少释放1次“众恶的焚场”&gt; 3星通关主题曲6-10；必须编入非助战烛煌并上场，且至少使用2次“众恶的焚场”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战寻澜并上场，且使用寻澜歼灭至少3个敌人&gt; 3星通关主题曲3-5；必须编入非助战寻澜并上场，且至少使用2次洞悉</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="17" t="inlineStr">
         <is>
-          <t>诺威尔</t>
+          <t>烛煌</t>
         </is>
       </c>
       <c r="B396" s="17" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C396" s="17" t="inlineStr">
@@ -28458,132 +28458,132 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>*maa://47175 (66.67), maa://47174 (100.00)</t>
+          <t>maa://63890 (98.08), maa://64043 (100.00)</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战诺威尔并上场，且每次战斗至少释放1次生命不息&gt; 3星通关主题曲5-7；必须编入非助战诺威尔并上场，且队伍中不能有其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战烛煌并上场，且每次战斗至少释放1次“众恶的焚场”&gt; 3星通关主题曲6-10；必须编入非助战烛煌并上场，且至少使用2次“众恶的焚场”</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="17" t="inlineStr">
         <is>
+          <t>诺威尔</t>
+        </is>
+      </c>
+      <c r="B397" s="17" t="inlineStr">
+        <is>
+          <t>5-7</t>
+        </is>
+      </c>
+      <c r="C397" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>*maa://47175 (66.67), maa://47174 (100.00)</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>&gt; 完成5次战斗；必须编入非助战诺威尔并上场，且每次战斗至少释放1次生命不息&gt; 3星通关主题曲5-7；必须编入非助战诺威尔并上场，且队伍中不能有其他医疗干员</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="17" t="inlineStr">
+        <is>
           <t>隐德来希</t>
         </is>
       </c>
-      <c r="B397" s="17" t="inlineStr">
+      <c r="B398" s="17" t="inlineStr">
         <is>
           <t>10-12</t>
         </is>
       </c>
-      <c r="C397" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
+      <c r="C398" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
         <is>
           <t>maa://47023 (87.50)</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr">
+      <c r="E398" t="inlineStr">
         <is>
           <t>&gt; 使用非助战隐德来希累计造成100000点伤害&gt; 3星通关主题曲10-12标准实战环境；必须编入非助战隐德来希并上场，且隐德来希至少使用3次灵与欲的惜别</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" s="28" t="inlineStr">
+    <row r="399">
+      <c r="A399" s="28" t="inlineStr">
         <is>
           <t>水灯心</t>
         </is>
       </c>
-      <c r="B398" s="28" t="inlineStr">
+      <c r="B399" s="28" t="inlineStr">
         <is>
           <t>4-6</t>
         </is>
       </c>
-      <c r="C398" s="28" t="inlineStr">
+      <c r="C399" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D398" s="29" t="inlineStr">
+      <c r="D399" s="29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E398" s="29" t="inlineStr">
+      <c r="E399" s="29" t="inlineStr">
         <is>
           <t>&gt; 由非助战水灯心累计造成20歼灭数&gt; 3星通关主题曲4-6；必须编入非助战水灯心并上场，且至少使用2次可驯服的</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="17" t="inlineStr">
-        <is>
-          <t>钼铅</t>
-        </is>
-      </c>
-      <c r="B399" s="17" t="inlineStr">
-        <is>
-          <t>9-6</t>
-        </is>
-      </c>
-      <c r="C399" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>**maa://48618 (50.00)</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>&gt; 战斗中非助战钼铅累计部署矿石“杀手”30个&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战钼铅并上场，且使用钼铅至少击败1名深池重甲卫士</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="17" t="inlineStr">
         <is>
-          <t>死芒</t>
+          <t>钼铅</t>
         </is>
       </c>
       <c r="B400" s="17" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C400" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>maa://59533 (97.96), maa://59577 (100.00)</t>
+          <t>**maa://48618 (50.00)</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战死芒并上场，且每次战斗至少释放2次“冠死以冕”&gt; 3星通关主题曲4-8，必须编入非助战死芒并上场，其他成员仅可编入辅助干员</t>
+          <t>&gt; 战斗中非助战钼铅累计部署矿石“杀手”30个&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战钼铅并上场，且使用钼铅至少击败1名深池重甲卫士</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="17" t="inlineStr">
         <is>
-          <t>骋风</t>
+          <t>死芒</t>
         </is>
       </c>
       <c r="B401" s="17" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C401" s="17" t="inlineStr">
@@ -28593,213 +28593,213 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>**maa://51907 (50.00), maa://51908 (100.00)</t>
+          <t>maa://59533 (97.96), maa://59577 (100.00)</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战骋风并上场，且每次战斗至少释放1次招无虚发&gt; 3星通关插曲SN-2；必须编入非助战骋风并上场，且使用2次招无虚发</t>
+          <t>&gt; 完成5次战斗；必须编入非助战死芒并上场，且每次战斗至少释放2次“冠死以冕”&gt; 3星通关主题曲4-8，必须编入非助战死芒并上场，其他成员仅可编入辅助干员</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="17" t="inlineStr">
         <is>
-          <t>阿兰娜</t>
+          <t>骋风</t>
         </is>
       </c>
       <c r="B402" s="17" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C402" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>**maa://59691 (50.00)</t>
+          <t>**maa://51907 (50.00), maa://51908 (100.00)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战阿兰娜累计部署15个“支援装置”&gt; 3星通关主题曲7-14；必须编入非助战阿兰娜并上场，且至少使用2次“万斤顶”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战骋风并上场，且每次战斗至少释放1次招无虚发&gt; 3星通关插曲SN-2；必须编入非助战骋风并上场，且使用2次招无虚发</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="17" t="inlineStr">
         <is>
-          <t>信仰搅拌机</t>
+          <t>阿兰娜</t>
         </is>
       </c>
       <c r="B403" s="17" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C403" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>maa://51898 (100.00), maa://57241 (100.00)</t>
+          <t>**maa://59691 (50.00)</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战信仰搅拌机并上场，且每次战斗至少释放1次退休前布道&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战信仰搅拌机并上场，且使用信仰搅拌机歼灭至少10名敌人</t>
+          <t>&gt; 使用非助战阿兰娜累计部署15个“支援装置”&gt; 3星通关主题曲7-14；必须编入非助战阿兰娜并上场，且至少使用2次“万斤顶”</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="17" t="inlineStr">
         <is>
-          <t>蕾缪安</t>
+          <t>信仰搅拌机</t>
         </is>
       </c>
       <c r="B404" s="17" t="inlineStr">
         <is>
-          <t>13-13</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C404" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>maa://51880 (99.28), maa://56651 (100.00), maa://51878 (100.00)</t>
+          <t>maa://51898 (100.00), maa://57241 (100.00)</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>&gt; 由非助战蕾缪安累计造成30歼灭数&gt; 3星通关主题曲13-13标准实战环境；必须编入非助战蕾缪安并上场，且蕾缪安歼灭至少2个萨卡兹骸骨鞭笞者</t>
+          <t>&gt; 完成5次战斗；必须编入非助战信仰搅拌机并上场，且每次战斗至少释放1次退休前布道&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战信仰搅拌机并上场，且使用信仰搅拌机歼灭至少10名敌人</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="17" t="inlineStr">
         <is>
-          <t>新约能天使</t>
+          <t>蕾缪安</t>
         </is>
       </c>
       <c r="B405" s="17" t="inlineStr">
         <is>
-          <t>GA-EX-5</t>
+          <t>13-13</t>
         </is>
       </c>
       <c r="C405" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>maa://51872 (96.69), maa://51876 (99.07), maa://63228 (88.57), maa://51873 (100.00), maa://62047 (92.86)</t>
+          <t>maa://51880 (99.28), maa://56651 (100.00), maa://51878 (100.00)</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战新约能天使累计使用开火成瘾症8次&gt; 3星通关插曲GA-EX-5；必须编入非助战新约能天使并上场，且使用2次开火成瘾症</t>
+          <t>&gt; 由非助战蕾缪安累计造成30歼灭数&gt; 3星通关主题曲13-13标准实战环境；必须编入非助战蕾缪安并上场，且蕾缪安歼灭至少2个萨卡兹骸骨鞭笞者</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="17" t="inlineStr">
         <is>
-          <t>Miss.Christine</t>
+          <t>新约能天使</t>
         </is>
       </c>
       <c r="B406" s="17" t="inlineStr">
         <is>
-          <t>DM-7</t>
+          <t>GA-EX-5</t>
         </is>
       </c>
       <c r="C406" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>*maa://67814 (66.67)</t>
+          <t>maa://51872 (96.70), maa://51876 (99.08), maa://63228 (88.57), maa://51873 (100.00), maa://62047 (92.86)</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战Miss.Christine累计使用“狂饮之宴”10次&gt; 3星通关插曲DM-7，必须编入非助战Miss.Christine并上场，且至少使用2次“狂饮之宴”</t>
+          <t>&gt; 战斗中非助战新约能天使累计使用开火成瘾症8次&gt; 3星通关插曲GA-EX-5；必须编入非助战新约能天使并上场，且使用2次开火成瘾症</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="17" t="inlineStr">
         <is>
-          <t>酒神</t>
+          <t>Miss.Christine</t>
         </is>
       </c>
       <c r="B407" s="17" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>DM-7</t>
         </is>
       </c>
       <c r="C407" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>maa://60449 (99.02), maa://59493 (96.90)</t>
+          <t>*maa://67814 (66.67)</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战酒神累计造成60000点神经损伤&gt; 3星通关主题曲9-6标准实战环境，必须编入非助战酒神并上场，且酒神使用至少2次“空剧场”</t>
+          <t>&gt; 战斗中非助战Miss.Christine累计使用“狂饮之宴”10次&gt; 3星通关插曲DM-7，必须编入非助战Miss.Christine并上场，且至少使用2次“狂饮之宴”</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="17" t="inlineStr">
         <is>
-          <t>录武官</t>
+          <t>酒神</t>
         </is>
       </c>
       <c r="B408" s="17" t="inlineStr">
         <is>
-          <t>HS-5</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C408" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>maa://67815 (100.00)</t>
+          <t>maa://60449 (99.04), maa://59493 (96.90)</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战录武官累计使用“一点关窍”6次&gt; 3星通关插曲HS-5，必须编入非助战录武官并上场，且不编入其他医疗干员</t>
+          <t>&gt; 使用非助战酒神累计造成60000点神经损伤&gt; 3星通关主题曲9-6标准实战环境，必须编入非助战酒神并上场，且酒神使用至少2次“空剧场”</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="17" t="inlineStr">
         <is>
-          <t>司霆惊蛰</t>
+          <t>录武官</t>
         </is>
       </c>
       <c r="B409" s="17" t="inlineStr">
         <is>
-          <t>DV-7</t>
+          <t>HS-5</t>
         </is>
       </c>
       <c r="C409" s="17" t="inlineStr">
@@ -28809,24 +28809,24 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>maa://62756 (96.05)</t>
+          <t>maa://67815 (100.00)</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>&gt; 由非助战司霆惊蛰累计造成120000点伤害&gt; 3星通关插曲DV-7；必须编入非助战司霆惊蛰并上场，且使用1次“天地通明”</t>
+          <t>&gt; 战斗中非助战录武官累计使用“一点关窍”6次&gt; 3星通关插曲HS-5，必须编入非助战录武官并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="17" t="inlineStr">
         <is>
-          <t>吉星</t>
+          <t>司霆惊蛰</t>
         </is>
       </c>
       <c r="B410" s="17" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>DV-7</t>
         </is>
       </c>
       <c r="C410" s="17" t="inlineStr">
@@ -28836,78 +28836,78 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>maa://67816 (100.00)</t>
+          <t>maa://62756 (96.05)</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>&gt; 由非助战吉星累计造成30歼灭数&gt; 3星通关主题曲S5-9，必须编入非助战吉星并上场，且至少使用2次“吉星高照！”</t>
+          <t>&gt; 由非助战司霆惊蛰累计造成120000点伤害&gt; 3星通关插曲DV-7；必须编入非助战司霆惊蛰并上场，且使用1次“天地通明”</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="17" t="inlineStr">
         <is>
-          <t>遥</t>
+          <t>吉星</t>
         </is>
       </c>
       <c r="B411" s="17" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C411" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>maa://64040 (99.05), maa://52505 (98.25), maa://66377 (93.75), ***maa://66376 (20.00), ***maa://70187 (20.00)</t>
+          <t>maa://67816 (100.00)</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战遥累计使用“夏末游鳞”10次&gt; 3星通关主题曲7-14；必须编入非助战遥并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战吉星累计造成30歼灭数&gt; 3星通关主题曲S5-9，必须编入非助战吉星并上场，且至少使用2次“吉星高照！”</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="17" t="inlineStr">
         <is>
-          <t>祐天寺若麦</t>
+          <t>遥</t>
         </is>
       </c>
       <c r="B412" s="17" t="inlineStr">
         <is>
-          <t>ZT-4</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C412" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>maa://67090 (90.24)</t>
+          <t>maa://64040 (99.07), maa://52505 (97.99), maa://66377 (93.75), ***maa://66376 (16.67), ***maa://70187 (16.67)</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>&gt; 由非助战祐天寺若麦累计造成80000点伤害&gt; 3星通关插曲崔林特尔梅之金ZT-4；必须编入非助战祐天寺若麦并上场，且祐天寺若麦歼灭至少2个残党乐团鼓手</t>
+          <t>&gt; 战斗中非助战遥累计使用“夏末游鳞”10次&gt; 3星通关主题曲7-14；必须编入非助战遥并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="17" t="inlineStr">
         <is>
-          <t>八幡海铃</t>
+          <t>祐天寺若麦</t>
         </is>
       </c>
       <c r="B413" s="17" t="inlineStr">
         <is>
-          <t>BB-7</t>
+          <t>ZT-4</t>
         </is>
       </c>
       <c r="C413" s="17" t="inlineStr">
@@ -28917,147 +28917,201 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>maa://67388 (92.16)</t>
+          <t>maa://67090 (90.70)</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战八幡海铃并上场，且每次战斗至少释放1次无存之所&gt; 3星通关插曲巴别塔BB-7；必须编入非助战八幡海铃并上场，且八幡海铃歼灭至少1个自由佣兵“贝斯”</t>
+          <t>&gt; 由非助战祐天寺若麦累计造成80000点伤害&gt; 3星通关插曲崔林特尔梅之金ZT-4；必须编入非助战祐天寺若麦并上场，且祐天寺若麦歼灭至少2个残党乐团鼓手</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="17" t="inlineStr">
         <is>
-          <t>若叶睦</t>
+          <t>八幡海铃</t>
         </is>
       </c>
       <c r="B414" s="17" t="inlineStr">
         <is>
-          <t>13-16</t>
+          <t>BB-7</t>
         </is>
       </c>
       <c r="C414" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>maa://67089 (95.83), maa://67271 (94.44)</t>
+          <t>maa://67388 (89.47)</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战若叶睦累计使用6次破坏与滋养&gt; 3星通关主题曲13-16标准实战环境；必须编入非助战若叶睦并上场，且不编入其他特种干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战八幡海铃并上场，且每次战斗至少释放1次无存之所&gt; 3星通关插曲巴别塔BB-7；必须编入非助战八幡海铃并上场，且八幡海铃歼灭至少1个自由佣兵“贝斯”</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="17" t="inlineStr">
         <is>
-          <t>三角初华</t>
+          <t>若叶睦</t>
         </is>
       </c>
       <c r="B415" s="17" t="inlineStr">
         <is>
-          <t>ZT-6</t>
+          <t>13-16</t>
         </is>
       </c>
       <c r="C415" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>maa://67088 (92.65)</t>
+          <t>maa://67089 (95.92), maa://67271 (95.00)</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战三角初华累计使用6次我悲悯的&gt; 3星通关插曲崔林特尔梅之金ZT-6；必须编入非助战三角初华并上场，且所有干员不被击倒</t>
+          <t>&gt; 战斗中非助战若叶睦累计使用6次破坏与滋养&gt; 3星通关主题曲13-16标准实战环境；必须编入非助战若叶睦并上场，且不编入其他特种干员</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="17" t="inlineStr">
         <is>
+          <t>三角初华</t>
+        </is>
+      </c>
+      <c r="B416" s="17" t="inlineStr">
+        <is>
+          <t>ZT-6</t>
+        </is>
+      </c>
+      <c r="C416" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>maa://67088 (93.06)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战三角初华累计使用6次我悲悯的&gt; 3星通关插曲崔林特尔梅之金ZT-6；必须编入非助战三角初华并上场，且所有干员不被击倒</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="17" t="inlineStr">
+        <is>
           <t>丰川祥子</t>
         </is>
       </c>
-      <c r="B416" s="17" t="inlineStr">
+      <c r="B417" s="17" t="inlineStr">
         <is>
           <t>IS-7</t>
         </is>
       </c>
-      <c r="C416" s="17" t="inlineStr">
+      <c r="C417" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>maa://67087 (94.74), maa://67268 (96.84), maa://67269 (88.89), maa://67648 (100.00)</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>maa://67087 (94.87), maa://67268 (96.97), maa://67269 (88.89), maa://67648 (100.00)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
         <is>
           <t>&gt; 由非助战丰川祥子累计造成50歼灭数&gt; 3星通关插曲叙拉古人IS-7；必须编入非助战丰川祥子并上场，且至少使用2次残月的余响</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" s="28" t="inlineStr">
-        <is>
-          <t>冬时</t>
-        </is>
-      </c>
-      <c r="B417" s="28" t="inlineStr">
-        <is>
-          <t>R8-2</t>
-        </is>
-      </c>
-      <c r="C417" s="28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D417" s="29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E417" s="29" t="inlineStr">
-        <is>
-          <t>&gt; 战斗中累计部署非助战冬时12次&gt; 3星通关主题曲R8-2；必须编入非助战冬时并上场，且至少使用2次循理归因</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="28" t="inlineStr">
         <is>
+          <t>冬时</t>
+        </is>
+      </c>
+      <c r="B418" s="28" t="inlineStr">
+        <is>
+          <t>R8-2</t>
+        </is>
+      </c>
+      <c r="C418" s="28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D418" s="29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E418" s="29" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中累计部署非助战冬时12次&gt; 3星通关主题曲R8-2；必须编入非助战冬时并上场，且至少使用2次循理归因</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="28" t="inlineStr">
+        <is>
           <t>折桠</t>
         </is>
       </c>
-      <c r="B418" s="28" t="inlineStr">
+      <c r="B419" s="28" t="inlineStr">
         <is>
           <t>MB-5</t>
         </is>
       </c>
-      <c r="C418" s="28" t="inlineStr">
+      <c r="C419" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D418" s="29" t="inlineStr">
+      <c r="D419" s="29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E418" s="29" t="inlineStr">
+      <c r="E419" s="29" t="inlineStr">
         <is>
           <t>&gt; 战斗中非助战折桠累计使用8次生存决心&gt; 3星通关插曲孤岛风云MB-5；必须编入非助战折桠并上场，且不编入其他重装干员</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="17" t="inlineStr">
+        <is>
+          <t>真言</t>
+        </is>
+      </c>
+      <c r="B420" s="17" t="inlineStr">
+        <is>
+          <t>FC-5</t>
+        </is>
+      </c>
+      <c r="C420" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>maa://70877 (88.89)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>&gt; 由非助战真言累计造成60000点元素伤害&gt; 3星通关插曲照我以火FC-5；必须编入非助战真言并上场，且使用真言歼灭至少6名敌人</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业作者版.xlsx
+++ b/Excel/悖论&模组作业作者版.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>maa://25390 (98.89), maa://24702 (95.28), maa://36681 (85.71)</t>
+          <t>maa://25390 (98.93), maa://24702 (95.29), maa://36681 (85.87)</t>
         </is>
       </c>
       <c r="E2" s="19" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>maa://58660 (99.11), maa://39402 (96.26), *maa://34787 (75.24), *maa://54304 (70.00)</t>
+          <t>maa://58660 (99.15), maa://39402 (96.32), *maa://34787 (74.53), *maa://54304 (70.00)</t>
         </is>
       </c>
       <c r="M2" s="19" t="n"/>
@@ -774,7 +774,7 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>maa://22742 (98.01), maa://66635 (99.49)</t>
+          <t>maa://22742 (98.06), maa://66635 (99.51)</t>
         </is>
       </c>
       <c r="U2" s="19" t="n"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="AB2" s="8" t="inlineStr">
         <is>
-          <t>maa://36684 (98.78), maa://21246 (91.19)</t>
+          <t>maa://36684 (98.83), maa://21246 (91.19)</t>
         </is>
       </c>
       <c r="AC2" s="19" t="n"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>maa://59087 (98.21), maa://25251 (91.67)</t>
+          <t>maa://59087 (98.30), maa://25251 (91.67)</t>
         </is>
       </c>
       <c r="AG2" s="16" t="n"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>maa://40192 (99.55), maa://36987 (97.40), maa://39849 (94.12)</t>
+          <t>maa://40192 (99.53), maa://36987 (97.44), maa://39849 (94.44)</t>
         </is>
       </c>
       <c r="E3" s="19" t="n"/>
@@ -856,7 +856,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>maa://21247 (99.51)</t>
+          <t>maa://21247 (99.53)</t>
         </is>
       </c>
       <c r="I3" s="19" t="n"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
-          <t>maa://22880 (94.12), maa://20276 (94.79), maa://22749 (86.84)</t>
+          <t>maa://22880 (94.36), maa://20276 (94.84), maa://22749 (87.80)</t>
         </is>
       </c>
       <c r="M3" s="19" t="n"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>maa://21249 (98.95), maa://26254 (95.83), maa://22738 (85.71)</t>
+          <t>maa://21249 (98.99), maa://26254 (95.83), maa://22738 (85.71)</t>
         </is>
       </c>
       <c r="Q3" s="19" t="n"/>
@@ -904,7 +904,7 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>maa://60545 (99.25), maa://45854 (90.75), maa://24617 (91.30)</t>
+          <t>maa://60545 (99.23), maa://45854 (90.88), maa://24617 (91.37)</t>
         </is>
       </c>
       <c r="U3" s="19" t="n"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="X3" s="8" t="inlineStr">
         <is>
-          <t>maa://27396 (95.44), maa://27484 (99.31), maa://27480 (87.88)</t>
+          <t>maa://27396 (95.59), maa://27484 (99.32), maa://27480 (88.24)</t>
         </is>
       </c>
       <c r="Y3" s="19" t="n"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="AB3" s="8" t="inlineStr">
         <is>
-          <t>maa://52241 (99.37), maa://24390 (97.30)</t>
+          <t>maa://52241 (99.40), maa://24390 (97.33)</t>
         </is>
       </c>
       <c r="AC3" s="19" t="n"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="AF3" s="8" t="inlineStr">
         <is>
-          <t>maa://21289 (93.79)</t>
+          <t>maa://21289 (94.12)</t>
         </is>
       </c>
       <c r="AG3" s="16" t="n"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>maa://24632 (98.84), maa://22499 (90.91), maa://22746 (88.89)</t>
+          <t>maa://24632 (98.89), maa://22499 (91.30), maa://22746 (88.89)</t>
         </is>
       </c>
       <c r="E4" s="19" t="n"/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>maa://49983 (99.46), maa://50121 (97.66)</t>
+          <t>maa://49983 (99.44), maa://50121 (97.73)</t>
         </is>
       </c>
       <c r="Q4" s="19" t="n"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>maa://27295 (98.48), maa://32509 (97.01), maa://31008 (95.54), maa://70489 (99.49), maa://22754 (88.16)</t>
+          <t>maa://27295 (98.53), maa://32509 (97.05), maa://70489 (99.53), maa://31008 (95.59), maa://22754 (88.16)</t>
         </is>
       </c>
       <c r="U4" s="19" t="n"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="X4" s="8" t="inlineStr">
         <is>
-          <t>maa://43217 (99.17)</t>
+          <t>maa://43217 (99.21)</t>
         </is>
       </c>
       <c r="Y4" s="19" t="n"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB4" s="8" t="inlineStr">
         <is>
-          <t>*maa://32658 (75.86)</t>
+          <t>*maa://32658 (76.27)</t>
         </is>
       </c>
       <c r="AC4" s="19" t="n"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AF4" s="8" t="inlineStr">
         <is>
-          <t>*maa://39394 (53.57), *maa://30062 (62.69), ***maa://26209 (12.00)</t>
+          <t>*maa://39394 (52.54), *maa://30062 (62.69), ***maa://26209 (12.00)</t>
         </is>
       </c>
       <c r="AG4" s="16" t="n"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>maa://54105 (98.84), maa://21245 (92.71), *maa://22744 (80.00)</t>
+          <t>maa://54105 (98.84), maa://21245 (92.87), *maa://22744 (80.00)</t>
         </is>
       </c>
       <c r="E5" s="19" t="n"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t>maa://22757 (94.12)</t>
+          <t>maa://22757 (94.57)</t>
         </is>
       </c>
       <c r="M5" s="19" t="n"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>maa://21919 (99.15), maa://21281 (84.21)</t>
+          <t>maa://21919 (99.21), maa://21281 (84.21)</t>
         </is>
       </c>
       <c r="Q5" s="19" t="n"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="X5" s="8" t="inlineStr">
         <is>
-          <t>maa://21290 (99.05)</t>
+          <t>maa://21290 (99.10)</t>
         </is>
       </c>
       <c r="Y5" s="19" t="n"/>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AB5" s="8" t="inlineStr">
         <is>
-          <t>*maa://29863 (58.93), ***maa://22752 (11.76), **maa://26013 (33.33)</t>
+          <t>*maa://29863 (59.65), ***maa://22752 (11.76), **maa://26013 (33.33)</t>
         </is>
       </c>
       <c r="AC5" s="19" t="n"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>maa://42407 (98.47)</t>
+          <t>maa://42407 (98.54)</t>
         </is>
       </c>
       <c r="E6" s="19" t="n"/>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>maa://24370 (98.45)</t>
+          <t>maa://24370 (98.51)</t>
         </is>
       </c>
       <c r="I6" s="19" t="n"/>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>maa://24839 (99.60)</t>
+          <t>maa://24839 (99.62)</t>
         </is>
       </c>
       <c r="M6" s="19" t="n"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>maa://31836 (99.31), maa://30381 (95.45)</t>
+          <t>maa://31836 (99.35), maa://30381 (95.65)</t>
         </is>
       </c>
       <c r="Q6" s="19" t="n"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>maa://37411 (85.00)</t>
+          <t>maa://37411 (85.48)</t>
         </is>
       </c>
       <c r="U6" s="19" t="n"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="X6" s="8" t="inlineStr">
         <is>
-          <t>maa://52754 (96.63), maa://71825 (98.43)</t>
+          <t>maa://52754 (96.21), maa://71825 (97.97)</t>
         </is>
       </c>
       <c r="Y6" s="19" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB6" s="8" t="inlineStr">
         <is>
-          <t>maa://22739 (90.76)</t>
+          <t>maa://22739 (90.98)</t>
         </is>
       </c>
       <c r="AC6" s="19" t="n"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AF6" s="8" t="inlineStr">
         <is>
-          <t>maa://33152 (87.17)</t>
+          <t>maa://33152 (87.61)</t>
         </is>
       </c>
       <c r="AG6" s="16" t="n"/>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>maa://21955 (98.81)</t>
+          <t>maa://21955 (98.88)</t>
         </is>
       </c>
       <c r="E7" s="19" t="n"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>maa://22763 (81.01), maa://64972 (95.83)</t>
+          <t>maa://22763 (82.14), maa://64972 (96.15)</t>
         </is>
       </c>
       <c r="I7" s="19" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>maa://28624 (99.10), maa://24957 (92.86)</t>
+          <t>maa://28624 (99.15), maa://24957 (92.86)</t>
         </is>
       </c>
       <c r="M7" s="19" t="n"/>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="P7" s="8" t="inlineStr">
         <is>
-          <t>maa://22750 (97.99)</t>
+          <t>maa://22750 (98.11)</t>
         </is>
       </c>
       <c r="Q7" s="19" t="n"/>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>maa://21291 (94.58)</t>
+          <t>maa://21291 (94.90)</t>
         </is>
       </c>
       <c r="U7" s="19" t="n"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="X7" s="8" t="inlineStr">
         <is>
-          <t>maa://22399 (98.25), maa://22758 (85.04)</t>
+          <t>maa://22399 (98.33), maa://22758 (85.16)</t>
         </is>
       </c>
       <c r="Y7" s="19" t="n"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AF7" s="8" t="inlineStr">
         <is>
-          <t>maa://45272 (99.72), *maa://26191 (71.00)</t>
+          <t>maa://45272 (99.74), *maa://26191 (71.00)</t>
         </is>
       </c>
       <c r="AG7" s="16" t="n"/>
@@ -1485,7 +1485,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>更新日期：2025.11.13 13:22:25</t>
+          <t>更新日期：2025.11.16 13:20:51</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>maa://21476 (93.75)</t>
+          <t>maa://21476 (94.05), *maa://39431 (70.27)</t>
         </is>
       </c>
       <c r="E8" s="19" t="n"/>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>maa://24371 (85.51)</t>
+          <t>maa://24371 (86.11)</t>
         </is>
       </c>
       <c r="I8" s="19" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>maa://32931 (93.56), maa://23252 (91.67), maa://37496 (98.73)</t>
+          <t>maa://32931 (93.78), maa://23252 (91.67), maa://37496 (98.75)</t>
         </is>
       </c>
       <c r="Q8" s="19" t="n"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>maa://21411 (96.41), maa://67587 (98.85)</t>
+          <t>maa://21411 (96.45), maa://67587 (98.85)</t>
         </is>
       </c>
       <c r="Y8" s="19" t="n"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AB8" s="8" t="inlineStr">
         <is>
-          <t>maa://25389 (96.67)</t>
+          <t>maa://25389 (96.74)</t>
         </is>
       </c>
       <c r="AC8" s="19" t="n"/>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="AF8" s="8" t="inlineStr">
         <is>
-          <t>maa://24479 (90.13)</t>
+          <t>maa://24479 (90.27)</t>
         </is>
       </c>
       <c r="AG8" s="16" t="n"/>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>maa://22765 (97.52), maa://21915 (85.00)</t>
+          <t>maa://22765 (97.64), maa://21915 (86.15)</t>
         </is>
       </c>
       <c r="E9" s="19" t="n"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>maa://47450 (86.49), maa://56348 (97.14)</t>
+          <t>maa://47450 (86.84), maa://56348 (97.22)</t>
         </is>
       </c>
       <c r="I9" s="19" t="n"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t>maa://22762 (96.91), maa://39552 (90.24)</t>
+          <t>maa://22762 (96.72), maa://39552 (90.48)</t>
         </is>
       </c>
       <c r="M9" s="19" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="P9" s="8" t="inlineStr">
         <is>
-          <t>maa://64516 (100.00), maa://22736 (83.06)</t>
+          <t>maa://64516 (100.00), maa://22736 (83.20)</t>
         </is>
       </c>
       <c r="Q9" s="19" t="n"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>maa://26222 (99.70)</t>
+          <t>maa://26222 (99.71)</t>
         </is>
       </c>
       <c r="U9" s="19" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="X9" s="8" t="inlineStr">
         <is>
-          <t>maa://52237 (99.78), maa://26223 (98.38)</t>
+          <t>maa://52237 (99.79), maa://26223 (98.40)</t>
         </is>
       </c>
       <c r="Y9" s="19" t="n"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
-          <t>maa://28711 (96.03), maa://40166 (95.25)</t>
+          <t>maa://28711 (96.13), maa://40166 (95.20)</t>
         </is>
       </c>
       <c r="AC9" s="19" t="n"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AF9" s="8" t="inlineStr">
         <is>
-          <t>maa://26206 (92.13), maa://66916 (98.86)</t>
+          <t>maa://26206 (92.21), maa://66916 (98.92)</t>
         </is>
       </c>
       <c r="AG9" s="16" t="n"/>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>maa://54000 (93.57), *maa://45271 (70.51)</t>
+          <t>maa://54000 (93.79), *maa://45271 (71.25)</t>
         </is>
       </c>
       <c r="E10" s="19" t="n"/>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>maa://32651 (95.08)</t>
+          <t>maa://32651 (95.38)</t>
         </is>
       </c>
       <c r="I10" s="19" t="n"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P10" s="8" t="inlineStr">
         <is>
-          <t>maa://28977 (93.69), *maa://36669 (75.29)</t>
+          <t>maa://28977 (93.84), *maa://36669 (75.58)</t>
         </is>
       </c>
       <c r="Q10" s="19" t="n"/>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>maa://27395 (99.48), maa://22755 (92.61), maa://63521 (96.49), maa://73485 (98.04)</t>
+          <t>maa://27395 (99.49), maa://22755 (92.68), maa://63521 (96.52), maa://73485 (98.36)</t>
         </is>
       </c>
       <c r="U10" s="19" t="n"/>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t>maa://45828 (99.57), maa://22301 (97.68), maa://22726 (100.00)</t>
+          <t>maa://45828 (99.59), maa://22301 (97.70), maa://22726 (100.00)</t>
         </is>
       </c>
       <c r="Y10" s="19" t="n"/>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AF10" s="8" t="inlineStr">
         <is>
-          <t>maa://74007 (100.00)</t>
+          <t>maa://74007 (92.00)</t>
         </is>
       </c>
       <c r="AG10" s="16" t="n"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>maa://21287 (95.20)</t>
+          <t>maa://21287 (95.21)</t>
         </is>
       </c>
       <c r="M11" s="19" t="n"/>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="P11" s="8" t="inlineStr">
         <is>
-          <t>maa://45557 (96.25)</t>
+          <t>maa://45557 (96.34)</t>
         </is>
       </c>
       <c r="Q11" s="19" t="n"/>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>maa://22747 (95.39), maa://22501 (99.65), maa://64808 (99.63), maa://45521 (94.44)</t>
+          <t>maa://22747 (95.57), maa://22501 (99.66), maa://64808 (99.64), maa://45521 (94.44)</t>
         </is>
       </c>
       <c r="U11" s="19" t="n"/>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="X11" s="8" t="inlineStr">
         <is>
-          <t>maa://36713 (99.53)</t>
+          <t>maa://36713 (99.54)</t>
         </is>
       </c>
       <c r="Y11" s="19" t="n"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AB11" s="8" t="inlineStr">
         <is>
-          <t>maa://29912 (99.71), maa://22516 (85.56)</t>
+          <t>maa://29912 (99.72), maa://22516 (85.56)</t>
         </is>
       </c>
       <c r="AC11" s="19" t="n"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AF11" s="8" t="inlineStr">
         <is>
-          <t>maa://31203 (98.25)</t>
+          <t>maa://31203 (98.31)</t>
         </is>
       </c>
       <c r="AG11" s="16" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>maa://36678 (98.26), maa://30766 (91.89)</t>
+          <t>maa://36678 (98.37), maa://30766 (91.89)</t>
         </is>
       </c>
       <c r="E12" s="19" t="n"/>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>maa://21867 (94.55), maa://54294 (98.38)</t>
+          <t>maa://21867 (94.70), maa://54294 (98.53)</t>
         </is>
       </c>
       <c r="I12" s="19" t="n"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>maa://63896 (98.62), maa://64046 (98.99)</t>
+          <t>maa://63896 (98.65), maa://64046 (99.02)</t>
         </is>
       </c>
       <c r="M12" s="19" t="n"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="P12" s="8" t="inlineStr">
         <is>
-          <t>maa://57541 (91.55)</t>
+          <t>maa://57541 (91.03)</t>
         </is>
       </c>
       <c r="Q12" s="19" t="n"/>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>maa://37962 (98.80), maa://21485 (84.13), maa://22753 (93.41), maa://73860 (96.43)</t>
+          <t>maa://37962 (98.82), maa://21485 (84.59), maa://22753 (93.41), maa://73860 (96.76)</t>
         </is>
       </c>
       <c r="Y12" s="19" t="n"/>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
-          <t>maa://36677 (99.23), maa://23669 (95.06), maa://39872 (98.38)</t>
+          <t>maa://36677 (99.20), maa://23669 (95.07), maa://39872 (98.43)</t>
         </is>
       </c>
       <c r="AC12" s="19" t="n"/>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AF12" s="8" t="inlineStr">
         <is>
-          <t>maa://28932 (95.99)</t>
+          <t>maa://28932 (96.06)</t>
         </is>
       </c>
       <c r="AG12" s="16" t="n"/>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>maa://24999 (97.79), maa://36673 (95.38), maa://25001 (89.42)</t>
+          <t>maa://24999 (97.90), maa://36673 (95.40), maa://25001 (89.72)</t>
         </is>
       </c>
       <c r="E13" s="19" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>*maa://21248 (74.95), maa://66545 (98.76), *maa://22728 (74.19)</t>
+          <t>*maa://21248 (74.63), maa://66545 (98.78), *maa://22728 (76.12)</t>
         </is>
       </c>
       <c r="I13" s="19" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P13" s="8" t="inlineStr">
         <is>
-          <t>maa://22676 (98.09), maa://22583 (93.51), *maa://22500 (73.97)</t>
+          <t>maa://22676 (98.15), maa://22583 (93.63), *maa://22500 (74.67)</t>
         </is>
       </c>
       <c r="Q13" s="19" t="n"/>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>maa://21484 (99.34)</t>
+          <t>maa://21484 (99.39)</t>
         </is>
       </c>
       <c r="U13" s="19" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="X13" s="8" t="inlineStr">
         <is>
-          <t>maa://34957 (95.98)</t>
+          <t>maa://34957 (96.14)</t>
         </is>
       </c>
       <c r="Y13" s="19" t="n"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AF13" s="8" t="inlineStr">
         <is>
-          <t>maa://39883 (95.63)</t>
+          <t>maa://39883 (95.82)</t>
         </is>
       </c>
       <c r="AG13" s="16" t="n"/>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>maa://30764 (95.98)</t>
+          <t>maa://30764 (96.12)</t>
         </is>
       </c>
       <c r="E14" s="19" t="n"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>maa://39841 (99.35), maa://36682 (98.53), maa://26245 (97.17), maa://21288 (96.43)</t>
+          <t>maa://39841 (99.38), maa://36682 (98.55), maa://26245 (97.18), maa://21288 (96.43)</t>
         </is>
       </c>
       <c r="M14" s="19" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P14" s="8" t="inlineStr">
         <is>
-          <t>maa://23250 (99.74), maa://20107 (87.50), maa://22772 (100.00), maa://68732 (100.00)</t>
+          <t>maa://23250 (99.75), maa://20107 (87.50), maa://22772 (100.00), maa://68732 (100.00)</t>
         </is>
       </c>
       <c r="Q14" s="19" t="n"/>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>maa://42751 (99.35), maa://22521 (96.91)</t>
+          <t>maa://42751 (99.38), maa://22521 (97.12)</t>
         </is>
       </c>
       <c r="U14" s="19" t="n"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="X14" s="8" t="inlineStr">
         <is>
-          <t>maa://37468 (98.87)</t>
+          <t>maa://37468 (98.92)</t>
         </is>
       </c>
       <c r="Y14" s="19" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB14" s="8" t="inlineStr">
         <is>
-          <t>maa://22764 (99.34)</t>
+          <t>maa://22764 (99.36)</t>
         </is>
       </c>
       <c r="AC14" s="19" t="n"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>maa://22743 (88.90), maa://45058 (98.67), maa://22734 (85.40), *maa://36048 (78.54), maa://69928 (97.12)</t>
+          <t>maa://22743 (89.12), maa://45058 (98.59), maa://22734 (85.51), *maa://36048 (78.92), maa://69928 (97.20)</t>
         </is>
       </c>
       <c r="E15" s="19" t="n"/>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>maa://24304 (98.20), maa://21478 (90.91)</t>
+          <t>maa://24304 (98.28), maa://21478 (91.11)</t>
         </is>
       </c>
       <c r="I15" s="19" t="n"/>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>*maa://21334 (73.08), maa://73742 (100.00)</t>
+          <t>*maa://21334 (73.42), maa://73742 (100.00)</t>
         </is>
       </c>
       <c r="M15" s="19" t="n"/>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>maa://24762 (98.31), *maa://22727 (70.00)</t>
+          <t>maa://24762 (98.36), *maa://22727 (70.00)</t>
         </is>
       </c>
       <c r="Q15" s="19" t="n"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>maa://23892 (98.41)</t>
+          <t>maa://23892 (98.46)</t>
         </is>
       </c>
       <c r="U15" s="19" t="n"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="X15" s="8" t="inlineStr">
         <is>
-          <t>maa://38786 (94.83), maa://56102 (100.00)</t>
+          <t>maa://38786 (95.08), maa://56102 (100.00)</t>
         </is>
       </c>
       <c r="Y15" s="19" t="n"/>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AF15" s="8" t="inlineStr">
         <is>
-          <t>maa://36666 (97.11), maa://21364 (84.91), *maa://22766 (71.13), maa://68306 (91.98)</t>
+          <t>maa://36666 (97.18), maa://21364 (85.04), maa://68306 (91.86), *maa://22766 (71.13)</t>
         </is>
       </c>
       <c r="AG15" s="16" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>maa://37650 (99.79), maa://21441 (96.68), maa://36679 (94.64)</t>
+          <t>maa://37650 (99.80), maa://21441 (96.71), maa://36679 (94.64)</t>
         </is>
       </c>
       <c r="E16" s="19" t="n"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>maa://28504 (97.64)</t>
+          <t>maa://28504 (97.75)</t>
         </is>
       </c>
       <c r="Q16" s="19" t="n"/>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>maa://36674 (98.36), maa://22729 (97.10), *maa://28648 (77.89)</t>
+          <t>maa://36674 (98.41), maa://22729 (97.22), *maa://28648 (78.12)</t>
         </is>
       </c>
       <c r="U16" s="19" t="n"/>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>maa://28501 (99.50), maa://28051 (97.50)</t>
+          <t>maa://28501 (99.52), maa://28051 (97.56)</t>
         </is>
       </c>
       <c r="Y16" s="19" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AB16" s="8" t="inlineStr">
         <is>
-          <t>maa://26228 (98.55)</t>
+          <t>maa://26228 (98.59)</t>
         </is>
       </c>
       <c r="AC16" s="19" t="n"/>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AF16" s="8" t="inlineStr">
         <is>
-          <t>maa://23911 (92.05), maa://67613 (99.28), maa://27755 (93.75)</t>
+          <t>maa://23911 (92.20), maa://67613 (99.33), maa://27755 (93.75)</t>
         </is>
       </c>
       <c r="AG16" s="16" t="n"/>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>maa://21624 (89.29), maa://56358 (100.00)</t>
+          <t>maa://21624 (89.47), maa://56358 (100.00)</t>
         </is>
       </c>
       <c r="E17" s="19" t="n"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>maa://39599 (98.94), maa://22430 (90.57)</t>
+          <t>maa://39599 (98.98), maa://22430 (90.57)</t>
         </is>
       </c>
       <c r="I17" s="19" t="n"/>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>maa://21679 (91.89)</t>
+          <t>maa://21679 (92.31)</t>
         </is>
       </c>
       <c r="M17" s="19" t="n"/>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>maa://23890 (84.09), maa://56238 (98.33)</t>
+          <t>maa://23890 (84.09), maa://56238 (98.42)</t>
         </is>
       </c>
       <c r="Q17" s="19" t="n"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>*maa://42324 (75.00)</t>
+          <t>*maa://42324 (75.83)</t>
         </is>
       </c>
       <c r="U17" s="19" t="n"/>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AF17" s="8" t="inlineStr">
         <is>
-          <t>maa://50136 (99.35)</t>
+          <t>maa://50136 (99.40)</t>
         </is>
       </c>
       <c r="AG17" s="16" t="n"/>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>maa://24570 (98.78)</t>
+          <t>maa://24570 (98.82)</t>
         </is>
       </c>
       <c r="E18" s="19" t="n"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>maa://24421 (96.62)</t>
+          <t>maa://24421 (96.70)</t>
         </is>
       </c>
       <c r="I18" s="19" t="n"/>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>maa://52226 (99.69), maa://22466 (93.04)</t>
+          <t>maa://52226 (99.71), maa://22466 (93.07)</t>
         </is>
       </c>
       <c r="M18" s="19" t="n"/>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>maa://54153 (99.83), maa://24379 (100.00), maa://24380 (100.00)</t>
+          <t>maa://54153 (99.84), maa://24379 (100.00), maa://24380 (100.00)</t>
         </is>
       </c>
       <c r="Q18" s="19" t="n"/>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>maa://24385 (97.89)</t>
+          <t>maa://24385 (97.92)</t>
         </is>
       </c>
       <c r="U18" s="19" t="n"/>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t>maa://21917 (99.31), maa://22741 (94.74)</t>
+          <t>maa://21917 (99.34), maa://22741 (95.24)</t>
         </is>
       </c>
       <c r="Y18" s="19" t="n"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="AB18" s="8" t="inlineStr">
         <is>
-          <t>maa://24393 (99.38)</t>
+          <t>maa://24393 (99.12)</t>
         </is>
       </c>
       <c r="AC18" s="19" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="AF18" s="8" t="inlineStr">
         <is>
-          <t>maa://47854 (95.62), *maa://68715 (75.00), maa://74015 (92.86)</t>
+          <t>maa://47854 (95.80), *maa://68715 (80.00), maa://74015 (95.00)</t>
         </is>
       </c>
       <c r="AG18" s="16" t="n"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>maa://62850 (99.50)</t>
+          <t>maa://62850 (99.52)</t>
         </is>
       </c>
       <c r="E19" s="19" t="n"/>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>maa://66740 (95.45)</t>
+          <t>maa://66740 (91.30)</t>
         </is>
       </c>
       <c r="I19" s="19" t="n"/>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>maa://39347 (98.72), maa://56392 (100.00)</t>
+          <t>maa://39347 (98.77), maa://56392 (100.00)</t>
         </is>
       </c>
       <c r="M19" s="19" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>maa://24386 (99.69)</t>
+          <t>maa://24386 (99.70)</t>
         </is>
       </c>
       <c r="U19" s="19" t="n"/>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t>maa://31386 (96.97), maa://58490 (92.31)</t>
+          <t>maa://31386 (95.71), maa://58490 (92.86)</t>
         </is>
       </c>
       <c r="Y19" s="19" t="n"/>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
-          <t>maa://30709 (90.95), *maa://36668 (72.22)</t>
+          <t>maa://30709 (91.27), *maa://36668 (72.44)</t>
         </is>
       </c>
       <c r="AC19" s="19" t="n"/>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AF19" s="8" t="inlineStr">
         <is>
-          <t>maa://52239 (92.22)</t>
+          <t>maa://52239 (91.67)</t>
         </is>
       </c>
       <c r="AG19" s="16" t="n"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>maa://25198 (98.19), maa://36680 (99.11), maa://21432 (91.87)</t>
+          <t>maa://36680 (99.14), maa://25198 (98.22), maa://21432 (91.94)</t>
         </is>
       </c>
       <c r="E20" s="19" t="n"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>maa://22864 (96.95), *maa://53361 (72.16)</t>
+          <t>maa://22864 (97.03), *maa://53361 (73.53)</t>
         </is>
       </c>
       <c r="I20" s="19" t="n"/>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>maa://41331 (96.61)</t>
+          <t>maa://41331 (96.74)</t>
         </is>
       </c>
       <c r="M20" s="19" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>maa://37442 (99.16)</t>
+          <t>maa://37442 (99.19)</t>
         </is>
       </c>
       <c r="Q20" s="19" t="n"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>maa://29113 (95.87)</t>
+          <t>maa://29113 (95.97)</t>
         </is>
       </c>
       <c r="U20" s="19" t="n"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>maa://56241 (98.68), maa://50085 (97.43), maa://49976 (88.99)</t>
+          <t>maa://56241 (98.70), maa://50085 (97.50), maa://49976 (89.19)</t>
         </is>
       </c>
       <c r="Y20" s="19" t="n"/>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>maa://21261 (99.35)</t>
+          <t>maa://21261 (99.38)</t>
         </is>
       </c>
       <c r="E21" s="19" t="n"/>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>maa://24372 (99.35)</t>
+          <t>maa://24372 (99.38)</t>
         </is>
       </c>
       <c r="I21" s="19" t="n"/>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>maa://31731 (97.60)</t>
+          <t>maa://31731 (97.74)</t>
         </is>
       </c>
       <c r="M21" s="19" t="n"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
-          <t>maa://24381 (86.27)</t>
+          <t>maa://24381 (86.79)</t>
         </is>
       </c>
       <c r="Q21" s="19" t="n"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>maa://21993 (93.02)</t>
+          <t>maa://21993 (93.33)</t>
         </is>
       </c>
       <c r="U21" s="19" t="n"/>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="X21" s="8" t="inlineStr">
         <is>
-          <t>maa://34946 (98.55), maa://20110 (87.18)</t>
+          <t>maa://34946 (98.60), maa://20110 (87.18)</t>
         </is>
       </c>
       <c r="Y21" s="19" t="n"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AB21" s="8" t="inlineStr">
         <is>
-          <t>maa://21443 (88.04), maa://52223 (90.72)</t>
+          <t>maa://52223 (90.95), maa://21443 (88.14)</t>
         </is>
       </c>
       <c r="AC21" s="19" t="n"/>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AF21" s="8" t="inlineStr">
         <is>
-          <t>maa://22432 (95.90), maa://64221 (98.29), maa://22524 (82.84)</t>
+          <t>maa://22432 (96.07), maa://64221 (98.22), maa://22524 (82.95)</t>
         </is>
       </c>
       <c r="AG21" s="16" t="n"/>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>maa://25236 (99.36)</t>
+          <t>maa://25236 (99.39)</t>
         </is>
       </c>
       <c r="I22" s="19" t="n"/>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>maa://27127 (85.45), maa://66865 (99.72), *maa://22751 (71.26)</t>
+          <t>maa://27127 (85.51), maa://66865 (99.60), *maa://22751 (71.26)</t>
         </is>
       </c>
       <c r="M22" s="19" t="n"/>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>maa://37649 (95.90), maa://21282 (99.11)</t>
+          <t>maa://37649 (96.09), maa://21282 (99.13)</t>
         </is>
       </c>
       <c r="Y22" s="19" t="n"/>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AF22" s="8" t="inlineStr">
         <is>
-          <t>maa://29658 (97.74)</t>
+          <t>maa://29658 (97.86)</t>
         </is>
       </c>
       <c r="AG22" s="16" t="n"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>*maa://41753 (74.51), **maa://28036 (31.58)</t>
+          <t>*maa://41753 (74.55), **maa://28036 (31.58)</t>
         </is>
       </c>
       <c r="E23" s="19" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>maa://39756 (99.07), maa://39875 (95.59)</t>
+          <t>maa://39756 (99.11), maa://39875 (95.62)</t>
         </is>
       </c>
       <c r="M23" s="19" t="n"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>maa://30587 (97.84), maa://29748 (83.87), *maa://37566 (79.71)</t>
+          <t>maa://30587 (97.91), maa://29748 (84.02), *maa://37566 (79.71)</t>
         </is>
       </c>
       <c r="Q23" s="19" t="n"/>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>maa://31212 (96.59), maa://24387 (86.00), maa://67084 (90.91)</t>
+          <t>maa://31212 (96.67), maa://24387 (86.00), maa://67084 (90.91)</t>
         </is>
       </c>
       <c r="U23" s="19" t="n"/>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="X23" s="8" t="inlineStr">
         <is>
-          <t>*maa://28503 (61.66)</t>
+          <t>*maa://28503 (61.00)</t>
         </is>
       </c>
       <c r="Y23" s="19" t="n"/>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB23" s="8" t="inlineStr">
         <is>
-          <t>maa://29652 (97.74)</t>
+          <t>maa://29652 (97.78)</t>
         </is>
       </c>
       <c r="AC23" s="19" t="n"/>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AF23" s="8" t="inlineStr">
         <is>
-          <t>maa://31489 (98.92)</t>
+          <t>maa://31489 (98.97)</t>
         </is>
       </c>
       <c r="AG23" s="16" t="n"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>maa://24368 (87.97), maa://46650 (93.46)</t>
+          <t>maa://24368 (88.17), maa://46650 (93.46)</t>
         </is>
       </c>
       <c r="E24" s="19" t="n"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>maa://73341 (98.39)</t>
+          <t>maa://73341 (98.62)</t>
         </is>
       </c>
       <c r="U24" s="19" t="n"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>maa://29988 (97.69), maa://23504 (94.19), maa://25141 (81.33), maa://52227 (97.95), maa://36663 (80.53)</t>
+          <t>maa://29988 (97.78), maa://23504 (94.20), maa://25141 (81.44), maa://52227 (97.97), maa://36663 (80.53)</t>
         </is>
       </c>
       <c r="Y24" s="19" t="n"/>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB24" s="8" t="inlineStr">
         <is>
-          <t>maa://39349 (98.44)</t>
+          <t>maa://39349 (98.61)</t>
         </is>
       </c>
       <c r="AC24" s="19" t="n"/>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="AF24" s="8" t="inlineStr">
         <is>
-          <t>maa://64165 (99.35), *maa://22523 (79.82), maa://29910 (94.20), maa://45831 (95.00)</t>
+          <t>maa://64165 (99.31), *maa://22523 (79.82), maa://29910 (94.20), maa://45831 (95.12)</t>
         </is>
       </c>
       <c r="AG24" s="16" t="n"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>maa://29753 (97.20), maa://63016 (99.53)</t>
+          <t>maa://29753 (97.25), maa://63016 (99.55)</t>
         </is>
       </c>
       <c r="E25" s="19" t="n"/>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>maa://29063 (80.88), *maa://25311 (71.15), maa://45047 (87.10)</t>
+          <t>maa://29063 (81.10), *maa://25311 (71.34), maa://45047 (87.50)</t>
         </is>
       </c>
       <c r="I25" s="19" t="n"/>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>maa://24378 (94.38), maa://68415 (92.11)</t>
+          <t>maa://24378 (94.57), maa://68415 (90.70)</t>
         </is>
       </c>
       <c r="M25" s="19" t="n"/>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>maa://24382 (96.15)</t>
+          <t>maa://24382 (96.34)</t>
         </is>
       </c>
       <c r="Q25" s="19" t="n"/>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>maa://20109 (97.59), maa://22545 (99.87)</t>
+          <t>maa://20109 (97.68), maa://22545 (99.88)</t>
         </is>
       </c>
       <c r="U25" s="19" t="n"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="X25" s="8" t="inlineStr">
         <is>
-          <t>maa://29890 (94.18)</t>
+          <t>maa://29890 (94.33)</t>
         </is>
       </c>
       <c r="Y25" s="19" t="n"/>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AB25" s="8" t="inlineStr">
         <is>
-          <t>maa://31215 (94.15), maa://68311 (98.49), *maa://24516 (78.43), maa://26001 (81.97)</t>
+          <t>maa://31215 (94.25), maa://68311 (98.60), *maa://24516 (78.43), maa://26001 (81.97)</t>
         </is>
       </c>
       <c r="AC25" s="19" t="n"/>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AF25" s="8" t="inlineStr">
         <is>
-          <t>maa://20108 (98.99), maa://36676 (99.88), maa://24621 (96.99), maa://22771 (88.89), maa://37772 (87.50)</t>
+          <t>maa://20108 (98.89), maa://36676 (99.88), maa://24621 (97.01), maa://22771 (88.89), maa://37772 (87.50)</t>
         </is>
       </c>
       <c r="AG25" s="16" t="n"/>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>maa://56374 (100.00), maa://41802 (98.26)</t>
+          <t>maa://56374 (100.00), maa://41802 (98.36)</t>
         </is>
       </c>
       <c r="E26" s="19" t="n"/>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>maa://56240 (96.08), maa://24913 (93.02)</t>
+          <t>maa://56240 (96.06), maa://24913 (93.02)</t>
         </is>
       </c>
       <c r="I26" s="19" t="n"/>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>maa://56625 (99.21), maa://39870 (95.45)</t>
+          <t>maa://56625 (99.22), maa://39870 (95.45)</t>
         </is>
       </c>
       <c r="Q26" s="19" t="n"/>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="X26" s="8" t="inlineStr">
         <is>
-          <t>maa://24389 (98.91)</t>
+          <t>maa://24389 (98.95)</t>
         </is>
       </c>
       <c r="Y26" s="19" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AB26" s="8" t="inlineStr">
         <is>
-          <t>maa://42235 (99.03)</t>
+          <t>maa://42235 (99.07)</t>
         </is>
       </c>
       <c r="AC26" s="19" t="n"/>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AF26" s="8" t="inlineStr">
         <is>
-          <t>*maa://30511 (73.96), **maa://29760 (45.45)</t>
+          <t>*maa://30511 (73.74), **maa://29760 (43.48)</t>
         </is>
       </c>
       <c r="AG26" s="16" t="n"/>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>maa://39601 (94.87), maa://34494 (96.30)</t>
+          <t>maa://39601 (95.08), maa://34494 (96.33)</t>
         </is>
       </c>
       <c r="I27" s="19" t="n"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>maa://28071 (93.55)</t>
+          <t>maa://28071 (93.81)</t>
         </is>
       </c>
       <c r="M27" s="19" t="n"/>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>maa://30624 (92.25)</t>
+          <t>maa://30624 (92.34)</t>
         </is>
       </c>
       <c r="U27" s="19" t="n"/>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AF27" s="8" t="inlineStr">
         <is>
-          <t>maa://24023 (98.55)</t>
+          <t>maa://24023 (98.62)</t>
         </is>
       </c>
       <c r="AG27" s="16" t="n"/>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>maa://24465 (96.85), maa://25725 (87.16)</t>
+          <t>maa://24465 (96.90), maa://25725 (87.33)</t>
         </is>
       </c>
       <c r="E28" s="19" t="n"/>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>maa://30770 (91.54)</t>
+          <t>maa://30770 (91.91)</t>
         </is>
       </c>
       <c r="M28" s="19" t="n"/>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>maa://29765 (95.62), maa://23263 (97.38)</t>
+          <t>maa://29765 (95.77), maa://23263 (97.45)</t>
         </is>
       </c>
       <c r="U28" s="19" t="n"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t>maa://39929 (98.13), maa://41749 (97.51)</t>
+          <t>maa://39929 (98.19), maa://41749 (97.54)</t>
         </is>
       </c>
       <c r="Y28" s="19" t="n"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="AF28" s="8" t="inlineStr">
         <is>
-          <t>maa://36660 (95.23), maa://65700 (98.87)</t>
+          <t>maa://36660 (95.16), maa://65700 (98.75)</t>
         </is>
       </c>
       <c r="AG28" s="16" t="n"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>maa://31694 (99.52)</t>
+          <t>maa://31694 (99.53)</t>
         </is>
       </c>
       <c r="E29" s="19" t="n"/>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>maa://73558 (94.44)</t>
+          <t>maa://73558 (95.24)</t>
         </is>
       </c>
       <c r="I29" s="19" t="n"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>maa://28432 (98.53), maa://31400 (98.37), maa://28440 (87.36)</t>
+          <t>maa://28432 (98.58), maa://31400 (98.40), maa://28440 (87.71)</t>
         </is>
       </c>
       <c r="M29" s="19" t="n"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>maa://54169 (97.13)</t>
+          <t>maa://54169 (97.32)</t>
         </is>
       </c>
       <c r="Q29" s="19" t="n"/>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="AF29" s="8" t="inlineStr">
         <is>
-          <t>maa://42865 (94.62)</t>
+          <t>maa://42865 (94.85)</t>
         </is>
       </c>
       <c r="AG29" s="16" t="n"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>maa://45792 (96.55), maa://64191 (96.47)</t>
+          <t>maa://45792 (96.59), maa://64191 (96.67)</t>
         </is>
       </c>
       <c r="E30" s="19" t="n"/>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>maa://30442 (98.27)</t>
+          <t>maa://30442 (98.31)</t>
         </is>
       </c>
       <c r="M30" s="19" t="n"/>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>maa://32940 (81.25), maa://24388 (96.77)</t>
+          <t>maa://32940 (81.82), maa://24388 (96.77)</t>
         </is>
       </c>
       <c r="U30" s="19" t="n"/>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="X30" s="8" t="inlineStr">
         <is>
-          <t>maa://39477 (96.34)</t>
+          <t>maa://39477 (96.47)</t>
         </is>
       </c>
       <c r="Y30" s="19" t="n"/>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>maa://42979 (99.65), maa://45822 (100.00), maa://45045 (94.74)</t>
+          <t>maa://42979 (99.66), maa://45822 (100.00), maa://45045 (95.45)</t>
         </is>
       </c>
       <c r="AC30" s="19" t="n"/>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>maa://35926 (98.73), maa://36258 (94.32), maa://43904 (92.96)</t>
+          <t>maa://35926 (98.78), maa://36258 (94.24), maa://43904 (92.96)</t>
         </is>
       </c>
       <c r="M31" s="19" t="n"/>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>maa://30711 (97.58), maa://30768 (100.00)</t>
+          <t>maa://30711 (97.70), maa://30768 (100.00)</t>
         </is>
       </c>
       <c r="U31" s="19" t="n"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AB31" s="8" t="inlineStr">
         <is>
-          <t>maa://66997 (97.56)</t>
+          <t>maa://66997 (95.35)</t>
         </is>
       </c>
       <c r="AC31" s="19" t="n"/>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>maa://36667 (99.69), maa://21895 (98.10), maa://22760 (100.00)</t>
+          <t>maa://36667 (99.70), maa://21895 (98.11), maa://22760 (100.00)</t>
         </is>
       </c>
       <c r="I32" s="19" t="n"/>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>maa://28065 (97.83)</t>
+          <t>maa://28065 (97.92)</t>
         </is>
       </c>
       <c r="M32" s="19" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>maa://42859 (99.50), maa://41108 (89.23), maa://41238 (98.31), maa://45523 (100.00)</t>
+          <t>maa://42859 (99.49), maa://41108 (89.39), maa://41238 (98.35), maa://45523 (100.00)</t>
         </is>
       </c>
       <c r="U32" s="19" t="n"/>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t>maa://64104 (97.54)</t>
+          <t>maa://64104 (97.62)</t>
         </is>
       </c>
       <c r="Y32" s="19" t="n"/>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AF32" s="8" t="inlineStr">
         <is>
-          <t>maa://42408 (96.36)</t>
+          <t>maa://42408 (96.49)</t>
         </is>
       </c>
       <c r="AG32" s="16" t="n"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>maa://21956 (95.77), maa://69135 (99.04), maa://73357 (100.00)</t>
+          <t>maa://21956 (96.09), maa://69135 (99.06), maa://73357 (100.00)</t>
         </is>
       </c>
       <c r="Q33" s="19" t="n"/>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>maa://45558 (92.31)</t>
+          <t>maa://45558 (92.45)</t>
         </is>
       </c>
       <c r="U33" s="19" t="n"/>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AB33" s="8" t="inlineStr">
         <is>
-          <t>maa://73340 (99.74), maa://73523 (97.96)</t>
+          <t>maa://73340 (99.54), maa://73523 (98.28)</t>
         </is>
       </c>
       <c r="AC33" s="19" t="n"/>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>maa://66817 (99.31)</t>
+          <t>maa://66817 (99.35)</t>
         </is>
       </c>
       <c r="I34" s="19" t="n"/>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>maa://56235 (99.49), maa://48817 (99.48)</t>
+          <t>maa://56235 (99.27), maa://48817 (99.49)</t>
         </is>
       </c>
       <c r="Q34" s="19" t="n"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>maa://24526 (97.99)</t>
+          <t>maa://24526 (98.05)</t>
         </is>
       </c>
       <c r="U34" s="19" t="n"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB34" s="8" t="inlineStr">
         <is>
-          <t>maa://64329 (99.06)</t>
+          <t>maa://64329 (99.07)</t>
         </is>
       </c>
       <c r="AC34" s="19" t="n"/>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AF34" s="8" t="inlineStr">
         <is>
-          <t>maa://32650 (90.67)</t>
+          <t>maa://32650 (90.91)</t>
         </is>
       </c>
       <c r="AG34" s="16" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>maa://41296 (99.52)</t>
+          <t>maa://41296 (99.53)</t>
         </is>
       </c>
       <c r="M35" s="19" t="n"/>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>maa://24842 (97.54)</t>
+          <t>maa://24842 (97.64)</t>
         </is>
       </c>
       <c r="U35" s="19" t="n"/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AF35" s="8" t="inlineStr">
         <is>
-          <t>maa://39479 (93.67)</t>
+          <t>maa://39479 (93.90)</t>
         </is>
       </c>
       <c r="AG35" s="16" t="n"/>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>maa://24375 (96.08)</t>
+          <t>maa://24375 (96.30)</t>
         </is>
       </c>
       <c r="I36" s="19" t="n"/>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>maa://42240 (99.24)</t>
+          <t>maa://42240 (99.26)</t>
         </is>
       </c>
       <c r="M36" s="19" t="n"/>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>maa://27613 (99.69)</t>
+          <t>maa://27613 (99.71)</t>
         </is>
       </c>
       <c r="U36" s="19" t="n"/>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AB36" s="19" t="inlineStr">
         <is>
-          <t>maa://64106 (97.14)</t>
+          <t>maa://64106 (97.18)</t>
         </is>
       </c>
       <c r="AC36" s="19" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>*maa://24374 (62.50)</t>
+          <t>*maa://24374 (63.01)</t>
         </is>
       </c>
       <c r="I37" s="19" t="n"/>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>maa://45718 (99.08), maa://56336 (99.51), maa://47069 (90.00), maa://45789 (100.00)</t>
+          <t>maa://45718 (99.09), maa://56336 (99.52), maa://47069 (90.16), maa://45789 (100.00)</t>
         </is>
       </c>
       <c r="M37" s="19" t="n"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>maa://21280 (98.26), *maa://21239 (72.22)</t>
+          <t>maa://21280 (98.31), *maa://21239 (72.22)</t>
         </is>
       </c>
       <c r="Q37" s="19" t="n"/>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>*maa://39354 (62.50)</t>
+          <t>*maa://39354 (64.71)</t>
         </is>
       </c>
       <c r="U37" s="19" t="n"/>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>maa://39384 (99.14), maa://49735 (90.00)</t>
+          <t>maa://39384 (99.18), maa://49735 (90.00)</t>
         </is>
       </c>
       <c r="M38" s="19" t="n"/>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="P38" s="8" t="inlineStr">
         <is>
-          <t>maa://24383 (86.67)</t>
+          <t>maa://24383 (86.97)</t>
         </is>
       </c>
       <c r="Q38" s="19" t="n"/>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>maa://30713 (98.84)</t>
+          <t>maa://30713 (98.85)</t>
         </is>
       </c>
       <c r="U38" s="19" t="n"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AF38" s="8" t="inlineStr">
         <is>
-          <t>maa://36697 (96.12), maa://68397 (99.16)</t>
+          <t>maa://36697 (96.14), maa://68397 (99.22)</t>
         </is>
       </c>
       <c r="AG38" s="16" t="n"/>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>maa://45059 (95.81), maa://25199 (85.71), maa://30434 (95.75), maa://44165 (85.71)</t>
+          <t>maa://45059 (96.00), maa://25199 (85.90), maa://30434 (95.83), maa://44165 (85.71)</t>
         </is>
       </c>
       <c r="I39" s="19" t="n"/>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>maa://47093 (98.90), maa://24709 (94.70)</t>
+          <t>maa://47093 (98.83), maa://24709 (94.79)</t>
         </is>
       </c>
       <c r="Q39" s="19" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>maa://47079 (96.68), maa://45790 (89.32), *maa://56232 (75.00)</t>
+          <t>maa://47079 (96.78), maa://45790 (89.42), *maa://56232 (75.91)</t>
         </is>
       </c>
       <c r="U39" s="19" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AF39" s="8" t="inlineStr">
         <is>
-          <t>maa://62953 (97.44)</t>
+          <t>maa://62953 (97.53)</t>
         </is>
       </c>
       <c r="AG39" s="16" t="n"/>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>maa://23278 (98.44), maa://21386 (95.73), maa://36664 (88.37), *maa://45550 (71.43)</t>
+          <t>maa://23278 (98.50), maa://21386 (95.73), maa://36664 (88.51), *maa://45550 (71.43)</t>
         </is>
       </c>
       <c r="Q40" s="19" t="n"/>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>maa://65283 (97.81), *maa://64107 (74.00), maa://64205 (95.24)</t>
+          <t>maa://65283 (97.61), *maa://64107 (74.51), maa://64205 (95.24)</t>
         </is>
       </c>
       <c r="AG40" s="16" t="n"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>maa://24466 (94.44)</t>
+          <t>maa://24466 (94.79)</t>
         </is>
       </c>
       <c r="I41" s="19" t="n"/>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t>maa://43177 (97.27)</t>
+          <t>maa://43177 (97.33)</t>
         </is>
       </c>
       <c r="Q41" s="19" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>maa://21284 (98.65)</t>
+          <t>maa://21284 (98.70)</t>
         </is>
       </c>
       <c r="I43" s="19" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="P43" s="8" t="inlineStr">
         <is>
-          <t>maa://47403 (92.59)</t>
+          <t>maa://47403 (93.10)</t>
         </is>
       </c>
       <c r="Q43" s="19" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>maa://43198 (100.00), maa://46286 (95.00)</t>
+          <t>maa://43198 (100.00), maa://46286 (95.24)</t>
         </is>
       </c>
       <c r="U43" s="19" t="n"/>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>maa://29768 (98.57), maa://56386 (99.70), maa://27728 (96.49)</t>
+          <t>maa://56386 (99.72), maa://29768 (98.59), maa://27728 (96.49)</t>
         </is>
       </c>
       <c r="I44" s="19" t="n"/>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>maa://39366 (94.74)</t>
+          <t>maa://39366 (94.89)</t>
         </is>
       </c>
       <c r="U44" s="19" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>maa://42459 (99.06), maa://21229 (87.55), maa://30807 (94.68), maa://22767 (83.10)</t>
+          <t>maa://42459 (98.89), maa://21229 (87.73), maa://30807 (94.74), maa://22767 (83.45)</t>
         </is>
       </c>
       <c r="I45" s="19" t="n"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>*maa://39364 (75.21), maa://73997 (100.00)</t>
+          <t>*maa://39364 (75.53), maa://73997 (100.00)</t>
         </is>
       </c>
       <c r="U45" s="19" t="n"/>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>maa://35931 (97.01), maa://43901 (97.91)</t>
+          <t>maa://35931 (97.10), maa://43901 (97.98)</t>
         </is>
       </c>
       <c r="I46" s="19" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>maa://27410 (97.76), maa://56236 (99.89), maa://29661 (97.47), maa://28038 (84.62)</t>
+          <t>maa://27410 (97.80), maa://56236 (99.89), maa://29661 (97.49), maa://28038 (84.62)</t>
         </is>
       </c>
       <c r="I47" s="19" t="n"/>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>maa://68392 (99.79), maa://67476 (99.61)</t>
+          <t>maa://68392 (99.81), maa://67476 (99.61)</t>
         </is>
       </c>
       <c r="U47" s="19" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P49" s="8" t="inlineStr">
         <is>
-          <t>maa://39643 (84.58)</t>
+          <t>maa://39643 (85.17)</t>
         </is>
       </c>
       <c r="Q49" s="19" t="n"/>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="T49" s="19" t="inlineStr">
         <is>
-          <t>maa://67231 (99.43)</t>
+          <t>maa://67231 (99.45)</t>
         </is>
       </c>
       <c r="U49" s="19" t="n"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P50" s="8" t="inlineStr">
         <is>
-          <t>maa://62852 (94.72), maa://73565 (97.66)</t>
+          <t>maa://62852 (94.77), maa://73565 (97.93)</t>
         </is>
       </c>
       <c r="Q50" s="19" t="n"/>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>maa://30769 (90.24)</t>
+          <t>maa://30769 (90.70)</t>
         </is>
       </c>
       <c r="I51" s="19" t="n"/>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>maa://24376 (99.46)</t>
+          <t>maa://24376 (99.48)</t>
         </is>
       </c>
       <c r="I52" s="19" t="n"/>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="P52" s="8" t="inlineStr">
         <is>
-          <t>maa://59394 (99.54), maa://65511 (100.00), maa://59378 (94.05)</t>
+          <t>maa://59394 (99.49), maa://65511 (100.00), maa://59378 (94.05)</t>
         </is>
       </c>
       <c r="Q52" s="19" t="n"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>maa://32534 (98.63)</t>
+          <t>maa://32534 (98.67)</t>
         </is>
       </c>
       <c r="I53" s="19" t="n"/>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>maa://32532 (98.54)</t>
+          <t>maa://32532 (98.58)</t>
         </is>
       </c>
       <c r="I55" s="19" t="n"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P55" s="16" t="inlineStr">
         <is>
-          <t>maa://73349 (98.15)</t>
+          <t>maa://73349 (98.39)</t>
         </is>
       </c>
       <c r="Q55" s="16" t="n"/>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>maa://56237 (98.62), maa://25176 (97.73), maa://73737 (100.00)</t>
+          <t>maa://56237 (98.63), maa://25176 (97.73), maa://73737 (100.00)</t>
         </is>
       </c>
       <c r="I57" s="19" t="n"/>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>*maa://37964 (73.60)</t>
+          <t>*maa://37964 (73.91)</t>
         </is>
       </c>
       <c r="I58" s="19" t="n"/>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>maa://31270 (98.94), maa://27746 (90.24)</t>
+          <t>maa://31270 (98.96), maa://27746 (90.38)</t>
         </is>
       </c>
       <c r="I59" s="19" t="n"/>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>maa://40438 (94.79), maa://73999 (84.62)</t>
+          <t>maa://40438 (94.91), maa://73999 (88.89)</t>
         </is>
       </c>
       <c r="I60" s="19" t="n"/>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>maa://42981 (96.36), maa://56228 (98.98), maa://43903 (100.00)</t>
+          <t>maa://42981 (96.36), maa://56228 (99.02), maa://43903 (100.00)</t>
         </is>
       </c>
       <c r="I62" s="19" t="n"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>maa://59534 (99.66), *maa://59693 (72.58), maa://59413 (98.44)</t>
+          <t>maa://59534 (99.67), *maa://59693 (73.02), maa://59413 (98.54)</t>
         </is>
       </c>
       <c r="I63" s="19" t="n"/>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>maa://44405 (92.41)</t>
+          <t>maa://44405 (92.68)</t>
         </is>
       </c>
       <c r="I64" s="19" t="n"/>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>maa://73343 (99.22)</t>
+          <t>maa://73343 (99.23)</t>
         </is>
       </c>
       <c r="I65" s="19" t="n"/>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="H75" s="19" t="inlineStr">
         <is>
-          <t>maa://67748 (90.83)</t>
+          <t>maa://67748 (91.23)</t>
         </is>
       </c>
       <c r="I75" s="19" t="n"/>
@@ -7307,7 +7307,7 @@
     <row r="1" ht="13.5" customFormat="1" customHeight="1" s="22">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>更新日期：2025.11.13 13:22:25</t>
+          <t>更新日期：2025.11.16 13:20:51</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>maa://20888 (81.82)</t>
+          <t>maa://20888 (83.33)</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>maa://20863 (90.88), maa://20832 (98.53), maa://20727 (100.00)</t>
+          <t>maa://20863 (90.94), maa://20832 (98.53), maa://20727 (100.00)</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>maa://36644 (90.82), maa://36866 (97.26), maa://62759 (100.00), maa://45572 (88.89), maa://27794 (100.00), maa://70680 (100.00), maa://20960 (100.00), maa://20843 (100.00), *maa://20893 (75.00), **maa://24483 (50.00), maa://20862 (85.71), maa://74314 (100.00)</t>
+          <t>maa://36644 (90.85), maa://36866 (97.26), maa://62759 (100.00), maa://45572 (88.89), maa://27794 (100.00), maa://70680 (100.00), maa://20960 (100.00), maa://20843 (100.00), *maa://20893 (75.00), **maa://24483 (50.00), maa://20862 (85.71), maa://74314 (92.31)</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>maa://30500 (99.00), *maa://27290 (72.22), ***maa://42154 (8.33)</t>
+          <t>maa://30500 (99.02), *maa://27290 (72.22), ***maa://42154 (8.33)</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>maa://27376 (91.55), maa://42635 (94.83), *maa://20838 (55.00)</t>
+          <t>maa://27376 (90.28), maa://42635 (94.83), *maa://20838 (55.00)</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>maa://20953 (97.37), maa://31173 (95.12)</t>
+          <t>maa://31173 (95.12), maa://20953 (97.44)</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>maa://20932 (96.17), maa://42415 (96.55), maa://40838 (100.00), maa://68386 (100.00)</t>
+          <t>maa://20932 (96.20), maa://42415 (96.55), maa://40838 (100.00), maa://68386 (100.00)</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>maa://27970 (98.96), maa://41118 (90.00)</t>
+          <t>maa://27970 (98.97), maa://41118 (90.00)</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>maa://20841 (99.32), maa://31559 (94.34), maa://24093 (100.00), maa://20924 (95.24), maa://25777 (100.00), maa://20631 (100.00), maa://28241 (100.00), maa://66633 (100.00)</t>
+          <t>maa://20841 (99.33), maa://31559 (94.34), maa://24093 (100.00), maa://20924 (95.24), maa://25777 (100.00), maa://20631 (100.00), maa://28241 (100.00), maa://66633 (100.00)</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>maa://20944 (96.49), maa://35393 (100.00)</t>
+          <t>maa://20944 (96.55), maa://35393 (100.00)</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>maa://20943 (99.50), maa://30673 (100.00), maa://30672 (100.00), maa://20856 (100.00), maa://71555 (90.00)</t>
+          <t>maa://20943 (99.50), maa://30673 (100.00), maa://30672 (100.00), maa://20856 (100.00), maa://71555 (95.00)</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>maa://20958 (95.92), ***maa://39769 (20.00)</t>
+          <t>maa://20958 (96.00), ***maa://39769 (20.00)</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>maa://24472 (91.32), *maa://35841 (65.38)</t>
+          <t>maa://24472 (91.35), *maa://35841 (65.38)</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>maa://40157 (90.00)</t>
+          <t>maa://40157 (90.91)</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>maa://20991 (100.00), maa://51015 (87.72)</t>
+          <t>maa://20991 (100.00), maa://51015 (87.93)</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>maa://51881 (98.71), maa://25018 (97.03), maa://25776 (92.77), maa://28361 (95.56), maa://25772 (94.12), maa://56588 (94.59), maa://45194 (86.36), maa://32653 (81.25), maa://25161 (84.21), maa://61839 (100.00), **maa://60902 (38.46), maa://61275 (100.00), *maa://73473 (75.00)</t>
+          <t>maa://51881 (98.74), maa://25018 (97.03), maa://25776 (92.77), maa://28361 (95.56), maa://25772 (94.12), maa://56588 (94.74), maa://45194 (86.36), maa://32653 (81.25), maa://25161 (84.21), maa://61839 (100.00), **maa://60902 (38.46), maa://61275 (100.00), maa://73473 (83.33)</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>maa://20908 (98.25), maa://35723 (96.08), *maa://23346 (77.78), maa://38822 (100.00), maa://58659 (92.31)</t>
+          <t>maa://20908 (98.26), maa://35723 (96.08), *maa://23346 (77.78), maa://38822 (100.00), maa://58659 (92.31)</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>maa://20869 (100.00), maa://44690 (96.55)</t>
+          <t>maa://20869 (100.00), maa://44690 (96.61)</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>maa://21422 (99.01)</t>
+          <t>maa://21422 (99.02)</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="D152" s="13" t="inlineStr">
         <is>
-          <t>maa://28828 (88.24), maa://20846 (96.15), *maa://47286 (75.00)</t>
+          <t>maa://28828 (88.24), maa://20846 (96.30), *maa://47286 (75.00)</t>
         </is>
       </c>
       <c r="E152" s="14" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>maa://40957 (94.78), maa://36641 (98.28), maa://36865 (95.65), maa://44635 (88.18), maa://44660 (92.68), maa://41128 (84.21), maa://46108 (96.88), maa://42918 (100.00), maa://44119 (97.44), maa://64408 (91.67), maa://37300 (100.00), maa://42917 (100.00)</t>
+          <t>maa://40957 (94.82), maa://36641 (98.28), maa://36865 (95.65), maa://44635 (88.18), maa://44660 (92.68), maa://41128 (84.21), maa://46108 (97.06), maa://42918 (100.00), maa://44119 (97.44), maa://64408 (91.67), maa://37300 (100.00), maa://42917 (100.00)</t>
         </is>
       </c>
       <c r="E153" s="14" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>maa://51549 (95.77), maa://51923 (96.67), *maa://67508 (71.43)</t>
+          <t>maa://51549 (95.89), maa://51923 (96.67), *maa://67508 (71.43)</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>maa://47950 (96.00), maa://20975 (91.67), maa://30806 (100.00)</t>
+          <t>maa://47950 (96.30), maa://20975 (91.67), maa://30806 (100.00)</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
@@ -16482,12 +16482,12 @@
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>maa://29633 (91.80), maa://29627 (93.01), maa://29659 (83.72), maa://49074 (94.29), **maa://30679 (50.00), maa://29861 (100.00), maa://42343 (100.00)</t>
+          <t>maa://29633 (91.80), maa://29627 (93.01), maa://29659 (83.72), maa://49074 (94.29), **maa://30679 (50.00), maa://29861 (100.00), maa://42343 (100.00), maa://69887 (100.00)</t>
         </is>
       </c>
       <c r="E171" s="14" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>maa://44224 (90.61), maa://35854 (84.75), maa://50388 (98.31), maa://25760 (86.55), ***maa://43911 (11.11), maa://63024 (96.67), *maa://20872 (52.00), maa://51066 (87.50), maa://70161 (100.00), *maa://72380 (75.00), maa://74410 (100.00)</t>
+          <t>maa://44224 (90.70), maa://35854 (84.75), maa://50388 (98.31), maa://25760 (86.55), ***maa://43911 (11.11), maa://63024 (96.67), *maa://20872 (52.00), maa://51066 (87.50), maa://70161 (100.00), *maa://72380 (80.00), maa://74410 (100.00)</t>
         </is>
       </c>
       <c r="E201" s="14" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>maa://42223 (99.28), maa://49077 (94.64), maa://42292 (97.30), maa://42402 (100.00)</t>
+          <t>maa://42223 (99.29), maa://49077 (94.64), maa://42292 (97.30), maa://42402 (100.00)</t>
         </is>
       </c>
       <c r="E205" s="14" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>*maa://30667 (79.02), maa://30666 (83.90), **maa://30739 (42.11), *maa://30723 (59.70), maa://39588 (86.67), *maa://64079 (80.00), maa://65726 (84.62), maa://68226 (92.31)</t>
+          <t>*maa://30667 (79.02), maa://30666 (83.90), **maa://30739 (42.11), *maa://30723 (59.70), maa://39588 (86.67), *maa://64079 (80.00), maa://65726 (84.62), maa://68226 (92.86)</t>
         </is>
       </c>
       <c r="E246" s="14" t="inlineStr">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>maa://42287 (93.75), maa://45570 (95.45), maa://60678 (93.75), maa://42225 (94.44)</t>
+          <t>maa://42287 (93.99), maa://45570 (95.45), maa://60678 (93.75), maa://42225 (94.44)</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
@@ -22427,7 +22427,7 @@
       </c>
       <c r="D281" s="13" t="inlineStr">
         <is>
-          <t>maa://51881 (98.71), maa://51630 (96.46), maa://56588 (94.59), *maa://55171 (60.87), maa://51893 (90.00), **maa://60902 (38.46), *maa://66758 (76.92)</t>
+          <t>maa://51881 (98.74), maa://51630 (96.46), maa://56588 (94.74), *maa://55171 (60.87), maa://51893 (90.00), **maa://60902 (38.46), *maa://66758 (76.92)</t>
         </is>
       </c>
       <c r="E281" s="14" t="inlineStr">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>maa://30710 (97.99), maa://36845 (95.95), maa://31558 (97.22), **maa://39217 (36.84), maa://30668 (87.10)</t>
+          <t>maa://30710 (97.99), maa://36845 (95.97), maa://31558 (97.22), **maa://39217 (36.84), maa://30668 (87.10)</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="D345" s="22" t="inlineStr">
         <is>
-          <t>maa://44234 (99.21)</t>
+          <t>maa://44234 (99.22)</t>
         </is>
       </c>
       <c r="E345" s="22" t="inlineStr">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="D362" s="22" t="inlineStr">
         <is>
-          <t>maa://34865 (97.91), maa://34717 (94.20), *maa://45066 (71.43)</t>
+          <t>maa://34865 (97.92), maa://34717 (94.20), *maa://45066 (71.43)</t>
         </is>
       </c>
       <c r="E362" s="22" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="D366" s="22" t="inlineStr">
         <is>
-          <t>maa://36868 (99.41), maa://35996 (98.04), maa://47349 (98.04), **maa://39217 (36.84), maa://71203 (92.31)</t>
+          <t>maa://36868 (99.22), maa://35996 (98.04), maa://47349 (98.06), **maa://39217 (36.84), maa://71203 (94.12)</t>
         </is>
       </c>
       <c r="E366" s="22" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="D367" s="22" t="inlineStr">
         <is>
-          <t>maa://49696 (99.62), maa://49695 (100.00), maa://49758 (98.85), *maa://52357 (78.95), *maa://59402 (56.25), *maa://63091 (66.67)</t>
+          <t>maa://49696 (99.62), maa://49695 (100.00), maa://49758 (98.85), *maa://52357 (80.00), *maa://59402 (56.25), *maa://63091 (65.00)</t>
         </is>
       </c>
       <c r="E367" s="22" t="inlineStr">
@@ -27179,7 +27179,7 @@
       </c>
       <c r="D369" s="22" t="inlineStr">
         <is>
-          <t>maa://42299 (98.04), maa://42224 (85.71)</t>
+          <t>maa://42299 (98.08), maa://42224 (85.71)</t>
         </is>
       </c>
       <c r="E369" s="22" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="D370" s="22" t="inlineStr">
         <is>
-          <t>maa://49648 (96.55), *maa://49662 (76.47)</t>
+          <t>maa://49648 (96.55), *maa://49662 (77.14)</t>
         </is>
       </c>
       <c r="E370" s="22" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="D371" s="22" t="inlineStr">
         <is>
-          <t>maa://36646 (98.92), maa://36845 (95.95), **maa://39217 (36.84), maa://51007 (98.36), maa://70752 (100.00), maa://71932 (100.00)</t>
+          <t>maa://36646 (98.92), maa://36845 (95.97), **maa://39217 (36.84), maa://51007 (98.36), maa://70752 (100.00), maa://71932 (100.00)</t>
         </is>
       </c>
       <c r="E371" s="22" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="D372" s="22" t="inlineStr">
         <is>
-          <t>maa://36645 (98.49), maa://36841 (92.86), maa://37484 (94.34), maa://37858 (93.55), *maa://56268 (55.56), maa://40489 (100.00)</t>
+          <t>maa://36645 (98.50), maa://36841 (92.96), maa://37484 (94.34), maa://37858 (93.55), *maa://56268 (55.56), maa://40489 (100.00)</t>
         </is>
       </c>
       <c r="E372" s="22" t="inlineStr">
@@ -27557,7 +27557,7 @@
       </c>
       <c r="D376" s="22" t="inlineStr">
         <is>
-          <t>maa://40957 (94.78), maa://48026 (94.74), maa://44635 (88.18), maa://41035 (93.59), *maa://60251 (73.68), maa://44660 (92.68), maa://41128 (84.21)</t>
+          <t>maa://40957 (94.82), maa://48026 (94.74), maa://44635 (88.18), maa://41035 (93.59), *maa://60251 (73.68), maa://44660 (92.68), maa://41128 (84.21)</t>
         </is>
       </c>
       <c r="E376" s="22" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="D378" s="22" t="inlineStr">
         <is>
-          <t>maa://63883 (97.83), maa://64045 (100.00), maa://64041 (83.33)</t>
+          <t>maa://63883 (97.87), maa://64045 (100.00), maa://64041 (83.33)</t>
         </is>
       </c>
       <c r="E378" s="22" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="D381" s="22" t="inlineStr">
         <is>
-          <t>maa://71182 (96.21), maa://70756 (97.67), maa://71524 (100.00), maa://72244 (100.00)</t>
+          <t>maa://71182 (95.86), maa://70756 (97.67), maa://71524 (100.00), maa://72244 (100.00)</t>
         </is>
       </c>
       <c r="E381" s="22" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>maa://42970 (80.49), maa://44745 (98.38), **maa://49516 (47.06), *maa://45952 (57.14), ***maa://46851 (10.00), *maa://44896 (72.73)</t>
+          <t>maa://42970 (80.21), maa://44745 (98.42), **maa://49516 (45.71), *maa://45952 (57.14), ***maa://46851 (10.00), *maa://44896 (72.73)</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -28691,7 +28691,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>maa://63890 (98.41), maa://64043 (100.00)</t>
+          <t>maa://63890 (98.44), maa://64043 (100.00)</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -28961,7 +28961,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>maa://51872 (96.60), maa://51876 (99.12), maa://63228 (86.11), maa://51873 (98.04), maa://62047 (90.32)</t>
+          <t>maa://51872 (96.61), maa://51876 (99.12), maa://63228 (86.11), maa://51873 (98.04), maa://62047 (90.32)</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -29015,7 +29015,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>maa://60449 (98.60), maa://59493 (96.95)</t>
+          <t>maa://60449 (98.63), maa://59493 (96.24)</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -29069,7 +29069,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>maa://62756 (96.34)</t>
+          <t>maa://62756 (96.39)</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -29123,7 +29123,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>maa://52505 (97.97), maa://64040 (99.16), maa://66377 (94.44), ***maa://66376 (14.29), ***maa://70187 (9.09)</t>
+          <t>maa://52505 (97.99), maa://64040 (99.16), maa://66377 (94.44), ***maa://66376 (14.29), ***maa://70187 (9.09)</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>maa://73193 (100.00), maa://74820 (83.33)</t>
+          <t>maa://73193 (98.82), maa://74820 (90.00)</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>maa://67388 (89.06), maa://71184 (85.71)</t>
+          <t>maa://67388 (87.69), maa://71184 (84.38)</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>maa://67089 (96.67), maa://67271 (92.59)</t>
+          <t>maa://67089 (96.72), maa://67271 (92.59)</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -29258,7 +29258,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>maa://67088 (93.41)</t>
+          <t>maa://67088 (93.48)</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -29285,7 +29285,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>maa://67087 (97.79), maa://67268 (98.10), maa://67269 (89.66), maa://67648 (100.00)</t>
+          <t>maa://67087 (97.90), maa://67268 (98.14), maa://67269 (89.66), maa://67648 (93.75)</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -29366,7 +29366,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>maa://70877 (98.63)</t>
+          <t>maa://70877 (98.67)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -29474,7 +29474,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>maa://73227 (97.59), maa://73422 (97.06), maa://73447 (100.00)</t>
+          <t>maa://73227 (98.12), maa://73422 (97.78), maa://73447 (100.00)</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
